--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -341,6 +341,159 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -710,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -826,6 +979,46 @@
         <v>0</v>
       </c>
       <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="56" t="n">
+        <v>303748.3059307933</v>
+      </c>
+      <c r="D3" s="57" t="n">
+        <v>29448.30848187208</v>
+      </c>
+      <c r="E3" s="58" t="n">
+        <v>274299.9974489212</v>
+      </c>
+      <c r="F3" s="59" t="n">
+        <v>3748.305930793285</v>
+      </c>
+      <c r="G3" s="60" t="n">
+        <v>0.01249435310264429</v>
+      </c>
+      <c r="H3" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="63" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -856,454 +1049,454 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  22 Apr 2026</t>
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  23 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="67" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="67" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="67" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="67" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="67" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C3" s="70" t="n">
         <v>2000</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="71" t="n">
         <v>13.7</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E3" s="72" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="73">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="74">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="75">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="78" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="79" t="n">
         <v>2500</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="80" t="n">
         <v>11.4</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="81" t="n">
         <v>11.39999961853027</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="82">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="83">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="84">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="I4" s="85" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="78" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="79" t="n">
         <v>20200</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="80" t="n">
         <v>1.41</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="81" t="n">
         <v>1.409999966621399</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="82">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="83">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="84">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="33" t="inlineStr">
+      <c r="I5" s="85" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="68" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="70" t="n">
         <v>6400</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="71" t="n">
         <v>4.4</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="72" t="n">
         <v>4.420000076293945</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="73">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="74">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="75">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="70" t="n">
         <v>1000</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="71" t="n">
         <v>26</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="72" t="n">
         <v>28.25</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="73">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="74">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="75">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="24" t="inlineStr">
+      <c r="I7" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="77" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="78" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="79" t="n">
         <v>4200</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="80" t="n">
         <v>6.7</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="81" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="82">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="83">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="84">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="33" t="inlineStr">
+      <c r="I8" s="85" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="78" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="79" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="80" t="n">
         <v>17.2</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="81" t="n">
         <v>17</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="82">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="83">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="84">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="33" t="inlineStr">
+      <c r="I9" s="85" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="69" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="70" t="n">
         <v>1300</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="71" t="n">
         <v>20.5</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="72" t="n">
         <v>20.79999923706055</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="73">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="74">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="75">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I10" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="70" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="71" t="n">
         <v>29.25</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="72" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="73">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="74">
         <f>F11-C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="75">
         <f>(E11-D11)/D11</f>
         <v/>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="70" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="71" t="n">
         <v>113.5</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="72" t="n">
         <v>114</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="73">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="74">
         <f>F12-C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="75">
         <f>(E12-D12)/D12</f>
         <v/>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="76" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="86" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="87">
         <f>SUM(F3:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="88">
         <f>SUM(G3:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="89">
         <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
@@ -1338,14 +1531,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  22 Apr 2026</t>
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  23 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="90" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -1383,509 +1576,509 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="66" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="67" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="67" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="67" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="67" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="67" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="67" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="15" t="inlineStr">
+      <c r="J2" s="67" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="91" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B3" s="40" t="inlineStr">
+      <c r="B3" s="92" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="93" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="43" t="n">
+      <c r="E3" s="95" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="44" t="n">
+      <c r="F3" s="96" t="n">
         <v>113.5</v>
       </c>
-      <c r="G3" s="43" t="n">
+      <c r="G3" s="95" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="97">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="46" t="inlineStr">
+      <c r="I3" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="47" t="inlineStr">
+      <c r="J3" s="99" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="100" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="78" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="79" t="n">
         <v>20200</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="80" t="n">
         <v>1.41</v>
       </c>
-      <c r="G4" s="27" t="n">
+      <c r="G4" s="79" t="n">
         <v>202</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="82">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="50" t="inlineStr">
+      <c r="I4" s="102" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="51" t="inlineStr">
+      <c r="J4" s="103" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="91" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="92" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="93" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="43" t="n">
+      <c r="E5" s="95" t="n">
         <v>2500</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="96" t="n">
         <v>11.4</v>
       </c>
-      <c r="G5" s="43" t="n">
+      <c r="G5" s="95" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="97">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="46" t="inlineStr">
+      <c r="I5" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="47" t="inlineStr">
+      <c r="J5" s="99" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="100" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="78" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr">
+      <c r="D6" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="79" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="80" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="30">
+      <c r="H6" s="82">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="50" t="inlineStr">
+      <c r="I6" s="102" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="51" t="inlineStr">
+      <c r="J6" s="103" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="91" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="93" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="95" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="96" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="43" t="n">
+      <c r="G7" s="95" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="45">
+      <c r="H7" s="97">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="46" t="inlineStr">
+      <c r="I7" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="47" t="inlineStr">
+      <c r="J7" s="99" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="100" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="78" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr">
+      <c r="D8" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="79" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="80" t="n">
         <v>13.7</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="79" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="82">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="50" t="inlineStr">
+      <c r="I8" s="102" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="51" t="inlineStr">
+      <c r="J8" s="103" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="91" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="93" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D9" s="42" t="inlineStr">
+      <c r="D9" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="95" t="n">
         <v>6400</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="96" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="43" t="n">
+      <c r="G9" s="95" t="n">
         <v>64</v>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="97">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="46" t="inlineStr">
+      <c r="I9" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="47" t="inlineStr">
+      <c r="J9" s="99" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="100" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="78" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
+      <c r="D10" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="79" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="80" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="79" t="n">
         <v>42</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="82">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="50" t="inlineStr">
+      <c r="I10" s="102" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="51" t="inlineStr">
+      <c r="J10" s="103" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B11" s="40" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="93" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D11" s="42" t="inlineStr">
+      <c r="D11" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="95" t="n">
         <v>1600</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="96" t="n">
         <v>17.2</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="95" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="97">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="46" t="inlineStr">
+      <c r="I11" s="98" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="47" t="inlineStr">
+      <c r="J11" s="99" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="100" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="78" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D12" s="42" t="inlineStr">
+      <c r="D12" s="94" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="79" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="80" t="n">
         <v>20.5</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="79" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="82">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="50" t="inlineStr">
+      <c r="I12" s="102" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="51" t="inlineStr">
+      <c r="J12" s="103" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -1897,11 +2090,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="53">
+      <c r="H14" s="104">
         <f>SUM(H3:H12)</f>
         <v/>
       </c>
-      <c r="I14" s="53">
+      <c r="I14" s="104">
         <f>SUM(I3:I12)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -126,7 +126,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -158,6 +158,11 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -185,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -435,6 +440,258 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -863,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -943,82 +1200,122 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="56" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="57" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="58" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="7" t="n">
+      <c r="F2" s="59" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="G2" s="60" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="13" t="n">
+      <c r="L2" s="65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="54" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="B3" s="55" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="56" t="n">
-        <v>303748.3059307933</v>
-      </c>
-      <c r="D3" s="57" t="n">
+      <c r="B3" s="106" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="107" t="n">
+        <v>299325.3084818721</v>
+      </c>
+      <c r="D3" s="108" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E3" s="58" t="n">
-        <v>274299.9974489212</v>
-      </c>
-      <c r="F3" s="59" t="n">
-        <v>3748.305930793285</v>
-      </c>
-      <c r="G3" s="60" t="n">
-        <v>0.01249435310264429</v>
-      </c>
-      <c r="H3" s="61" t="n">
+      <c r="E3" s="109" t="n">
+        <v>269877</v>
+      </c>
+      <c r="F3" s="110" t="n">
+        <v>-674.6915181279182</v>
+      </c>
+      <c r="G3" s="111" t="n">
+        <v>-0.002248971727093061</v>
+      </c>
+      <c r="H3" s="112" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="62" t="n">
+      <c r="I3" s="113" t="n">
+        <v>-0.01456138968534346</v>
+      </c>
+      <c r="J3" s="114" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="115" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="63" t="n">
+      <c r="L3" s="116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="147" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B4" s="148" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="149" t="n">
+        <v>299325.3084818721</v>
+      </c>
+      <c r="D4" s="150" t="n">
+        <v>29448.30848187208</v>
+      </c>
+      <c r="E4" s="151" t="n">
+        <v>269877</v>
+      </c>
+      <c r="F4" s="152" t="n">
+        <v>-674.6915181279182</v>
+      </c>
+      <c r="G4" s="153" t="n">
+        <v>-0.002248971727093061</v>
+      </c>
+      <c r="H4" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="155" t="n">
+        <v>-0.01456138968534346</v>
+      </c>
+      <c r="J4" s="156" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="64" t="n">
+      <c r="K4" s="157" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="65" t="n">
+      <c r="L4" s="158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,454 +1346,454 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="66" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  23 Apr 2026</t>
+      <c r="A1" s="159" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="160" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="160" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="160" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="160" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="67" t="inlineStr">
+      <c r="E2" s="160" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="67" t="inlineStr">
+      <c r="F2" s="160" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="67" t="inlineStr">
+      <c r="G2" s="160" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="67" t="inlineStr">
+      <c r="H2" s="160" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="67" t="inlineStr">
+      <c r="I2" s="160" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="161" t="inlineStr">
+        <is>
+          <t>TU.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="162" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="C3" s="163" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D3" s="164" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E3" s="165" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F3" s="166">
+        <f>C3*E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="167">
+        <f>F3-C3*D3</f>
+        <v/>
+      </c>
+      <c r="H3" s="168">
+        <f>(E3-D3)/D3</f>
+        <v/>
+      </c>
+      <c r="I3" s="169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="161" t="inlineStr">
+        <is>
+          <t>SIRI.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="162" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
+      <c r="C4" s="163" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D4" s="164" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E4" s="165" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F4" s="166">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="167">
+        <f>F4-C4*D4</f>
+        <v/>
+      </c>
+      <c r="H4" s="168">
+        <f>(E4-D4)/D4</f>
+        <v/>
+      </c>
+      <c r="I4" s="169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="161" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="162" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C5" s="163" t="n">
+        <v>6400</v>
+      </c>
+      <c r="D5" s="164" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E5" s="165" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F5" s="166">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="167">
+        <f>F5-C5*D5</f>
+        <v/>
+      </c>
+      <c r="H5" s="168">
+        <f>(E5-D5)/D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="161" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="162" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C6" s="163" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D6" s="164" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" s="165" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F6" s="166">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="167">
+        <f>F6-C6*D6</f>
+        <v/>
+      </c>
+      <c r="H6" s="168">
+        <f>(E6-D6)/D6</f>
+        <v/>
+      </c>
+      <c r="I6" s="169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="161" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="162" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C7" s="163" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="164" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E7" s="165" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F7" s="166">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="167">
+        <f>F7-C7*D7</f>
+        <v/>
+      </c>
+      <c r="H7" s="168">
+        <f>(E7-D7)/D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="169" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="161" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="B3" s="69" t="inlineStr">
+      <c r="B8" s="162" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="C3" s="70" t="n">
+      <c r="C8" s="163" t="n">
         <v>2000</v>
       </c>
-      <c r="D3" s="71" t="n">
+      <c r="D8" s="164" t="n">
         <v>13.7</v>
       </c>
-      <c r="E3" s="72" t="n">
-        <v>14.30000019073486</v>
-      </c>
-      <c r="F3" s="73">
-        <f>C3*E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="74">
-        <f>F3-C3*D3</f>
-        <v/>
-      </c>
-      <c r="H3" s="75">
-        <f>(E3-D3)/D3</f>
-        <v/>
-      </c>
-      <c r="I3" s="76" t="inlineStr">
+      <c r="E8" s="165" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F8" s="166">
+        <f>C8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="167">
+        <f>F8-C8*D8</f>
+        <v/>
+      </c>
+      <c r="H8" s="168">
+        <f>(E8-D8)/D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="169" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="77" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="78" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="C4" s="79" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D4" s="80" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E4" s="81" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="F4" s="82">
-        <f>C4*E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="83">
-        <f>F4-C4*D4</f>
-        <v/>
-      </c>
-      <c r="H4" s="84">
-        <f>(E4-D4)/D4</f>
-        <v/>
-      </c>
-      <c r="I4" s="85" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="161" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B9" s="162" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C9" s="163" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D9" s="164" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E9" s="165" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F9" s="166">
+        <f>C9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="167">
+        <f>F9-C9*D9</f>
+        <v/>
+      </c>
+      <c r="H9" s="168">
+        <f>(E9-D9)/D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="169" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="77" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="78" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C5" s="79" t="n">
-        <v>20200</v>
-      </c>
-      <c r="D5" s="80" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E5" s="81" t="n">
-        <v>1.409999966621399</v>
-      </c>
-      <c r="F5" s="82">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="83">
-        <f>F5-C5*D5</f>
-        <v/>
-      </c>
-      <c r="H5" s="84">
-        <f>(E5-D5)/D5</f>
-        <v/>
-      </c>
-      <c r="I5" s="85" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="161" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B10" s="162" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C10" s="163" t="n">
+        <v>900</v>
+      </c>
+      <c r="D10" s="164" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E10" s="165" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F10" s="166">
+        <f>C10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="167">
+        <f>F10-C10*D10</f>
+        <v/>
+      </c>
+      <c r="H10" s="168">
+        <f>(E10-D10)/D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="169" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="68" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C6" s="70" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D6" s="71" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E6" s="72" t="n">
-        <v>4.420000076293945</v>
-      </c>
-      <c r="F6" s="73">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="74">
-        <f>F6-C6*D6</f>
-        <v/>
-      </c>
-      <c r="H6" s="75">
-        <f>(E6-D6)/D6</f>
-        <v/>
-      </c>
-      <c r="I6" s="76" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="161" t="inlineStr">
+        <is>
+          <t>BAY.BK</t>
+        </is>
+      </c>
+      <c r="B11" s="162" t="inlineStr">
+        <is>
+          <t>BAY</t>
+        </is>
+      </c>
+      <c r="C11" s="163" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="164" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" s="165" t="n">
+        <v>26</v>
+      </c>
+      <c r="F11" s="166">
+        <f>C11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="167">
+        <f>F11-C11*D11</f>
+        <v/>
+      </c>
+      <c r="H11" s="168">
+        <f>(E11-D11)/D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="169" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="68" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="69" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="C7" s="70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="71" t="n">
-        <v>26</v>
-      </c>
-      <c r="E7" s="72" t="n">
-        <v>28.25</v>
-      </c>
-      <c r="F7" s="73">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="74">
-        <f>F7-C7*D7</f>
-        <v/>
-      </c>
-      <c r="H7" s="75">
-        <f>(E7-D7)/D7</f>
-        <v/>
-      </c>
-      <c r="I7" s="76" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="161" t="inlineStr">
+        <is>
+          <t>TISCO.BK</t>
+        </is>
+      </c>
+      <c r="B12" s="162" t="inlineStr">
+        <is>
+          <t>TISCO</t>
+        </is>
+      </c>
+      <c r="C12" s="163" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" s="164" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E12" s="165" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F12" s="166">
+        <f>C12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="167">
+        <f>F12-C12*D12</f>
+        <v/>
+      </c>
+      <c r="H12" s="168">
+        <f>(E12-D12)/D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="169" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="78" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C8" s="79" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D8" s="80" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E8" s="81" t="n">
-        <v>6.699999809265137</v>
-      </c>
-      <c r="F8" s="82">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="83">
-        <f>F8-C8*D8</f>
-        <v/>
-      </c>
-      <c r="H8" s="84">
-        <f>(E8-D8)/D8</f>
-        <v/>
-      </c>
-      <c r="I8" s="85" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B9" s="78" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C9" s="79" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D9" s="80" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E9" s="81" t="n">
-        <v>17</v>
-      </c>
-      <c r="F9" s="82">
-        <f>C9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="83">
-        <f>F9-C9*D9</f>
-        <v/>
-      </c>
-      <c r="H9" s="84">
-        <f>(E9-D9)/D9</f>
-        <v/>
-      </c>
-      <c r="I9" s="85" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="68" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C10" s="70" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D10" s="71" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E10" s="72" t="n">
-        <v>20.79999923706055</v>
-      </c>
-      <c r="F10" s="73">
-        <f>C10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="74">
-        <f>F10-C10*D10</f>
-        <v/>
-      </c>
-      <c r="H10" s="75">
-        <f>(E10-D10)/D10</f>
-        <v/>
-      </c>
-      <c r="I10" s="76" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="68" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B11" s="69" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C11" s="70" t="n">
-        <v>900</v>
-      </c>
-      <c r="D11" s="71" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E11" s="72" t="n">
-        <v>30</v>
-      </c>
-      <c r="F11" s="73">
-        <f>C11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="74">
-        <f>F11-C11*D11</f>
-        <v/>
-      </c>
-      <c r="H11" s="75">
-        <f>(E11-D11)/D11</f>
-        <v/>
-      </c>
-      <c r="I11" s="76" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="68" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="C12" s="70" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" s="71" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="E12" s="72" t="n">
-        <v>114</v>
-      </c>
-      <c r="F12" s="73">
-        <f>C12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="74">
-        <f>F12-C12*D12</f>
-        <v/>
-      </c>
-      <c r="H12" s="75">
-        <f>(E12-D12)/D12</f>
-        <v/>
-      </c>
-      <c r="I12" s="76" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="86" t="inlineStr">
+      <c r="B13" s="170" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="171">
         <f>SUM(F3:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="172">
         <f>SUM(G3:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="89">
+      <c r="H13" s="173">
         <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
@@ -1531,14 +1828,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="66" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  23 Apr 2026</t>
+      <c r="A1" s="159" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="90" t="inlineStr">
+      <c r="A3" s="174" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -1576,509 +1873,509 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="66" t="inlineStr">
+      <c r="A1" s="159" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="160" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="67" t="inlineStr">
+      <c r="B2" s="160" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="67" t="inlineStr">
+      <c r="C2" s="160" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="67" t="inlineStr">
+      <c r="D2" s="160" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="67" t="inlineStr">
+      <c r="E2" s="160" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="67" t="inlineStr">
+      <c r="F2" s="160" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="67" t="inlineStr">
+      <c r="G2" s="160" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="67" t="inlineStr">
+      <c r="H2" s="160" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="67" t="inlineStr">
+      <c r="I2" s="160" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="67" t="inlineStr">
+      <c r="J2" s="160" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="91" t="inlineStr">
+      <c r="A3" s="175" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B3" s="92" t="inlineStr">
+      <c r="B3" s="176" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="C3" s="93" t="inlineStr">
+      <c r="C3" s="177" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="D3" s="94" t="inlineStr">
+      <c r="D3" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="95" t="n">
+      <c r="E3" s="179" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="96" t="n">
+      <c r="F3" s="180" t="n">
         <v>113.5</v>
       </c>
-      <c r="G3" s="95" t="n">
+      <c r="G3" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="97">
+      <c r="H3" s="181">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="98" t="inlineStr">
+      <c r="I3" s="182" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="99" t="inlineStr">
+      <c r="J3" s="183" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="100" t="inlineStr">
+      <c r="A4" s="184" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B4" s="101" t="inlineStr">
+      <c r="B4" s="185" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="C4" s="78" t="inlineStr">
+      <c r="C4" s="162" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="D4" s="94" t="inlineStr">
+      <c r="D4" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="79" t="n">
+      <c r="E4" s="163" t="n">
         <v>20200</v>
       </c>
-      <c r="F4" s="80" t="n">
+      <c r="F4" s="164" t="n">
         <v>1.41</v>
       </c>
-      <c r="G4" s="79" t="n">
+      <c r="G4" s="163" t="n">
         <v>202</v>
       </c>
-      <c r="H4" s="82">
+      <c r="H4" s="166">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="102" t="inlineStr">
+      <c r="I4" s="186" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="103" t="inlineStr">
+      <c r="J4" s="187" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="175" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B5" s="92" t="inlineStr">
+      <c r="B5" s="176" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C5" s="93" t="inlineStr">
+      <c r="C5" s="177" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D5" s="94" t="inlineStr">
+      <c r="D5" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="95" t="n">
+      <c r="E5" s="179" t="n">
         <v>2500</v>
       </c>
-      <c r="F5" s="96" t="n">
+      <c r="F5" s="180" t="n">
         <v>11.4</v>
       </c>
-      <c r="G5" s="95" t="n">
+      <c r="G5" s="179" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="97">
+      <c r="H5" s="181">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="182" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="99" t="inlineStr">
+      <c r="J5" s="183" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="100" t="inlineStr">
+      <c r="A6" s="184" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B6" s="101" t="inlineStr">
+      <c r="B6" s="185" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="C6" s="78" t="inlineStr">
+      <c r="C6" s="162" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="D6" s="94" t="inlineStr">
+      <c r="D6" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="79" t="n">
+      <c r="E6" s="163" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="80" t="n">
+      <c r="F6" s="164" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="79" t="n">
+      <c r="G6" s="163" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="82">
+      <c r="H6" s="166">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="102" t="inlineStr">
+      <c r="I6" s="186" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="103" t="inlineStr">
+      <c r="J6" s="187" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="91" t="inlineStr">
+      <c r="A7" s="175" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B7" s="92" t="inlineStr">
+      <c r="B7" s="176" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="93" t="inlineStr">
+      <c r="C7" s="177" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="94" t="inlineStr">
+      <c r="D7" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="95" t="n">
+      <c r="E7" s="179" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="96" t="n">
+      <c r="F7" s="180" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="95" t="n">
+      <c r="G7" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="97">
+      <c r="H7" s="181">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="98" t="inlineStr">
+      <c r="I7" s="182" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="99" t="inlineStr">
+      <c r="J7" s="183" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="100" t="inlineStr">
+      <c r="A8" s="184" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B8" s="101" t="inlineStr">
+      <c r="B8" s="185" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="C8" s="78" t="inlineStr">
+      <c r="C8" s="162" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="D8" s="94" t="inlineStr">
+      <c r="D8" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="79" t="n">
+      <c r="E8" s="163" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="80" t="n">
+      <c r="F8" s="164" t="n">
         <v>13.7</v>
       </c>
-      <c r="G8" s="79" t="n">
+      <c r="G8" s="163" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="82">
+      <c r="H8" s="166">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="102" t="inlineStr">
+      <c r="I8" s="186" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="103" t="inlineStr">
+      <c r="J8" s="187" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="91" t="inlineStr">
+      <c r="A9" s="175" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B9" s="92" t="inlineStr">
+      <c r="B9" s="176" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C9" s="93" t="inlineStr">
+      <c r="C9" s="177" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D9" s="94" t="inlineStr">
+      <c r="D9" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E9" s="95" t="n">
+      <c r="E9" s="179" t="n">
         <v>6400</v>
       </c>
-      <c r="F9" s="96" t="n">
+      <c r="F9" s="180" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="95" t="n">
+      <c r="G9" s="179" t="n">
         <v>64</v>
       </c>
-      <c r="H9" s="97">
+      <c r="H9" s="181">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="98" t="inlineStr">
+      <c r="I9" s="182" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="99" t="inlineStr">
+      <c r="J9" s="183" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="100" t="inlineStr">
+      <c r="A10" s="184" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B10" s="101" t="inlineStr">
+      <c r="B10" s="185" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="78" t="inlineStr">
+      <c r="C10" s="162" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="94" t="inlineStr">
+      <c r="D10" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E10" s="79" t="n">
+      <c r="E10" s="163" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="80" t="n">
+      <c r="F10" s="164" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="79" t="n">
+      <c r="G10" s="163" t="n">
         <v>42</v>
       </c>
-      <c r="H10" s="82">
+      <c r="H10" s="166">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="102" t="inlineStr">
+      <c r="I10" s="186" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="103" t="inlineStr">
+      <c r="J10" s="187" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="91" t="inlineStr">
+      <c r="A11" s="175" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B11" s="92" t="inlineStr">
+      <c r="B11" s="176" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C11" s="93" t="inlineStr">
+      <c r="C11" s="177" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D11" s="94" t="inlineStr">
+      <c r="D11" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="179" t="n">
         <v>1600</v>
       </c>
-      <c r="F11" s="96" t="n">
+      <c r="F11" s="180" t="n">
         <v>17.2</v>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="G11" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="97">
+      <c r="H11" s="181">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="98" t="inlineStr">
+      <c r="I11" s="182" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="99" t="inlineStr">
+      <c r="J11" s="183" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="100" t="inlineStr">
+      <c r="A12" s="184" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B12" s="101" t="inlineStr">
+      <c r="B12" s="185" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C12" s="78" t="inlineStr">
+      <c r="C12" s="162" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D12" s="94" t="inlineStr">
+      <c r="D12" s="178" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="79" t="n">
+      <c r="E12" s="163" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="80" t="n">
+      <c r="F12" s="164" t="n">
         <v>20.5</v>
       </c>
-      <c r="G12" s="79" t="n">
+      <c r="G12" s="163" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="82">
+      <c r="H12" s="166">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="102" t="inlineStr">
+      <c r="I12" s="186" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="103" t="inlineStr">
+      <c r="J12" s="187" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2090,11 +2387,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="104">
+      <c r="H14" s="188">
         <f>SUM(H3:H12)</f>
         <v/>
       </c>
-      <c r="I14" s="104">
+      <c r="I14" s="188">
         <f>SUM(I3:I12)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -707,6 +707,192 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1200,13 +1386,13 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="105" t="inlineStr">
+      <c r="A2" s="189" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" s="55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="56" t="n">
         <v>303748.3059307933</v>
@@ -1240,82 +1426,82 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="105" t="inlineStr">
+      <c r="A3" s="189" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="B3" s="106" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" s="107" t="n">
+      <c r="B3" s="190" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="191" t="n">
         <v>299325.3084818721</v>
       </c>
-      <c r="D3" s="108" t="n">
+      <c r="D3" s="192" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E3" s="109" t="n">
+      <c r="E3" s="193" t="n">
         <v>269877</v>
       </c>
-      <c r="F3" s="110" t="n">
+      <c r="F3" s="194" t="n">
         <v>-674.6915181279182</v>
       </c>
-      <c r="G3" s="111" t="n">
+      <c r="G3" s="195" t="n">
         <v>-0.002248971727093061</v>
       </c>
-      <c r="H3" s="112" t="n">
+      <c r="H3" s="196" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="113" t="n">
+      <c r="I3" s="197" t="n">
         <v>-0.01456138968534346</v>
       </c>
-      <c r="J3" s="114" t="n">
+      <c r="J3" s="198" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="115" t="n">
+      <c r="K3" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="116" t="n">
+      <c r="L3" s="200" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="147" t="inlineStr">
+      <c r="A4" s="189" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B4" s="148" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="149" t="n">
-        <v>299325.3084818721</v>
-      </c>
-      <c r="D4" s="150" t="n">
+      <c r="B4" s="190" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="191" t="n">
+        <v>299017.3066517711</v>
+      </c>
+      <c r="D4" s="192" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E4" s="151" t="n">
-        <v>269877</v>
-      </c>
-      <c r="F4" s="152" t="n">
-        <v>-674.6915181279182</v>
-      </c>
-      <c r="G4" s="153" t="n">
-        <v>-0.002248971727093061</v>
-      </c>
-      <c r="H4" s="154" t="n">
+      <c r="E4" s="193" t="n">
+        <v>269568.998169899</v>
+      </c>
+      <c r="F4" s="194" t="n">
+        <v>-982.6933482289314</v>
+      </c>
+      <c r="G4" s="195" t="n">
+        <v>-0.003275644494096438</v>
+      </c>
+      <c r="H4" s="196" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="155" t="n">
-        <v>-0.01456138968534346</v>
-      </c>
-      <c r="J4" s="156" t="n">
+      <c r="I4" s="197" t="n">
+        <v>-0.01557539313519707</v>
+      </c>
+      <c r="J4" s="198" t="n">
         <v>10</v>
       </c>
-      <c r="K4" s="157" t="n">
+      <c r="K4" s="199" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="158" t="n">
+      <c r="L4" s="200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1346,454 +1532,454 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="159" t="inlineStr">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>Current Holdings  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="160" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="160" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="160" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="160" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="160" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="160" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="160" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="160" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="160" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="161" t="inlineStr">
+      <c r="A3" s="203" t="inlineStr">
+        <is>
+          <t>SIRI.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="204" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
+      <c r="C3" s="205" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D3" s="206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E3" s="207" t="n">
+        <v>1.409999966621399</v>
+      </c>
+      <c r="F3" s="208">
+        <f>C3*E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="209">
+        <f>F3-C3*D3</f>
+        <v/>
+      </c>
+      <c r="H3" s="210">
+        <f>(E3-D3)/D3</f>
+        <v/>
+      </c>
+      <c r="I3" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="203" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="204" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C4" s="205" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D4" s="206" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" s="207" t="n">
+        <v>6.699999809265137</v>
+      </c>
+      <c r="F4" s="208">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="209">
+        <f>F4-C4*D4</f>
+        <v/>
+      </c>
+      <c r="H4" s="210">
+        <f>(E4-D4)/D4</f>
+        <v/>
+      </c>
+      <c r="I4" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="203" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="204" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C5" s="205" t="n">
+        <v>6400</v>
+      </c>
+      <c r="D5" s="206" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E5" s="207" t="n">
+        <v>4.380000114440918</v>
+      </c>
+      <c r="F5" s="208">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="209">
+        <f>F5-C5*D5</f>
+        <v/>
+      </c>
+      <c r="H5" s="210">
+        <f>(E5-D5)/D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="203" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B3" s="162" t="inlineStr">
+      <c r="B6" s="204" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C3" s="163" t="n">
+      <c r="C6" s="205" t="n">
         <v>2500</v>
       </c>
-      <c r="D3" s="164" t="n">
+      <c r="D6" s="206" t="n">
         <v>11.4</v>
       </c>
-      <c r="E3" s="165" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F3" s="166">
-        <f>C3*E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="167">
-        <f>F3-C3*D3</f>
-        <v/>
-      </c>
-      <c r="H3" s="168">
-        <f>(E3-D3)/D3</f>
-        <v/>
-      </c>
-      <c r="I3" s="169" t="inlineStr">
+      <c r="E6" s="207" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="F6" s="208">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="209">
+        <f>F6-C6*D6</f>
+        <v/>
+      </c>
+      <c r="H6" s="210">
+        <f>(E6-D6)/D6</f>
+        <v/>
+      </c>
+      <c r="I6" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="161" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="162" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C4" s="163" t="n">
-        <v>20200</v>
-      </c>
-      <c r="D4" s="164" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E4" s="165" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F4" s="166">
-        <f>C4*E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="167">
-        <f>F4-C4*D4</f>
-        <v/>
-      </c>
-      <c r="H4" s="168">
-        <f>(E4-D4)/D4</f>
-        <v/>
-      </c>
-      <c r="I4" s="169" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="212" t="inlineStr">
+        <is>
+          <t>TQM.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="213" t="inlineStr">
+        <is>
+          <t>TQM</t>
+        </is>
+      </c>
+      <c r="C7" s="214" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="215" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E7" s="216" t="n">
+        <v>13.80000019073486</v>
+      </c>
+      <c r="F7" s="217">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="218">
+        <f>F7-C7*D7</f>
+        <v/>
+      </c>
+      <c r="H7" s="219">
+        <f>(E7-D7)/D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="220" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="161" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="162" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C5" s="163" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D5" s="164" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E5" s="165" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F5" s="166">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="167">
-        <f>F5-C5*D5</f>
-        <v/>
-      </c>
-      <c r="H5" s="168">
-        <f>(E5-D5)/D5</f>
-        <v/>
-      </c>
-      <c r="I5" s="169" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="212" t="inlineStr">
+        <is>
+          <t>BAY.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="213" t="inlineStr">
+        <is>
+          <t>BAY</t>
+        </is>
+      </c>
+      <c r="C8" s="214" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="215" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="216" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F8" s="217">
+        <f>C8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="218">
+        <f>F8-C8*D8</f>
+        <v/>
+      </c>
+      <c r="H8" s="219">
+        <f>(E8-D8)/D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="220" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="161" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="162" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C6" s="163" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D6" s="164" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E6" s="165" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F6" s="166">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="167">
-        <f>F6-C6*D6</f>
-        <v/>
-      </c>
-      <c r="H6" s="168">
-        <f>(E6-D6)/D6</f>
-        <v/>
-      </c>
-      <c r="I6" s="169" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="221" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B9" s="222" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C9" s="223" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D9" s="224" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E9" s="225" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F9" s="226">
+        <f>C9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="227">
+        <f>F9-C9*D9</f>
+        <v/>
+      </c>
+      <c r="H9" s="228">
+        <f>(E9-D9)/D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="229" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="161" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="162" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C7" s="163" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D7" s="164" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E7" s="165" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F7" s="166">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="167">
-        <f>F7-C7*D7</f>
-        <v/>
-      </c>
-      <c r="H7" s="168">
-        <f>(E7-D7)/D7</f>
-        <v/>
-      </c>
-      <c r="I7" s="169" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="203" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B10" s="204" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C10" s="205" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D10" s="206" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E10" s="207" t="n">
+        <v>20.29999923706055</v>
+      </c>
+      <c r="F10" s="208">
+        <f>C10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="209">
+        <f>F10-C10*D10</f>
+        <v/>
+      </c>
+      <c r="H10" s="210">
+        <f>(E10-D10)/D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="161" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="162" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="C8" s="163" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D8" s="164" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="E8" s="165" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F8" s="166">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="167">
-        <f>F8-C8*D8</f>
-        <v/>
-      </c>
-      <c r="H8" s="168">
-        <f>(E8-D8)/D8</f>
-        <v/>
-      </c>
-      <c r="I8" s="169" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="203" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B11" s="204" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C11" s="205" t="n">
+        <v>900</v>
+      </c>
+      <c r="D11" s="206" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E11" s="207" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F11" s="208">
+        <f>C11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="230">
+        <f>F11-C11*D11</f>
+        <v/>
+      </c>
+      <c r="H11" s="231">
+        <f>(E11-D11)/D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="161" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B9" s="162" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C9" s="163" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D9" s="164" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E9" s="165" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F9" s="166">
-        <f>C9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="167">
-        <f>F9-C9*D9</f>
-        <v/>
-      </c>
-      <c r="H9" s="168">
-        <f>(E9-D9)/D9</f>
-        <v/>
-      </c>
-      <c r="I9" s="169" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="203" t="inlineStr">
+        <is>
+          <t>TISCO.BK</t>
+        </is>
+      </c>
+      <c r="B12" s="204" t="inlineStr">
+        <is>
+          <t>TISCO</t>
+        </is>
+      </c>
+      <c r="C12" s="205" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" s="206" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E12" s="207" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F12" s="208">
+        <f>C12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="230">
+        <f>F12-C12*D12</f>
+        <v/>
+      </c>
+      <c r="H12" s="231">
+        <f>(E12-D12)/D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="161" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B10" s="162" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C10" s="163" t="n">
-        <v>900</v>
-      </c>
-      <c r="D10" s="164" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E10" s="165" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F10" s="166">
-        <f>C10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="167">
-        <f>F10-C10*D10</f>
-        <v/>
-      </c>
-      <c r="H10" s="168">
-        <f>(E10-D10)/D10</f>
-        <v/>
-      </c>
-      <c r="I10" s="169" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="161" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="B11" s="162" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="C11" s="163" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="164" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" s="165" t="n">
-        <v>26</v>
-      </c>
-      <c r="F11" s="166">
-        <f>C11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="167">
-        <f>F11-C11*D11</f>
-        <v/>
-      </c>
-      <c r="H11" s="168">
-        <f>(E11-D11)/D11</f>
-        <v/>
-      </c>
-      <c r="I11" s="169" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="161" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="B12" s="162" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="C12" s="163" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" s="164" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="E12" s="165" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="F12" s="166">
-        <f>C12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="167">
-        <f>F12-C12*D12</f>
-        <v/>
-      </c>
-      <c r="H12" s="168">
-        <f>(E12-D12)/D12</f>
-        <v/>
-      </c>
-      <c r="I12" s="169" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="170" t="inlineStr">
+      <c r="B13" s="232" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="171">
+      <c r="F13" s="233">
         <f>SUM(F3:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="172">
+      <c r="G13" s="234">
         <f>SUM(G3:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="173">
+      <c r="H13" s="235">
         <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
@@ -1828,14 +2014,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="159" t="inlineStr">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>Today's Trades  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="174" t="inlineStr">
+      <c r="A3" s="236" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -1873,509 +2059,509 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="159" t="inlineStr">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="160" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="160" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="160" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="160" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="160" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="160" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="160" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="160" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="160" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="160" t="inlineStr">
+      <c r="J2" s="202" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="175" t="inlineStr">
+      <c r="A3" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B3" s="176" t="inlineStr">
+      <c r="B3" s="238" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="C3" s="177" t="inlineStr">
+      <c r="C3" s="239" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="D3" s="178" t="inlineStr">
+      <c r="D3" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="179" t="n">
+      <c r="E3" s="241" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="180" t="n">
+      <c r="F3" s="242" t="n">
         <v>113.5</v>
       </c>
-      <c r="G3" s="179" t="n">
+      <c r="G3" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="181">
+      <c r="H3" s="243">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="182" t="inlineStr">
+      <c r="I3" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="183" t="inlineStr">
+      <c r="J3" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="184" t="inlineStr">
+      <c r="A4" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B4" s="185" t="inlineStr">
+      <c r="B4" s="247" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="C4" s="162" t="inlineStr">
+      <c r="C4" s="204" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="D4" s="178" t="inlineStr">
+      <c r="D4" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="163" t="n">
+      <c r="E4" s="205" t="n">
         <v>20200</v>
       </c>
-      <c r="F4" s="164" t="n">
+      <c r="F4" s="206" t="n">
         <v>1.41</v>
       </c>
-      <c r="G4" s="163" t="n">
+      <c r="G4" s="205" t="n">
         <v>202</v>
       </c>
-      <c r="H4" s="166">
+      <c r="H4" s="208">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="186" t="inlineStr">
+      <c r="I4" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="187" t="inlineStr">
+      <c r="J4" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="175" t="inlineStr">
+      <c r="A5" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B5" s="176" t="inlineStr">
+      <c r="B5" s="238" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C5" s="177" t="inlineStr">
+      <c r="C5" s="239" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D5" s="178" t="inlineStr">
+      <c r="D5" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="179" t="n">
+      <c r="E5" s="241" t="n">
         <v>2500</v>
       </c>
-      <c r="F5" s="180" t="n">
+      <c r="F5" s="242" t="n">
         <v>11.4</v>
       </c>
-      <c r="G5" s="179" t="n">
+      <c r="G5" s="241" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="181">
+      <c r="H5" s="243">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="182" t="inlineStr">
+      <c r="I5" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="183" t="inlineStr">
+      <c r="J5" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="184" t="inlineStr">
+      <c r="A6" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B6" s="185" t="inlineStr">
+      <c r="B6" s="247" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="C6" s="162" t="inlineStr">
+      <c r="C6" s="204" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="D6" s="178" t="inlineStr">
+      <c r="D6" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="163" t="n">
+      <c r="E6" s="205" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="164" t="n">
+      <c r="F6" s="206" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="163" t="n">
+      <c r="G6" s="205" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="166">
+      <c r="H6" s="208">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="186" t="inlineStr">
+      <c r="I6" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="187" t="inlineStr">
+      <c r="J6" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="175" t="inlineStr">
+      <c r="A7" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B7" s="176" t="inlineStr">
+      <c r="B7" s="238" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="177" t="inlineStr">
+      <c r="C7" s="239" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="178" t="inlineStr">
+      <c r="D7" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="179" t="n">
+      <c r="E7" s="241" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="180" t="n">
+      <c r="F7" s="242" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="179" t="n">
+      <c r="G7" s="241" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="181">
+      <c r="H7" s="243">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="182" t="inlineStr">
+      <c r="I7" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="183" t="inlineStr">
+      <c r="J7" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="184" t="inlineStr">
+      <c r="A8" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B8" s="185" t="inlineStr">
+      <c r="B8" s="247" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="C8" s="162" t="inlineStr">
+      <c r="C8" s="204" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="D8" s="178" t="inlineStr">
+      <c r="D8" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="163" t="n">
+      <c r="E8" s="205" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="164" t="n">
+      <c r="F8" s="206" t="n">
         <v>13.7</v>
       </c>
-      <c r="G8" s="163" t="n">
+      <c r="G8" s="205" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="166">
+      <c r="H8" s="208">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="186" t="inlineStr">
+      <c r="I8" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="187" t="inlineStr">
+      <c r="J8" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="175" t="inlineStr">
+      <c r="A9" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B9" s="176" t="inlineStr">
+      <c r="B9" s="238" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C9" s="177" t="inlineStr">
+      <c r="C9" s="239" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D9" s="178" t="inlineStr">
+      <c r="D9" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E9" s="179" t="n">
+      <c r="E9" s="241" t="n">
         <v>6400</v>
       </c>
-      <c r="F9" s="180" t="n">
+      <c r="F9" s="242" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="179" t="n">
+      <c r="G9" s="241" t="n">
         <v>64</v>
       </c>
-      <c r="H9" s="181">
+      <c r="H9" s="243">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="182" t="inlineStr">
+      <c r="I9" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="183" t="inlineStr">
+      <c r="J9" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="184" t="inlineStr">
+      <c r="A10" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B10" s="185" t="inlineStr">
+      <c r="B10" s="247" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="162" t="inlineStr">
+      <c r="C10" s="204" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="178" t="inlineStr">
+      <c r="D10" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E10" s="163" t="n">
+      <c r="E10" s="205" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="164" t="n">
+      <c r="F10" s="206" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="163" t="n">
+      <c r="G10" s="205" t="n">
         <v>42</v>
       </c>
-      <c r="H10" s="166">
+      <c r="H10" s="208">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="186" t="inlineStr">
+      <c r="I10" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="187" t="inlineStr">
+      <c r="J10" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="175" t="inlineStr">
+      <c r="A11" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B11" s="176" t="inlineStr">
+      <c r="B11" s="238" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C11" s="177" t="inlineStr">
+      <c r="C11" s="239" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D11" s="178" t="inlineStr">
+      <c r="D11" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="179" t="n">
+      <c r="E11" s="241" t="n">
         <v>1600</v>
       </c>
-      <c r="F11" s="180" t="n">
+      <c r="F11" s="242" t="n">
         <v>17.2</v>
       </c>
-      <c r="G11" s="179" t="n">
+      <c r="G11" s="241" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="181">
+      <c r="H11" s="243">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="182" t="inlineStr">
+      <c r="I11" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="183" t="inlineStr">
+      <c r="J11" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="184" t="inlineStr">
+      <c r="A12" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B12" s="185" t="inlineStr">
+      <c r="B12" s="247" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C12" s="162" t="inlineStr">
+      <c r="C12" s="204" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D12" s="178" t="inlineStr">
+      <c r="D12" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="163" t="n">
+      <c r="E12" s="205" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="164" t="n">
+      <c r="F12" s="206" t="n">
         <v>20.5</v>
       </c>
-      <c r="G12" s="163" t="n">
+      <c r="G12" s="205" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="166">
+      <c r="H12" s="208">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="186" t="inlineStr">
+      <c r="I12" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="187" t="inlineStr">
+      <c r="J12" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2387,11 +2573,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="188">
+      <c r="H14" s="250">
         <f>SUM(H3:H12)</f>
         <v/>
       </c>
-      <c r="I14" s="188">
+      <c r="I14" s="250">
         <f>SUM(I3:I12)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -875,6 +881,216 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1306,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1721,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="251" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="252" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="253" t="n">
+        <v>299017.3066517711</v>
+      </c>
+      <c r="D5" s="254" t="n">
+        <v>29448.30848187208</v>
+      </c>
+      <c r="E5" s="255" t="n">
+        <v>269568.998169899</v>
+      </c>
+      <c r="F5" s="256" t="n">
+        <v>-982.6933482289314</v>
+      </c>
+      <c r="G5" s="257" t="n">
+        <v>-0.003275644494096438</v>
+      </c>
+      <c r="H5" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="259" t="n">
+        <v>-0.01557539313519707</v>
+      </c>
+      <c r="J5" s="260" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1517,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1529,464 +1785,556 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
+      <c r="J2" s="264" t="inlineStr">
+        <is>
+          <t>Comp Score</t>
+        </is>
+      </c>
+      <c r="K2" s="264" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="203" t="inlineStr">
+      <c r="A3" s="265" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="B3" s="204" t="inlineStr">
+      <c r="B3" s="266" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="C3" s="205" t="n">
+      <c r="C3" s="267" t="n">
         <v>20200</v>
       </c>
-      <c r="D3" s="206" t="n">
+      <c r="D3" s="268" t="n">
         <v>1.41</v>
       </c>
-      <c r="E3" s="207" t="n">
+      <c r="E3" s="269" t="n">
         <v>1.409999966621399</v>
       </c>
-      <c r="F3" s="208">
+      <c r="F3" s="270">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="209">
+      <c r="G3" s="271">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="210">
+      <c r="H3" s="272">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="211" t="inlineStr">
+      <c r="I3" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J3" s="274" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K3" s="275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="203" t="inlineStr">
+      <c r="A4" s="265" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="204" t="inlineStr">
+      <c r="B4" s="266" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="205" t="n">
+      <c r="C4" s="267" t="n">
         <v>4200</v>
       </c>
-      <c r="D4" s="206" t="n">
+      <c r="D4" s="268" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="207" t="n">
+      <c r="E4" s="269" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F4" s="208">
+      <c r="F4" s="270">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="209">
+      <c r="G4" s="271">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="210">
+      <c r="H4" s="272">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="211" t="inlineStr">
+      <c r="I4" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J4" s="276" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="K4" s="277" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="203" t="inlineStr">
+      <c r="A5" s="265" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B5" s="204" t="inlineStr">
+      <c r="B5" s="266" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C5" s="205" t="n">
+      <c r="C5" s="267" t="n">
         <v>6400</v>
       </c>
-      <c r="D5" s="206" t="n">
+      <c r="D5" s="268" t="n">
         <v>4.4</v>
       </c>
-      <c r="E5" s="207" t="n">
+      <c r="E5" s="269" t="n">
         <v>4.380000114440918</v>
       </c>
-      <c r="F5" s="208">
+      <c r="F5" s="270">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="209">
+      <c r="G5" s="271">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="210">
+      <c r="H5" s="272">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="211" t="inlineStr">
+      <c r="I5" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J5" s="276" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="K5" s="277" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="203" t="inlineStr">
+      <c r="A6" s="265" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B6" s="204" t="inlineStr">
+      <c r="B6" s="266" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C6" s="205" t="n">
+      <c r="C6" s="267" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="206" t="n">
+      <c r="D6" s="268" t="n">
         <v>11.4</v>
       </c>
-      <c r="E6" s="207" t="n">
+      <c r="E6" s="269" t="n">
         <v>11.19999980926514</v>
       </c>
-      <c r="F6" s="208">
+      <c r="F6" s="270">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="209">
+      <c r="G6" s="271">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="210">
+      <c r="H6" s="272">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="211" t="inlineStr">
+      <c r="I6" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J6" s="274" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K6" s="275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="212" t="inlineStr">
+      <c r="A7" s="278" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="B7" s="213" t="inlineStr">
+      <c r="B7" s="279" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="C7" s="214" t="n">
+      <c r="C7" s="280" t="n">
         <v>2000</v>
       </c>
-      <c r="D7" s="215" t="n">
+      <c r="D7" s="281" t="n">
         <v>13.7</v>
       </c>
-      <c r="E7" s="216" t="n">
+      <c r="E7" s="282" t="n">
         <v>13.80000019073486</v>
       </c>
-      <c r="F7" s="217">
+      <c r="F7" s="283">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="218">
+      <c r="G7" s="284">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="219">
+      <c r="H7" s="285">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="220" t="inlineStr">
+      <c r="I7" s="286" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J7" s="287" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K7" s="288" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="212" t="inlineStr">
+      <c r="A8" s="278" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="B8" s="213" t="inlineStr">
+      <c r="B8" s="279" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="C8" s="214" t="n">
+      <c r="C8" s="280" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="215" t="n">
+      <c r="D8" s="281" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="216" t="n">
+      <c r="E8" s="282" t="n">
         <v>27.5</v>
       </c>
-      <c r="F8" s="217">
+      <c r="F8" s="283">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="218">
+      <c r="G8" s="284">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="219">
+      <c r="H8" s="285">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="220" t="inlineStr">
+      <c r="I8" s="286" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J8" s="287" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K8" s="288" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="221" t="inlineStr">
+      <c r="A9" s="289" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B9" s="222" t="inlineStr">
+      <c r="B9" s="290" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C9" s="223" t="n">
+      <c r="C9" s="291" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="224" t="n">
+      <c r="D9" s="292" t="n">
         <v>17.2</v>
       </c>
-      <c r="E9" s="225" t="n">
+      <c r="E9" s="293" t="n">
         <v>16.5</v>
       </c>
-      <c r="F9" s="226">
+      <c r="F9" s="294">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="227">
+      <c r="G9" s="295">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="228">
+      <c r="H9" s="296">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="229" t="inlineStr">
+      <c r="I9" s="297" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J9" s="298" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K9" s="299" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="203" t="inlineStr">
+      <c r="A10" s="265" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B10" s="204" t="inlineStr">
+      <c r="B10" s="266" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C10" s="205" t="n">
+      <c r="C10" s="267" t="n">
         <v>1300</v>
       </c>
-      <c r="D10" s="206" t="n">
+      <c r="D10" s="268" t="n">
         <v>20.5</v>
       </c>
-      <c r="E10" s="207" t="n">
+      <c r="E10" s="269" t="n">
         <v>20.29999923706055</v>
       </c>
-      <c r="F10" s="208">
+      <c r="F10" s="270">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="209">
+      <c r="G10" s="271">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="210">
+      <c r="H10" s="272">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="211" t="inlineStr">
+      <c r="I10" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J10" s="274" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="K10" s="275" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="203" t="inlineStr">
+      <c r="A11" s="265" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B11" s="204" t="inlineStr">
+      <c r="B11" s="266" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C11" s="205" t="n">
+      <c r="C11" s="267" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="206" t="n">
+      <c r="D11" s="268" t="n">
         <v>29.25</v>
       </c>
-      <c r="E11" s="207" t="n">
+      <c r="E11" s="269" t="n">
         <v>29.25</v>
       </c>
-      <c r="F11" s="208">
+      <c r="F11" s="270">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="230">
+      <c r="G11" s="300">
         <f>F11-C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="231">
+      <c r="H11" s="301">
         <f>(E11-D11)/D11</f>
         <v/>
       </c>
-      <c r="I11" s="211" t="inlineStr">
+      <c r="I11" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J11" s="274" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K11" s="275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="203" t="inlineStr">
+      <c r="A12" s="265" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="B12" s="204" t="inlineStr">
+      <c r="B12" s="266" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="C12" s="205" t="n">
+      <c r="C12" s="267" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="206" t="n">
+      <c r="D12" s="268" t="n">
         <v>113.5</v>
       </c>
-      <c r="E12" s="207" t="n">
+      <c r="E12" s="269" t="n">
         <v>113.5</v>
       </c>
-      <c r="F12" s="208">
+      <c r="F12" s="270">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="230">
+      <c r="G12" s="300">
         <f>F12-C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="231">
+      <c r="H12" s="301">
         <f>(E12-D12)/D12</f>
         <v/>
       </c>
-      <c r="I12" s="211" t="inlineStr">
+      <c r="I12" s="273" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="J12" s="276" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="K12" s="277" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="232" t="inlineStr">
+      <c r="B13" s="302" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="233">
+      <c r="F13" s="303">
         <f>SUM(F3:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="234">
+      <c r="G13" s="304">
         <f>SUM(G3:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="235">
+      <c r="H13" s="305">
         <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,14 +2362,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="236" t="inlineStr">
+      <c r="A3" s="306" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2059,509 +2407,509 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
+      <c r="A1" s="263" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="202" t="inlineStr">
+      <c r="J2" s="264" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="237" t="inlineStr">
+      <c r="A3" s="307" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B3" s="238" t="inlineStr">
+      <c r="B3" s="308" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="C3" s="239" t="inlineStr">
+      <c r="C3" s="309" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="D3" s="240" t="inlineStr">
+      <c r="D3" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="241" t="n">
+      <c r="E3" s="311" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="242" t="n">
+      <c r="F3" s="312" t="n">
         <v>113.5</v>
       </c>
-      <c r="G3" s="241" t="n">
+      <c r="G3" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="243">
+      <c r="H3" s="313">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="244" t="inlineStr">
+      <c r="I3" s="314" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="245" t="inlineStr">
+      <c r="J3" s="315" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="246" t="inlineStr">
+      <c r="A4" s="316" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B4" s="247" t="inlineStr">
+      <c r="B4" s="317" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="C4" s="204" t="inlineStr">
+      <c r="C4" s="266" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="D4" s="240" t="inlineStr">
+      <c r="D4" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="205" t="n">
+      <c r="E4" s="267" t="n">
         <v>20200</v>
       </c>
-      <c r="F4" s="206" t="n">
+      <c r="F4" s="268" t="n">
         <v>1.41</v>
       </c>
-      <c r="G4" s="205" t="n">
+      <c r="G4" s="267" t="n">
         <v>202</v>
       </c>
-      <c r="H4" s="208">
+      <c r="H4" s="270">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="248" t="inlineStr">
+      <c r="I4" s="318" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="249" t="inlineStr">
+      <c r="J4" s="319" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="237" t="inlineStr">
+      <c r="A5" s="307" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B5" s="238" t="inlineStr">
+      <c r="B5" s="308" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C5" s="239" t="inlineStr">
+      <c r="C5" s="309" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D5" s="240" t="inlineStr">
+      <c r="D5" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="241" t="n">
+      <c r="E5" s="311" t="n">
         <v>2500</v>
       </c>
-      <c r="F5" s="242" t="n">
+      <c r="F5" s="312" t="n">
         <v>11.4</v>
       </c>
-      <c r="G5" s="241" t="n">
+      <c r="G5" s="311" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="243">
+      <c r="H5" s="313">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="244" t="inlineStr">
+      <c r="I5" s="314" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="245" t="inlineStr">
+      <c r="J5" s="315" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="246" t="inlineStr">
+      <c r="A6" s="316" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B6" s="247" t="inlineStr">
+      <c r="B6" s="317" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="C6" s="204" t="inlineStr">
+      <c r="C6" s="266" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="D6" s="240" t="inlineStr">
+      <c r="D6" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="205" t="n">
+      <c r="E6" s="267" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="206" t="n">
+      <c r="F6" s="268" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="205" t="n">
+      <c r="G6" s="267" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="208">
+      <c r="H6" s="270">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="248" t="inlineStr">
+      <c r="I6" s="318" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="249" t="inlineStr">
+      <c r="J6" s="319" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="237" t="inlineStr">
+      <c r="A7" s="307" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B7" s="238" t="inlineStr">
+      <c r="B7" s="308" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="239" t="inlineStr">
+      <c r="C7" s="309" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="240" t="inlineStr">
+      <c r="D7" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="241" t="n">
+      <c r="E7" s="311" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="242" t="n">
+      <c r="F7" s="312" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="241" t="n">
+      <c r="G7" s="311" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="243">
+      <c r="H7" s="313">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="244" t="inlineStr">
+      <c r="I7" s="314" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="245" t="inlineStr">
+      <c r="J7" s="315" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="246" t="inlineStr">
+      <c r="A8" s="316" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B8" s="247" t="inlineStr">
+      <c r="B8" s="317" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="C8" s="204" t="inlineStr">
+      <c r="C8" s="266" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="D8" s="240" t="inlineStr">
+      <c r="D8" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="205" t="n">
+      <c r="E8" s="267" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="206" t="n">
+      <c r="F8" s="268" t="n">
         <v>13.7</v>
       </c>
-      <c r="G8" s="205" t="n">
+      <c r="G8" s="267" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="208">
+      <c r="H8" s="270">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="248" t="inlineStr">
+      <c r="I8" s="318" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="249" t="inlineStr">
+      <c r="J8" s="319" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="237" t="inlineStr">
+      <c r="A9" s="307" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B9" s="238" t="inlineStr">
+      <c r="B9" s="308" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C9" s="239" t="inlineStr">
+      <c r="C9" s="309" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D9" s="240" t="inlineStr">
+      <c r="D9" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E9" s="241" t="n">
+      <c r="E9" s="311" t="n">
         <v>6400</v>
       </c>
-      <c r="F9" s="242" t="n">
+      <c r="F9" s="312" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="241" t="n">
+      <c r="G9" s="311" t="n">
         <v>64</v>
       </c>
-      <c r="H9" s="243">
+      <c r="H9" s="313">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="244" t="inlineStr">
+      <c r="I9" s="314" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="245" t="inlineStr">
+      <c r="J9" s="315" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="246" t="inlineStr">
+      <c r="A10" s="316" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B10" s="247" t="inlineStr">
+      <c r="B10" s="317" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="204" t="inlineStr">
+      <c r="C10" s="266" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="240" t="inlineStr">
+      <c r="D10" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E10" s="205" t="n">
+      <c r="E10" s="267" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="206" t="n">
+      <c r="F10" s="268" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="205" t="n">
+      <c r="G10" s="267" t="n">
         <v>42</v>
       </c>
-      <c r="H10" s="208">
+      <c r="H10" s="270">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="248" t="inlineStr">
+      <c r="I10" s="318" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="249" t="inlineStr">
+      <c r="J10" s="319" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="237" t="inlineStr">
+      <c r="A11" s="307" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B11" s="238" t="inlineStr">
+      <c r="B11" s="308" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C11" s="239" t="inlineStr">
+      <c r="C11" s="309" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D11" s="240" t="inlineStr">
+      <c r="D11" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="241" t="n">
+      <c r="E11" s="311" t="n">
         <v>1600</v>
       </c>
-      <c r="F11" s="242" t="n">
+      <c r="F11" s="312" t="n">
         <v>17.2</v>
       </c>
-      <c r="G11" s="241" t="n">
+      <c r="G11" s="311" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="243">
+      <c r="H11" s="313">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="244" t="inlineStr">
+      <c r="I11" s="314" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="245" t="inlineStr">
+      <c r="J11" s="315" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="246" t="inlineStr">
+      <c r="A12" s="316" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B12" s="247" t="inlineStr">
+      <c r="B12" s="317" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C12" s="204" t="inlineStr">
+      <c r="C12" s="266" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D12" s="240" t="inlineStr">
+      <c r="D12" s="310" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="205" t="n">
+      <c r="E12" s="267" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="206" t="n">
+      <c r="F12" s="268" t="n">
         <v>20.5</v>
       </c>
-      <c r="G12" s="205" t="n">
+      <c r="G12" s="267" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="208">
+      <c r="H12" s="270">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="248" t="inlineStr">
+      <c r="I12" s="318" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="249" t="inlineStr">
+      <c r="J12" s="319" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2573,11 +2921,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="250">
+      <c r="H14" s="320">
         <f>SUM(H3:H12)</f>
         <v/>
       </c>
-      <c r="I14" s="250">
+      <c r="I14" s="320">
         <f>SUM(I3:I12)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFC000"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="321">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -881,216 +875,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1522,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1721,46 +1505,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="251" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B5" s="252" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="253" t="n">
-        <v>299017.3066517711</v>
-      </c>
-      <c r="D5" s="254" t="n">
-        <v>29448.30848187208</v>
-      </c>
-      <c r="E5" s="255" t="n">
-        <v>269568.998169899</v>
-      </c>
-      <c r="F5" s="256" t="n">
-        <v>-982.6933482289314</v>
-      </c>
-      <c r="G5" s="257" t="n">
-        <v>-0.003275644494096438</v>
-      </c>
-      <c r="H5" s="258" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="259" t="n">
-        <v>-0.01557539313519707</v>
-      </c>
-      <c r="J5" s="260" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" s="261" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="262" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1773,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1785,556 +1529,464 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  27 Apr 2026</t>
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
-        <is>
-          <t>Comp Score</t>
-        </is>
-      </c>
-      <c r="K2" s="264" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="265" t="inlineStr">
+      <c r="A3" s="203" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B3" s="204" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="C3" s="267" t="n">
+      <c r="C3" s="205" t="n">
         <v>20200</v>
       </c>
-      <c r="D3" s="268" t="n">
+      <c r="D3" s="206" t="n">
         <v>1.41</v>
       </c>
-      <c r="E3" s="269" t="n">
+      <c r="E3" s="207" t="n">
         <v>1.409999966621399</v>
       </c>
-      <c r="F3" s="270">
+      <c r="F3" s="208">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="271">
+      <c r="G3" s="209">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="272">
+      <c r="H3" s="210">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="273" t="inlineStr">
+      <c r="I3" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J3" s="274" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K3" s="275" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="265" t="inlineStr">
+      <c r="A4" s="203" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="266" t="inlineStr">
+      <c r="B4" s="204" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="267" t="n">
+      <c r="C4" s="205" t="n">
         <v>4200</v>
       </c>
-      <c r="D4" s="268" t="n">
+      <c r="D4" s="206" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="269" t="n">
+      <c r="E4" s="207" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F4" s="270">
+      <c r="F4" s="208">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="271">
+      <c r="G4" s="209">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="272">
+      <c r="H4" s="210">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="273" t="inlineStr">
+      <c r="I4" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J4" s="276" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="K4" s="277" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="265" t="inlineStr">
+      <c r="A5" s="203" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B5" s="266" t="inlineStr">
+      <c r="B5" s="204" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C5" s="267" t="n">
+      <c r="C5" s="205" t="n">
         <v>6400</v>
       </c>
-      <c r="D5" s="268" t="n">
+      <c r="D5" s="206" t="n">
         <v>4.4</v>
       </c>
-      <c r="E5" s="269" t="n">
+      <c r="E5" s="207" t="n">
         <v>4.380000114440918</v>
       </c>
-      <c r="F5" s="270">
+      <c r="F5" s="208">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="271">
+      <c r="G5" s="209">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="272">
+      <c r="H5" s="210">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="273" t="inlineStr">
+      <c r="I5" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J5" s="276" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="K5" s="277" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="265" t="inlineStr">
+      <c r="A6" s="203" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B6" s="266" t="inlineStr">
+      <c r="B6" s="204" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C6" s="267" t="n">
+      <c r="C6" s="205" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="268" t="n">
+      <c r="D6" s="206" t="n">
         <v>11.4</v>
       </c>
-      <c r="E6" s="269" t="n">
+      <c r="E6" s="207" t="n">
         <v>11.19999980926514</v>
       </c>
-      <c r="F6" s="270">
+      <c r="F6" s="208">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="271">
+      <c r="G6" s="209">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="272">
+      <c r="H6" s="210">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="273" t="inlineStr">
+      <c r="I6" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J6" s="274" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="K6" s="275" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="278" t="inlineStr">
+      <c r="A7" s="212" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="B7" s="279" t="inlineStr">
+      <c r="B7" s="213" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="C7" s="280" t="n">
+      <c r="C7" s="214" t="n">
         <v>2000</v>
       </c>
-      <c r="D7" s="281" t="n">
+      <c r="D7" s="215" t="n">
         <v>13.7</v>
       </c>
-      <c r="E7" s="282" t="n">
+      <c r="E7" s="216" t="n">
         <v>13.80000019073486</v>
       </c>
-      <c r="F7" s="283">
+      <c r="F7" s="217">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="284">
+      <c r="G7" s="218">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="285">
+      <c r="H7" s="219">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="286" t="inlineStr">
+      <c r="I7" s="220" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J7" s="287" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="K7" s="288" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="278" t="inlineStr">
+      <c r="A8" s="212" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="B8" s="279" t="inlineStr">
+      <c r="B8" s="213" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="C8" s="280" t="n">
+      <c r="C8" s="214" t="n">
         <v>1000</v>
       </c>
-      <c r="D8" s="281" t="n">
+      <c r="D8" s="215" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="282" t="n">
+      <c r="E8" s="216" t="n">
         <v>27.5</v>
       </c>
-      <c r="F8" s="283">
+      <c r="F8" s="217">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="284">
+      <c r="G8" s="218">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="285">
+      <c r="H8" s="219">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="286" t="inlineStr">
+      <c r="I8" s="220" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J8" s="287" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K8" s="288" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="289" t="inlineStr">
+      <c r="A9" s="221" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B9" s="290" t="inlineStr">
+      <c r="B9" s="222" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C9" s="291" t="n">
+      <c r="C9" s="223" t="n">
         <v>1600</v>
       </c>
-      <c r="D9" s="292" t="n">
+      <c r="D9" s="224" t="n">
         <v>17.2</v>
       </c>
-      <c r="E9" s="293" t="n">
+      <c r="E9" s="225" t="n">
         <v>16.5</v>
       </c>
-      <c r="F9" s="294">
+      <c r="F9" s="226">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="295">
+      <c r="G9" s="227">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="296">
+      <c r="H9" s="228">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="297" t="inlineStr">
+      <c r="I9" s="229" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J9" s="298" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K9" s="299" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="265" t="inlineStr">
+      <c r="A10" s="203" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B10" s="266" t="inlineStr">
+      <c r="B10" s="204" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C10" s="267" t="n">
+      <c r="C10" s="205" t="n">
         <v>1300</v>
       </c>
-      <c r="D10" s="268" t="n">
+      <c r="D10" s="206" t="n">
         <v>20.5</v>
       </c>
-      <c r="E10" s="269" t="n">
+      <c r="E10" s="207" t="n">
         <v>20.29999923706055</v>
       </c>
-      <c r="F10" s="270">
+      <c r="F10" s="208">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="271">
+      <c r="G10" s="209">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="272">
+      <c r="H10" s="210">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="273" t="inlineStr">
+      <c r="I10" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J10" s="274" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="K10" s="275" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="265" t="inlineStr">
+      <c r="A11" s="203" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B11" s="266" t="inlineStr">
+      <c r="B11" s="204" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C11" s="267" t="n">
+      <c r="C11" s="205" t="n">
         <v>900</v>
       </c>
-      <c r="D11" s="268" t="n">
+      <c r="D11" s="206" t="n">
         <v>29.25</v>
       </c>
-      <c r="E11" s="269" t="n">
+      <c r="E11" s="207" t="n">
         <v>29.25</v>
       </c>
-      <c r="F11" s="270">
+      <c r="F11" s="208">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="300">
+      <c r="G11" s="230">
         <f>F11-C11*D11</f>
         <v/>
       </c>
-      <c r="H11" s="301">
+      <c r="H11" s="231">
         <f>(E11-D11)/D11</f>
         <v/>
       </c>
-      <c r="I11" s="273" t="inlineStr">
+      <c r="I11" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J11" s="274" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K11" s="275" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="265" t="inlineStr">
+      <c r="A12" s="203" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="B12" s="266" t="inlineStr">
+      <c r="B12" s="204" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="C12" s="267" t="n">
+      <c r="C12" s="205" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="268" t="n">
+      <c r="D12" s="206" t="n">
         <v>113.5</v>
       </c>
-      <c r="E12" s="269" t="n">
+      <c r="E12" s="207" t="n">
         <v>113.5</v>
       </c>
-      <c r="F12" s="270">
+      <c r="F12" s="208">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="300">
+      <c r="G12" s="230">
         <f>F12-C12*D12</f>
         <v/>
       </c>
-      <c r="H12" s="301">
+      <c r="H12" s="231">
         <f>(E12-D12)/D12</f>
         <v/>
       </c>
-      <c r="I12" s="273" t="inlineStr">
+      <c r="I12" s="211" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="J12" s="276" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="K12" s="277" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="302" t="inlineStr">
+      <c r="B13" s="232" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="303">
+      <c r="F13" s="233">
         <f>SUM(F3:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="304">
+      <c r="G13" s="234">
         <f>SUM(G3:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="305">
+      <c r="H13" s="235">
         <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2362,14 +2014,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  27 Apr 2026</t>
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="306" t="inlineStr">
+      <c r="A3" s="236" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2407,509 +2059,509 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="202" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="307" t="inlineStr">
+      <c r="A3" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B3" s="308" t="inlineStr">
+      <c r="B3" s="238" t="inlineStr">
         <is>
           <t>TISCO.BK</t>
         </is>
       </c>
-      <c r="C3" s="309" t="inlineStr">
+      <c r="C3" s="239" t="inlineStr">
         <is>
           <t>TISCO</t>
         </is>
       </c>
-      <c r="D3" s="310" t="inlineStr">
+      <c r="D3" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="311" t="n">
+      <c r="E3" s="241" t="n">
         <v>200</v>
       </c>
-      <c r="F3" s="312" t="n">
+      <c r="F3" s="242" t="n">
         <v>113.5</v>
       </c>
-      <c r="G3" s="311" t="n">
+      <c r="G3" s="241" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="313">
+      <c r="H3" s="243">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="314" t="inlineStr">
+      <c r="I3" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="315" t="inlineStr">
+      <c r="J3" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="316" t="inlineStr">
+      <c r="A4" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B4" s="317" t="inlineStr">
+      <c r="B4" s="247" t="inlineStr">
         <is>
           <t>SIRI.BK</t>
         </is>
       </c>
-      <c r="C4" s="266" t="inlineStr">
+      <c r="C4" s="204" t="inlineStr">
         <is>
           <t>SIRI</t>
         </is>
       </c>
-      <c r="D4" s="310" t="inlineStr">
+      <c r="D4" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="267" t="n">
+      <c r="E4" s="205" t="n">
         <v>20200</v>
       </c>
-      <c r="F4" s="268" t="n">
+      <c r="F4" s="206" t="n">
         <v>1.41</v>
       </c>
-      <c r="G4" s="267" t="n">
+      <c r="G4" s="205" t="n">
         <v>202</v>
       </c>
-      <c r="H4" s="270">
+      <c r="H4" s="208">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="318" t="inlineStr">
+      <c r="I4" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="319" t="inlineStr">
+      <c r="J4" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="307" t="inlineStr">
+      <c r="A5" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B5" s="308" t="inlineStr">
+      <c r="B5" s="238" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C5" s="309" t="inlineStr">
+      <c r="C5" s="239" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D5" s="310" t="inlineStr">
+      <c r="D5" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="311" t="n">
+      <c r="E5" s="241" t="n">
         <v>2500</v>
       </c>
-      <c r="F5" s="312" t="n">
+      <c r="F5" s="242" t="n">
         <v>11.4</v>
       </c>
-      <c r="G5" s="311" t="n">
+      <c r="G5" s="241" t="n">
         <v>25</v>
       </c>
-      <c r="H5" s="313">
+      <c r="H5" s="243">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="314" t="inlineStr">
+      <c r="I5" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="315" t="inlineStr">
+      <c r="J5" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="316" t="inlineStr">
+      <c r="A6" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B6" s="317" t="inlineStr">
+      <c r="B6" s="247" t="inlineStr">
         <is>
           <t>BAY.BK</t>
         </is>
       </c>
-      <c r="C6" s="266" t="inlineStr">
+      <c r="C6" s="204" t="inlineStr">
         <is>
           <t>BAY</t>
         </is>
       </c>
-      <c r="D6" s="310" t="inlineStr">
+      <c r="D6" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="267" t="n">
+      <c r="E6" s="205" t="n">
         <v>1000</v>
       </c>
-      <c r="F6" s="268" t="n">
+      <c r="F6" s="206" t="n">
         <v>26</v>
       </c>
-      <c r="G6" s="267" t="n">
+      <c r="G6" s="205" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="270">
+      <c r="H6" s="208">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="318" t="inlineStr">
+      <c r="I6" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="319" t="inlineStr">
+      <c r="J6" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="307" t="inlineStr">
+      <c r="A7" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B7" s="308" t="inlineStr">
+      <c r="B7" s="238" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="309" t="inlineStr">
+      <c r="C7" s="239" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="310" t="inlineStr">
+      <c r="D7" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="311" t="n">
+      <c r="E7" s="241" t="n">
         <v>900</v>
       </c>
-      <c r="F7" s="312" t="n">
+      <c r="F7" s="242" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="311" t="n">
+      <c r="G7" s="241" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="313">
+      <c r="H7" s="243">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="314" t="inlineStr">
+      <c r="I7" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="315" t="inlineStr">
+      <c r="J7" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="316" t="inlineStr">
+      <c r="A8" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B8" s="317" t="inlineStr">
+      <c r="B8" s="247" t="inlineStr">
         <is>
           <t>TQM.BK</t>
         </is>
       </c>
-      <c r="C8" s="266" t="inlineStr">
+      <c r="C8" s="204" t="inlineStr">
         <is>
           <t>TQM</t>
         </is>
       </c>
-      <c r="D8" s="310" t="inlineStr">
+      <c r="D8" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="267" t="n">
+      <c r="E8" s="205" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="268" t="n">
+      <c r="F8" s="206" t="n">
         <v>13.7</v>
       </c>
-      <c r="G8" s="267" t="n">
+      <c r="G8" s="205" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="270">
+      <c r="H8" s="208">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="318" t="inlineStr">
+      <c r="I8" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="319" t="inlineStr">
+      <c r="J8" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="307" t="inlineStr">
+      <c r="A9" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B9" s="308" t="inlineStr">
+      <c r="B9" s="238" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C9" s="309" t="inlineStr">
+      <c r="C9" s="239" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D9" s="310" t="inlineStr">
+      <c r="D9" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E9" s="311" t="n">
+      <c r="E9" s="241" t="n">
         <v>6400</v>
       </c>
-      <c r="F9" s="312" t="n">
+      <c r="F9" s="242" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="311" t="n">
+      <c r="G9" s="241" t="n">
         <v>64</v>
       </c>
-      <c r="H9" s="313">
+      <c r="H9" s="243">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="314" t="inlineStr">
+      <c r="I9" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="315" t="inlineStr">
+      <c r="J9" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="316" t="inlineStr">
+      <c r="A10" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B10" s="317" t="inlineStr">
+      <c r="B10" s="247" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="266" t="inlineStr">
+      <c r="C10" s="204" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="310" t="inlineStr">
+      <c r="D10" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E10" s="267" t="n">
+      <c r="E10" s="205" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="268" t="n">
+      <c r="F10" s="206" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="267" t="n">
+      <c r="G10" s="205" t="n">
         <v>42</v>
       </c>
-      <c r="H10" s="270">
+      <c r="H10" s="208">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="318" t="inlineStr">
+      <c r="I10" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="319" t="inlineStr">
+      <c r="J10" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="307" t="inlineStr">
+      <c r="A11" s="237" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B11" s="308" t="inlineStr">
+      <c r="B11" s="238" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C11" s="309" t="inlineStr">
+      <c r="C11" s="239" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D11" s="310" t="inlineStr">
+      <c r="D11" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="311" t="n">
+      <c r="E11" s="241" t="n">
         <v>1600</v>
       </c>
-      <c r="F11" s="312" t="n">
+      <c r="F11" s="242" t="n">
         <v>17.2</v>
       </c>
-      <c r="G11" s="311" t="n">
+      <c r="G11" s="241" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="313">
+      <c r="H11" s="243">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="314" t="inlineStr">
+      <c r="I11" s="244" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="315" t="inlineStr">
+      <c r="J11" s="245" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="316" t="inlineStr">
+      <c r="A12" s="246" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="B12" s="317" t="inlineStr">
+      <c r="B12" s="247" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C12" s="266" t="inlineStr">
+      <c r="C12" s="204" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D12" s="310" t="inlineStr">
+      <c r="D12" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="267" t="n">
+      <c r="E12" s="205" t="n">
         <v>1300</v>
       </c>
-      <c r="F12" s="268" t="n">
+      <c r="F12" s="206" t="n">
         <v>20.5</v>
       </c>
-      <c r="G12" s="267" t="n">
+      <c r="G12" s="205" t="n">
         <v>13</v>
       </c>
-      <c r="H12" s="270">
+      <c r="H12" s="208">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="318" t="inlineStr">
+      <c r="I12" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="319" t="inlineStr">
+      <c r="J12" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2921,11 +2573,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="320">
+      <c r="H14" s="250">
         <f>SUM(H3:H12)</f>
         <v/>
       </c>
-      <c r="I14" s="320">
+      <c r="I14" s="250">
         <f>SUM(I3:I12)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -896,6 +902,207 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1306,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1712,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="251" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="252" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="253" t="n">
+        <v>300229.8165025711</v>
+      </c>
+      <c r="D5" s="254" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E5" s="255" t="n">
+        <v>281805.9986114502</v>
+      </c>
+      <c r="F5" s="256" t="n">
+        <v>229.816502571106</v>
+      </c>
+      <c r="G5" s="257" t="n">
+        <v>0.0007660550085703531</v>
+      </c>
+      <c r="H5" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="260" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="261" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1517,7 +1764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1529,464 +1776,372 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
+      <c r="J2" s="264" t="inlineStr">
+        <is>
+          <t>Comp Score</t>
+        </is>
+      </c>
+      <c r="K2" s="264" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="203" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C3" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="D3" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E3" s="207" t="n">
-        <v>1.409999966621399</v>
-      </c>
-      <c r="F3" s="208">
+      <c r="A3" s="265" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="266" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C3" s="267" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D3" s="268" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E3" s="269" t="n">
+        <v>4.420000076293945</v>
+      </c>
+      <c r="F3" s="270">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="209">
+      <c r="G3" s="271">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="210">
+      <c r="H3" s="272">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I3" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J3" s="274" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K3" s="275" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="203" t="inlineStr">
+      <c r="A4" s="265" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="266" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C4" s="267" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D4" s="268" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E4" s="269" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F4" s="270">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="271">
+        <f>F4-C4*D4</f>
+        <v/>
+      </c>
+      <c r="H4" s="272">
+        <f>(E4-D4)/D4</f>
+        <v/>
+      </c>
+      <c r="I4" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J4" s="276" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K4" s="277" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="266" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C5" s="267" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="268" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E5" s="269" t="n">
+        <v>20.39999961853027</v>
+      </c>
+      <c r="F5" s="270">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="271">
+        <f>F5-C5*D5</f>
+        <v/>
+      </c>
+      <c r="H5" s="272">
+        <f>(E5-D5)/D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J5" s="278" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K5" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="280" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="204" t="inlineStr">
+      <c r="B6" s="281" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D4" s="206" t="n">
+      <c r="C6" s="282" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="283" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="207" t="n">
+      <c r="E6" s="284" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F4" s="208">
-        <f>C4*E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="209">
-        <f>F4-C4*D4</f>
-        <v/>
-      </c>
-      <c r="H4" s="210">
-        <f>(E4-D4)/D4</f>
-        <v/>
-      </c>
-      <c r="I4" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="203" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="204" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C5" s="205" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D5" s="206" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E5" s="207" t="n">
-        <v>4.380000114440918</v>
-      </c>
-      <c r="F5" s="208">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="209">
-        <f>F5-C5*D5</f>
-        <v/>
-      </c>
-      <c r="H5" s="210">
-        <f>(E5-D5)/D5</f>
-        <v/>
-      </c>
-      <c r="I5" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="203" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="204" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="C6" s="205" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="206" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E6" s="207" t="n">
-        <v>11.19999980926514</v>
-      </c>
-      <c r="F6" s="208">
+      <c r="F6" s="285">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="209">
+      <c r="G6" s="286">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="210">
+      <c r="H6" s="287">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I6" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J6" s="289" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K6" s="290" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="212" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="213" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="C7" s="214" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D7" s="215" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="E7" s="216" t="n">
-        <v>13.80000019073486</v>
-      </c>
-      <c r="F7" s="217">
+      <c r="A7" s="280" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="281" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="282" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="283" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E7" s="284" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F7" s="285">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="218">
+      <c r="G7" s="291">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="219">
+      <c r="H7" s="292">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I7" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J7" s="293" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K7" s="294" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="212" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="213" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="C8" s="214" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="215" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" s="216" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F8" s="217">
+      <c r="A8" s="280" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="281" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C8" s="282" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D8" s="283" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E8" s="284" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F8" s="285">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="218">
+      <c r="G8" s="291">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="219">
+      <c r="H8" s="292">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="221" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B9" s="222" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C9" s="223" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D9" s="224" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E9" s="225" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F9" s="226">
-        <f>C9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="227">
-        <f>F9-C9*D9</f>
-        <v/>
-      </c>
-      <c r="H9" s="228">
-        <f>(E9-D9)/D9</f>
-        <v/>
-      </c>
-      <c r="I9" s="229" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="203" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B10" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C10" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D10" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E10" s="207" t="n">
-        <v>20.29999923706055</v>
-      </c>
-      <c r="F10" s="208">
-        <f>C10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="209">
-        <f>F10-C10*D10</f>
-        <v/>
-      </c>
-      <c r="H10" s="210">
-        <f>(E10-D10)/D10</f>
-        <v/>
-      </c>
-      <c r="I10" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="203" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B11" s="204" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C11" s="205" t="n">
-        <v>900</v>
-      </c>
-      <c r="D11" s="206" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E11" s="207" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F11" s="208">
-        <f>C11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="230">
-        <f>F11-C11*D11</f>
-        <v/>
-      </c>
-      <c r="H11" s="231">
-        <f>(E11-D11)/D11</f>
-        <v/>
-      </c>
-      <c r="I11" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="203" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="B12" s="204" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="C12" s="205" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" s="206" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="E12" s="207" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="F12" s="208">
-        <f>C12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="230">
-        <f>F12-C12*D12</f>
-        <v/>
-      </c>
-      <c r="H12" s="231">
-        <f>(E12-D12)/D12</f>
-        <v/>
-      </c>
-      <c r="I12" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="232" t="inlineStr">
+      <c r="I8" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J8" s="289" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K8" s="290" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="295" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="233">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="234">
-        <f>SUM(G3:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="235">
-        <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
+      <c r="F9" s="296">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="297">
+        <f>SUM(G3:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="298">
+        <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1999,7 +2154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2014,23 +2169,313 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  24 Apr 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="236" t="inlineStr">
-        <is>
-          <t>No trades were executed today.</t>
-        </is>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  27 Apr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="264" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B2" s="264" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C2" s="264" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D2" s="264" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E2" s="264" t="inlineStr">
+        <is>
+          <t>Price (฿)</t>
+        </is>
+      </c>
+      <c r="F2" s="264" t="inlineStr">
+        <is>
+          <t>Lots</t>
+        </is>
+      </c>
+      <c r="G2" s="264" t="inlineStr">
+        <is>
+          <t>Value (฿)</t>
+        </is>
+      </c>
+      <c r="H2" s="264" t="inlineStr">
+        <is>
+          <t>Realised P&amp;L (฿)</t>
+        </is>
+      </c>
+      <c r="I2" s="264" t="inlineStr">
+        <is>
+          <t>Reason / Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3" s="300" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C3" s="267" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D3" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E3" s="268" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F3" s="267" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" s="270">
+        <f>C3*E3</f>
+        <v/>
+      </c>
+      <c r="H3" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B4" s="300" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C4" s="267" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D4" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E4" s="268" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F4" s="267" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" s="270">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="300" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C5" s="267" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D5" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E5" s="268" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F5" s="267" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" s="270">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B6" s="300" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C6" s="267" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D6" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E6" s="268" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="F6" s="267" t="n">
+        <v>108</v>
+      </c>
+      <c r="G6" s="270">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B7" s="300" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="267" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E7" s="268" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F7" s="267" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="270">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="299" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B8" s="300" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C8" s="267" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D8" s="279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E8" s="268" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F8" s="267" t="n">
+        <v>70</v>
+      </c>
+      <c r="G8" s="270">
+        <f>C8*E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="301" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="302" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="G9" s="295" t="inlineStr">
+        <is>
+          <t>TODAY'S P&amp;L</t>
+        </is>
+      </c>
+      <c r="H9" s="303">
+        <f>SUM(H3:H8)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2043,7 +2488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2059,526 +2504,346 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Complete Trade History  —  since 2026-04-21</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="202" t="inlineStr">
+      <c r="J2" s="264" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B3" s="238" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="C3" s="239" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="D3" s="240" t="inlineStr">
+      <c r="A3" s="304" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3" s="305" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="C3" s="306" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="D3" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="241" t="n">
-        <v>200</v>
-      </c>
-      <c r="F3" s="242" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="G3" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="243">
+      <c r="E3" s="308" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F3" s="309" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G3" s="308" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" s="310">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="244" t="inlineStr">
+      <c r="I3" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="245" t="inlineStr">
+      <c r="J3" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B4" s="247" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="C4" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="D4" s="240" t="inlineStr">
+      <c r="A4" s="313" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B4" s="314" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="C4" s="281" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="D4" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="F4" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G4" s="205" t="n">
-        <v>202</v>
-      </c>
-      <c r="H4" s="208">
+      <c r="E4" s="282" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F4" s="283" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G4" s="282" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" s="285">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="248" t="inlineStr">
+      <c r="I4" s="315" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="249" t="inlineStr">
+      <c r="J4" s="316" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B5" s="238" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="C5" s="239" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="D5" s="240" t="inlineStr">
+      <c r="A5" s="304" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="305" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="C5" s="306" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="D5" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="241" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F5" s="242" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G5" s="241" t="n">
-        <v>25</v>
-      </c>
-      <c r="H5" s="243">
+      <c r="E5" s="308" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F5" s="309" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G5" s="308" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="310">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="244" t="inlineStr">
+      <c r="I5" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="245" t="inlineStr">
+      <c r="J5" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B6" s="247" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="C6" s="204" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="D6" s="240" t="inlineStr">
+      <c r="A6" s="313" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B6" s="314" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="C6" s="281" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="D6" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="205" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="206" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" s="205" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="208">
+      <c r="E6" s="282" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F6" s="283" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G6" s="282" t="n">
+        <v>108</v>
+      </c>
+      <c r="H6" s="285">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="248" t="inlineStr">
+      <c r="I6" s="315" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="249" t="inlineStr">
+      <c r="J6" s="316" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B7" s="238" t="inlineStr">
+      <c r="A7" s="304" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B7" s="305" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="239" t="inlineStr">
+      <c r="C7" s="306" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="240" t="inlineStr">
+      <c r="D7" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="241" t="n">
-        <v>900</v>
-      </c>
-      <c r="F7" s="242" t="n">
+      <c r="E7" s="308" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F7" s="309" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="241" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="243">
+      <c r="G7" s="308" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="310">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="244" t="inlineStr">
+      <c r="I7" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="245" t="inlineStr">
+      <c r="J7" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B8" s="247" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="C8" s="204" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="D8" s="240" t="inlineStr">
+      <c r="A8" s="313" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B8" s="314" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="C8" s="281" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="D8" s="307" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="205" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F8" s="206" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="G8" s="205" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="208">
+      <c r="E8" s="282" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="283" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G8" s="282" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" s="285">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="248" t="inlineStr">
+      <c r="I8" s="315" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="249" t="inlineStr">
+      <c r="J8" s="316" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B9" s="238" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="C9" s="239" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="D9" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E9" s="241" t="n">
-        <v>6400</v>
-      </c>
-      <c r="F9" s="242" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G9" s="241" t="n">
-        <v>64</v>
-      </c>
-      <c r="H9" s="243">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B10" s="247" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="C10" s="204" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="D10" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E10" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F10" s="206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G10" s="205" t="n">
-        <v>42</v>
-      </c>
-      <c r="H10" s="208">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B11" s="238" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="C11" s="239" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="D11" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E11" s="241" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F11" s="242" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G11" s="241" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="243">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B12" s="247" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="C12" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="D12" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E12" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F12" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G12" s="205" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" s="208">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="G14" s="52" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="G10" s="52" t="inlineStr">
         <is>
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="250">
-        <f>SUM(H3:H12)</f>
-        <v/>
-      </c>
-      <c r="I14" s="250">
-        <f>SUM(I3:I12)</f>
+      <c r="H10" s="317">
+        <f>SUM(H3:H8)</f>
+        <v/>
+      </c>
+      <c r="I10" s="317">
+        <f>SUM(I3:I8)</f>
         <v/>
       </c>
     </row>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="385">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -902,6 +902,207 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1593,47 +1794,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="189" t="inlineStr">
+      <c r="A2" s="251" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="55" t="n">
+      <c r="B2" s="252" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="56" t="n">
+      <c r="C2" s="253" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="57" t="n">
+      <c r="D2" s="254" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="58" t="n">
+      <c r="E2" s="255" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="59" t="n">
+      <c r="F2" s="256" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="60" t="n">
+      <c r="G2" s="257" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="61" t="n">
+      <c r="H2" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="62" t="n">
+      <c r="I2" s="259" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="63" t="n">
+      <c r="J2" s="260" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="64" t="n">
+      <c r="K2" s="261" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="65" t="n">
+      <c r="L2" s="262" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="189" t="inlineStr">
+      <c r="A3" s="251" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1673,7 +1874,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="189" t="inlineStr">
+      <c r="A4" s="251" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1713,42 +1914,42 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="251" t="inlineStr">
+      <c r="A5" s="318" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="252" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="253" t="n">
+      <c r="B5" s="319" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="320" t="n">
         <v>300229.8165025711</v>
       </c>
-      <c r="D5" s="254" t="n">
+      <c r="D5" s="321" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="255" t="n">
+      <c r="E5" s="322" t="n">
         <v>281805.9986114502</v>
       </c>
-      <c r="F5" s="256" t="n">
+      <c r="F5" s="323" t="n">
         <v>229.816502571106</v>
       </c>
-      <c r="G5" s="257" t="n">
+      <c r="G5" s="324" t="n">
         <v>0.0007660550085703531</v>
       </c>
-      <c r="H5" s="258" t="n">
+      <c r="H5" s="325" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="259" t="n">
+      <c r="I5" s="326" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="260" t="n">
+      <c r="J5" s="327" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="261" t="n">
+      <c r="K5" s="328" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="262" t="n">
+      <c r="L5" s="329" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1781,360 +1982,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="330" t="inlineStr">
         <is>
           <t>Current Holdings  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="331" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="331" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="331" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="331" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="331" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="331" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="331" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="331" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="331" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="331" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="264" t="inlineStr">
+      <c r="K2" s="331" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="265" t="inlineStr">
+      <c r="A3" s="332" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B3" s="333" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="267" t="n">
+      <c r="C3" s="334" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="268" t="n">
+      <c r="D3" s="335" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="269" t="n">
+      <c r="E3" s="336" t="n">
         <v>4.420000076293945</v>
       </c>
-      <c r="F3" s="270">
+      <c r="F3" s="337">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="271">
+      <c r="G3" s="338">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="272">
+      <c r="H3" s="339">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="273" t="inlineStr">
+      <c r="I3" s="340" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="274" t="n">
+      <c r="J3" s="341" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="275" t="inlineStr">
+      <c r="K3" s="342" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="265" t="inlineStr">
+      <c r="A4" s="332" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B4" s="266" t="inlineStr">
+      <c r="B4" s="333" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C4" s="267" t="n">
+      <c r="C4" s="334" t="n">
         <v>2700</v>
       </c>
-      <c r="D4" s="268" t="n">
+      <c r="D4" s="335" t="n">
         <v>17.4</v>
       </c>
-      <c r="E4" s="269" t="n">
+      <c r="E4" s="336" t="n">
         <v>17.5</v>
       </c>
-      <c r="F4" s="270">
+      <c r="F4" s="337">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="271">
+      <c r="G4" s="338">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="272">
+      <c r="H4" s="339">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="273" t="inlineStr">
+      <c r="I4" s="340" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="276" t="n">
+      <c r="J4" s="343" t="n">
         <v>6.32</v>
       </c>
-      <c r="K4" s="277" t="inlineStr">
+      <c r="K4" s="344" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="265" t="inlineStr">
+      <c r="A5" s="332" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B5" s="266" t="inlineStr">
+      <c r="B5" s="333" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C5" s="267" t="n">
+      <c r="C5" s="334" t="n">
         <v>2300</v>
       </c>
-      <c r="D5" s="268" t="n">
+      <c r="D5" s="335" t="n">
         <v>20.3</v>
       </c>
-      <c r="E5" s="269" t="n">
+      <c r="E5" s="336" t="n">
         <v>20.39999961853027</v>
       </c>
-      <c r="F5" s="270">
+      <c r="F5" s="337">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="271">
+      <c r="G5" s="338">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="272">
+      <c r="H5" s="339">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="273" t="inlineStr">
+      <c r="I5" s="340" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="278" t="n">
+      <c r="J5" s="345" t="n">
         <v>7.76</v>
       </c>
-      <c r="K5" s="279" t="inlineStr">
+      <c r="K5" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="280" t="inlineStr">
+      <c r="A6" s="347" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B6" s="281" t="inlineStr">
+      <c r="B6" s="348" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C6" s="282" t="n">
+      <c r="C6" s="349" t="n">
         <v>7000</v>
       </c>
-      <c r="D6" s="283" t="n">
+      <c r="D6" s="350" t="n">
         <v>6.7</v>
       </c>
-      <c r="E6" s="284" t="n">
+      <c r="E6" s="351" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F6" s="285">
+      <c r="F6" s="352">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="286">
+      <c r="G6" s="353">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="287">
+      <c r="H6" s="354">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="288" t="inlineStr">
+      <c r="I6" s="355" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="289" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K6" s="290" t="inlineStr">
+      <c r="J6" s="356" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K6" s="357" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="347" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="281" t="inlineStr">
+      <c r="B7" s="348" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="282" t="n">
+      <c r="C7" s="349" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="283" t="n">
+      <c r="D7" s="350" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="284" t="n">
+      <c r="E7" s="351" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="285">
+      <c r="F7" s="352">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="291">
+      <c r="G7" s="358">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="292">
+      <c r="H7" s="359">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="288" t="inlineStr">
+      <c r="I7" s="355" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="293" t="n">
+      <c r="J7" s="360" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="294" t="inlineStr">
+      <c r="K7" s="361" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="280" t="inlineStr">
+      <c r="A8" s="347" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B8" s="281" t="inlineStr">
+      <c r="B8" s="348" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C8" s="282" t="n">
+      <c r="C8" s="349" t="n">
         <v>2800</v>
       </c>
-      <c r="D8" s="283" t="n">
+      <c r="D8" s="350" t="n">
         <v>16.5</v>
       </c>
-      <c r="E8" s="284" t="n">
+      <c r="E8" s="351" t="n">
         <v>16.5</v>
       </c>
-      <c r="F8" s="285">
+      <c r="F8" s="352">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="291">
+      <c r="G8" s="358">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="292">
+      <c r="H8" s="359">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="288" t="inlineStr">
+      <c r="I8" s="355" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="289" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K8" s="290" t="inlineStr">
+      <c r="J8" s="356" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K8" s="357" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="295" t="inlineStr">
+      <c r="B9" s="362" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="296">
+      <c r="F9" s="363">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="297">
+      <c r="G9" s="364">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="298">
+      <c r="H9" s="365">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2169,306 +2370,306 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="330" t="inlineStr">
         <is>
           <t>Today's Trades  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="331" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="331" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="331" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="331" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="331" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="331" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="331" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="331" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="331" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="299" t="inlineStr">
+      <c r="A3" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="300" t="inlineStr">
+      <c r="B3" s="367" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="267" t="n">
+      <c r="C3" s="334" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="279" t="inlineStr">
+      <c r="D3" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="268" t="n">
+      <c r="E3" s="335" t="n">
         <v>20.3</v>
       </c>
-      <c r="F3" s="267" t="n">
+      <c r="F3" s="334" t="n">
         <v>23</v>
       </c>
-      <c r="G3" s="270">
+      <c r="G3" s="337">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="H3" s="301" t="inlineStr">
+      <c r="H3" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="302" t="inlineStr">
+      <c r="I3" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="299" t="inlineStr">
+      <c r="A4" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="300" t="inlineStr">
+      <c r="B4" s="367" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C4" s="267" t="n">
+      <c r="C4" s="334" t="n">
         <v>2800</v>
       </c>
-      <c r="D4" s="279" t="inlineStr">
+      <c r="D4" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="268" t="n">
+      <c r="E4" s="335" t="n">
         <v>16.5</v>
       </c>
-      <c r="F4" s="267" t="n">
+      <c r="F4" s="334" t="n">
         <v>28</v>
       </c>
-      <c r="G4" s="270">
+      <c r="G4" s="337">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="H4" s="301" t="inlineStr">
+      <c r="H4" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="302" t="inlineStr">
+      <c r="I4" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="299" t="inlineStr">
+      <c r="A5" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="300" t="inlineStr">
+      <c r="B5" s="367" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C5" s="267" t="n">
+      <c r="C5" s="334" t="n">
         <v>2700</v>
       </c>
-      <c r="D5" s="279" t="inlineStr">
+      <c r="D5" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="268" t="n">
+      <c r="E5" s="335" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="267" t="n">
+      <c r="F5" s="334" t="n">
         <v>27</v>
       </c>
-      <c r="G5" s="270">
+      <c r="G5" s="337">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="H5" s="301" t="inlineStr">
+      <c r="H5" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="302" t="inlineStr">
+      <c r="I5" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="299" t="inlineStr">
+      <c r="A6" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="300" t="inlineStr">
+      <c r="B6" s="367" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C6" s="267" t="n">
+      <c r="C6" s="334" t="n">
         <v>10800</v>
       </c>
-      <c r="D6" s="279" t="inlineStr">
+      <c r="D6" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="268" t="n">
+      <c r="E6" s="335" t="n">
         <v>4.38</v>
       </c>
-      <c r="F6" s="267" t="n">
+      <c r="F6" s="334" t="n">
         <v>108</v>
       </c>
-      <c r="G6" s="270">
+      <c r="G6" s="337">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="301" t="inlineStr">
+      <c r="H6" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="302" t="inlineStr">
+      <c r="I6" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="299" t="inlineStr">
+      <c r="A7" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="300" t="inlineStr">
+      <c r="B7" s="367" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="267" t="n">
+      <c r="C7" s="334" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="279" t="inlineStr">
+      <c r="D7" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="268" t="n">
+      <c r="E7" s="335" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="267" t="n">
+      <c r="F7" s="334" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="270">
+      <c r="G7" s="337">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="301" t="inlineStr">
+      <c r="H7" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="302" t="inlineStr">
+      <c r="I7" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="299" t="inlineStr">
+      <c r="A8" s="366" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="300" t="inlineStr">
+      <c r="B8" s="367" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C8" s="267" t="n">
+      <c r="C8" s="334" t="n">
         <v>7000</v>
       </c>
-      <c r="D8" s="279" t="inlineStr">
+      <c r="D8" s="346" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="268" t="n">
+      <c r="E8" s="335" t="n">
         <v>6.7</v>
       </c>
-      <c r="F8" s="267" t="n">
+      <c r="F8" s="334" t="n">
         <v>70</v>
       </c>
-      <c r="G8" s="270">
+      <c r="G8" s="337">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="301" t="inlineStr">
+      <c r="H8" s="368" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="302" t="inlineStr">
+      <c r="I8" s="369" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="G9" s="295" t="inlineStr">
+      <c r="G9" s="362" t="inlineStr">
         <is>
           <t>TODAY'S P&amp;L</t>
         </is>
       </c>
-      <c r="H9" s="303">
+      <c r="H9" s="370">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
@@ -2504,329 +2705,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="330" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="331" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="331" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="331" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="331" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="331" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="331" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="331" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="331" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="331" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="331" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="304" t="inlineStr">
+      <c r="A3" s="371" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="305" t="inlineStr">
+      <c r="B3" s="372" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="306" t="inlineStr">
+      <c r="C3" s="373" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="307" t="inlineStr">
+      <c r="D3" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="308" t="n">
+      <c r="E3" s="375" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="309" t="n">
+      <c r="F3" s="376" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="308" t="n">
+      <c r="G3" s="375" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="310">
+      <c r="H3" s="377">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="311" t="inlineStr">
+      <c r="I3" s="378" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="312" t="inlineStr">
+      <c r="J3" s="379" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="313" t="inlineStr">
+      <c r="A4" s="380" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="314" t="inlineStr">
+      <c r="B4" s="381" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="281" t="inlineStr">
+      <c r="C4" s="348" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="307" t="inlineStr">
+      <c r="D4" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="282" t="n">
+      <c r="E4" s="349" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="283" t="n">
+      <c r="F4" s="350" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="282" t="n">
+      <c r="G4" s="349" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="285">
+      <c r="H4" s="352">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="315" t="inlineStr">
+      <c r="I4" s="382" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="316" t="inlineStr">
+      <c r="J4" s="383" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="304" t="inlineStr">
+      <c r="A5" s="371" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="305" t="inlineStr">
+      <c r="B5" s="372" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="306" t="inlineStr">
+      <c r="C5" s="373" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="307" t="inlineStr">
+      <c r="D5" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="308" t="n">
+      <c r="E5" s="375" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="309" t="n">
+      <c r="F5" s="376" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="308" t="n">
+      <c r="G5" s="375" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="310">
+      <c r="H5" s="377">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="311" t="inlineStr">
+      <c r="I5" s="378" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="312" t="inlineStr">
+      <c r="J5" s="379" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="313" t="inlineStr">
+      <c r="A6" s="380" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="314" t="inlineStr">
+      <c r="B6" s="381" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="281" t="inlineStr">
+      <c r="C6" s="348" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="307" t="inlineStr">
+      <c r="D6" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="282" t="n">
+      <c r="E6" s="349" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="283" t="n">
+      <c r="F6" s="350" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="282" t="n">
+      <c r="G6" s="349" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="285">
+      <c r="H6" s="352">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="315" t="inlineStr">
+      <c r="I6" s="382" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="316" t="inlineStr">
+      <c r="J6" s="383" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="304" t="inlineStr">
+      <c r="A7" s="371" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="305" t="inlineStr">
+      <c r="B7" s="372" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="306" t="inlineStr">
+      <c r="C7" s="373" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="307" t="inlineStr">
+      <c r="D7" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="308" t="n">
+      <c r="E7" s="375" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="309" t="n">
+      <c r="F7" s="376" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="308" t="n">
+      <c r="G7" s="375" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="310">
+      <c r="H7" s="377">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="311" t="inlineStr">
+      <c r="I7" s="378" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="312" t="inlineStr">
+      <c r="J7" s="379" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="313" t="inlineStr">
+      <c r="A8" s="380" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="314" t="inlineStr">
+      <c r="B8" s="381" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="281" t="inlineStr">
+      <c r="C8" s="348" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="307" t="inlineStr">
+      <c r="D8" s="374" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="282" t="n">
+      <c r="E8" s="349" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="283" t="n">
+      <c r="F8" s="350" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="282" t="n">
+      <c r="G8" s="349" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="285">
+      <c r="H8" s="352">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="315" t="inlineStr">
+      <c r="I8" s="382" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="316" t="inlineStr">
+      <c r="J8" s="383" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2838,11 +3039,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="317">
+      <c r="H10" s="384">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="317">
+      <c r="I10" s="384">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="385">
+  <cellXfs count="452">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -902,6 +902,207 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1794,47 +1995,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="251" t="inlineStr">
+      <c r="A2" s="318" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="252" t="n">
+      <c r="B2" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="253" t="n">
+      <c r="C2" s="320" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="254" t="n">
+      <c r="D2" s="321" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="255" t="n">
+      <c r="E2" s="322" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="256" t="n">
+      <c r="F2" s="323" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="257" t="n">
+      <c r="G2" s="324" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="258" t="n">
+      <c r="H2" s="325" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="259" t="n">
+      <c r="I2" s="326" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="260" t="n">
+      <c r="J2" s="327" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="261" t="n">
+      <c r="K2" s="328" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="262" t="n">
+      <c r="L2" s="329" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="251" t="inlineStr">
+      <c r="A3" s="318" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1874,7 +2075,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="318" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1914,42 +2115,42 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="318" t="inlineStr">
+      <c r="A5" s="385" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="319" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="320" t="n">
+      <c r="B5" s="386" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="387" t="n">
         <v>300229.8165025711</v>
       </c>
-      <c r="D5" s="321" t="n">
+      <c r="D5" s="388" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="322" t="n">
+      <c r="E5" s="389" t="n">
         <v>281805.9986114502</v>
       </c>
-      <c r="F5" s="323" t="n">
+      <c r="F5" s="390" t="n">
         <v>229.816502571106</v>
       </c>
-      <c r="G5" s="324" t="n">
+      <c r="G5" s="391" t="n">
         <v>0.0007660550085703531</v>
       </c>
-      <c r="H5" s="325" t="n">
+      <c r="H5" s="392" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="326" t="n">
+      <c r="I5" s="393" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="327" t="n">
+      <c r="J5" s="394" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="328" t="n">
+      <c r="K5" s="395" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="329" t="n">
+      <c r="L5" s="396" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1982,360 +2183,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="330" t="inlineStr">
+      <c r="A1" s="397" t="inlineStr">
         <is>
           <t>Current Holdings  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="331" t="inlineStr">
+      <c r="A2" s="398" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="331" t="inlineStr">
+      <c r="B2" s="398" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="331" t="inlineStr">
+      <c r="C2" s="398" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="331" t="inlineStr">
+      <c r="D2" s="398" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="331" t="inlineStr">
+      <c r="E2" s="398" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="331" t="inlineStr">
+      <c r="F2" s="398" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="331" t="inlineStr">
+      <c r="G2" s="398" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="331" t="inlineStr">
+      <c r="H2" s="398" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="331" t="inlineStr">
+      <c r="I2" s="398" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="331" t="inlineStr">
+      <c r="J2" s="398" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="331" t="inlineStr">
+      <c r="K2" s="398" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="332" t="inlineStr">
+      <c r="A3" s="399" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="333" t="inlineStr">
+      <c r="B3" s="400" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="334" t="n">
+      <c r="C3" s="401" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="335" t="n">
+      <c r="D3" s="402" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="336" t="n">
+      <c r="E3" s="403" t="n">
         <v>4.420000076293945</v>
       </c>
-      <c r="F3" s="337">
+      <c r="F3" s="404">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="338">
+      <c r="G3" s="405">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="339">
+      <c r="H3" s="406">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="340" t="inlineStr">
+      <c r="I3" s="407" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="341" t="n">
+      <c r="J3" s="408" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="342" t="inlineStr">
+      <c r="K3" s="409" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="332" t="inlineStr">
+      <c r="A4" s="399" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B4" s="333" t="inlineStr">
+      <c r="B4" s="400" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C4" s="334" t="n">
+      <c r="C4" s="401" t="n">
         <v>2700</v>
       </c>
-      <c r="D4" s="335" t="n">
+      <c r="D4" s="402" t="n">
         <v>17.4</v>
       </c>
-      <c r="E4" s="336" t="n">
+      <c r="E4" s="403" t="n">
         <v>17.5</v>
       </c>
-      <c r="F4" s="337">
+      <c r="F4" s="404">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="338">
+      <c r="G4" s="405">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="339">
+      <c r="H4" s="406">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="340" t="inlineStr">
+      <c r="I4" s="407" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="343" t="n">
+      <c r="J4" s="410" t="n">
         <v>6.32</v>
       </c>
-      <c r="K4" s="344" t="inlineStr">
+      <c r="K4" s="411" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="332" t="inlineStr">
+      <c r="A5" s="399" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B5" s="333" t="inlineStr">
+      <c r="B5" s="400" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C5" s="334" t="n">
+      <c r="C5" s="401" t="n">
         <v>2300</v>
       </c>
-      <c r="D5" s="335" t="n">
+      <c r="D5" s="402" t="n">
         <v>20.3</v>
       </c>
-      <c r="E5" s="336" t="n">
+      <c r="E5" s="403" t="n">
         <v>20.39999961853027</v>
       </c>
-      <c r="F5" s="337">
+      <c r="F5" s="404">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="338">
+      <c r="G5" s="405">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="339">
+      <c r="H5" s="406">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="340" t="inlineStr">
+      <c r="I5" s="407" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="345" t="n">
+      <c r="J5" s="412" t="n">
         <v>7.76</v>
       </c>
-      <c r="K5" s="346" t="inlineStr">
+      <c r="K5" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="347" t="inlineStr">
+      <c r="A6" s="414" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B6" s="348" t="inlineStr">
+      <c r="B6" s="415" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C6" s="349" t="n">
+      <c r="C6" s="416" t="n">
         <v>7000</v>
       </c>
-      <c r="D6" s="350" t="n">
+      <c r="D6" s="417" t="n">
         <v>6.7</v>
       </c>
-      <c r="E6" s="351" t="n">
+      <c r="E6" s="418" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F6" s="352">
+      <c r="F6" s="419">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="353">
+      <c r="G6" s="420">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="354">
+      <c r="H6" s="421">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="355" t="inlineStr">
+      <c r="I6" s="422" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="356" t="n">
+      <c r="J6" s="423" t="n">
         <v>5.48</v>
       </c>
-      <c r="K6" s="357" t="inlineStr">
+      <c r="K6" s="424" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="347" t="inlineStr">
+      <c r="A7" s="414" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="348" t="inlineStr">
+      <c r="B7" s="415" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="349" t="n">
+      <c r="C7" s="416" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="350" t="n">
+      <c r="D7" s="417" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="351" t="n">
+      <c r="E7" s="418" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="352">
+      <c r="F7" s="419">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="358">
+      <c r="G7" s="425">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="359">
+      <c r="H7" s="426">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="355" t="inlineStr">
+      <c r="I7" s="422" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="360" t="n">
+      <c r="J7" s="427" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="361" t="inlineStr">
+      <c r="K7" s="428" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="347" t="inlineStr">
+      <c r="A8" s="414" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B8" s="348" t="inlineStr">
+      <c r="B8" s="415" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C8" s="349" t="n">
+      <c r="C8" s="416" t="n">
         <v>2800</v>
       </c>
-      <c r="D8" s="350" t="n">
+      <c r="D8" s="417" t="n">
         <v>16.5</v>
       </c>
-      <c r="E8" s="351" t="n">
+      <c r="E8" s="418" t="n">
         <v>16.5</v>
       </c>
-      <c r="F8" s="352">
+      <c r="F8" s="419">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="358">
+      <c r="G8" s="425">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="359">
+      <c r="H8" s="426">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="355" t="inlineStr">
+      <c r="I8" s="422" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="356" t="n">
+      <c r="J8" s="423" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="357" t="inlineStr">
+      <c r="K8" s="424" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="362" t="inlineStr">
+      <c r="B9" s="429" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="363">
+      <c r="F9" s="430">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="364">
+      <c r="G9" s="431">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="365">
+      <c r="H9" s="432">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2370,306 +2571,306 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="330" t="inlineStr">
+      <c r="A1" s="397" t="inlineStr">
         <is>
           <t>Today's Trades  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="331" t="inlineStr">
+      <c r="A2" s="398" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="331" t="inlineStr">
+      <c r="B2" s="398" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C2" s="331" t="inlineStr">
+      <c r="C2" s="398" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="331" t="inlineStr">
+      <c r="D2" s="398" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="331" t="inlineStr">
+      <c r="E2" s="398" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="331" t="inlineStr">
+      <c r="F2" s="398" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="G2" s="331" t="inlineStr">
+      <c r="G2" s="398" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="H2" s="331" t="inlineStr">
+      <c r="H2" s="398" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="I2" s="331" t="inlineStr">
+      <c r="I2" s="398" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="366" t="inlineStr">
+      <c r="A3" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="367" t="inlineStr">
+      <c r="B3" s="434" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="334" t="n">
+      <c r="C3" s="401" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="346" t="inlineStr">
+      <c r="D3" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="335" t="n">
+      <c r="E3" s="402" t="n">
         <v>20.3</v>
       </c>
-      <c r="F3" s="334" t="n">
+      <c r="F3" s="401" t="n">
         <v>23</v>
       </c>
-      <c r="G3" s="337">
+      <c r="G3" s="404">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="H3" s="368" t="inlineStr">
+      <c r="H3" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="369" t="inlineStr">
+      <c r="I3" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="366" t="inlineStr">
+      <c r="A4" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="367" t="inlineStr">
+      <c r="B4" s="434" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C4" s="334" t="n">
+      <c r="C4" s="401" t="n">
         <v>2800</v>
       </c>
-      <c r="D4" s="346" t="inlineStr">
+      <c r="D4" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="335" t="n">
+      <c r="E4" s="402" t="n">
         <v>16.5</v>
       </c>
-      <c r="F4" s="334" t="n">
+      <c r="F4" s="401" t="n">
         <v>28</v>
       </c>
-      <c r="G4" s="337">
+      <c r="G4" s="404">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="H4" s="368" t="inlineStr">
+      <c r="H4" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="369" t="inlineStr">
+      <c r="I4" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="366" t="inlineStr">
+      <c r="A5" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="367" t="inlineStr">
+      <c r="B5" s="434" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C5" s="334" t="n">
+      <c r="C5" s="401" t="n">
         <v>2700</v>
       </c>
-      <c r="D5" s="346" t="inlineStr">
+      <c r="D5" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="335" t="n">
+      <c r="E5" s="402" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="334" t="n">
+      <c r="F5" s="401" t="n">
         <v>27</v>
       </c>
-      <c r="G5" s="337">
+      <c r="G5" s="404">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="H5" s="368" t="inlineStr">
+      <c r="H5" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="369" t="inlineStr">
+      <c r="I5" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="366" t="inlineStr">
+      <c r="A6" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="367" t="inlineStr">
+      <c r="B6" s="434" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C6" s="334" t="n">
+      <c r="C6" s="401" t="n">
         <v>10800</v>
       </c>
-      <c r="D6" s="346" t="inlineStr">
+      <c r="D6" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="335" t="n">
+      <c r="E6" s="402" t="n">
         <v>4.38</v>
       </c>
-      <c r="F6" s="334" t="n">
+      <c r="F6" s="401" t="n">
         <v>108</v>
       </c>
-      <c r="G6" s="337">
+      <c r="G6" s="404">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="368" t="inlineStr">
+      <c r="H6" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="369" t="inlineStr">
+      <c r="I6" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="366" t="inlineStr">
+      <c r="A7" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="367" t="inlineStr">
+      <c r="B7" s="434" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="334" t="n">
+      <c r="C7" s="401" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="346" t="inlineStr">
+      <c r="D7" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="335" t="n">
+      <c r="E7" s="402" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="334" t="n">
+      <c r="F7" s="401" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="337">
+      <c r="G7" s="404">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="368" t="inlineStr">
+      <c r="H7" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="369" t="inlineStr">
+      <c r="I7" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="366" t="inlineStr">
+      <c r="A8" s="433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="367" t="inlineStr">
+      <c r="B8" s="434" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C8" s="334" t="n">
+      <c r="C8" s="401" t="n">
         <v>7000</v>
       </c>
-      <c r="D8" s="346" t="inlineStr">
+      <c r="D8" s="413" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="335" t="n">
+      <c r="E8" s="402" t="n">
         <v>6.7</v>
       </c>
-      <c r="F8" s="334" t="n">
+      <c r="F8" s="401" t="n">
         <v>70</v>
       </c>
-      <c r="G8" s="337">
+      <c r="G8" s="404">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="368" t="inlineStr">
+      <c r="H8" s="435" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="369" t="inlineStr">
+      <c r="I8" s="436" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="G9" s="362" t="inlineStr">
+      <c r="G9" s="429" t="inlineStr">
         <is>
           <t>TODAY'S P&amp;L</t>
         </is>
       </c>
-      <c r="H9" s="370">
+      <c r="H9" s="437">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
@@ -2705,329 +2906,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="330" t="inlineStr">
+      <c r="A1" s="397" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="331" t="inlineStr">
+      <c r="A2" s="398" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="331" t="inlineStr">
+      <c r="B2" s="398" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="331" t="inlineStr">
+      <c r="C2" s="398" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="331" t="inlineStr">
+      <c r="D2" s="398" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="331" t="inlineStr">
+      <c r="E2" s="398" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="331" t="inlineStr">
+      <c r="F2" s="398" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="331" t="inlineStr">
+      <c r="G2" s="398" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="331" t="inlineStr">
+      <c r="H2" s="398" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="331" t="inlineStr">
+      <c r="I2" s="398" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="331" t="inlineStr">
+      <c r="J2" s="398" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="371" t="inlineStr">
+      <c r="A3" s="438" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="372" t="inlineStr">
+      <c r="B3" s="439" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="373" t="inlineStr">
+      <c r="C3" s="440" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="374" t="inlineStr">
+      <c r="D3" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="375" t="n">
+      <c r="E3" s="442" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="376" t="n">
+      <c r="F3" s="443" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="375" t="n">
+      <c r="G3" s="442" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="377">
+      <c r="H3" s="444">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="378" t="inlineStr">
+      <c r="I3" s="445" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="379" t="inlineStr">
+      <c r="J3" s="446" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="380" t="inlineStr">
+      <c r="A4" s="447" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="381" t="inlineStr">
+      <c r="B4" s="448" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="348" t="inlineStr">
+      <c r="C4" s="415" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="374" t="inlineStr">
+      <c r="D4" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="349" t="n">
+      <c r="E4" s="416" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="350" t="n">
+      <c r="F4" s="417" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="349" t="n">
+      <c r="G4" s="416" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="352">
+      <c r="H4" s="419">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="382" t="inlineStr">
+      <c r="I4" s="449" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="383" t="inlineStr">
+      <c r="J4" s="450" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="371" t="inlineStr">
+      <c r="A5" s="438" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="372" t="inlineStr">
+      <c r="B5" s="439" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="373" t="inlineStr">
+      <c r="C5" s="440" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="374" t="inlineStr">
+      <c r="D5" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="375" t="n">
+      <c r="E5" s="442" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="376" t="n">
+      <c r="F5" s="443" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="375" t="n">
+      <c r="G5" s="442" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="377">
+      <c r="H5" s="444">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="378" t="inlineStr">
+      <c r="I5" s="445" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="379" t="inlineStr">
+      <c r="J5" s="446" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="380" t="inlineStr">
+      <c r="A6" s="447" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="381" t="inlineStr">
+      <c r="B6" s="448" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="348" t="inlineStr">
+      <c r="C6" s="415" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="374" t="inlineStr">
+      <c r="D6" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="349" t="n">
+      <c r="E6" s="416" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="350" t="n">
+      <c r="F6" s="417" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="349" t="n">
+      <c r="G6" s="416" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="352">
+      <c r="H6" s="419">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="382" t="inlineStr">
+      <c r="I6" s="449" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="383" t="inlineStr">
+      <c r="J6" s="450" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="371" t="inlineStr">
+      <c r="A7" s="438" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="372" t="inlineStr">
+      <c r="B7" s="439" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="373" t="inlineStr">
+      <c r="C7" s="440" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="374" t="inlineStr">
+      <c r="D7" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="375" t="n">
+      <c r="E7" s="442" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="376" t="n">
+      <c r="F7" s="443" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="375" t="n">
+      <c r="G7" s="442" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="377">
+      <c r="H7" s="444">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="378" t="inlineStr">
+      <c r="I7" s="445" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="379" t="inlineStr">
+      <c r="J7" s="446" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="380" t="inlineStr">
+      <c r="A8" s="447" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="381" t="inlineStr">
+      <c r="B8" s="448" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="348" t="inlineStr">
+      <c r="C8" s="415" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="374" t="inlineStr">
+      <c r="D8" s="441" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="349" t="n">
+      <c r="E8" s="416" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="350" t="n">
+      <c r="F8" s="417" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="349" t="n">
+      <c r="G8" s="416" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="352">
+      <c r="H8" s="419">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="382" t="inlineStr">
+      <c r="I8" s="449" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="383" t="inlineStr">
+      <c r="J8" s="450" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3039,11 +3240,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="384">
+      <c r="H10" s="451">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="384">
+      <c r="I10" s="451">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="452">
+  <cellXfs count="519">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -902,6 +902,207 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1995,47 +2196,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="318" t="inlineStr">
+      <c r="A2" s="385" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="319" t="n">
+      <c r="B2" s="386" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="320" t="n">
+      <c r="C2" s="387" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="321" t="n">
+      <c r="D2" s="388" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="322" t="n">
+      <c r="E2" s="389" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="323" t="n">
+      <c r="F2" s="390" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="324" t="n">
+      <c r="G2" s="391" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="325" t="n">
+      <c r="H2" s="392" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="326" t="n">
+      <c r="I2" s="393" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="327" t="n">
+      <c r="J2" s="394" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="328" t="n">
+      <c r="K2" s="395" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="329" t="n">
+      <c r="L2" s="396" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="318" t="inlineStr">
+      <c r="A3" s="385" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -2075,7 +2276,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="318" t="inlineStr">
+      <c r="A4" s="385" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -2115,42 +2316,42 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="385" t="inlineStr">
+      <c r="A5" s="452" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="386" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="387" t="n">
+      <c r="B5" s="453" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="454" t="n">
         <v>300229.8165025711</v>
       </c>
-      <c r="D5" s="388" t="n">
+      <c r="D5" s="455" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="389" t="n">
+      <c r="E5" s="456" t="n">
         <v>281805.9986114502</v>
       </c>
-      <c r="F5" s="390" t="n">
+      <c r="F5" s="457" t="n">
         <v>229.816502571106</v>
       </c>
-      <c r="G5" s="391" t="n">
+      <c r="G5" s="458" t="n">
         <v>0.0007660550085703531</v>
       </c>
-      <c r="H5" s="392" t="n">
+      <c r="H5" s="459" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="393" t="n">
+      <c r="I5" s="460" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="394" t="n">
+      <c r="J5" s="461" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="395" t="n">
+      <c r="K5" s="462" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="396" t="n">
+      <c r="L5" s="463" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2183,360 +2384,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="397" t="inlineStr">
+      <c r="A1" s="464" t="inlineStr">
         <is>
           <t>Current Holdings  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="398" t="inlineStr">
+      <c r="A2" s="465" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="398" t="inlineStr">
+      <c r="B2" s="465" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="398" t="inlineStr">
+      <c r="C2" s="465" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="398" t="inlineStr">
+      <c r="D2" s="465" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="398" t="inlineStr">
+      <c r="E2" s="465" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="398" t="inlineStr">
+      <c r="F2" s="465" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="398" t="inlineStr">
+      <c r="G2" s="465" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="398" t="inlineStr">
+      <c r="H2" s="465" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="398" t="inlineStr">
+      <c r="I2" s="465" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="398" t="inlineStr">
+      <c r="J2" s="465" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="398" t="inlineStr">
+      <c r="K2" s="465" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="399" t="inlineStr">
+      <c r="A3" s="466" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="400" t="inlineStr">
+      <c r="B3" s="467" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="401" t="n">
+      <c r="C3" s="468" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="402" t="n">
+      <c r="D3" s="469" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="403" t="n">
+      <c r="E3" s="470" t="n">
         <v>4.420000076293945</v>
       </c>
-      <c r="F3" s="404">
+      <c r="F3" s="471">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="405">
+      <c r="G3" s="472">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="406">
+      <c r="H3" s="473">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="407" t="inlineStr">
+      <c r="I3" s="474" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="408" t="n">
+      <c r="J3" s="475" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="409" t="inlineStr">
+      <c r="K3" s="476" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="399" t="inlineStr">
+      <c r="A4" s="466" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B4" s="400" t="inlineStr">
+      <c r="B4" s="467" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C4" s="401" t="n">
+      <c r="C4" s="468" t="n">
         <v>2700</v>
       </c>
-      <c r="D4" s="402" t="n">
+      <c r="D4" s="469" t="n">
         <v>17.4</v>
       </c>
-      <c r="E4" s="403" t="n">
+      <c r="E4" s="470" t="n">
         <v>17.5</v>
       </c>
-      <c r="F4" s="404">
+      <c r="F4" s="471">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="405">
+      <c r="G4" s="472">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="406">
+      <c r="H4" s="473">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="407" t="inlineStr">
+      <c r="I4" s="474" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="410" t="n">
+      <c r="J4" s="477" t="n">
         <v>6.32</v>
       </c>
-      <c r="K4" s="411" t="inlineStr">
+      <c r="K4" s="478" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="399" t="inlineStr">
+      <c r="A5" s="466" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B5" s="400" t="inlineStr">
+      <c r="B5" s="467" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C5" s="401" t="n">
+      <c r="C5" s="468" t="n">
         <v>2300</v>
       </c>
-      <c r="D5" s="402" t="n">
+      <c r="D5" s="469" t="n">
         <v>20.3</v>
       </c>
-      <c r="E5" s="403" t="n">
+      <c r="E5" s="470" t="n">
         <v>20.39999961853027</v>
       </c>
-      <c r="F5" s="404">
+      <c r="F5" s="471">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="405">
+      <c r="G5" s="472">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="406">
+      <c r="H5" s="473">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="407" t="inlineStr">
+      <c r="I5" s="474" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="412" t="n">
+      <c r="J5" s="479" t="n">
         <v>7.76</v>
       </c>
-      <c r="K5" s="413" t="inlineStr">
+      <c r="K5" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="414" t="inlineStr">
+      <c r="A6" s="481" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B6" s="415" t="inlineStr">
+      <c r="B6" s="482" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C6" s="416" t="n">
+      <c r="C6" s="483" t="n">
         <v>7000</v>
       </c>
-      <c r="D6" s="417" t="n">
+      <c r="D6" s="484" t="n">
         <v>6.7</v>
       </c>
-      <c r="E6" s="418" t="n">
+      <c r="E6" s="485" t="n">
         <v>6.699999809265137</v>
       </c>
-      <c r="F6" s="419">
+      <c r="F6" s="486">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="420">
+      <c r="G6" s="487">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="421">
+      <c r="H6" s="488">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="422" t="inlineStr">
+      <c r="I6" s="489" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="423" t="n">
+      <c r="J6" s="490" t="n">
         <v>5.48</v>
       </c>
-      <c r="K6" s="424" t="inlineStr">
+      <c r="K6" s="491" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="414" t="inlineStr">
+      <c r="A7" s="481" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="415" t="inlineStr">
+      <c r="B7" s="482" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="416" t="n">
+      <c r="C7" s="483" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="417" t="n">
+      <c r="D7" s="484" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="418" t="n">
+      <c r="E7" s="485" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="419">
+      <c r="F7" s="486">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="425">
+      <c r="G7" s="492">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="426">
+      <c r="H7" s="493">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="422" t="inlineStr">
+      <c r="I7" s="489" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="427" t="n">
+      <c r="J7" s="494" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="428" t="inlineStr">
+      <c r="K7" s="495" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="414" t="inlineStr">
+      <c r="A8" s="481" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B8" s="415" t="inlineStr">
+      <c r="B8" s="482" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C8" s="416" t="n">
+      <c r="C8" s="483" t="n">
         <v>2800</v>
       </c>
-      <c r="D8" s="417" t="n">
+      <c r="D8" s="484" t="n">
         <v>16.5</v>
       </c>
-      <c r="E8" s="418" t="n">
+      <c r="E8" s="485" t="n">
         <v>16.5</v>
       </c>
-      <c r="F8" s="419">
+      <c r="F8" s="486">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="425">
+      <c r="G8" s="492">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="426">
+      <c r="H8" s="493">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="422" t="inlineStr">
+      <c r="I8" s="489" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="423" t="n">
+      <c r="J8" s="490" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="424" t="inlineStr">
+      <c r="K8" s="491" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="429" t="inlineStr">
+      <c r="B9" s="496" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="430">
+      <c r="F9" s="497">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="431">
+      <c r="G9" s="498">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="432">
+      <c r="H9" s="499">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2571,306 +2772,306 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="397" t="inlineStr">
+      <c r="A1" s="464" t="inlineStr">
         <is>
           <t>Today's Trades  —  27 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="398" t="inlineStr">
+      <c r="A2" s="465" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="398" t="inlineStr">
+      <c r="B2" s="465" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C2" s="398" t="inlineStr">
+      <c r="C2" s="465" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="398" t="inlineStr">
+      <c r="D2" s="465" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="398" t="inlineStr">
+      <c r="E2" s="465" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="398" t="inlineStr">
+      <c r="F2" s="465" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="G2" s="398" t="inlineStr">
+      <c r="G2" s="465" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="H2" s="398" t="inlineStr">
+      <c r="H2" s="465" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="I2" s="398" t="inlineStr">
+      <c r="I2" s="465" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="433" t="inlineStr">
+      <c r="A3" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="434" t="inlineStr">
+      <c r="B3" s="501" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="401" t="n">
+      <c r="C3" s="468" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="413" t="inlineStr">
+      <c r="D3" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="402" t="n">
+      <c r="E3" s="469" t="n">
         <v>20.3</v>
       </c>
-      <c r="F3" s="401" t="n">
+      <c r="F3" s="468" t="n">
         <v>23</v>
       </c>
-      <c r="G3" s="404">
+      <c r="G3" s="471">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="H3" s="435" t="inlineStr">
+      <c r="H3" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I3" s="436" t="inlineStr">
+      <c r="I3" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="433" t="inlineStr">
+      <c r="A4" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="434" t="inlineStr">
+      <c r="B4" s="501" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C4" s="401" t="n">
+      <c r="C4" s="468" t="n">
         <v>2800</v>
       </c>
-      <c r="D4" s="413" t="inlineStr">
+      <c r="D4" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="402" t="n">
+      <c r="E4" s="469" t="n">
         <v>16.5</v>
       </c>
-      <c r="F4" s="401" t="n">
+      <c r="F4" s="468" t="n">
         <v>28</v>
       </c>
-      <c r="G4" s="404">
+      <c r="G4" s="471">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="H4" s="435" t="inlineStr">
+      <c r="H4" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="436" t="inlineStr">
+      <c r="I4" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="433" t="inlineStr">
+      <c r="A5" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="434" t="inlineStr">
+      <c r="B5" s="501" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C5" s="401" t="n">
+      <c r="C5" s="468" t="n">
         <v>2700</v>
       </c>
-      <c r="D5" s="413" t="inlineStr">
+      <c r="D5" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="402" t="n">
+      <c r="E5" s="469" t="n">
         <v>17.4</v>
       </c>
-      <c r="F5" s="401" t="n">
+      <c r="F5" s="468" t="n">
         <v>27</v>
       </c>
-      <c r="G5" s="404">
+      <c r="G5" s="471">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="H5" s="435" t="inlineStr">
+      <c r="H5" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="436" t="inlineStr">
+      <c r="I5" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="433" t="inlineStr">
+      <c r="A6" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="434" t="inlineStr">
+      <c r="B6" s="501" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C6" s="401" t="n">
+      <c r="C6" s="468" t="n">
         <v>10800</v>
       </c>
-      <c r="D6" s="413" t="inlineStr">
+      <c r="D6" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="402" t="n">
+      <c r="E6" s="469" t="n">
         <v>4.38</v>
       </c>
-      <c r="F6" s="401" t="n">
+      <c r="F6" s="468" t="n">
         <v>108</v>
       </c>
-      <c r="G6" s="404">
+      <c r="G6" s="471">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="H6" s="435" t="inlineStr">
+      <c r="H6" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="436" t="inlineStr">
+      <c r="I6" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="433" t="inlineStr">
+      <c r="A7" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="434" t="inlineStr">
+      <c r="B7" s="501" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="401" t="n">
+      <c r="C7" s="468" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="413" t="inlineStr">
+      <c r="D7" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="402" t="n">
+      <c r="E7" s="469" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="401" t="n">
+      <c r="F7" s="468" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="404">
+      <c r="G7" s="471">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="H7" s="435" t="inlineStr">
+      <c r="H7" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="436" t="inlineStr">
+      <c r="I7" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="433" t="inlineStr">
+      <c r="A8" s="500" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="434" t="inlineStr">
+      <c r="B8" s="501" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C8" s="401" t="n">
+      <c r="C8" s="468" t="n">
         <v>7000</v>
       </c>
-      <c r="D8" s="413" t="inlineStr">
+      <c r="D8" s="480" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="402" t="n">
+      <c r="E8" s="469" t="n">
         <v>6.7</v>
       </c>
-      <c r="F8" s="401" t="n">
+      <c r="F8" s="468" t="n">
         <v>70</v>
       </c>
-      <c r="G8" s="404">
+      <c r="G8" s="471">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="H8" s="435" t="inlineStr">
+      <c r="H8" s="502" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="436" t="inlineStr">
+      <c r="I8" s="503" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="G9" s="429" t="inlineStr">
+      <c r="G9" s="496" t="inlineStr">
         <is>
           <t>TODAY'S P&amp;L</t>
         </is>
       </c>
-      <c r="H9" s="437">
+      <c r="H9" s="504">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
@@ -2906,329 +3107,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="397" t="inlineStr">
+      <c r="A1" s="464" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="398" t="inlineStr">
+      <c r="A2" s="465" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="398" t="inlineStr">
+      <c r="B2" s="465" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="398" t="inlineStr">
+      <c r="C2" s="465" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="398" t="inlineStr">
+      <c r="D2" s="465" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="398" t="inlineStr">
+      <c r="E2" s="465" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="398" t="inlineStr">
+      <c r="F2" s="465" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="398" t="inlineStr">
+      <c r="G2" s="465" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="398" t="inlineStr">
+      <c r="H2" s="465" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="398" t="inlineStr">
+      <c r="I2" s="465" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="398" t="inlineStr">
+      <c r="J2" s="465" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="438" t="inlineStr">
+      <c r="A3" s="505" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="439" t="inlineStr">
+      <c r="B3" s="506" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="440" t="inlineStr">
+      <c r="C3" s="507" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="441" t="inlineStr">
+      <c r="D3" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="442" t="n">
+      <c r="E3" s="509" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="443" t="n">
+      <c r="F3" s="510" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="442" t="n">
+      <c r="G3" s="509" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="444">
+      <c r="H3" s="511">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="445" t="inlineStr">
+      <c r="I3" s="512" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="446" t="inlineStr">
+      <c r="J3" s="513" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="447" t="inlineStr">
+      <c r="A4" s="514" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="448" t="inlineStr">
+      <c r="B4" s="515" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="415" t="inlineStr">
+      <c r="C4" s="482" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="441" t="inlineStr">
+      <c r="D4" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="416" t="n">
+      <c r="E4" s="483" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="417" t="n">
+      <c r="F4" s="484" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="416" t="n">
+      <c r="G4" s="483" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="419">
+      <c r="H4" s="486">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="449" t="inlineStr">
+      <c r="I4" s="516" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="450" t="inlineStr">
+      <c r="J4" s="517" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="438" t="inlineStr">
+      <c r="A5" s="505" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="439" t="inlineStr">
+      <c r="B5" s="506" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="440" t="inlineStr">
+      <c r="C5" s="507" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="441" t="inlineStr">
+      <c r="D5" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="442" t="n">
+      <c r="E5" s="509" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="443" t="n">
+      <c r="F5" s="510" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="442" t="n">
+      <c r="G5" s="509" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="444">
+      <c r="H5" s="511">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="445" t="inlineStr">
+      <c r="I5" s="512" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="446" t="inlineStr">
+      <c r="J5" s="513" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="447" t="inlineStr">
+      <c r="A6" s="514" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="448" t="inlineStr">
+      <c r="B6" s="515" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="415" t="inlineStr">
+      <c r="C6" s="482" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="441" t="inlineStr">
+      <c r="D6" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="416" t="n">
+      <c r="E6" s="483" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="417" t="n">
+      <c r="F6" s="484" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="416" t="n">
+      <c r="G6" s="483" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="419">
+      <c r="H6" s="486">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="449" t="inlineStr">
+      <c r="I6" s="516" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="450" t="inlineStr">
+      <c r="J6" s="517" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="438" t="inlineStr">
+      <c r="A7" s="505" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="439" t="inlineStr">
+      <c r="B7" s="506" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="440" t="inlineStr">
+      <c r="C7" s="507" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="441" t="inlineStr">
+      <c r="D7" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="442" t="n">
+      <c r="E7" s="509" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="443" t="n">
+      <c r="F7" s="510" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="442" t="n">
+      <c r="G7" s="509" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="444">
+      <c r="H7" s="511">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="445" t="inlineStr">
+      <c r="I7" s="512" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="446" t="inlineStr">
+      <c r="J7" s="513" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="447" t="inlineStr">
+      <c r="A8" s="514" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="448" t="inlineStr">
+      <c r="B8" s="515" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="415" t="inlineStr">
+      <c r="C8" s="482" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="441" t="inlineStr">
+      <c r="D8" s="508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="416" t="n">
+      <c r="E8" s="483" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="417" t="n">
+      <c r="F8" s="484" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="416" t="n">
+      <c r="G8" s="483" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="419">
+      <c r="H8" s="486">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="449" t="inlineStr">
+      <c r="I8" s="516" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="450" t="inlineStr">
+      <c r="J8" s="517" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3240,11 +3441,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="451">
+      <c r="H10" s="518">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="451">
+      <c r="I10" s="518">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -893,6 +899,195 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1306,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1700,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="251" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B5" s="252" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="253" t="n">
+        <v>300229.8165025711</v>
+      </c>
+      <c r="D5" s="254" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E5" s="255" t="n">
+        <v>281805.9986114502</v>
+      </c>
+      <c r="F5" s="256" t="n">
+        <v>229.816502571106</v>
+      </c>
+      <c r="G5" s="257" t="n">
+        <v>0.0007660550085703531</v>
+      </c>
+      <c r="H5" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="260" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1517,7 +1752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1529,464 +1764,372 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  28 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="J2" s="264" t="inlineStr">
+        <is>
+          <t>Comp Score</t>
+        </is>
+      </c>
+      <c r="K2" s="264" t="inlineStr">
+        <is>
+          <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="203" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C3" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="D3" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E3" s="207" t="n">
-        <v>1.409999966621399</v>
-      </c>
-      <c r="F3" s="208">
+      <c r="A3" s="265" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="266" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C3" s="267" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D3" s="268" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E3" s="269" t="n">
+        <v>4.420000076293945</v>
+      </c>
+      <c r="F3" s="270">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="209">
+      <c r="G3" s="271">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="210">
+      <c r="H3" s="272">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I3" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J3" s="274" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="K3" s="275" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="203" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="204" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C4" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D4" s="206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E4" s="207" t="n">
-        <v>6.699999809265137</v>
-      </c>
-      <c r="F4" s="208">
+      <c r="A4" s="265" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="266" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C4" s="267" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D4" s="268" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E4" s="269" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F4" s="270">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="209">
+      <c r="G4" s="271">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="210">
+      <c r="H4" s="272">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I4" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J4" s="276" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K4" s="277" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="203" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="204" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C5" s="205" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D5" s="206" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E5" s="207" t="n">
-        <v>4.380000114440918</v>
-      </c>
-      <c r="F5" s="208">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="266" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C5" s="267" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="268" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E5" s="269" t="n">
+        <v>20.39999961853027</v>
+      </c>
+      <c r="F5" s="270">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="209">
+      <c r="G5" s="271">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="210">
+      <c r="H5" s="272">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I5" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J5" s="278" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="K5" s="279" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="203" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="204" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="C6" s="205" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="206" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E6" s="207" t="n">
-        <v>11.19999980926514</v>
-      </c>
-      <c r="F6" s="208">
+      <c r="A6" s="280" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="281" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C6" s="282" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="283" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" s="284" t="n">
+        <v>6.699999809265137</v>
+      </c>
+      <c r="F6" s="285">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="209">
+      <c r="G6" s="286">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="210">
+      <c r="H6" s="287">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I6" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J6" s="289" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="K6" s="290" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="212" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="213" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="C7" s="214" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D7" s="215" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="E7" s="216" t="n">
-        <v>13.80000019073486</v>
-      </c>
-      <c r="F7" s="217">
+      <c r="A7" s="280" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="281" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="282" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="283" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E7" s="284" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F7" s="285">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="218">
+      <c r="G7" s="291">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="219">
+      <c r="H7" s="292">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I7" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J7" s="293" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K7" s="294" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="212" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="213" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="C8" s="214" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="215" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" s="216" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F8" s="217">
+      <c r="A8" s="280" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="281" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C8" s="282" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D8" s="283" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E8" s="284" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F8" s="285">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="218">
+      <c r="G8" s="291">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="219">
+      <c r="H8" s="292">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I8" s="288" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J8" s="293" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K8" s="294" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="221" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B9" s="222" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C9" s="223" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D9" s="224" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E9" s="225" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F9" s="226">
-        <f>C9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="227">
-        <f>F9-C9*D9</f>
-        <v/>
-      </c>
-      <c r="H9" s="228">
-        <f>(E9-D9)/D9</f>
-        <v/>
-      </c>
-      <c r="I9" s="229" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="203" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B10" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C10" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D10" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E10" s="207" t="n">
-        <v>20.29999923706055</v>
-      </c>
-      <c r="F10" s="208">
-        <f>C10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="209">
-        <f>F10-C10*D10</f>
-        <v/>
-      </c>
-      <c r="H10" s="210">
-        <f>(E10-D10)/D10</f>
-        <v/>
-      </c>
-      <c r="I10" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="203" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B11" s="204" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C11" s="205" t="n">
-        <v>900</v>
-      </c>
-      <c r="D11" s="206" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E11" s="207" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F11" s="208">
-        <f>C11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="230">
-        <f>F11-C11*D11</f>
-        <v/>
-      </c>
-      <c r="H11" s="231">
-        <f>(E11-D11)/D11</f>
-        <v/>
-      </c>
-      <c r="I11" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="203" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="B12" s="204" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="C12" s="205" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" s="206" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="E12" s="207" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="F12" s="208">
-        <f>C12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="230">
-        <f>F12-C12*D12</f>
-        <v/>
-      </c>
-      <c r="H12" s="231">
-        <f>(E12-D12)/D12</f>
-        <v/>
-      </c>
-      <c r="I12" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="232" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="295" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="233">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="234">
-        <f>SUM(G3:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="235">
-        <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
+      <c r="F9" s="296">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="297">
+        <f>SUM(G3:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="298">
+        <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,14 +2157,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  28 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="236" t="inlineStr">
+      <c r="A3" s="299" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2043,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2059,526 +2202,346 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Complete Trade History  —  since 2026-04-21</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="202" t="inlineStr">
+      <c r="J2" s="264" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B3" s="238" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="C3" s="239" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="D3" s="240" t="inlineStr">
+      <c r="A3" s="300" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3" s="301" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="C3" s="302" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="D3" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="241" t="n">
-        <v>200</v>
-      </c>
-      <c r="F3" s="242" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="G3" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="243">
+      <c r="E3" s="304" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F3" s="305" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G3" s="304" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" s="306">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="244" t="inlineStr">
+      <c r="I3" s="307" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="245" t="inlineStr">
+      <c r="J3" s="308" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B4" s="247" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="C4" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="D4" s="240" t="inlineStr">
+      <c r="A4" s="309" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B4" s="310" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="C4" s="281" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="D4" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="F4" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G4" s="205" t="n">
-        <v>202</v>
-      </c>
-      <c r="H4" s="208">
+      <c r="E4" s="282" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F4" s="283" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G4" s="282" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" s="285">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="248" t="inlineStr">
+      <c r="I4" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="249" t="inlineStr">
+      <c r="J4" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B5" s="238" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="C5" s="239" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="D5" s="240" t="inlineStr">
+      <c r="A5" s="300" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="301" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="C5" s="302" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="D5" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="241" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F5" s="242" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G5" s="241" t="n">
-        <v>25</v>
-      </c>
-      <c r="H5" s="243">
+      <c r="E5" s="304" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F5" s="305" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G5" s="304" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="306">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="244" t="inlineStr">
+      <c r="I5" s="307" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="245" t="inlineStr">
+      <c r="J5" s="308" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B6" s="247" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="C6" s="204" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="D6" s="240" t="inlineStr">
+      <c r="A6" s="309" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B6" s="310" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="C6" s="281" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="D6" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="205" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="206" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" s="205" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="208">
+      <c r="E6" s="282" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F6" s="283" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G6" s="282" t="n">
+        <v>108</v>
+      </c>
+      <c r="H6" s="285">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="248" t="inlineStr">
+      <c r="I6" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="249" t="inlineStr">
+      <c r="J6" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B7" s="238" t="inlineStr">
+      <c r="A7" s="300" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B7" s="301" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="239" t="inlineStr">
+      <c r="C7" s="302" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="240" t="inlineStr">
+      <c r="D7" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="241" t="n">
-        <v>900</v>
-      </c>
-      <c r="F7" s="242" t="n">
+      <c r="E7" s="304" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F7" s="305" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="241" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="243">
+      <c r="G7" s="304" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="306">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="244" t="inlineStr">
+      <c r="I7" s="307" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="245" t="inlineStr">
+      <c r="J7" s="308" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B8" s="247" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="C8" s="204" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="D8" s="240" t="inlineStr">
+      <c r="A8" s="309" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B8" s="310" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="C8" s="281" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="D8" s="303" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="205" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F8" s="206" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="G8" s="205" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="208">
+      <c r="E8" s="282" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="283" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G8" s="282" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" s="285">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="248" t="inlineStr">
+      <c r="I8" s="311" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="249" t="inlineStr">
+      <c r="J8" s="312" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B9" s="238" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="C9" s="239" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="D9" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E9" s="241" t="n">
-        <v>6400</v>
-      </c>
-      <c r="F9" s="242" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G9" s="241" t="n">
-        <v>64</v>
-      </c>
-      <c r="H9" s="243">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B10" s="247" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="C10" s="204" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="D10" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E10" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F10" s="206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G10" s="205" t="n">
-        <v>42</v>
-      </c>
-      <c r="H10" s="208">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B11" s="238" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="C11" s="239" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="D11" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E11" s="241" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F11" s="242" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G11" s="241" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="243">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B12" s="247" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="C12" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="D12" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E12" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F12" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G12" s="205" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" s="208">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="G14" s="52" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="G10" s="52" t="inlineStr">
         <is>
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="250">
-        <f>SUM(H3:H12)</f>
-        <v/>
-      </c>
-      <c r="I14" s="250">
-        <f>SUM(I3:I12)</f>
+      <c r="H10" s="313">
+        <f>SUM(H3:H8)</f>
+        <v/>
+      </c>
+      <c r="I10" s="313">
+        <f>SUM(I3:I8)</f>
         <v/>
       </c>
     </row>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="314">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1088,6 +1088,210 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1501,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1581,47 +1785,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="189" t="inlineStr">
+      <c r="A2" s="251" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="55" t="n">
+      <c r="B2" s="252" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="56" t="n">
+      <c r="C2" s="253" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="57" t="n">
+      <c r="D2" s="254" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="58" t="n">
+      <c r="E2" s="255" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="59" t="n">
+      <c r="F2" s="256" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="60" t="n">
+      <c r="G2" s="257" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="61" t="n">
+      <c r="H2" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="62" t="n">
+      <c r="I2" s="259" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="63" t="n">
+      <c r="J2" s="260" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="64" t="n">
+      <c r="K2" s="261" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="65" t="n">
+      <c r="L2" s="262" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="189" t="inlineStr">
+      <c r="A3" s="251" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1661,7 +1865,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="189" t="inlineStr">
+      <c r="A4" s="251" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1737,6 +1941,46 @@
         <v>0</v>
       </c>
       <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="314" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B6" s="315" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="316" t="n">
+        <v>298807.8158082962</v>
+      </c>
+      <c r="D6" s="317" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E6" s="318" t="n">
+        <v>280383.9979171753</v>
+      </c>
+      <c r="F6" s="319" t="n">
+        <v>-1192.184191703796</v>
+      </c>
+      <c r="G6" s="320" t="n">
+        <v>-0.003973947305679322</v>
+      </c>
+      <c r="H6" s="321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="322" t="n">
+        <v>-0.004736373991231229</v>
+      </c>
+      <c r="J6" s="323" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1769,360 +2013,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  28 Apr 2026</t>
+      <c r="A1" s="326" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  29 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="327" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="327" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="327" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="327" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="327" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="327" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="327" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="327" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="327" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="327" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="264" t="inlineStr">
+      <c r="K2" s="327" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="265" t="inlineStr">
+      <c r="A3" s="328" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B3" s="329" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="267" t="n">
+      <c r="C3" s="330" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="268" t="n">
+      <c r="D3" s="331" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="269" t="n">
-        <v>4.420000076293945</v>
-      </c>
-      <c r="F3" s="270">
+      <c r="E3" s="332" t="n">
+        <v>4.380000114440918</v>
+      </c>
+      <c r="F3" s="333">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="271">
+      <c r="G3" s="334">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="272">
+      <c r="H3" s="335">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="273" t="inlineStr">
+      <c r="I3" s="336" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="274" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="K3" s="275" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+      <c r="J3" s="337" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K3" s="338" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="265" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="266" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C4" s="267" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D4" s="268" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E4" s="269" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F4" s="270">
+      <c r="A4" s="328" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="329" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C4" s="330" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D4" s="331" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" s="332" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="F4" s="333">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="271">
+      <c r="G4" s="334">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="272">
+      <c r="H4" s="335">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="273" t="inlineStr">
+      <c r="I4" s="336" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="276" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="K4" s="277" t="inlineStr">
+      <c r="J4" s="337" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K4" s="338" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="265" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="266" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C5" s="267" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D5" s="268" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E5" s="269" t="n">
-        <v>20.39999961853027</v>
-      </c>
-      <c r="F5" s="270">
+      <c r="A5" s="328" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="329" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C5" s="330" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D5" s="331" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E5" s="332" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F5" s="333">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="271">
+      <c r="G5" s="334">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="272">
+      <c r="H5" s="335">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="273" t="inlineStr">
+      <c r="I5" s="336" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="278" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="K5" s="279" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
+      <c r="J5" s="339" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K5" s="340" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="280" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="281" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C6" s="282" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D6" s="283" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E6" s="284" t="n">
-        <v>6.699999809265137</v>
-      </c>
-      <c r="F6" s="285">
+      <c r="A6" s="328" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="329" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C6" s="330" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D6" s="331" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E6" s="332" t="n">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="F6" s="333">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="286">
+      <c r="G6" s="334">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="287">
+      <c r="H6" s="335">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="288" t="inlineStr">
+      <c r="I6" s="336" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="289" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="K6" s="290" t="inlineStr">
+      <c r="J6" s="339" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="K6" s="340" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="280" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="281" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C7" s="282" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D7" s="283" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E7" s="284" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F7" s="285">
+      <c r="A7" s="341" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="342" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C7" s="343" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D7" s="344" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E7" s="345" t="n">
+        <v>20.10000038146973</v>
+      </c>
+      <c r="F7" s="346">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="291">
+      <c r="G7" s="347">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="292">
+      <c r="H7" s="348">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="288" t="inlineStr">
+      <c r="I7" s="349" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="293" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K7" s="294" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J7" s="350" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="K7" s="351" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="280" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="281" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C8" s="282" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D8" s="283" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E8" s="284" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F8" s="285">
+      <c r="A8" s="352" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="353" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C8" s="354" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D8" s="355" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E8" s="356" t="n">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="F8" s="357">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="291">
+      <c r="G8" s="358">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="292">
+      <c r="H8" s="359">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="288" t="inlineStr">
+      <c r="I8" s="360" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="293" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K8" s="294" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J8" s="361" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K8" s="362" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="295" t="inlineStr">
+      <c r="B9" s="363" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="296">
+      <c r="F9" s="364">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="297">
+      <c r="G9" s="365">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="298">
+      <c r="H9" s="366">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2157,14 +2401,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  28 Apr 2026</t>
+      <c r="A1" s="326" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  29 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="299" t="inlineStr">
+      <c r="A3" s="367" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2202,329 +2446,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="326" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="327" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="327" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="327" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="327" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="327" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="327" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="327" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="327" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="327" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="327" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="300" t="inlineStr">
+      <c r="A3" s="368" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="301" t="inlineStr">
+      <c r="B3" s="369" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="302" t="inlineStr">
+      <c r="C3" s="370" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="303" t="inlineStr">
+      <c r="D3" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="304" t="n">
+      <c r="E3" s="372" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="305" t="n">
+      <c r="F3" s="373" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="304" t="n">
+      <c r="G3" s="372" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="306">
+      <c r="H3" s="374">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="307" t="inlineStr">
+      <c r="I3" s="375" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="308" t="inlineStr">
+      <c r="J3" s="376" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="309" t="inlineStr">
+      <c r="A4" s="377" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="310" t="inlineStr">
+      <c r="B4" s="378" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="281" t="inlineStr">
+      <c r="C4" s="342" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="303" t="inlineStr">
+      <c r="D4" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="282" t="n">
+      <c r="E4" s="343" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="283" t="n">
+      <c r="F4" s="344" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="282" t="n">
+      <c r="G4" s="343" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="285">
+      <c r="H4" s="346">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="311" t="inlineStr">
+      <c r="I4" s="379" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="312" t="inlineStr">
+      <c r="J4" s="380" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="300" t="inlineStr">
+      <c r="A5" s="368" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="301" t="inlineStr">
+      <c r="B5" s="369" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="302" t="inlineStr">
+      <c r="C5" s="370" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="303" t="inlineStr">
+      <c r="D5" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="304" t="n">
+      <c r="E5" s="372" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="305" t="n">
+      <c r="F5" s="373" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="304" t="n">
+      <c r="G5" s="372" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="306">
+      <c r="H5" s="374">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="307" t="inlineStr">
+      <c r="I5" s="375" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="308" t="inlineStr">
+      <c r="J5" s="376" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="309" t="inlineStr">
+      <c r="A6" s="377" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="310" t="inlineStr">
+      <c r="B6" s="378" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="281" t="inlineStr">
+      <c r="C6" s="342" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="303" t="inlineStr">
+      <c r="D6" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="282" t="n">
+      <c r="E6" s="343" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="283" t="n">
+      <c r="F6" s="344" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="282" t="n">
+      <c r="G6" s="343" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="285">
+      <c r="H6" s="346">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="311" t="inlineStr">
+      <c r="I6" s="379" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="312" t="inlineStr">
+      <c r="J6" s="380" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="300" t="inlineStr">
+      <c r="A7" s="368" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="301" t="inlineStr">
+      <c r="B7" s="369" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="302" t="inlineStr">
+      <c r="C7" s="370" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="303" t="inlineStr">
+      <c r="D7" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="304" t="n">
+      <c r="E7" s="372" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="305" t="n">
+      <c r="F7" s="373" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="304" t="n">
+      <c r="G7" s="372" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="306">
+      <c r="H7" s="374">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="307" t="inlineStr">
+      <c r="I7" s="375" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="308" t="inlineStr">
+      <c r="J7" s="376" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="309" t="inlineStr">
+      <c r="A8" s="377" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="310" t="inlineStr">
+      <c r="B8" s="378" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="281" t="inlineStr">
+      <c r="C8" s="342" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="303" t="inlineStr">
+      <c r="D8" s="371" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="282" t="n">
+      <c r="E8" s="343" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="283" t="n">
+      <c r="F8" s="344" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="282" t="n">
+      <c r="G8" s="343" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="285">
+      <c r="H8" s="346">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="311" t="inlineStr">
+      <c r="I8" s="379" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="312" t="inlineStr">
+      <c r="J8" s="380" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2536,11 +2780,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="313">
+      <c r="H10" s="381">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="313">
+      <c r="I10" s="381">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,12 +125,6 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFC000"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="382">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -887,399 +881,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1705,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1785,47 +1386,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="251" t="inlineStr">
+      <c r="A2" s="189" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="252" t="n">
+      <c r="B2" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="253" t="n">
+      <c r="C2" s="56" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="254" t="n">
+      <c r="D2" s="57" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="255" t="n">
+      <c r="E2" s="58" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="256" t="n">
+      <c r="F2" s="59" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="257" t="n">
+      <c r="G2" s="60" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="258" t="n">
+      <c r="H2" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="259" t="n">
+      <c r="I2" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="260" t="n">
+      <c r="J2" s="63" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="261" t="n">
+      <c r="K2" s="64" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="262" t="n">
+      <c r="L2" s="65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="251" t="inlineStr">
+      <c r="A3" s="189" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1865,7 +1466,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="189" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1901,86 +1502,6 @@
         <v>0</v>
       </c>
       <c r="L4" s="200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="251" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B5" s="252" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="253" t="n">
-        <v>300229.8165025711</v>
-      </c>
-      <c r="D5" s="254" t="n">
-        <v>18423.81789112091</v>
-      </c>
-      <c r="E5" s="255" t="n">
-        <v>281805.9986114502</v>
-      </c>
-      <c r="F5" s="256" t="n">
-        <v>229.816502571106</v>
-      </c>
-      <c r="G5" s="257" t="n">
-        <v>0.0007660550085703531</v>
-      </c>
-      <c r="H5" s="258" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="259" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="260" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" s="261" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="314" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B6" s="315" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="316" t="n">
-        <v>298807.8158082962</v>
-      </c>
-      <c r="D6" s="317" t="n">
-        <v>18423.81789112091</v>
-      </c>
-      <c r="E6" s="318" t="n">
-        <v>280383.9979171753</v>
-      </c>
-      <c r="F6" s="319" t="n">
-        <v>-1192.184191703796</v>
-      </c>
-      <c r="G6" s="320" t="n">
-        <v>-0.003973947305679322</v>
-      </c>
-      <c r="H6" s="321" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="322" t="n">
-        <v>-0.004736373991231229</v>
-      </c>
-      <c r="J6" s="323" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" s="324" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="325" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1996,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2008,372 +1529,464 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="326" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  29 Apr 2026</t>
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="327" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="327" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="327" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="327" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="327" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="327" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="327" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="327" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="327" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="327" t="inlineStr">
-        <is>
-          <t>Comp Score</t>
-        </is>
-      </c>
-      <c r="K2" s="327" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="328" t="inlineStr">
+      <c r="A3" s="203" t="inlineStr">
+        <is>
+          <t>SIRI.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="204" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
+      <c r="C3" s="205" t="n">
+        <v>20200</v>
+      </c>
+      <c r="D3" s="206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E3" s="207" t="n">
+        <v>1.409999966621399</v>
+      </c>
+      <c r="F3" s="208">
+        <f>C3*E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="209">
+        <f>F3-C3*D3</f>
+        <v/>
+      </c>
+      <c r="H3" s="210">
+        <f>(E3-D3)/D3</f>
+        <v/>
+      </c>
+      <c r="I3" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="203" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="204" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C4" s="205" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D4" s="206" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" s="207" t="n">
+        <v>6.699999809265137</v>
+      </c>
+      <c r="F4" s="208">
+        <f>C4*E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="209">
+        <f>F4-C4*D4</f>
+        <v/>
+      </c>
+      <c r="H4" s="210">
+        <f>(E4-D4)/D4</f>
+        <v/>
+      </c>
+      <c r="I4" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="203" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="329" t="inlineStr">
+      <c r="B5" s="204" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="330" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D3" s="331" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E3" s="332" t="n">
+      <c r="C5" s="205" t="n">
+        <v>6400</v>
+      </c>
+      <c r="D5" s="206" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E5" s="207" t="n">
         <v>4.380000114440918</v>
       </c>
-      <c r="F3" s="333">
-        <f>C3*E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="334">
-        <f>F3-C3*D3</f>
-        <v/>
-      </c>
-      <c r="H3" s="335">
-        <f>(E3-D3)/D3</f>
-        <v/>
-      </c>
-      <c r="I3" s="336" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J3" s="337" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="K3" s="338" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="328" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="329" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C4" s="330" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D4" s="331" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E4" s="332" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="F4" s="333">
-        <f>C4*E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="334">
-        <f>F4-C4*D4</f>
-        <v/>
-      </c>
-      <c r="H4" s="335">
-        <f>(E4-D4)/D4</f>
-        <v/>
-      </c>
-      <c r="I4" s="336" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J4" s="337" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K4" s="338" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="328" t="inlineStr">
+      <c r="F5" s="208">
+        <f>C5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="209">
+        <f>F5-C5*D5</f>
+        <v/>
+      </c>
+      <c r="H5" s="210">
+        <f>(E5-D5)/D5</f>
+        <v/>
+      </c>
+      <c r="I5" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="203" t="inlineStr">
+        <is>
+          <t>TU.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="204" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="C6" s="205" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="206" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E6" s="207" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="F6" s="208">
+        <f>C6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="209">
+        <f>F6-C6*D6</f>
+        <v/>
+      </c>
+      <c r="H6" s="210">
+        <f>(E6-D6)/D6</f>
+        <v/>
+      </c>
+      <c r="I6" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="212" t="inlineStr">
+        <is>
+          <t>TQM.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="213" t="inlineStr">
+        <is>
+          <t>TQM</t>
+        </is>
+      </c>
+      <c r="C7" s="214" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D7" s="215" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E7" s="216" t="n">
+        <v>13.80000019073486</v>
+      </c>
+      <c r="F7" s="217">
+        <f>C7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="218">
+        <f>F7-C7*D7</f>
+        <v/>
+      </c>
+      <c r="H7" s="219">
+        <f>(E7-D7)/D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="212" t="inlineStr">
+        <is>
+          <t>BAY.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="213" t="inlineStr">
+        <is>
+          <t>BAY</t>
+        </is>
+      </c>
+      <c r="C8" s="214" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="215" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="216" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F8" s="217">
+        <f>C8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="218">
+        <f>F8-C8*D8</f>
+        <v/>
+      </c>
+      <c r="H8" s="219">
+        <f>(E8-D8)/D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="221" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B9" s="222" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C9" s="223" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D9" s="224" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E9" s="225" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F9" s="226">
+        <f>C9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="227">
+        <f>F9-C9*D9</f>
+        <v/>
+      </c>
+      <c r="H9" s="228">
+        <f>(E9-D9)/D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="229" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="203" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B10" s="204" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C10" s="205" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D10" s="206" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E10" s="207" t="n">
+        <v>20.29999923706055</v>
+      </c>
+      <c r="F10" s="208">
+        <f>C10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="209">
+        <f>F10-C10*D10</f>
+        <v/>
+      </c>
+      <c r="H10" s="210">
+        <f>(E10-D10)/D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="203" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B5" s="329" t="inlineStr">
+      <c r="B11" s="204" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C5" s="330" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D5" s="331" t="n">
+      <c r="C11" s="205" t="n">
+        <v>900</v>
+      </c>
+      <c r="D11" s="206" t="n">
         <v>29.25</v>
       </c>
-      <c r="E5" s="332" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="F5" s="333">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="334">
-        <f>F5-C5*D5</f>
-        <v/>
-      </c>
-      <c r="H5" s="335">
-        <f>(E5-D5)/D5</f>
-        <v/>
-      </c>
-      <c r="I5" s="336" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J5" s="339" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K5" s="340" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="328" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="329" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C6" s="330" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D6" s="331" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E6" s="332" t="n">
-        <v>16.79999923706055</v>
-      </c>
-      <c r="F6" s="333">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="334">
-        <f>F6-C6*D6</f>
-        <v/>
-      </c>
-      <c r="H6" s="335">
-        <f>(E6-D6)/D6</f>
-        <v/>
-      </c>
-      <c r="I6" s="336" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J6" s="339" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="K6" s="340" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="341" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="342" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C7" s="343" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D7" s="344" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E7" s="345" t="n">
-        <v>20.10000038146973</v>
-      </c>
-      <c r="F7" s="346">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="347">
-        <f>F7-C7*D7</f>
-        <v/>
-      </c>
-      <c r="H7" s="348">
-        <f>(E7-D7)/D7</f>
-        <v/>
-      </c>
-      <c r="I7" s="349" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J7" s="350" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="K7" s="351" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="352" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="353" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C8" s="354" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D8" s="355" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E8" s="356" t="n">
-        <v>16.79999923706055</v>
-      </c>
-      <c r="F8" s="357">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="358">
-        <f>F8-C8*D8</f>
-        <v/>
-      </c>
-      <c r="H8" s="359">
-        <f>(E8-D8)/D8</f>
-        <v/>
-      </c>
-      <c r="I8" s="360" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J8" s="361" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="K8" s="362" t="inlineStr">
-        <is>
-          <t>AVOID</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="363" t="inlineStr">
+      <c r="E11" s="207" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F11" s="208">
+        <f>C11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="230">
+        <f>F11-C11*D11</f>
+        <v/>
+      </c>
+      <c r="H11" s="231">
+        <f>(E11-D11)/D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="203" t="inlineStr">
+        <is>
+          <t>TISCO.BK</t>
+        </is>
+      </c>
+      <c r="B12" s="204" t="inlineStr">
+        <is>
+          <t>TISCO</t>
+        </is>
+      </c>
+      <c r="C12" s="205" t="n">
+        <v>200</v>
+      </c>
+      <c r="D12" s="206" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E12" s="207" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="F12" s="208">
+        <f>C12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="230">
+        <f>F12-C12*D12</f>
+        <v/>
+      </c>
+      <c r="H12" s="231">
+        <f>(E12-D12)/D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="232" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="364">
-        <f>SUM(F3:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="365">
-        <f>SUM(G3:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="366">
-        <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
+      <c r="F13" s="233">
+        <f>SUM(F3:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="234">
+        <f>SUM(G3:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="235">
+        <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2401,14 +2014,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="326" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  29 Apr 2026</t>
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  24 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="367" t="inlineStr">
+      <c r="A3" s="236" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2430,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2446,346 +2059,526 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="326" t="inlineStr">
-        <is>
-          <t>Complete Trade History  —  since 2026-04-27</t>
+      <c r="A1" s="201" t="inlineStr">
+        <is>
+          <t>Complete Trade History  —  since 2026-04-21</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="327" t="inlineStr">
+      <c r="A2" s="202" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="327" t="inlineStr">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="327" t="inlineStr">
+      <c r="C2" s="202" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="327" t="inlineStr">
+      <c r="D2" s="202" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="327" t="inlineStr">
+      <c r="E2" s="202" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="327" t="inlineStr">
+      <c r="F2" s="202" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="327" t="inlineStr">
+      <c r="G2" s="202" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="327" t="inlineStr">
+      <c r="H2" s="202" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="327" t="inlineStr">
+      <c r="I2" s="202" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="327" t="inlineStr">
+      <c r="J2" s="202" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="368" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B3" s="369" t="inlineStr">
+      <c r="A3" s="237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B3" s="238" t="inlineStr">
+        <is>
+          <t>TISCO.BK</t>
+        </is>
+      </c>
+      <c r="C3" s="239" t="inlineStr">
+        <is>
+          <t>TISCO</t>
+        </is>
+      </c>
+      <c r="D3" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E3" s="241" t="n">
+        <v>200</v>
+      </c>
+      <c r="F3" s="242" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="G3" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="243">
+        <f>E3*F3</f>
+        <v/>
+      </c>
+      <c r="I3" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="245" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B4" s="247" t="inlineStr">
+        <is>
+          <t>SIRI.BK</t>
+        </is>
+      </c>
+      <c r="C4" s="204" t="inlineStr">
+        <is>
+          <t>SIRI</t>
+        </is>
+      </c>
+      <c r="D4" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E4" s="205" t="n">
+        <v>20200</v>
+      </c>
+      <c r="F4" s="206" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G4" s="205" t="n">
+        <v>202</v>
+      </c>
+      <c r="H4" s="208">
+        <f>E4*F4</f>
+        <v/>
+      </c>
+      <c r="I4" s="248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="249" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B5" s="238" t="inlineStr">
+        <is>
+          <t>TU.BK</t>
+        </is>
+      </c>
+      <c r="C5" s="239" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="D5" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E5" s="241" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F5" s="242" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G5" s="241" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="243">
+        <f>E5*F5</f>
+        <v/>
+      </c>
+      <c r="I5" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="245" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B6" s="247" t="inlineStr">
+        <is>
+          <t>BAY.BK</t>
+        </is>
+      </c>
+      <c r="C6" s="204" t="inlineStr">
+        <is>
+          <t>BAY</t>
+        </is>
+      </c>
+      <c r="D6" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E6" s="205" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="206" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" s="205" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="208">
+        <f>E6*F6</f>
+        <v/>
+      </c>
+      <c r="I6" s="248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="249" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B7" s="238" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="C7" s="239" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="D7" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E7" s="241" t="n">
+        <v>900</v>
+      </c>
+      <c r="F7" s="242" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="G7" s="241" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="243">
+        <f>E7*F7</f>
+        <v/>
+      </c>
+      <c r="I7" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="245" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B8" s="247" t="inlineStr">
+        <is>
+          <t>TQM.BK</t>
+        </is>
+      </c>
+      <c r="C8" s="204" t="inlineStr">
+        <is>
+          <t>TQM</t>
+        </is>
+      </c>
+      <c r="D8" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E8" s="205" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="206" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G8" s="205" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="208">
+        <f>E8*F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="249" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B9" s="238" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="C9" s="239" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="D9" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E9" s="241" t="n">
+        <v>6400</v>
+      </c>
+      <c r="F9" s="242" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G9" s="241" t="n">
+        <v>64</v>
+      </c>
+      <c r="H9" s="243">
+        <f>E9*F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="245" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B10" s="247" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="C10" s="204" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="D10" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E10" s="205" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F10" s="206" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" s="205" t="n">
+        <v>42</v>
+      </c>
+      <c r="H10" s="208">
+        <f>E10*F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="248" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="249" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B11" s="238" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="C11" s="239" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="D11" s="240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E11" s="241" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F11" s="242" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G11" s="241" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="243">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="244" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="245" t="inlineStr">
+        <is>
+          <t>BUY (Day 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B12" s="247" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="370" t="inlineStr">
+      <c r="C12" s="204" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="371" t="inlineStr">
+      <c r="D12" s="240" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="372" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F3" s="373" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G3" s="372" t="n">
-        <v>23</v>
-      </c>
-      <c r="H3" s="374">
-        <f>E3*F3</f>
-        <v/>
-      </c>
-      <c r="I3" s="375" t="inlineStr">
+      <c r="E12" s="205" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="206" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G12" s="205" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" s="208">
+        <f>E12*F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="248" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="376" t="inlineStr">
+      <c r="J12" s="249" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="377" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B4" s="378" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="C4" s="342" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="D4" s="371" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E4" s="343" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F4" s="344" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G4" s="343" t="n">
-        <v>28</v>
-      </c>
-      <c r="H4" s="346">
-        <f>E4*F4</f>
-        <v/>
-      </c>
-      <c r="I4" s="379" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="380" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="368" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B5" s="369" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="C5" s="370" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="D5" s="371" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E5" s="372" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F5" s="373" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G5" s="372" t="n">
-        <v>27</v>
-      </c>
-      <c r="H5" s="374">
-        <f>E5*F5</f>
-        <v/>
-      </c>
-      <c r="I5" s="375" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="376" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="377" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B6" s="378" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="C6" s="342" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="D6" s="371" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E6" s="343" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F6" s="344" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="G6" s="343" t="n">
-        <v>108</v>
-      </c>
-      <c r="H6" s="346">
-        <f>E6*F6</f>
-        <v/>
-      </c>
-      <c r="I6" s="379" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="380" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="368" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B7" s="369" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="C7" s="370" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="D7" s="371" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E7" s="372" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F7" s="373" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="G7" s="372" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="374">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-      <c r="I7" s="375" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="376" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="377" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="B8" s="378" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="C8" s="342" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="D8" s="371" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E8" s="343" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F8" s="344" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G8" s="343" t="n">
-        <v>70</v>
-      </c>
-      <c r="H8" s="346">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-      <c r="I8" s="379" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="380" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="G10" s="52" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="G14" s="52" t="inlineStr">
         <is>
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="381">
-        <f>SUM(H3:H8)</f>
-        <v/>
-      </c>
-      <c r="I10" s="381">
-        <f>SUM(I3:I8)</f>
+      <c r="H14" s="250">
+        <f>SUM(H3:H12)</f>
+        <v/>
+      </c>
+      <c r="I14" s="250">
+        <f>SUM(I3:I12)</f>
         <v/>
       </c>
     </row>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trade History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,12 @@
       <color rgb="0000B050"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -190,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -893,6 +899,177 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1306,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1682,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="251" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B5" s="252" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="253" t="n">
+        <v>304153.8160982132</v>
+      </c>
+      <c r="D5" s="254" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E5" s="255" t="n">
+        <v>285729.9982070923</v>
+      </c>
+      <c r="F5" s="256" t="n">
+        <v>4153.816098213196</v>
+      </c>
+      <c r="G5" s="257" t="n">
+        <v>0.01384605366071065</v>
+      </c>
+      <c r="H5" s="258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="260" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1517,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1529,464 +1746,372 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  29 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="J2" s="264" t="inlineStr">
+        <is>
+          <t>Comp Score</t>
+        </is>
+      </c>
+      <c r="K2" s="264" t="inlineStr">
+        <is>
+          <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="203" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C3" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="D3" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E3" s="207" t="n">
-        <v>1.409999966621399</v>
-      </c>
-      <c r="F3" s="208">
+      <c r="A3" s="265" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="266" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C3" s="267" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D3" s="268" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E3" s="269" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F3" s="270">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="209">
+      <c r="G3" s="271">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="210">
+      <c r="H3" s="272">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I3" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J3" s="274" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="K3" s="275" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="203" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="204" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C4" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D4" s="206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E4" s="207" t="n">
-        <v>6.699999809265137</v>
-      </c>
-      <c r="F4" s="208">
+      <c r="A4" s="265" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="266" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C4" s="267" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D4" s="268" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E4" s="269" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" s="270">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="209">
+      <c r="G4" s="271">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="210">
+      <c r="H4" s="272">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I4" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J4" s="276" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="K4" s="277" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="203" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="204" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C5" s="205" t="n">
-        <v>6400</v>
-      </c>
-      <c r="D5" s="206" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E5" s="207" t="n">
-        <v>4.380000114440918</v>
-      </c>
-      <c r="F5" s="208">
+      <c r="A5" s="265" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="266" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C5" s="267" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="268" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E5" s="269" t="n">
+        <v>6.800000190734863</v>
+      </c>
+      <c r="F5" s="270">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="209">
+      <c r="G5" s="271">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="210">
+      <c r="H5" s="272">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I5" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J5" s="274" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="K5" s="275" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="203" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="204" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="C6" s="205" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="206" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E6" s="207" t="n">
-        <v>11.19999980926514</v>
-      </c>
-      <c r="F6" s="208">
+      <c r="A6" s="265" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="266" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C6" s="267" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D6" s="268" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E6" s="269" t="n">
+        <v>16.89999961853027</v>
+      </c>
+      <c r="F6" s="270">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="209">
+      <c r="G6" s="271">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="210">
+      <c r="H6" s="272">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I6" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J6" s="276" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K6" s="277" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="212" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="213" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="C7" s="214" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D7" s="215" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="E7" s="216" t="n">
-        <v>13.80000019073486</v>
-      </c>
-      <c r="F7" s="217">
+      <c r="A7" s="265" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="266" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="267" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="268" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E7" s="269" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F7" s="270">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="218">
+      <c r="G7" s="271">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="219">
+      <c r="H7" s="272">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I7" s="273" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J7" s="276" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K7" s="277" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="212" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="213" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="C8" s="214" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="215" t="n">
-        <v>26</v>
-      </c>
-      <c r="E8" s="216" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F8" s="217">
+      <c r="A8" s="278" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="279" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C8" s="280" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D8" s="281" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E8" s="282" t="n">
+        <v>17.29999923706055</v>
+      </c>
+      <c r="F8" s="283">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="218">
+      <c r="G8" s="284">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="219">
+      <c r="H8" s="285">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="220" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
+      <c r="I8" s="286" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="J8" s="287" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K8" s="288" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="221" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B9" s="222" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C9" s="223" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D9" s="224" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E9" s="225" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F9" s="226">
-        <f>C9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="227">
-        <f>F9-C9*D9</f>
-        <v/>
-      </c>
-      <c r="H9" s="228">
-        <f>(E9-D9)/D9</f>
-        <v/>
-      </c>
-      <c r="I9" s="229" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="203" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B10" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C10" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D10" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E10" s="207" t="n">
-        <v>20.29999923706055</v>
-      </c>
-      <c r="F10" s="208">
-        <f>C10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="209">
-        <f>F10-C10*D10</f>
-        <v/>
-      </c>
-      <c r="H10" s="210">
-        <f>(E10-D10)/D10</f>
-        <v/>
-      </c>
-      <c r="I10" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="203" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B11" s="204" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C11" s="205" t="n">
-        <v>900</v>
-      </c>
-      <c r="D11" s="206" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E11" s="207" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F11" s="208">
-        <f>C11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="230">
-        <f>F11-C11*D11</f>
-        <v/>
-      </c>
-      <c r="H11" s="231">
-        <f>(E11-D11)/D11</f>
-        <v/>
-      </c>
-      <c r="I11" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="203" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="B12" s="204" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="C12" s="205" t="n">
-        <v>200</v>
-      </c>
-      <c r="D12" s="206" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="E12" s="207" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="F12" s="208">
-        <f>C12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="230">
-        <f>F12-C12*D12</f>
-        <v/>
-      </c>
-      <c r="H12" s="231">
-        <f>(E12-D12)/D12</f>
-        <v/>
-      </c>
-      <c r="I12" s="211" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="232" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="289" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="233">
-        <f>SUM(F3:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="234">
-        <f>SUM(G3:G12)</f>
-        <v/>
-      </c>
-      <c r="H13" s="235">
-        <f>G13/SUMPRODUCT(C3:C12,D3:D12)</f>
+      <c r="F9" s="290">
+        <f>SUM(F3:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="291">
+        <f>SUM(G3:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="292">
+        <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2014,14 +2139,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  24 Apr 2026</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  29 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="236" t="inlineStr">
+      <c r="A3" s="293" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2043,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2059,526 +2184,346 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="201" t="inlineStr">
-        <is>
-          <t>Complete Trade History  —  since 2026-04-21</t>
+      <c r="A1" s="263" t="inlineStr">
+        <is>
+          <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="202" t="inlineStr">
+      <c r="A2" s="264" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="202" t="inlineStr">
+      <c r="B2" s="264" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="202" t="inlineStr">
+      <c r="C2" s="264" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="202" t="inlineStr">
+      <c r="D2" s="264" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="202" t="inlineStr">
+      <c r="E2" s="264" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="202" t="inlineStr">
+      <c r="F2" s="264" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="202" t="inlineStr">
+      <c r="G2" s="264" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="202" t="inlineStr">
+      <c r="H2" s="264" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="202" t="inlineStr">
+      <c r="I2" s="264" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="202" t="inlineStr">
+      <c r="J2" s="264" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B3" s="238" t="inlineStr">
-        <is>
-          <t>TISCO.BK</t>
-        </is>
-      </c>
-      <c r="C3" s="239" t="inlineStr">
-        <is>
-          <t>TISCO</t>
-        </is>
-      </c>
-      <c r="D3" s="240" t="inlineStr">
+      <c r="A3" s="294" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B3" s="295" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="C3" s="296" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="D3" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="241" t="n">
-        <v>200</v>
-      </c>
-      <c r="F3" s="242" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="G3" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="243">
+      <c r="E3" s="298" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F3" s="299" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G3" s="298" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" s="300">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="244" t="inlineStr">
+      <c r="I3" s="301" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="245" t="inlineStr">
+      <c r="J3" s="302" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B4" s="247" t="inlineStr">
-        <is>
-          <t>SIRI.BK</t>
-        </is>
-      </c>
-      <c r="C4" s="204" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="D4" s="240" t="inlineStr">
+      <c r="A4" s="303" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B4" s="304" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="C4" s="279" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="D4" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="205" t="n">
-        <v>20200</v>
-      </c>
-      <c r="F4" s="206" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G4" s="205" t="n">
-        <v>202</v>
-      </c>
-      <c r="H4" s="208">
+      <c r="E4" s="280" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F4" s="281" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G4" s="280" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" s="283">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="248" t="inlineStr">
+      <c r="I4" s="305" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="249" t="inlineStr">
+      <c r="J4" s="306" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B5" s="238" t="inlineStr">
-        <is>
-          <t>TU.BK</t>
-        </is>
-      </c>
-      <c r="C5" s="239" t="inlineStr">
-        <is>
-          <t>TU</t>
-        </is>
-      </c>
-      <c r="D5" s="240" t="inlineStr">
+      <c r="A5" s="294" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B5" s="295" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="C5" s="296" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="D5" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="241" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F5" s="242" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="G5" s="241" t="n">
-        <v>25</v>
-      </c>
-      <c r="H5" s="243">
+      <c r="E5" s="298" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F5" s="299" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G5" s="298" t="n">
+        <v>27</v>
+      </c>
+      <c r="H5" s="300">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="244" t="inlineStr">
+      <c r="I5" s="301" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="245" t="inlineStr">
+      <c r="J5" s="302" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B6" s="247" t="inlineStr">
-        <is>
-          <t>BAY.BK</t>
-        </is>
-      </c>
-      <c r="C6" s="204" t="inlineStr">
-        <is>
-          <t>BAY</t>
-        </is>
-      </c>
-      <c r="D6" s="240" t="inlineStr">
+      <c r="A6" s="303" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B6" s="304" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="C6" s="279" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="D6" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="205" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" s="206" t="n">
-        <v>26</v>
-      </c>
-      <c r="G6" s="205" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" s="208">
+      <c r="E6" s="280" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F6" s="281" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="G6" s="280" t="n">
+        <v>108</v>
+      </c>
+      <c r="H6" s="283">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="248" t="inlineStr">
+      <c r="I6" s="305" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="249" t="inlineStr">
+      <c r="J6" s="306" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B7" s="238" t="inlineStr">
+      <c r="A7" s="294" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B7" s="295" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="239" t="inlineStr">
+      <c r="C7" s="296" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="240" t="inlineStr">
+      <c r="D7" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="241" t="n">
-        <v>900</v>
-      </c>
-      <c r="F7" s="242" t="n">
+      <c r="E7" s="298" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F7" s="299" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="241" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" s="243">
+      <c r="G7" s="298" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="300">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="244" t="inlineStr">
+      <c r="I7" s="301" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="245" t="inlineStr">
+      <c r="J7" s="302" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B8" s="247" t="inlineStr">
-        <is>
-          <t>TQM.BK</t>
-        </is>
-      </c>
-      <c r="C8" s="204" t="inlineStr">
-        <is>
-          <t>TQM</t>
-        </is>
-      </c>
-      <c r="D8" s="240" t="inlineStr">
+      <c r="A8" s="303" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B8" s="304" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="C8" s="279" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="D8" s="297" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="205" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F8" s="206" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="G8" s="205" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="208">
+      <c r="E8" s="280" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F8" s="281" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G8" s="280" t="n">
+        <v>70</v>
+      </c>
+      <c r="H8" s="283">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="248" t="inlineStr">
+      <c r="I8" s="305" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="249" t="inlineStr">
+      <c r="J8" s="306" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B9" s="238" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="C9" s="239" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="D9" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E9" s="241" t="n">
-        <v>6400</v>
-      </c>
-      <c r="F9" s="242" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G9" s="241" t="n">
-        <v>64</v>
-      </c>
-      <c r="H9" s="243">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B10" s="247" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="C10" s="204" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="D10" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E10" s="205" t="n">
-        <v>4200</v>
-      </c>
-      <c r="F10" s="206" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G10" s="205" t="n">
-        <v>42</v>
-      </c>
-      <c r="H10" s="208">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="237" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B11" s="238" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="C11" s="239" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="D11" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E11" s="241" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F11" s="242" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G11" s="241" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="243">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="244" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="245" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="246" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B12" s="247" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="C12" s="204" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="D12" s="240" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E12" s="205" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F12" s="206" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G12" s="205" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" s="208">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="248" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="249" t="inlineStr">
-        <is>
-          <t>BUY (Day 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="G14" s="52" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="G10" s="52" t="inlineStr">
         <is>
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H14" s="250">
-        <f>SUM(H3:H12)</f>
-        <v/>
-      </c>
-      <c r="I14" s="250">
-        <f>SUM(I3:I12)</f>
+      <c r="H10" s="307">
+        <f>SUM(H3:H8)</f>
+        <v/>
+      </c>
+      <c r="I10" s="307">
+        <f>SUM(I3:I8)</f>
         <v/>
       </c>
     </row>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="367">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1058,6 +1058,183 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1483,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1563,47 +1740,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="189" t="inlineStr">
+      <c r="A2" s="251" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="55" t="n">
+      <c r="B2" s="252" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="56" t="n">
+      <c r="C2" s="253" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="57" t="n">
+      <c r="D2" s="254" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="58" t="n">
+      <c r="E2" s="255" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="59" t="n">
+      <c r="F2" s="256" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="60" t="n">
+      <c r="G2" s="257" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="61" t="n">
+      <c r="H2" s="258" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="62" t="n">
+      <c r="I2" s="259" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="63" t="n">
+      <c r="J2" s="260" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="64" t="n">
+      <c r="K2" s="261" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="65" t="n">
+      <c r="L2" s="262" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="189" t="inlineStr">
+      <c r="A3" s="251" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1643,7 +1820,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="189" t="inlineStr">
+      <c r="A4" s="251" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1719,6 +1896,46 @@
         <v>0</v>
       </c>
       <c r="L5" s="262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="308" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B6" s="309" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="310" t="n">
+        <v>304153.8160982132</v>
+      </c>
+      <c r="D6" s="311" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E6" s="312" t="n">
+        <v>285729.9982070923</v>
+      </c>
+      <c r="F6" s="313" t="n">
+        <v>4153.816098213196</v>
+      </c>
+      <c r="G6" s="314" t="n">
+        <v>0.01384605366071065</v>
+      </c>
+      <c r="H6" s="315" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="317" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="319" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1751,360 +1968,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  29 Apr 2026</t>
+      <c r="A1" s="320" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  30 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="321" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="321" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="321" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="321" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="321" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="321" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="321" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="321" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="321" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="321" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="264" t="inlineStr">
+      <c r="K2" s="321" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="265" t="inlineStr">
+      <c r="A3" s="322" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B3" s="323" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="267" t="n">
+      <c r="C3" s="324" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="268" t="n">
+      <c r="D3" s="325" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="269" t="n">
+      <c r="E3" s="326" t="n">
         <v>4.5</v>
       </c>
-      <c r="F3" s="270">
+      <c r="F3" s="327">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="271">
+      <c r="G3" s="328">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="272">
+      <c r="H3" s="329">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="273" t="inlineStr">
+      <c r="I3" s="330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="274" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="K3" s="275" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+      <c r="J3" s="331" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K3" s="332" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="265" t="inlineStr">
+      <c r="A4" s="322" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B4" s="266" t="inlineStr">
+      <c r="B4" s="323" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C4" s="267" t="n">
+      <c r="C4" s="324" t="n">
         <v>2300</v>
       </c>
-      <c r="D4" s="268" t="n">
+      <c r="D4" s="325" t="n">
         <v>20.3</v>
       </c>
-      <c r="E4" s="269" t="n">
+      <c r="E4" s="326" t="n">
         <v>21</v>
       </c>
-      <c r="F4" s="270">
+      <c r="F4" s="327">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="271">
+      <c r="G4" s="328">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="272">
+      <c r="H4" s="329">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="273" t="inlineStr">
+      <c r="I4" s="330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="276" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="K4" s="277" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
+      <c r="J4" s="333" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K4" s="334" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="265" t="inlineStr">
+      <c r="A5" s="322" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B5" s="266" t="inlineStr">
+      <c r="B5" s="323" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C5" s="267" t="n">
+      <c r="C5" s="324" t="n">
         <v>7000</v>
       </c>
-      <c r="D5" s="268" t="n">
+      <c r="D5" s="325" t="n">
         <v>6.7</v>
       </c>
-      <c r="E5" s="269" t="n">
+      <c r="E5" s="326" t="n">
         <v>6.800000190734863</v>
       </c>
-      <c r="F5" s="270">
+      <c r="F5" s="327">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="271">
+      <c r="G5" s="328">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="272">
+      <c r="H5" s="329">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="273" t="inlineStr">
+      <c r="I5" s="330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="274" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="K5" s="275" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J5" s="335" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K5" s="336" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="265" t="inlineStr">
+      <c r="A6" s="322" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B6" s="266" t="inlineStr">
+      <c r="B6" s="323" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C6" s="267" t="n">
+      <c r="C6" s="324" t="n">
         <v>2800</v>
       </c>
-      <c r="D6" s="268" t="n">
+      <c r="D6" s="325" t="n">
         <v>16.5</v>
       </c>
-      <c r="E6" s="269" t="n">
+      <c r="E6" s="326" t="n">
         <v>16.89999961853027</v>
       </c>
-      <c r="F6" s="270">
+      <c r="F6" s="327">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="271">
+      <c r="G6" s="328">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="272">
+      <c r="H6" s="329">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="273" t="inlineStr">
+      <c r="I6" s="330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="276" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K6" s="277" t="inlineStr">
+      <c r="J6" s="333" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K6" s="334" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="265" t="inlineStr">
+      <c r="A7" s="322" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="266" t="inlineStr">
+      <c r="B7" s="323" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="267" t="n">
+      <c r="C7" s="324" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="268" t="n">
+      <c r="D7" s="325" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="269" t="n">
+      <c r="E7" s="326" t="n">
         <v>29.5</v>
       </c>
-      <c r="F7" s="270">
+      <c r="F7" s="327">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="271">
+      <c r="G7" s="328">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="272">
+      <c r="H7" s="329">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="273" t="inlineStr">
+      <c r="I7" s="330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="276" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K7" s="277" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J7" s="331" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K7" s="332" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="278" t="inlineStr">
+      <c r="A8" s="337" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="279" t="inlineStr">
+      <c r="B8" s="338" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="280" t="n">
+      <c r="C8" s="339" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="281" t="n">
+      <c r="D8" s="340" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="282" t="n">
+      <c r="E8" s="341" t="n">
         <v>17.29999923706055</v>
       </c>
-      <c r="F8" s="283">
+      <c r="F8" s="342">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="284">
+      <c r="G8" s="343">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="285">
+      <c r="H8" s="344">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="286" t="inlineStr">
+      <c r="I8" s="345" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="287" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="K8" s="288" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J8" s="346" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K8" s="347" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="289" t="inlineStr">
+      <c r="B9" s="348" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="290">
+      <c r="F9" s="349">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="291">
+      <c r="G9" s="350">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="292">
+      <c r="H9" s="351">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2139,14 +2356,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  29 Apr 2026</t>
+      <c r="A1" s="320" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  30 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="293" t="inlineStr">
+      <c r="A3" s="352" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2184,329 +2401,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="263" t="inlineStr">
+      <c r="A1" s="320" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="264" t="inlineStr">
+      <c r="A2" s="321" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="264" t="inlineStr">
+      <c r="B2" s="321" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="264" t="inlineStr">
+      <c r="C2" s="321" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="264" t="inlineStr">
+      <c r="D2" s="321" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="264" t="inlineStr">
+      <c r="E2" s="321" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="264" t="inlineStr">
+      <c r="F2" s="321" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="264" t="inlineStr">
+      <c r="G2" s="321" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="264" t="inlineStr">
+      <c r="H2" s="321" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="264" t="inlineStr">
+      <c r="I2" s="321" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="264" t="inlineStr">
+      <c r="J2" s="321" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="294" t="inlineStr">
+      <c r="A3" s="353" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="295" t="inlineStr">
+      <c r="B3" s="354" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="296" t="inlineStr">
+      <c r="C3" s="355" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="297" t="inlineStr">
+      <c r="D3" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="298" t="n">
+      <c r="E3" s="357" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="299" t="n">
+      <c r="F3" s="358" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="298" t="n">
+      <c r="G3" s="357" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="300">
+      <c r="H3" s="359">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="301" t="inlineStr">
+      <c r="I3" s="360" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="302" t="inlineStr">
+      <c r="J3" s="361" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="303" t="inlineStr">
+      <c r="A4" s="362" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="304" t="inlineStr">
+      <c r="B4" s="363" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="279" t="inlineStr">
+      <c r="C4" s="338" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="297" t="inlineStr">
+      <c r="D4" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="280" t="n">
+      <c r="E4" s="339" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="281" t="n">
+      <c r="F4" s="340" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="280" t="n">
+      <c r="G4" s="339" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="283">
+      <c r="H4" s="342">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="305" t="inlineStr">
+      <c r="I4" s="364" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="306" t="inlineStr">
+      <c r="J4" s="365" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="294" t="inlineStr">
+      <c r="A5" s="353" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="295" t="inlineStr">
+      <c r="B5" s="354" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="296" t="inlineStr">
+      <c r="C5" s="355" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="297" t="inlineStr">
+      <c r="D5" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="298" t="n">
+      <c r="E5" s="357" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="299" t="n">
+      <c r="F5" s="358" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="298" t="n">
+      <c r="G5" s="357" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="300">
+      <c r="H5" s="359">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="301" t="inlineStr">
+      <c r="I5" s="360" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="302" t="inlineStr">
+      <c r="J5" s="361" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="303" t="inlineStr">
+      <c r="A6" s="362" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="304" t="inlineStr">
+      <c r="B6" s="363" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="279" t="inlineStr">
+      <c r="C6" s="338" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="297" t="inlineStr">
+      <c r="D6" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="280" t="n">
+      <c r="E6" s="339" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="281" t="n">
+      <c r="F6" s="340" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="280" t="n">
+      <c r="G6" s="339" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="283">
+      <c r="H6" s="342">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="305" t="inlineStr">
+      <c r="I6" s="364" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="306" t="inlineStr">
+      <c r="J6" s="365" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="294" t="inlineStr">
+      <c r="A7" s="353" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="295" t="inlineStr">
+      <c r="B7" s="354" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="296" t="inlineStr">
+      <c r="C7" s="355" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="297" t="inlineStr">
+      <c r="D7" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="298" t="n">
+      <c r="E7" s="357" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="299" t="n">
+      <c r="F7" s="358" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="298" t="n">
+      <c r="G7" s="357" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="300">
+      <c r="H7" s="359">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="301" t="inlineStr">
+      <c r="I7" s="360" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="302" t="inlineStr">
+      <c r="J7" s="361" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="303" t="inlineStr">
+      <c r="A8" s="362" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="304" t="inlineStr">
+      <c r="B8" s="363" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="279" t="inlineStr">
+      <c r="C8" s="338" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="297" t="inlineStr">
+      <c r="D8" s="356" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="280" t="n">
+      <c r="E8" s="339" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="281" t="n">
+      <c r="F8" s="340" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="280" t="n">
+      <c r="G8" s="339" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="283">
+      <c r="H8" s="342">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="305" t="inlineStr">
+      <c r="I8" s="364" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="306" t="inlineStr">
+      <c r="J8" s="365" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2518,11 +2735,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="307">
+      <c r="H10" s="366">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="307">
+      <c r="I10" s="366">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,6 +1235,216 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1740,47 +1950,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="251" t="inlineStr">
+      <c r="A2" s="308" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="252" t="n">
+      <c r="B2" s="309" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="253" t="n">
+      <c r="C2" s="310" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="254" t="n">
+      <c r="D2" s="311" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="255" t="n">
+      <c r="E2" s="312" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="256" t="n">
+      <c r="F2" s="313" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="257" t="n">
+      <c r="G2" s="314" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="258" t="n">
+      <c r="H2" s="315" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="259" t="n">
+      <c r="I2" s="316" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="260" t="n">
+      <c r="J2" s="317" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="261" t="n">
+      <c r="K2" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="262" t="n">
+      <c r="L2" s="319" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="251" t="inlineStr">
+      <c r="A3" s="308" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -1820,7 +2030,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="251" t="inlineStr">
+      <c r="A4" s="308" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -1860,82 +2070,82 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="251" t="inlineStr">
+      <c r="A5" s="308" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="252" t="n">
+      <c r="B5" s="309" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="253" t="n">
+      <c r="C5" s="310" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="254" t="n">
+      <c r="D5" s="311" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="255" t="n">
+      <c r="E5" s="312" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="256" t="n">
+      <c r="F5" s="313" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="257" t="n">
+      <c r="G5" s="314" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="258" t="n">
+      <c r="H5" s="315" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="259" t="n">
+      <c r="I5" s="316" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="260" t="n">
+      <c r="J5" s="317" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="261" t="n">
+      <c r="K5" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="262" t="n">
+      <c r="L5" s="319" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="308" t="inlineStr">
+      <c r="A6" s="367" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="309" t="n">
+      <c r="B6" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="310" t="n">
-        <v>304153.8160982132</v>
-      </c>
-      <c r="D6" s="311" t="n">
+      <c r="C6" s="369" t="n">
+        <v>302787.819642067</v>
+      </c>
+      <c r="D6" s="370" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="312" t="n">
-        <v>285729.9982070923</v>
-      </c>
-      <c r="F6" s="313" t="n">
-        <v>4153.816098213196</v>
-      </c>
-      <c r="G6" s="314" t="n">
-        <v>0.01384605366071065</v>
-      </c>
-      <c r="H6" s="315" t="n">
+      <c r="E6" s="371" t="n">
+        <v>284364.001750946</v>
+      </c>
+      <c r="F6" s="372" t="n">
+        <v>2787.819642066956</v>
+      </c>
+      <c r="G6" s="373" t="n">
+        <v>0.009292732140223185</v>
+      </c>
+      <c r="H6" s="374" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="316" t="n">
+      <c r="I6" s="375" t="n">
+        <v>-0.004491136996634464</v>
+      </c>
+      <c r="J6" s="376" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="377" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="317" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" s="318" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="319" t="n">
+      <c r="L6" s="378" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1968,360 +2178,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="379" t="inlineStr">
         <is>
           <t>Current Holdings  —  30 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+      <c r="A2" s="380" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="321" t="inlineStr">
+      <c r="B2" s="380" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="321" t="inlineStr">
+      <c r="C2" s="380" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="321" t="inlineStr">
+      <c r="D2" s="380" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="321" t="inlineStr">
+      <c r="E2" s="380" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="321" t="inlineStr">
+      <c r="F2" s="380" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="321" t="inlineStr">
+      <c r="G2" s="380" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="321" t="inlineStr">
+      <c r="H2" s="380" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="321" t="inlineStr">
+      <c r="I2" s="380" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="321" t="inlineStr">
+      <c r="J2" s="380" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="321" t="inlineStr">
+      <c r="K2" s="380" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="322" t="inlineStr">
+      <c r="A3" s="381" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="323" t="inlineStr">
+      <c r="B3" s="382" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="324" t="n">
+      <c r="C3" s="383" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="325" t="n">
+      <c r="D3" s="384" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="326" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F3" s="327">
+      <c r="E3" s="385" t="n">
+        <v>4.480000019073486</v>
+      </c>
+      <c r="F3" s="386">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="328">
+      <c r="G3" s="387">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="329">
+      <c r="H3" s="388">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="330" t="inlineStr">
+      <c r="I3" s="389" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="331" t="n">
+      <c r="J3" s="390" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="332" t="inlineStr">
+      <c r="K3" s="391" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="322" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="323" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C4" s="324" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D4" s="325" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E4" s="326" t="n">
-        <v>21</v>
-      </c>
-      <c r="F4" s="327">
+      <c r="A4" s="381" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="382" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C4" s="383" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D4" s="384" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E4" s="385" t="n">
+        <v>6.900000095367432</v>
+      </c>
+      <c r="F4" s="386">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="328">
+      <c r="G4" s="387">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="329">
+      <c r="H4" s="388">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="330" t="inlineStr">
+      <c r="I4" s="389" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="333" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K4" s="334" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J4" s="392" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="K4" s="393" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="322" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="323" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C5" s="324" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D5" s="325" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E5" s="326" t="n">
-        <v>6.800000190734863</v>
-      </c>
-      <c r="F5" s="327">
+      <c r="A5" s="381" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="382" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C5" s="383" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="384" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E5" s="385" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="386">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="328">
+      <c r="G5" s="387">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="329">
+      <c r="H5" s="388">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="330" t="inlineStr">
+      <c r="I5" s="389" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="335" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K5" s="336" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J5" s="394" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K5" s="395" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="322" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="323" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C6" s="324" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D6" s="325" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E6" s="326" t="n">
-        <v>16.89999961853027</v>
-      </c>
-      <c r="F6" s="327">
+      <c r="A6" s="381" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="382" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C6" s="383" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D6" s="384" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E6" s="385" t="n">
+        <v>20.60000038146973</v>
+      </c>
+      <c r="F6" s="386">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="328">
+      <c r="G6" s="387">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="329">
+      <c r="H6" s="388">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="330" t="inlineStr">
+      <c r="I6" s="389" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="333" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K6" s="334" t="inlineStr">
+      <c r="J6" s="394" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="K6" s="395" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="322" t="inlineStr">
+      <c r="A7" s="396" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="323" t="inlineStr">
+      <c r="B7" s="397" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="324" t="n">
+      <c r="C7" s="398" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="325" t="n">
+      <c r="D7" s="399" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="326" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="F7" s="327">
+      <c r="E7" s="400" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F7" s="401">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="328">
+      <c r="G7" s="402">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="329">
+      <c r="H7" s="403">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="330" t="inlineStr">
+      <c r="I7" s="404" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="331" t="n">
+      <c r="J7" s="405" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="332" t="inlineStr">
+      <c r="K7" s="406" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="337" t="inlineStr">
+      <c r="A8" s="407" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="338" t="inlineStr">
+      <c r="B8" s="408" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="339" t="n">
+      <c r="C8" s="409" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="340" t="n">
+      <c r="D8" s="410" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="341" t="n">
-        <v>17.29999923706055</v>
-      </c>
-      <c r="F8" s="342">
+      <c r="E8" s="411" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" s="412">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="343">
+      <c r="G8" s="413">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="344">
+      <c r="H8" s="414">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="345" t="inlineStr">
+      <c r="I8" s="415" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="346" t="n">
+      <c r="J8" s="416" t="n">
         <v>6.92</v>
       </c>
-      <c r="K8" s="347" t="inlineStr">
+      <c r="K8" s="417" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="348" t="inlineStr">
+      <c r="B9" s="418" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="349">
+      <c r="F9" s="419">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="350">
+      <c r="G9" s="420">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="351">
+      <c r="H9" s="421">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2356,14 +2566,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="379" t="inlineStr">
         <is>
           <t>Today's Trades  —  30 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="352" t="inlineStr">
+      <c r="A3" s="422" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2401,329 +2611,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="320" t="inlineStr">
+      <c r="A1" s="379" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="321" t="inlineStr">
+      <c r="A2" s="380" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="321" t="inlineStr">
+      <c r="B2" s="380" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="321" t="inlineStr">
+      <c r="C2" s="380" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="321" t="inlineStr">
+      <c r="D2" s="380" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="321" t="inlineStr">
+      <c r="E2" s="380" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="321" t="inlineStr">
+      <c r="F2" s="380" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="321" t="inlineStr">
+      <c r="G2" s="380" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="321" t="inlineStr">
+      <c r="H2" s="380" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="321" t="inlineStr">
+      <c r="I2" s="380" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="321" t="inlineStr">
+      <c r="J2" s="380" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="353" t="inlineStr">
+      <c r="A3" s="423" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="354" t="inlineStr">
+      <c r="B3" s="424" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="355" t="inlineStr">
+      <c r="C3" s="425" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="356" t="inlineStr">
+      <c r="D3" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="357" t="n">
+      <c r="E3" s="427" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="358" t="n">
+      <c r="F3" s="428" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="357" t="n">
+      <c r="G3" s="427" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="359">
+      <c r="H3" s="429">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="360" t="inlineStr">
+      <c r="I3" s="430" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="361" t="inlineStr">
+      <c r="J3" s="431" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="362" t="inlineStr">
+      <c r="A4" s="432" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="363" t="inlineStr">
+      <c r="B4" s="433" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="338" t="inlineStr">
+      <c r="C4" s="397" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="356" t="inlineStr">
+      <c r="D4" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="339" t="n">
+      <c r="E4" s="398" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="340" t="n">
+      <c r="F4" s="399" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="339" t="n">
+      <c r="G4" s="398" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="342">
+      <c r="H4" s="401">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="364" t="inlineStr">
+      <c r="I4" s="434" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="365" t="inlineStr">
+      <c r="J4" s="435" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="353" t="inlineStr">
+      <c r="A5" s="423" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="354" t="inlineStr">
+      <c r="B5" s="424" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="355" t="inlineStr">
+      <c r="C5" s="425" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="356" t="inlineStr">
+      <c r="D5" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="357" t="n">
+      <c r="E5" s="427" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="358" t="n">
+      <c r="F5" s="428" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="357" t="n">
+      <c r="G5" s="427" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="359">
+      <c r="H5" s="429">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="360" t="inlineStr">
+      <c r="I5" s="430" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="361" t="inlineStr">
+      <c r="J5" s="431" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="362" t="inlineStr">
+      <c r="A6" s="432" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="363" t="inlineStr">
+      <c r="B6" s="433" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="338" t="inlineStr">
+      <c r="C6" s="397" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="356" t="inlineStr">
+      <c r="D6" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="339" t="n">
+      <c r="E6" s="398" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="340" t="n">
+      <c r="F6" s="399" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="339" t="n">
+      <c r="G6" s="398" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="342">
+      <c r="H6" s="401">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="364" t="inlineStr">
+      <c r="I6" s="434" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="365" t="inlineStr">
+      <c r="J6" s="435" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="353" t="inlineStr">
+      <c r="A7" s="423" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="354" t="inlineStr">
+      <c r="B7" s="424" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="355" t="inlineStr">
+      <c r="C7" s="425" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="356" t="inlineStr">
+      <c r="D7" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="357" t="n">
+      <c r="E7" s="427" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="358" t="n">
+      <c r="F7" s="428" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="357" t="n">
+      <c r="G7" s="427" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="359">
+      <c r="H7" s="429">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="360" t="inlineStr">
+      <c r="I7" s="430" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="361" t="inlineStr">
+      <c r="J7" s="431" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="362" t="inlineStr">
+      <c r="A8" s="432" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="363" t="inlineStr">
+      <c r="B8" s="433" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="338" t="inlineStr">
+      <c r="C8" s="397" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="356" t="inlineStr">
+      <c r="D8" s="426" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="339" t="n">
+      <c r="E8" s="398" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="340" t="n">
+      <c r="F8" s="399" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="339" t="n">
+      <c r="G8" s="398" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="342">
+      <c r="H8" s="401">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="364" t="inlineStr">
+      <c r="I8" s="434" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="365" t="inlineStr">
+      <c r="J8" s="435" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2735,11 +2945,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="366">
+      <c r="H10" s="436">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="366">
+      <c r="I10" s="436">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="437">
+  <cellXfs count="507">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,6 +1235,216 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1870,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1950,47 +2160,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="308" t="inlineStr">
+      <c r="A2" s="367" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="309" t="n">
+      <c r="B2" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="310" t="n">
+      <c r="C2" s="369" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="311" t="n">
+      <c r="D2" s="370" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="312" t="n">
+      <c r="E2" s="371" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="313" t="n">
+      <c r="F2" s="372" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="314" t="n">
+      <c r="G2" s="373" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="315" t="n">
+      <c r="H2" s="374" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="316" t="n">
+      <c r="I2" s="375" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="317" t="n">
+      <c r="J2" s="376" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="318" t="n">
+      <c r="K2" s="377" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="319" t="n">
+      <c r="L2" s="378" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="308" t="inlineStr">
+      <c r="A3" s="367" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -2030,7 +2240,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="308" t="inlineStr">
+      <c r="A4" s="367" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -2070,42 +2280,42 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="308" t="inlineStr">
+      <c r="A5" s="367" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="309" t="n">
+      <c r="B5" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="310" t="n">
+      <c r="C5" s="369" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="311" t="n">
+      <c r="D5" s="370" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="312" t="n">
+      <c r="E5" s="371" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="313" t="n">
+      <c r="F5" s="372" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="314" t="n">
+      <c r="G5" s="373" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="315" t="n">
+      <c r="H5" s="374" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="316" t="n">
+      <c r="I5" s="375" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="317" t="n">
+      <c r="J5" s="376" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="318" t="n">
+      <c r="K5" s="377" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="319" t="n">
+      <c r="L5" s="378" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2146,6 +2356,46 @@
         <v>0</v>
       </c>
       <c r="L6" s="378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="437" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B7" s="438" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="439" t="n">
+        <v>302787.819642067</v>
+      </c>
+      <c r="D7" s="440" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E7" s="441" t="n">
+        <v>284364.001750946</v>
+      </c>
+      <c r="F7" s="442" t="n">
+        <v>2787.819642066956</v>
+      </c>
+      <c r="G7" s="443" t="n">
+        <v>0.009292732140223185</v>
+      </c>
+      <c r="H7" s="444" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="445" t="n">
+        <v>-0.004491136996634464</v>
+      </c>
+      <c r="J7" s="446" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="448" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2178,360 +2428,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="379" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  30 Apr 2026</t>
+      <c r="A1" s="449" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  01 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="380" t="inlineStr">
+      <c r="A2" s="450" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="380" t="inlineStr">
+      <c r="B2" s="450" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="380" t="inlineStr">
+      <c r="C2" s="450" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="380" t="inlineStr">
+      <c r="D2" s="450" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="380" t="inlineStr">
+      <c r="E2" s="450" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="380" t="inlineStr">
+      <c r="F2" s="450" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="380" t="inlineStr">
+      <c r="G2" s="450" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="380" t="inlineStr">
+      <c r="H2" s="450" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="380" t="inlineStr">
+      <c r="I2" s="450" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="380" t="inlineStr">
+      <c r="J2" s="450" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="380" t="inlineStr">
+      <c r="K2" s="450" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="381" t="inlineStr">
+      <c r="A3" s="451" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="382" t="inlineStr">
+      <c r="B3" s="452" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="383" t="n">
+      <c r="C3" s="453" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="384" t="n">
+      <c r="D3" s="454" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="385" t="n">
+      <c r="E3" s="455" t="n">
         <v>4.480000019073486</v>
       </c>
-      <c r="F3" s="386">
+      <c r="F3" s="456">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="387">
+      <c r="G3" s="457">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="388">
+      <c r="H3" s="458">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="389" t="inlineStr">
+      <c r="I3" s="459" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="390" t="n">
+      <c r="J3" s="460" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="391" t="inlineStr">
+      <c r="K3" s="461" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="381" t="inlineStr">
+      <c r="A4" s="451" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="382" t="inlineStr">
+      <c r="B4" s="452" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="383" t="n">
+      <c r="C4" s="453" t="n">
         <v>7000</v>
       </c>
-      <c r="D4" s="384" t="n">
+      <c r="D4" s="454" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="385" t="n">
+      <c r="E4" s="455" t="n">
         <v>6.900000095367432</v>
       </c>
-      <c r="F4" s="386">
+      <c r="F4" s="456">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="387">
+      <c r="G4" s="457">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="388">
+      <c r="H4" s="458">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="389" t="inlineStr">
+      <c r="I4" s="459" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="392" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="K4" s="393" t="inlineStr">
+      <c r="J4" s="462" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K4" s="463" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="381" t="inlineStr">
+      <c r="A5" s="451" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="382" t="inlineStr">
+      <c r="B5" s="452" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="383" t="n">
+      <c r="C5" s="453" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="384" t="n">
+      <c r="D5" s="454" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="385" t="n">
+      <c r="E5" s="455" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="386">
+      <c r="F5" s="456">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="387">
+      <c r="G5" s="457">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="388">
+      <c r="H5" s="458">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="389" t="inlineStr">
+      <c r="I5" s="459" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="394" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K5" s="395" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J5" s="460" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K5" s="461" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="381" t="inlineStr">
+      <c r="A6" s="451" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B6" s="382" t="inlineStr">
+      <c r="B6" s="452" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C6" s="383" t="n">
+      <c r="C6" s="453" t="n">
         <v>2300</v>
       </c>
-      <c r="D6" s="384" t="n">
+      <c r="D6" s="454" t="n">
         <v>20.3</v>
       </c>
-      <c r="E6" s="385" t="n">
+      <c r="E6" s="455" t="n">
         <v>20.60000038146973</v>
       </c>
-      <c r="F6" s="386">
+      <c r="F6" s="456">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="387">
+      <c r="G6" s="457">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="388">
+      <c r="H6" s="458">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="389" t="inlineStr">
+      <c r="I6" s="459" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="394" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K6" s="395" t="inlineStr">
+      <c r="J6" s="464" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K6" s="465" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="396" t="inlineStr">
+      <c r="A7" s="466" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="397" t="inlineStr">
+      <c r="B7" s="467" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="398" t="n">
+      <c r="C7" s="468" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="399" t="n">
+      <c r="D7" s="469" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="400" t="n">
+      <c r="E7" s="470" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="401">
+      <c r="F7" s="471">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="402">
+      <c r="G7" s="472">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="403">
+      <c r="H7" s="473">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="404" t="inlineStr">
+      <c r="I7" s="474" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="405" t="n">
+      <c r="J7" s="475" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="406" t="inlineStr">
+      <c r="K7" s="476" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="407" t="inlineStr">
+      <c r="A8" s="477" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="408" t="inlineStr">
+      <c r="B8" s="478" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="409" t="n">
+      <c r="C8" s="479" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="410" t="n">
+      <c r="D8" s="480" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="411" t="n">
+      <c r="E8" s="481" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="412">
+      <c r="F8" s="482">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="413">
+      <c r="G8" s="483">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="414">
+      <c r="H8" s="484">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="415" t="inlineStr">
+      <c r="I8" s="485" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="416" t="n">
+      <c r="J8" s="486" t="n">
         <v>6.92</v>
       </c>
-      <c r="K8" s="417" t="inlineStr">
+      <c r="K8" s="487" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="418" t="inlineStr">
+      <c r="B9" s="488" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="419">
+      <c r="F9" s="489">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="420">
+      <c r="G9" s="490">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="421">
+      <c r="H9" s="491">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2566,14 +2816,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="379" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  30 Apr 2026</t>
+      <c r="A1" s="449" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  01 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="422" t="inlineStr">
+      <c r="A3" s="492" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2611,329 +2861,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="379" t="inlineStr">
+      <c r="A1" s="449" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="380" t="inlineStr">
+      <c r="A2" s="450" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="380" t="inlineStr">
+      <c r="B2" s="450" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="380" t="inlineStr">
+      <c r="C2" s="450" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="380" t="inlineStr">
+      <c r="D2" s="450" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="380" t="inlineStr">
+      <c r="E2" s="450" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="380" t="inlineStr">
+      <c r="F2" s="450" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="380" t="inlineStr">
+      <c r="G2" s="450" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="380" t="inlineStr">
+      <c r="H2" s="450" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="380" t="inlineStr">
+      <c r="I2" s="450" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="380" t="inlineStr">
+      <c r="J2" s="450" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="423" t="inlineStr">
+      <c r="A3" s="493" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="424" t="inlineStr">
+      <c r="B3" s="494" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="425" t="inlineStr">
+      <c r="C3" s="495" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="426" t="inlineStr">
+      <c r="D3" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="427" t="n">
+      <c r="E3" s="497" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="428" t="n">
+      <c r="F3" s="498" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="427" t="n">
+      <c r="G3" s="497" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="429">
+      <c r="H3" s="499">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="430" t="inlineStr">
+      <c r="I3" s="500" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="431" t="inlineStr">
+      <c r="J3" s="501" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="432" t="inlineStr">
+      <c r="A4" s="502" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="433" t="inlineStr">
+      <c r="B4" s="503" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="397" t="inlineStr">
+      <c r="C4" s="467" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="426" t="inlineStr">
+      <c r="D4" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="398" t="n">
+      <c r="E4" s="468" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="399" t="n">
+      <c r="F4" s="469" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="398" t="n">
+      <c r="G4" s="468" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="401">
+      <c r="H4" s="471">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="434" t="inlineStr">
+      <c r="I4" s="504" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="435" t="inlineStr">
+      <c r="J4" s="505" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="423" t="inlineStr">
+      <c r="A5" s="493" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="424" t="inlineStr">
+      <c r="B5" s="494" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="425" t="inlineStr">
+      <c r="C5" s="495" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="426" t="inlineStr">
+      <c r="D5" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="427" t="n">
+      <c r="E5" s="497" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="428" t="n">
+      <c r="F5" s="498" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="427" t="n">
+      <c r="G5" s="497" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="429">
+      <c r="H5" s="499">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="430" t="inlineStr">
+      <c r="I5" s="500" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="431" t="inlineStr">
+      <c r="J5" s="501" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="432" t="inlineStr">
+      <c r="A6" s="502" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="433" t="inlineStr">
+      <c r="B6" s="503" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="397" t="inlineStr">
+      <c r="C6" s="467" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="426" t="inlineStr">
+      <c r="D6" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="398" t="n">
+      <c r="E6" s="468" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="399" t="n">
+      <c r="F6" s="469" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="398" t="n">
+      <c r="G6" s="468" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="401">
+      <c r="H6" s="471">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="434" t="inlineStr">
+      <c r="I6" s="504" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="435" t="inlineStr">
+      <c r="J6" s="505" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="423" t="inlineStr">
+      <c r="A7" s="493" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="424" t="inlineStr">
+      <c r="B7" s="494" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="425" t="inlineStr">
+      <c r="C7" s="495" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="426" t="inlineStr">
+      <c r="D7" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="427" t="n">
+      <c r="E7" s="497" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="428" t="n">
+      <c r="F7" s="498" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="427" t="n">
+      <c r="G7" s="497" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="429">
+      <c r="H7" s="499">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="430" t="inlineStr">
+      <c r="I7" s="500" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="431" t="inlineStr">
+      <c r="J7" s="501" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="432" t="inlineStr">
+      <c r="A8" s="502" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="433" t="inlineStr">
+      <c r="B8" s="503" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="397" t="inlineStr">
+      <c r="C8" s="467" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="426" t="inlineStr">
+      <c r="D8" s="496" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="398" t="n">
+      <c r="E8" s="468" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="399" t="n">
+      <c r="F8" s="469" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="398" t="n">
+      <c r="G8" s="468" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="401">
+      <c r="H8" s="471">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="434" t="inlineStr">
+      <c r="I8" s="504" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="435" t="inlineStr">
+      <c r="J8" s="505" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -2945,11 +3195,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="436">
+      <c r="H10" s="506">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="436">
+      <c r="I10" s="506">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="507">
+  <cellXfs count="577">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1235,6 +1235,216 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2080,7 +2290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2160,47 +2370,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="367" t="inlineStr">
+      <c r="A2" s="437" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="368" t="n">
+      <c r="B2" s="438" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="369" t="n">
+      <c r="C2" s="439" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="370" t="n">
+      <c r="D2" s="440" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="371" t="n">
+      <c r="E2" s="441" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="372" t="n">
+      <c r="F2" s="442" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="373" t="n">
+      <c r="G2" s="443" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="374" t="n">
+      <c r="H2" s="444" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="375" t="n">
+      <c r="I2" s="445" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="376" t="n">
+      <c r="J2" s="446" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="377" t="n">
+      <c r="K2" s="447" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="378" t="n">
+      <c r="L2" s="448" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="367" t="inlineStr">
+      <c r="A3" s="437" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -2240,7 +2450,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="367" t="inlineStr">
+      <c r="A4" s="437" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -2280,82 +2490,82 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="367" t="inlineStr">
+      <c r="A5" s="437" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="368" t="n">
+      <c r="B5" s="438" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="369" t="n">
+      <c r="C5" s="439" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="370" t="n">
+      <c r="D5" s="440" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="371" t="n">
+      <c r="E5" s="441" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="372" t="n">
+      <c r="F5" s="442" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="373" t="n">
+      <c r="G5" s="443" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="374" t="n">
+      <c r="H5" s="444" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="375" t="n">
+      <c r="I5" s="445" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="376" t="n">
+      <c r="J5" s="446" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="377" t="n">
+      <c r="K5" s="447" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="378" t="n">
+      <c r="L5" s="448" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="367" t="inlineStr">
+      <c r="A6" s="437" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="368" t="n">
+      <c r="B6" s="438" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="369" t="n">
+      <c r="C6" s="439" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="370" t="n">
+      <c r="D6" s="440" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="371" t="n">
+      <c r="E6" s="441" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="372" t="n">
+      <c r="F6" s="442" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="373" t="n">
+      <c r="G6" s="443" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="374" t="n">
+      <c r="H6" s="444" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="375" t="n">
+      <c r="I6" s="445" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="376" t="n">
+      <c r="J6" s="446" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="377" t="n">
+      <c r="K6" s="447" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="378" t="n">
+      <c r="L6" s="448" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2396,6 +2606,46 @@
         <v>0</v>
       </c>
       <c r="L7" s="448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="507" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B8" s="508" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="509" t="n">
+        <v>302787.819642067</v>
+      </c>
+      <c r="D8" s="510" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E8" s="511" t="n">
+        <v>284364.001750946</v>
+      </c>
+      <c r="F8" s="512" t="n">
+        <v>2787.819642066956</v>
+      </c>
+      <c r="G8" s="513" t="n">
+        <v>0.009292732140223185</v>
+      </c>
+      <c r="H8" s="514" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="515" t="n">
+        <v>-0.004491136996634464</v>
+      </c>
+      <c r="J8" s="516" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="518" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2428,360 +2678,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="449" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  01 May 2026</t>
+      <c r="A1" s="519" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  04 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="450" t="inlineStr">
+      <c r="A2" s="520" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="450" t="inlineStr">
+      <c r="B2" s="520" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="450" t="inlineStr">
+      <c r="C2" s="520" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="450" t="inlineStr">
+      <c r="D2" s="520" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="450" t="inlineStr">
+      <c r="E2" s="520" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="450" t="inlineStr">
+      <c r="F2" s="520" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="450" t="inlineStr">
+      <c r="G2" s="520" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="450" t="inlineStr">
+      <c r="H2" s="520" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="450" t="inlineStr">
+      <c r="I2" s="520" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="450" t="inlineStr">
+      <c r="J2" s="520" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="450" t="inlineStr">
+      <c r="K2" s="520" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="451" t="inlineStr">
+      <c r="A3" s="521" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="452" t="inlineStr">
+      <c r="B3" s="522" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="453" t="n">
+      <c r="C3" s="523" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="454" t="n">
+      <c r="D3" s="524" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="455" t="n">
+      <c r="E3" s="525" t="n">
         <v>4.480000019073486</v>
       </c>
-      <c r="F3" s="456">
+      <c r="F3" s="526">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="457">
+      <c r="G3" s="527">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="458">
+      <c r="H3" s="528">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="459" t="inlineStr">
+      <c r="I3" s="529" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="460" t="n">
+      <c r="J3" s="530" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="461" t="inlineStr">
+      <c r="K3" s="531" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="451" t="inlineStr">
+      <c r="A4" s="521" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="452" t="inlineStr">
+      <c r="B4" s="522" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="453" t="n">
+      <c r="C4" s="523" t="n">
         <v>7000</v>
       </c>
-      <c r="D4" s="454" t="n">
+      <c r="D4" s="524" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="455" t="n">
+      <c r="E4" s="525" t="n">
         <v>6.900000095367432</v>
       </c>
-      <c r="F4" s="456">
+      <c r="F4" s="526">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="457">
+      <c r="G4" s="527">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="458">
+      <c r="H4" s="528">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="459" t="inlineStr">
+      <c r="I4" s="529" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="462" t="n">
+      <c r="J4" s="532" t="n">
         <v>5.48</v>
       </c>
-      <c r="K4" s="463" t="inlineStr">
+      <c r="K4" s="533" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="451" t="inlineStr">
+      <c r="A5" s="521" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="452" t="inlineStr">
+      <c r="B5" s="522" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="453" t="n">
+      <c r="C5" s="523" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="454" t="n">
+      <c r="D5" s="524" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="455" t="n">
+      <c r="E5" s="525" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="456">
+      <c r="F5" s="526">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="457">
+      <c r="G5" s="527">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="458">
+      <c r="H5" s="528">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="459" t="inlineStr">
+      <c r="I5" s="529" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="460" t="n">
+      <c r="J5" s="530" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="461" t="inlineStr">
+      <c r="K5" s="531" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="451" t="inlineStr">
+      <c r="A6" s="521" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B6" s="452" t="inlineStr">
+      <c r="B6" s="522" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C6" s="453" t="n">
+      <c r="C6" s="523" t="n">
         <v>2300</v>
       </c>
-      <c r="D6" s="454" t="n">
+      <c r="D6" s="524" t="n">
         <v>20.3</v>
       </c>
-      <c r="E6" s="455" t="n">
+      <c r="E6" s="525" t="n">
         <v>20.60000038146973</v>
       </c>
-      <c r="F6" s="456">
+      <c r="F6" s="526">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="457">
+      <c r="G6" s="527">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="458">
+      <c r="H6" s="528">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="459" t="inlineStr">
+      <c r="I6" s="529" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="464" t="n">
+      <c r="J6" s="534" t="n">
         <v>7.52</v>
       </c>
-      <c r="K6" s="465" t="inlineStr">
+      <c r="K6" s="535" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="466" t="inlineStr">
+      <c r="A7" s="536" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="467" t="inlineStr">
+      <c r="B7" s="537" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="468" t="n">
+      <c r="C7" s="538" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="469" t="n">
+      <c r="D7" s="539" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="470" t="n">
+      <c r="E7" s="540" t="n">
         <v>29.25</v>
       </c>
-      <c r="F7" s="471">
+      <c r="F7" s="541">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="472">
+      <c r="G7" s="542">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="473">
+      <c r="H7" s="543">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="474" t="inlineStr">
+      <c r="I7" s="544" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="475" t="n">
+      <c r="J7" s="545" t="n">
         <v>6.52</v>
       </c>
-      <c r="K7" s="476" t="inlineStr">
+      <c r="K7" s="546" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="477" t="inlineStr">
+      <c r="A8" s="547" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="478" t="inlineStr">
+      <c r="B8" s="548" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="479" t="n">
+      <c r="C8" s="549" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="480" t="n">
+      <c r="D8" s="550" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="481" t="n">
+      <c r="E8" s="551" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="482">
+      <c r="F8" s="552">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="483">
+      <c r="G8" s="553">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="484">
+      <c r="H8" s="554">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="485" t="inlineStr">
+      <c r="I8" s="555" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="486" t="n">
+      <c r="J8" s="556" t="n">
         <v>6.92</v>
       </c>
-      <c r="K8" s="487" t="inlineStr">
+      <c r="K8" s="557" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="488" t="inlineStr">
+      <c r="B9" s="558" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="489">
+      <c r="F9" s="559">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="490">
+      <c r="G9" s="560">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="491">
+      <c r="H9" s="561">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -2816,14 +3066,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="449" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  01 May 2026</t>
+      <c r="A1" s="519" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  04 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="492" t="inlineStr">
+      <c r="A3" s="562" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -2861,329 +3111,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="449" t="inlineStr">
+      <c r="A1" s="519" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="450" t="inlineStr">
+      <c r="A2" s="520" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="450" t="inlineStr">
+      <c r="B2" s="520" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="450" t="inlineStr">
+      <c r="C2" s="520" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="450" t="inlineStr">
+      <c r="D2" s="520" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="450" t="inlineStr">
+      <c r="E2" s="520" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="450" t="inlineStr">
+      <c r="F2" s="520" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="450" t="inlineStr">
+      <c r="G2" s="520" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="450" t="inlineStr">
+      <c r="H2" s="520" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="450" t="inlineStr">
+      <c r="I2" s="520" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="450" t="inlineStr">
+      <c r="J2" s="520" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="493" t="inlineStr">
+      <c r="A3" s="563" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="494" t="inlineStr">
+      <c r="B3" s="564" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="495" t="inlineStr">
+      <c r="C3" s="565" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="496" t="inlineStr">
+      <c r="D3" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="497" t="n">
+      <c r="E3" s="567" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="498" t="n">
+      <c r="F3" s="568" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="497" t="n">
+      <c r="G3" s="567" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="499">
+      <c r="H3" s="569">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="500" t="inlineStr">
+      <c r="I3" s="570" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="501" t="inlineStr">
+      <c r="J3" s="571" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="502" t="inlineStr">
+      <c r="A4" s="572" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="503" t="inlineStr">
+      <c r="B4" s="573" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="467" t="inlineStr">
+      <c r="C4" s="537" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="496" t="inlineStr">
+      <c r="D4" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="468" t="n">
+      <c r="E4" s="538" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="469" t="n">
+      <c r="F4" s="539" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="468" t="n">
+      <c r="G4" s="538" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="471">
+      <c r="H4" s="541">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="504" t="inlineStr">
+      <c r="I4" s="574" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="505" t="inlineStr">
+      <c r="J4" s="575" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="493" t="inlineStr">
+      <c r="A5" s="563" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="494" t="inlineStr">
+      <c r="B5" s="564" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="495" t="inlineStr">
+      <c r="C5" s="565" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="496" t="inlineStr">
+      <c r="D5" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="497" t="n">
+      <c r="E5" s="567" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="498" t="n">
+      <c r="F5" s="568" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="497" t="n">
+      <c r="G5" s="567" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="499">
+      <c r="H5" s="569">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="500" t="inlineStr">
+      <c r="I5" s="570" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="501" t="inlineStr">
+      <c r="J5" s="571" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="502" t="inlineStr">
+      <c r="A6" s="572" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="503" t="inlineStr">
+      <c r="B6" s="573" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="467" t="inlineStr">
+      <c r="C6" s="537" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="496" t="inlineStr">
+      <c r="D6" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="468" t="n">
+      <c r="E6" s="538" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="469" t="n">
+      <c r="F6" s="539" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="468" t="n">
+      <c r="G6" s="538" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="471">
+      <c r="H6" s="541">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="504" t="inlineStr">
+      <c r="I6" s="574" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="505" t="inlineStr">
+      <c r="J6" s="575" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="493" t="inlineStr">
+      <c r="A7" s="563" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="494" t="inlineStr">
+      <c r="B7" s="564" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="495" t="inlineStr">
+      <c r="C7" s="565" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="496" t="inlineStr">
+      <c r="D7" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="497" t="n">
+      <c r="E7" s="567" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="498" t="n">
+      <c r="F7" s="568" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="497" t="n">
+      <c r="G7" s="567" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="499">
+      <c r="H7" s="569">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="500" t="inlineStr">
+      <c r="I7" s="570" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="501" t="inlineStr">
+      <c r="J7" s="571" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="502" t="inlineStr">
+      <c r="A8" s="572" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="503" t="inlineStr">
+      <c r="B8" s="573" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="467" t="inlineStr">
+      <c r="C8" s="537" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="496" t="inlineStr">
+      <c r="D8" s="566" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="468" t="n">
+      <c r="E8" s="538" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="469" t="n">
+      <c r="F8" s="539" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="468" t="n">
+      <c r="G8" s="538" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="471">
+      <c r="H8" s="541">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="504" t="inlineStr">
+      <c r="I8" s="574" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="505" t="inlineStr">
+      <c r="J8" s="575" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3195,11 +3445,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="506">
+      <c r="H10" s="576">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="506">
+      <c r="I10" s="576">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="577">
+  <cellXfs count="647">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1865,6 +1865,216 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2290,7 +2500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2370,47 +2580,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="437" t="inlineStr">
+      <c r="A2" s="507" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="438" t="n">
+      <c r="B2" s="508" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="439" t="n">
+      <c r="C2" s="509" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="440" t="n">
+      <c r="D2" s="510" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="441" t="n">
+      <c r="E2" s="511" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="442" t="n">
+      <c r="F2" s="512" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="443" t="n">
+      <c r="G2" s="513" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="444" t="n">
+      <c r="H2" s="514" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="445" t="n">
+      <c r="I2" s="515" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="446" t="n">
+      <c r="J2" s="516" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="447" t="n">
+      <c r="K2" s="517" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="448" t="n">
+      <c r="L2" s="518" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="437" t="inlineStr">
+      <c r="A3" s="507" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -2450,7 +2660,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="437" t="inlineStr">
+      <c r="A4" s="507" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -2490,122 +2700,122 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="437" t="inlineStr">
+      <c r="A5" s="507" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="438" t="n">
+      <c r="B5" s="508" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="439" t="n">
+      <c r="C5" s="509" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="440" t="n">
+      <c r="D5" s="510" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="441" t="n">
+      <c r="E5" s="511" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="442" t="n">
+      <c r="F5" s="512" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="443" t="n">
+      <c r="G5" s="513" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="444" t="n">
+      <c r="H5" s="514" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="445" t="n">
+      <c r="I5" s="515" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="446" t="n">
+      <c r="J5" s="516" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="447" t="n">
+      <c r="K5" s="517" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="448" t="n">
+      <c r="L5" s="518" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="437" t="inlineStr">
+      <c r="A6" s="507" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="438" t="n">
+      <c r="B6" s="508" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="439" t="n">
+      <c r="C6" s="509" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="440" t="n">
+      <c r="D6" s="510" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="441" t="n">
+      <c r="E6" s="511" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="442" t="n">
+      <c r="F6" s="512" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="443" t="n">
+      <c r="G6" s="513" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="444" t="n">
+      <c r="H6" s="514" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="445" t="n">
+      <c r="I6" s="515" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="446" t="n">
+      <c r="J6" s="516" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="447" t="n">
+      <c r="K6" s="517" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="448" t="n">
+      <c r="L6" s="518" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="437" t="inlineStr">
+      <c r="A7" s="507" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="438" t="n">
+      <c r="B7" s="508" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="439" t="n">
+      <c r="C7" s="509" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="440" t="n">
+      <c r="D7" s="510" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="441" t="n">
+      <c r="E7" s="511" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="442" t="n">
+      <c r="F7" s="512" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="443" t="n">
+      <c r="G7" s="513" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="444" t="n">
+      <c r="H7" s="514" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="445" t="n">
+      <c r="I7" s="515" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="446" t="n">
+      <c r="J7" s="516" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="447" t="n">
+      <c r="K7" s="517" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="448" t="n">
+      <c r="L7" s="518" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2646,6 +2856,46 @@
         <v>0</v>
       </c>
       <c r="L8" s="518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="577" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B9" s="578" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="579" t="n">
+        <v>301062.819642067</v>
+      </c>
+      <c r="D9" s="580" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E9" s="581" t="n">
+        <v>282639.001750946</v>
+      </c>
+      <c r="F9" s="582" t="n">
+        <v>1062.819642066956</v>
+      </c>
+      <c r="G9" s="583" t="n">
+        <v>0.003542732140223185</v>
+      </c>
+      <c r="H9" s="584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="585" t="n">
+        <v>-0.01016260948423589</v>
+      </c>
+      <c r="J9" s="586" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" s="587" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="588" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2678,360 +2928,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="519" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  04 May 2026</t>
+      <c r="A1" s="589" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  05 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="520" t="inlineStr">
+      <c r="A2" s="590" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="520" t="inlineStr">
+      <c r="B2" s="590" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="520" t="inlineStr">
+      <c r="C2" s="590" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="520" t="inlineStr">
+      <c r="D2" s="590" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="520" t="inlineStr">
+      <c r="E2" s="590" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="520" t="inlineStr">
+      <c r="F2" s="590" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="520" t="inlineStr">
+      <c r="G2" s="590" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="520" t="inlineStr">
+      <c r="H2" s="590" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="520" t="inlineStr">
+      <c r="I2" s="590" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="520" t="inlineStr">
+      <c r="J2" s="590" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="520" t="inlineStr">
+      <c r="K2" s="590" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="521" t="inlineStr">
+      <c r="A3" s="591" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="522" t="inlineStr">
+      <c r="B3" s="592" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="523" t="n">
+      <c r="C3" s="593" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="524" t="n">
+      <c r="D3" s="594" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="525" t="n">
+      <c r="E3" s="595" t="n">
         <v>4.480000019073486</v>
       </c>
-      <c r="F3" s="526">
+      <c r="F3" s="596">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="527">
+      <c r="G3" s="597">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="528">
+      <c r="H3" s="598">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="529" t="inlineStr">
+      <c r="I3" s="599" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="530" t="n">
+      <c r="J3" s="600" t="n">
         <v>6.92</v>
       </c>
-      <c r="K3" s="531" t="inlineStr">
+      <c r="K3" s="601" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="521" t="inlineStr">
+      <c r="A4" s="591" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="522" t="inlineStr">
+      <c r="B4" s="592" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="523" t="n">
+      <c r="C4" s="593" t="n">
         <v>7000</v>
       </c>
-      <c r="D4" s="524" t="n">
+      <c r="D4" s="594" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="525" t="n">
+      <c r="E4" s="595" t="n">
         <v>6.900000095367432</v>
       </c>
-      <c r="F4" s="526">
+      <c r="F4" s="596">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="527">
+      <c r="G4" s="597">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="528">
+      <c r="H4" s="598">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="529" t="inlineStr">
+      <c r="I4" s="599" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="532" t="n">
+      <c r="J4" s="602" t="n">
         <v>5.48</v>
       </c>
-      <c r="K4" s="533" t="inlineStr">
+      <c r="K4" s="603" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="521" t="inlineStr">
+      <c r="A5" s="591" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="522" t="inlineStr">
+      <c r="B5" s="592" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="523" t="n">
+      <c r="C5" s="593" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="524" t="n">
+      <c r="D5" s="594" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="525" t="n">
+      <c r="E5" s="595" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="526">
+      <c r="F5" s="596">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="527">
+      <c r="G5" s="597">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="528">
+      <c r="H5" s="598">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="529" t="inlineStr">
+      <c r="I5" s="599" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="530" t="n">
+      <c r="J5" s="600" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="531" t="inlineStr">
+      <c r="K5" s="601" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="521" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="522" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C6" s="523" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D6" s="524" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E6" s="525" t="n">
-        <v>20.60000038146973</v>
-      </c>
-      <c r="F6" s="526">
+      <c r="A6" s="604" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="605" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C6" s="606" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D6" s="607" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E6" s="608" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F6" s="609">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="527">
+      <c r="G6" s="610">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="528">
+      <c r="H6" s="611">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="529" t="inlineStr">
+      <c r="I6" s="612" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="534" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K6" s="535" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J6" s="613" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K6" s="614" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="536" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="537" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C7" s="538" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D7" s="539" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E7" s="540" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F7" s="541">
+      <c r="A7" s="615" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="616" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C7" s="617" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D7" s="618" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E7" s="619" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="620">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="542">
+      <c r="G7" s="621">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="543">
+      <c r="H7" s="622">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="544" t="inlineStr">
+      <c r="I7" s="623" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="545" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K7" s="546" t="inlineStr">
+      <c r="J7" s="624" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K7" s="625" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="547" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="548" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C8" s="549" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D8" s="550" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E8" s="551" t="n">
-        <v>17</v>
-      </c>
-      <c r="F8" s="552">
+      <c r="A8" s="615" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="616" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C8" s="617" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D8" s="618" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E8" s="619" t="n">
+        <v>19.85000038146973</v>
+      </c>
+      <c r="F8" s="620">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="553">
+      <c r="G8" s="621">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="554">
+      <c r="H8" s="622">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="555" t="inlineStr">
+      <c r="I8" s="623" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="556" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K8" s="557" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J8" s="626" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K8" s="627" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="558" t="inlineStr">
+      <c r="B9" s="628" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="559">
+      <c r="F9" s="629">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="560">
+      <c r="G9" s="630">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="561">
+      <c r="H9" s="631">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -3066,14 +3316,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="519" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  04 May 2026</t>
+      <c r="A1" s="589" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  05 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="562" t="inlineStr">
+      <c r="A3" s="632" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -3111,329 +3361,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="519" t="inlineStr">
+      <c r="A1" s="589" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="520" t="inlineStr">
+      <c r="A2" s="590" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="520" t="inlineStr">
+      <c r="B2" s="590" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="520" t="inlineStr">
+      <c r="C2" s="590" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="520" t="inlineStr">
+      <c r="D2" s="590" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="520" t="inlineStr">
+      <c r="E2" s="590" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="520" t="inlineStr">
+      <c r="F2" s="590" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="520" t="inlineStr">
+      <c r="G2" s="590" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="520" t="inlineStr">
+      <c r="H2" s="590" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="520" t="inlineStr">
+      <c r="I2" s="590" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="520" t="inlineStr">
+      <c r="J2" s="590" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="563" t="inlineStr">
+      <c r="A3" s="633" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="564" t="inlineStr">
+      <c r="B3" s="634" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="565" t="inlineStr">
+      <c r="C3" s="635" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="566" t="inlineStr">
+      <c r="D3" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="567" t="n">
+      <c r="E3" s="637" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="568" t="n">
+      <c r="F3" s="638" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="567" t="n">
+      <c r="G3" s="637" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="569">
+      <c r="H3" s="639">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="570" t="inlineStr">
+      <c r="I3" s="640" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="571" t="inlineStr">
+      <c r="J3" s="641" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="572" t="inlineStr">
+      <c r="A4" s="642" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="573" t="inlineStr">
+      <c r="B4" s="643" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="537" t="inlineStr">
+      <c r="C4" s="605" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="566" t="inlineStr">
+      <c r="D4" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="538" t="n">
+      <c r="E4" s="606" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="539" t="n">
+      <c r="F4" s="607" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="538" t="n">
+      <c r="G4" s="606" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="541">
+      <c r="H4" s="609">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="574" t="inlineStr">
+      <c r="I4" s="644" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="575" t="inlineStr">
+      <c r="J4" s="645" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="563" t="inlineStr">
+      <c r="A5" s="633" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="564" t="inlineStr">
+      <c r="B5" s="634" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="565" t="inlineStr">
+      <c r="C5" s="635" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="566" t="inlineStr">
+      <c r="D5" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="567" t="n">
+      <c r="E5" s="637" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="568" t="n">
+      <c r="F5" s="638" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="567" t="n">
+      <c r="G5" s="637" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="569">
+      <c r="H5" s="639">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="570" t="inlineStr">
+      <c r="I5" s="640" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="571" t="inlineStr">
+      <c r="J5" s="641" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="572" t="inlineStr">
+      <c r="A6" s="642" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="573" t="inlineStr">
+      <c r="B6" s="643" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="537" t="inlineStr">
+      <c r="C6" s="605" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="566" t="inlineStr">
+      <c r="D6" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="538" t="n">
+      <c r="E6" s="606" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="539" t="n">
+      <c r="F6" s="607" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="538" t="n">
+      <c r="G6" s="606" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="541">
+      <c r="H6" s="609">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="574" t="inlineStr">
+      <c r="I6" s="644" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="575" t="inlineStr">
+      <c r="J6" s="645" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="563" t="inlineStr">
+      <c r="A7" s="633" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="564" t="inlineStr">
+      <c r="B7" s="634" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="565" t="inlineStr">
+      <c r="C7" s="635" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="566" t="inlineStr">
+      <c r="D7" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="567" t="n">
+      <c r="E7" s="637" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="568" t="n">
+      <c r="F7" s="638" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="567" t="n">
+      <c r="G7" s="637" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="569">
+      <c r="H7" s="639">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="570" t="inlineStr">
+      <c r="I7" s="640" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="571" t="inlineStr">
+      <c r="J7" s="641" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="572" t="inlineStr">
+      <c r="A8" s="642" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="573" t="inlineStr">
+      <c r="B8" s="643" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="537" t="inlineStr">
+      <c r="C8" s="605" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="566" t="inlineStr">
+      <c r="D8" s="636" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="538" t="n">
+      <c r="E8" s="606" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="539" t="n">
+      <c r="F8" s="607" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="538" t="n">
+      <c r="G8" s="606" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="541">
+      <c r="H8" s="609">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="574" t="inlineStr">
+      <c r="I8" s="644" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="575" t="inlineStr">
+      <c r="J8" s="645" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3445,11 +3695,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="576">
+      <c r="H10" s="646">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="576">
+      <c r="I10" s="646">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="647">
+  <cellXfs count="710">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2123,6 +2123,195 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2500,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2580,47 +2769,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="507" t="inlineStr">
+      <c r="A2" s="577" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="508" t="n">
+      <c r="B2" s="578" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="509" t="n">
+      <c r="C2" s="579" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="510" t="n">
+      <c r="D2" s="580" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="511" t="n">
+      <c r="E2" s="581" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="512" t="n">
+      <c r="F2" s="582" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="513" t="n">
+      <c r="G2" s="583" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="514" t="n">
+      <c r="H2" s="584" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="515" t="n">
+      <c r="I2" s="585" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="516" t="n">
+      <c r="J2" s="586" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="517" t="n">
+      <c r="K2" s="587" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="518" t="n">
+      <c r="L2" s="588" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="507" t="inlineStr">
+      <c r="A3" s="577" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -2660,7 +2849,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="507" t="inlineStr">
+      <c r="A4" s="577" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -2700,162 +2889,162 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="507" t="inlineStr">
+      <c r="A5" s="577" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="508" t="n">
+      <c r="B5" s="578" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="509" t="n">
+      <c r="C5" s="579" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="510" t="n">
+      <c r="D5" s="580" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="511" t="n">
+      <c r="E5" s="581" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="512" t="n">
+      <c r="F5" s="582" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="513" t="n">
+      <c r="G5" s="583" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="514" t="n">
+      <c r="H5" s="584" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="515" t="n">
+      <c r="I5" s="585" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="516" t="n">
+      <c r="J5" s="586" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="517" t="n">
+      <c r="K5" s="587" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="518" t="n">
+      <c r="L5" s="588" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="507" t="inlineStr">
+      <c r="A6" s="577" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="508" t="n">
+      <c r="B6" s="578" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="509" t="n">
+      <c r="C6" s="579" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="510" t="n">
+      <c r="D6" s="580" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="511" t="n">
+      <c r="E6" s="581" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="512" t="n">
+      <c r="F6" s="582" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="513" t="n">
+      <c r="G6" s="583" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="514" t="n">
+      <c r="H6" s="584" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="515" t="n">
+      <c r="I6" s="585" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="516" t="n">
+      <c r="J6" s="586" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="517" t="n">
+      <c r="K6" s="587" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="518" t="n">
+      <c r="L6" s="588" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="507" t="inlineStr">
+      <c r="A7" s="577" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="508" t="n">
+      <c r="B7" s="578" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="509" t="n">
+      <c r="C7" s="579" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="510" t="n">
+      <c r="D7" s="580" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="511" t="n">
+      <c r="E7" s="581" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="512" t="n">
+      <c r="F7" s="582" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="513" t="n">
+      <c r="G7" s="583" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="514" t="n">
+      <c r="H7" s="584" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="515" t="n">
+      <c r="I7" s="585" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="516" t="n">
+      <c r="J7" s="586" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="517" t="n">
+      <c r="K7" s="587" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="518" t="n">
+      <c r="L7" s="588" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="507" t="inlineStr">
+      <c r="A8" s="577" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="508" t="n">
+      <c r="B8" s="578" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="509" t="n">
+      <c r="C8" s="579" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="510" t="n">
+      <c r="D8" s="580" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="511" t="n">
+      <c r="E8" s="581" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="512" t="n">
+      <c r="F8" s="582" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="513" t="n">
+      <c r="G8" s="583" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="514" t="n">
+      <c r="H8" s="584" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="515" t="n">
+      <c r="I8" s="585" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="516" t="n">
+      <c r="J8" s="586" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="517" t="n">
+      <c r="K8" s="587" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="518" t="n">
+      <c r="L8" s="588" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2896,6 +3085,46 @@
         <v>0</v>
       </c>
       <c r="L9" s="588" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="647" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B10" s="648" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="649" t="n">
+        <v>299729.8232736588</v>
+      </c>
+      <c r="D10" s="650" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E10" s="651" t="n">
+        <v>281306.0053825378</v>
+      </c>
+      <c r="F10" s="652" t="n">
+        <v>-270.1767263412476</v>
+      </c>
+      <c r="G10" s="653" t="n">
+        <v>-0.0009005890878041585</v>
+      </c>
+      <c r="H10" s="654" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="655" t="n">
+        <v>-0.01454524845785893</v>
+      </c>
+      <c r="J10" s="656" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="657" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="658" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2928,360 +3157,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="589" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  05 May 2026</t>
+      <c r="A1" s="659" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  06 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="590" t="inlineStr">
+      <c r="A2" s="660" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="590" t="inlineStr">
+      <c r="B2" s="660" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="590" t="inlineStr">
+      <c r="C2" s="660" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="590" t="inlineStr">
+      <c r="D2" s="660" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="590" t="inlineStr">
+      <c r="E2" s="660" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="590" t="inlineStr">
+      <c r="F2" s="660" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="590" t="inlineStr">
+      <c r="G2" s="660" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="590" t="inlineStr">
+      <c r="H2" s="660" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="590" t="inlineStr">
+      <c r="I2" s="660" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="590" t="inlineStr">
+      <c r="J2" s="660" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="590" t="inlineStr">
+      <c r="K2" s="660" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="591" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="592" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C3" s="593" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D3" s="594" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E3" s="595" t="n">
-        <v>4.480000019073486</v>
-      </c>
-      <c r="F3" s="596">
+      <c r="A3" s="661" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="662" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C3" s="663" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D3" s="664" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E3" s="665" t="n">
+        <v>17.70000076293945</v>
+      </c>
+      <c r="F3" s="666">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="597">
+      <c r="G3" s="667">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="598">
+      <c r="H3" s="668">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="599" t="inlineStr">
+      <c r="I3" s="669" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="600" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K3" s="601" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J3" s="670" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K3" s="671" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="591" t="inlineStr">
+      <c r="A4" s="661" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="B4" s="592" t="inlineStr">
+      <c r="B4" s="662" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="C4" s="593" t="n">
+      <c r="C4" s="663" t="n">
         <v>7000</v>
       </c>
-      <c r="D4" s="594" t="n">
+      <c r="D4" s="664" t="n">
         <v>6.7</v>
       </c>
-      <c r="E4" s="595" t="n">
+      <c r="E4" s="665" t="n">
         <v>6.900000095367432</v>
       </c>
-      <c r="F4" s="596">
+      <c r="F4" s="666">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="597">
+      <c r="G4" s="667">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="598">
+      <c r="H4" s="668">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="599" t="inlineStr">
+      <c r="I4" s="669" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="602" t="n">
+      <c r="J4" s="672" t="n">
         <v>5.48</v>
       </c>
-      <c r="K4" s="603" t="inlineStr">
+      <c r="K4" s="673" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="591" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="592" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C5" s="593" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="594" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E5" s="595" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" s="596">
+      <c r="A5" s="661" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="662" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C5" s="663" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D5" s="664" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E5" s="665" t="n">
+        <v>4.420000076293945</v>
+      </c>
+      <c r="F5" s="666">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="597">
+      <c r="G5" s="667">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="598">
+      <c r="H5" s="668">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="599" t="inlineStr">
+      <c r="I5" s="669" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="600" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="K5" s="601" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+      <c r="J5" s="670" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K5" s="671" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="604" t="inlineStr">
+      <c r="A6" s="661" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B6" s="605" t="inlineStr">
+      <c r="B6" s="662" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C6" s="606" t="n">
+      <c r="C6" s="663" t="n">
         <v>1600</v>
       </c>
-      <c r="D6" s="607" t="n">
+      <c r="D6" s="664" t="n">
         <v>29.25</v>
       </c>
-      <c r="E6" s="608" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F6" s="609">
+      <c r="E6" s="665" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F6" s="666">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="610">
+      <c r="G6" s="667">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="611">
+      <c r="H6" s="668">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="612" t="inlineStr">
+      <c r="I6" s="669" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="613" t="n">
+      <c r="J6" s="670" t="n">
         <v>6.52</v>
       </c>
-      <c r="K6" s="614" t="inlineStr">
+      <c r="K6" s="671" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="615" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="616" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C7" s="617" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D7" s="618" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E7" s="619" t="n">
-        <v>17</v>
-      </c>
-      <c r="F7" s="620">
+      <c r="A7" s="674" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="675" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C7" s="676" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D7" s="677" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E7" s="678" t="n">
+        <v>19.70000076293945</v>
+      </c>
+      <c r="F7" s="679">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="621">
+      <c r="G7" s="680">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="622">
+      <c r="H7" s="681">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="623" t="inlineStr">
+      <c r="I7" s="682" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="624" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K7" s="625" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J7" s="683" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K7" s="684" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="615" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="616" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C8" s="617" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D8" s="618" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E8" s="619" t="n">
-        <v>19.85000038146973</v>
-      </c>
-      <c r="F8" s="620">
+      <c r="A8" s="674" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="675" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C8" s="676" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D8" s="677" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E8" s="678" t="n">
+        <v>16</v>
+      </c>
+      <c r="F8" s="679">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="621">
+      <c r="G8" s="680">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="622">
+      <c r="H8" s="681">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="623" t="inlineStr">
+      <c r="I8" s="682" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="626" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K8" s="627" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J8" s="685" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K8" s="686" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="628" t="inlineStr">
+      <c r="B9" s="687" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="629">
+      <c r="F9" s="688">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="630">
+      <c r="G9" s="689">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="631">
+      <c r="H9" s="690">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -3316,14 +3545,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="589" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  05 May 2026</t>
+      <c r="A1" s="659" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  06 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="632" t="inlineStr">
+      <c r="A3" s="691" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -3361,329 +3590,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="589" t="inlineStr">
+      <c r="A1" s="659" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="590" t="inlineStr">
+      <c r="A2" s="660" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="590" t="inlineStr">
+      <c r="B2" s="660" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="590" t="inlineStr">
+      <c r="C2" s="660" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="590" t="inlineStr">
+      <c r="D2" s="660" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="590" t="inlineStr">
+      <c r="E2" s="660" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="590" t="inlineStr">
+      <c r="F2" s="660" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="590" t="inlineStr">
+      <c r="G2" s="660" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="590" t="inlineStr">
+      <c r="H2" s="660" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="590" t="inlineStr">
+      <c r="I2" s="660" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="590" t="inlineStr">
+      <c r="J2" s="660" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="633" t="inlineStr">
+      <c r="A3" s="692" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="634" t="inlineStr">
+      <c r="B3" s="693" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="635" t="inlineStr">
+      <c r="C3" s="694" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="636" t="inlineStr">
+      <c r="D3" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="637" t="n">
+      <c r="E3" s="696" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="638" t="n">
+      <c r="F3" s="697" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="637" t="n">
+      <c r="G3" s="696" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="639">
+      <c r="H3" s="698">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="640" t="inlineStr">
+      <c r="I3" s="699" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="641" t="inlineStr">
+      <c r="J3" s="700" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="642" t="inlineStr">
+      <c r="A4" s="701" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="643" t="inlineStr">
+      <c r="B4" s="702" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="605" t="inlineStr">
+      <c r="C4" s="703" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="636" t="inlineStr">
+      <c r="D4" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="606" t="n">
+      <c r="E4" s="704" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="607" t="n">
+      <c r="F4" s="705" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="606" t="n">
+      <c r="G4" s="704" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="609">
+      <c r="H4" s="706">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="644" t="inlineStr">
+      <c r="I4" s="707" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="645" t="inlineStr">
+      <c r="J4" s="708" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="633" t="inlineStr">
+      <c r="A5" s="692" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="634" t="inlineStr">
+      <c r="B5" s="693" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="635" t="inlineStr">
+      <c r="C5" s="694" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="636" t="inlineStr">
+      <c r="D5" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="637" t="n">
+      <c r="E5" s="696" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="638" t="n">
+      <c r="F5" s="697" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="637" t="n">
+      <c r="G5" s="696" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="639">
+      <c r="H5" s="698">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="640" t="inlineStr">
+      <c r="I5" s="699" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="641" t="inlineStr">
+      <c r="J5" s="700" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="642" t="inlineStr">
+      <c r="A6" s="701" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="643" t="inlineStr">
+      <c r="B6" s="702" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="605" t="inlineStr">
+      <c r="C6" s="703" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="636" t="inlineStr">
+      <c r="D6" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="606" t="n">
+      <c r="E6" s="704" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="607" t="n">
+      <c r="F6" s="705" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="606" t="n">
+      <c r="G6" s="704" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="609">
+      <c r="H6" s="706">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="644" t="inlineStr">
+      <c r="I6" s="707" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="645" t="inlineStr">
+      <c r="J6" s="708" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="633" t="inlineStr">
+      <c r="A7" s="692" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="634" t="inlineStr">
+      <c r="B7" s="693" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="635" t="inlineStr">
+      <c r="C7" s="694" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="636" t="inlineStr">
+      <c r="D7" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="637" t="n">
+      <c r="E7" s="696" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="638" t="n">
+      <c r="F7" s="697" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="637" t="n">
+      <c r="G7" s="696" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="639">
+      <c r="H7" s="698">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="640" t="inlineStr">
+      <c r="I7" s="699" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="641" t="inlineStr">
+      <c r="J7" s="700" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="642" t="inlineStr">
+      <c r="A8" s="701" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="643" t="inlineStr">
+      <c r="B8" s="702" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="605" t="inlineStr">
+      <c r="C8" s="703" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="636" t="inlineStr">
+      <c r="D8" s="695" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="606" t="n">
+      <c r="E8" s="704" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="607" t="n">
+      <c r="F8" s="705" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="606" t="n">
+      <c r="G8" s="704" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="609">
+      <c r="H8" s="706">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="644" t="inlineStr">
+      <c r="I8" s="707" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="645" t="inlineStr">
+      <c r="J8" s="708" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3695,11 +3924,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="646">
+      <c r="H10" s="709">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="646">
+      <c r="I10" s="709">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="710">
+  <cellXfs count="773">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2246,6 +2246,195 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2689,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2769,7 +2958,7 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="577" t="inlineStr">
+      <c r="A2" s="647" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -2809,87 +2998,87 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="577" t="inlineStr">
+      <c r="A3" s="647" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="B3" s="190" t="n">
+      <c r="B3" s="648" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="191" t="n">
+      <c r="C3" s="649" t="n">
         <v>299325.3084818721</v>
       </c>
-      <c r="D3" s="192" t="n">
+      <c r="D3" s="650" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E3" s="193" t="n">
+      <c r="E3" s="651" t="n">
         <v>269877</v>
       </c>
-      <c r="F3" s="194" t="n">
+      <c r="F3" s="652" t="n">
         <v>-674.6915181279182</v>
       </c>
-      <c r="G3" s="195" t="n">
+      <c r="G3" s="653" t="n">
         <v>-0.002248971727093061</v>
       </c>
-      <c r="H3" s="196" t="n">
+      <c r="H3" s="654" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="197" t="n">
+      <c r="I3" s="655" t="n">
         <v>-0.01456138968534346</v>
       </c>
-      <c r="J3" s="198" t="n">
+      <c r="J3" s="656" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="199" t="n">
+      <c r="K3" s="657" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="200" t="n">
+      <c r="L3" s="658" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="577" t="inlineStr">
+      <c r="A4" s="647" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B4" s="190" t="n">
+      <c r="B4" s="648" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="191" t="n">
+      <c r="C4" s="649" t="n">
         <v>299017.3066517711</v>
       </c>
-      <c r="D4" s="192" t="n">
+      <c r="D4" s="650" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E4" s="193" t="n">
+      <c r="E4" s="651" t="n">
         <v>269568.998169899</v>
       </c>
-      <c r="F4" s="194" t="n">
+      <c r="F4" s="652" t="n">
         <v>-982.6933482289314</v>
       </c>
-      <c r="G4" s="195" t="n">
+      <c r="G4" s="653" t="n">
         <v>-0.003275644494096438</v>
       </c>
-      <c r="H4" s="196" t="n">
+      <c r="H4" s="654" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="197" t="n">
+      <c r="I4" s="655" t="n">
         <v>-0.01557539313519707</v>
       </c>
-      <c r="J4" s="198" t="n">
+      <c r="J4" s="656" t="n">
         <v>10</v>
       </c>
-      <c r="K4" s="199" t="n">
+      <c r="K4" s="657" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="200" t="n">
+      <c r="L4" s="658" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="577" t="inlineStr">
+      <c r="A5" s="647" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
@@ -2929,7 +3118,7 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="577" t="inlineStr">
+      <c r="A6" s="647" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -2969,7 +3158,7 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="577" t="inlineStr">
+      <c r="A7" s="647" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
@@ -3009,7 +3198,7 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="577" t="inlineStr">
+      <c r="A8" s="647" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
@@ -3049,7 +3238,7 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="577" t="inlineStr">
+      <c r="A9" s="647" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
@@ -3125,6 +3314,46 @@
         <v>0</v>
       </c>
       <c r="L10" s="658" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="710" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B11" s="711" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="712" t="n">
+        <v>308341.8176355362</v>
+      </c>
+      <c r="D11" s="713" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E11" s="714" t="n">
+        <v>289917.9997444153</v>
+      </c>
+      <c r="F11" s="715" t="n">
+        <v>8341.817635536194</v>
+      </c>
+      <c r="G11" s="716" t="n">
+        <v>0.02780605878512065</v>
+      </c>
+      <c r="H11" s="717" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="718" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="719" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="720" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="721" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3157,360 +3386,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="659" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  06 May 2026</t>
+      <c r="A1" s="722" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  07 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="660" t="inlineStr">
+      <c r="A2" s="723" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="660" t="inlineStr">
+      <c r="B2" s="723" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="660" t="inlineStr">
+      <c r="C2" s="723" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="660" t="inlineStr">
+      <c r="D2" s="723" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="660" t="inlineStr">
+      <c r="E2" s="723" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="660" t="inlineStr">
+      <c r="F2" s="723" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="660" t="inlineStr">
+      <c r="G2" s="723" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="660" t="inlineStr">
+      <c r="H2" s="723" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="660" t="inlineStr">
+      <c r="I2" s="723" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="660" t="inlineStr">
+      <c r="J2" s="723" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="660" t="inlineStr">
+      <c r="K2" s="723" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="661" t="inlineStr">
+      <c r="A3" s="724" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="662" t="inlineStr">
+      <c r="B3" s="725" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="663" t="n">
+      <c r="C3" s="726" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="664" t="n">
+      <c r="D3" s="727" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="665" t="n">
-        <v>17.70000076293945</v>
-      </c>
-      <c r="F3" s="666">
+      <c r="E3" s="728" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F3" s="729">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="667">
+      <c r="G3" s="730">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="668">
+      <c r="H3" s="731">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="669" t="inlineStr">
+      <c r="I3" s="732" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="670" t="n">
+      <c r="J3" s="733" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="671" t="inlineStr">
+      <c r="K3" s="734" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="661" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="662" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C4" s="663" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D4" s="664" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E4" s="665" t="n">
-        <v>6.900000095367432</v>
-      </c>
-      <c r="F4" s="666">
+      <c r="A4" s="724" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="725" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C4" s="726" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D4" s="727" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E4" s="728" t="n">
+        <v>4.659999847412109</v>
+      </c>
+      <c r="F4" s="729">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="667">
+      <c r="G4" s="730">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="668">
+      <c r="H4" s="731">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="669" t="inlineStr">
+      <c r="I4" s="732" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="672" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K4" s="673" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J4" s="733" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="K4" s="734" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="661" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="662" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C5" s="663" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D5" s="664" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E5" s="665" t="n">
-        <v>4.420000076293945</v>
-      </c>
-      <c r="F5" s="666">
+      <c r="A5" s="724" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="725" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C5" s="726" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D5" s="727" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E5" s="728" t="n">
+        <v>6.900000095367432</v>
+      </c>
+      <c r="F5" s="729">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="667">
+      <c r="G5" s="730">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="668">
+      <c r="H5" s="731">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="669" t="inlineStr">
+      <c r="I5" s="732" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="670" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K5" s="671" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J5" s="735" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K5" s="736" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="661" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="662" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C6" s="663" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D6" s="664" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E6" s="665" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="F6" s="666">
+      <c r="A6" s="724" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="725" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C6" s="726" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D6" s="727" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E6" s="728" t="n">
+        <v>20.70000076293945</v>
+      </c>
+      <c r="F6" s="729">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="667">
+      <c r="G6" s="730">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="668">
+      <c r="H6" s="731">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="669" t="inlineStr">
+      <c r="I6" s="732" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="670" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K6" s="671" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J6" s="737" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K6" s="738" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="674" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="675" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C7" s="676" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D7" s="677" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E7" s="678" t="n">
-        <v>19.70000076293945</v>
-      </c>
-      <c r="F7" s="679">
+      <c r="A7" s="724" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="725" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="726" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="727" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E7" s="728" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F7" s="729">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="680">
+      <c r="G7" s="730">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="681">
+      <c r="H7" s="731">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="682" t="inlineStr">
+      <c r="I7" s="732" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="683" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K7" s="684" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J7" s="733" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K7" s="734" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="674" t="inlineStr">
+      <c r="A8" s="739" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="675" t="inlineStr">
+      <c r="B8" s="740" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="676" t="n">
+      <c r="C8" s="741" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="677" t="n">
+      <c r="D8" s="742" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="678" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" s="679">
+      <c r="E8" s="743" t="n">
+        <v>16.39999961853027</v>
+      </c>
+      <c r="F8" s="744">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="680">
+      <c r="G8" s="745">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="681">
+      <c r="H8" s="746">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="682" t="inlineStr">
+      <c r="I8" s="747" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="685" t="n">
+      <c r="J8" s="748" t="n">
         <v>6.92</v>
       </c>
-      <c r="K8" s="686" t="inlineStr">
+      <c r="K8" s="749" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="687" t="inlineStr">
+      <c r="B9" s="750" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="688">
+      <c r="F9" s="751">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="689">
+      <c r="G9" s="752">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="690">
+      <c r="H9" s="753">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -3545,14 +3774,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="659" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  06 May 2026</t>
+      <c r="A1" s="722" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  07 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="691" t="inlineStr">
+      <c r="A3" s="754" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -3590,329 +3819,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="659" t="inlineStr">
+      <c r="A1" s="722" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="660" t="inlineStr">
+      <c r="A2" s="723" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="660" t="inlineStr">
+      <c r="B2" s="723" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="660" t="inlineStr">
+      <c r="C2" s="723" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="660" t="inlineStr">
+      <c r="D2" s="723" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="660" t="inlineStr">
+      <c r="E2" s="723" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="660" t="inlineStr">
+      <c r="F2" s="723" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="660" t="inlineStr">
+      <c r="G2" s="723" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="660" t="inlineStr">
+      <c r="H2" s="723" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="660" t="inlineStr">
+      <c r="I2" s="723" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="660" t="inlineStr">
+      <c r="J2" s="723" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="692" t="inlineStr">
+      <c r="A3" s="755" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="693" t="inlineStr">
+      <c r="B3" s="756" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="694" t="inlineStr">
+      <c r="C3" s="757" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="695" t="inlineStr">
+      <c r="D3" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="696" t="n">
+      <c r="E3" s="759" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="697" t="n">
+      <c r="F3" s="760" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="696" t="n">
+      <c r="G3" s="759" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="698">
+      <c r="H3" s="761">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="699" t="inlineStr">
+      <c r="I3" s="762" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="700" t="inlineStr">
+      <c r="J3" s="763" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="701" t="inlineStr">
+      <c r="A4" s="764" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="702" t="inlineStr">
+      <c r="B4" s="765" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="703" t="inlineStr">
+      <c r="C4" s="766" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="695" t="inlineStr">
+      <c r="D4" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="704" t="n">
+      <c r="E4" s="767" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="705" t="n">
+      <c r="F4" s="768" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="704" t="n">
+      <c r="G4" s="767" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="706">
+      <c r="H4" s="769">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="707" t="inlineStr">
+      <c r="I4" s="770" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="708" t="inlineStr">
+      <c r="J4" s="771" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="692" t="inlineStr">
+      <c r="A5" s="755" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="693" t="inlineStr">
+      <c r="B5" s="756" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="694" t="inlineStr">
+      <c r="C5" s="757" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="695" t="inlineStr">
+      <c r="D5" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="696" t="n">
+      <c r="E5" s="759" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="697" t="n">
+      <c r="F5" s="760" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="696" t="n">
+      <c r="G5" s="759" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="698">
+      <c r="H5" s="761">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="699" t="inlineStr">
+      <c r="I5" s="762" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="700" t="inlineStr">
+      <c r="J5" s="763" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="701" t="inlineStr">
+      <c r="A6" s="764" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="702" t="inlineStr">
+      <c r="B6" s="765" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="703" t="inlineStr">
+      <c r="C6" s="766" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="695" t="inlineStr">
+      <c r="D6" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="704" t="n">
+      <c r="E6" s="767" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="705" t="n">
+      <c r="F6" s="768" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="704" t="n">
+      <c r="G6" s="767" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="706">
+      <c r="H6" s="769">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="707" t="inlineStr">
+      <c r="I6" s="770" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="708" t="inlineStr">
+      <c r="J6" s="771" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="692" t="inlineStr">
+      <c r="A7" s="755" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="693" t="inlineStr">
+      <c r="B7" s="756" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="694" t="inlineStr">
+      <c r="C7" s="757" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="695" t="inlineStr">
+      <c r="D7" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="696" t="n">
+      <c r="E7" s="759" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="697" t="n">
+      <c r="F7" s="760" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="696" t="n">
+      <c r="G7" s="759" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="698">
+      <c r="H7" s="761">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="699" t="inlineStr">
+      <c r="I7" s="762" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="700" t="inlineStr">
+      <c r="J7" s="763" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="701" t="inlineStr">
+      <c r="A8" s="764" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="702" t="inlineStr">
+      <c r="B8" s="765" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="703" t="inlineStr">
+      <c r="C8" s="766" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="695" t="inlineStr">
+      <c r="D8" s="758" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="704" t="n">
+      <c r="E8" s="767" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="705" t="n">
+      <c r="F8" s="768" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="704" t="n">
+      <c r="G8" s="767" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="706">
+      <c r="H8" s="769">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="707" t="inlineStr">
+      <c r="I8" s="770" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="708" t="inlineStr">
+      <c r="J8" s="771" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -3924,11 +4153,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="709">
+      <c r="H10" s="772">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="709">
+      <c r="I10" s="772">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -196,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="773">
+  <cellXfs count="832">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2501,6 +2501,183 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2878,7 +3055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2958,47 +3135,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="647" t="inlineStr">
+      <c r="A2" s="710" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="578" t="n">
+      <c r="B2" s="711" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="579" t="n">
+      <c r="C2" s="712" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="580" t="n">
+      <c r="D2" s="713" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="581" t="n">
+      <c r="E2" s="714" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="582" t="n">
+      <c r="F2" s="715" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="583" t="n">
+      <c r="G2" s="716" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="584" t="n">
+      <c r="H2" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="585" t="n">
+      <c r="I2" s="718" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="586" t="n">
+      <c r="J2" s="719" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="587" t="n">
+      <c r="K2" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="588" t="n">
+      <c r="L2" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="647" t="inlineStr">
+      <c r="A3" s="710" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -3038,7 +3215,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="647" t="inlineStr">
+      <c r="A4" s="710" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -3078,207 +3255,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="647" t="inlineStr">
+      <c r="A5" s="710" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="578" t="n">
+      <c r="B5" s="711" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="579" t="n">
+      <c r="C5" s="712" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="580" t="n">
+      <c r="D5" s="713" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="581" t="n">
+      <c r="E5" s="714" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="582" t="n">
+      <c r="F5" s="715" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="583" t="n">
+      <c r="G5" s="716" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="584" t="n">
+      <c r="H5" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="585" t="n">
+      <c r="I5" s="718" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="586" t="n">
+      <c r="J5" s="719" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="587" t="n">
+      <c r="K5" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="588" t="n">
+      <c r="L5" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="647" t="inlineStr">
+      <c r="A6" s="710" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="578" t="n">
+      <c r="B6" s="711" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="579" t="n">
+      <c r="C6" s="712" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="580" t="n">
+      <c r="D6" s="713" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="581" t="n">
+      <c r="E6" s="714" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="582" t="n">
+      <c r="F6" s="715" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="583" t="n">
+      <c r="G6" s="716" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="584" t="n">
+      <c r="H6" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="585" t="n">
+      <c r="I6" s="718" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="586" t="n">
+      <c r="J6" s="719" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="587" t="n">
+      <c r="K6" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="588" t="n">
+      <c r="L6" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="647" t="inlineStr">
+      <c r="A7" s="710" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="578" t="n">
+      <c r="B7" s="711" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="579" t="n">
+      <c r="C7" s="712" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="580" t="n">
+      <c r="D7" s="713" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="581" t="n">
+      <c r="E7" s="714" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="582" t="n">
+      <c r="F7" s="715" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="583" t="n">
+      <c r="G7" s="716" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="584" t="n">
+      <c r="H7" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="585" t="n">
+      <c r="I7" s="718" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="586" t="n">
+      <c r="J7" s="719" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="587" t="n">
+      <c r="K7" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="588" t="n">
+      <c r="L7" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="647" t="inlineStr">
+      <c r="A8" s="710" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="578" t="n">
+      <c r="B8" s="711" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="579" t="n">
+      <c r="C8" s="712" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="580" t="n">
+      <c r="D8" s="713" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="581" t="n">
+      <c r="E8" s="714" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="582" t="n">
+      <c r="F8" s="715" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="583" t="n">
+      <c r="G8" s="716" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="584" t="n">
+      <c r="H8" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="585" t="n">
+      <c r="I8" s="718" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="586" t="n">
+      <c r="J8" s="719" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="587" t="n">
+      <c r="K8" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="588" t="n">
+      <c r="L8" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="647" t="inlineStr">
+      <c r="A9" s="710" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="578" t="n">
+      <c r="B9" s="711" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="579" t="n">
+      <c r="C9" s="712" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="580" t="n">
+      <c r="D9" s="713" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="581" t="n">
+      <c r="E9" s="714" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="582" t="n">
+      <c r="F9" s="715" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="583" t="n">
+      <c r="G9" s="716" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="584" t="n">
+      <c r="H9" s="717" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="585" t="n">
+      <c r="I9" s="718" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="586" t="n">
+      <c r="J9" s="719" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="587" t="n">
+      <c r="K9" s="720" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="588" t="n">
+      <c r="L9" s="721" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="647" t="inlineStr">
+      <c r="A10" s="710" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -3354,6 +3531,46 @@
         <v>0</v>
       </c>
       <c r="L11" s="721" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="773" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B12" s="774" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="775" t="n">
+        <v>311587.818192482</v>
+      </c>
+      <c r="D12" s="776" t="n">
+        <v>18423.81789112091</v>
+      </c>
+      <c r="E12" s="777" t="n">
+        <v>293164.0003013611</v>
+      </c>
+      <c r="F12" s="778" t="n">
+        <v>11587.81819248199</v>
+      </c>
+      <c r="G12" s="779" t="n">
+        <v>0.03862606064160665</v>
+      </c>
+      <c r="H12" s="780" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="781" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="782" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="783" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="784" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3386,360 +3603,360 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="722" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  07 May 2026</t>
+      <c r="A1" s="785" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  08 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="723" t="inlineStr">
+      <c r="A2" s="786" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="723" t="inlineStr">
+      <c r="B2" s="786" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="723" t="inlineStr">
+      <c r="C2" s="786" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="723" t="inlineStr">
+      <c r="D2" s="786" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="723" t="inlineStr">
+      <c r="E2" s="786" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="723" t="inlineStr">
+      <c r="F2" s="786" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="723" t="inlineStr">
+      <c r="G2" s="786" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="723" t="inlineStr">
+      <c r="H2" s="786" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="723" t="inlineStr">
+      <c r="I2" s="786" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="723" t="inlineStr">
+      <c r="J2" s="786" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="723" t="inlineStr">
+      <c r="K2" s="786" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="724" t="inlineStr">
+      <c r="A3" s="787" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="725" t="inlineStr">
+      <c r="B3" s="788" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="726" t="n">
+      <c r="C3" s="789" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="727" t="n">
+      <c r="D3" s="790" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="728" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F3" s="729">
+      <c r="E3" s="791" t="n">
+        <v>18.60000038146973</v>
+      </c>
+      <c r="F3" s="792">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="730">
+      <c r="G3" s="793">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="731">
+      <c r="H3" s="794">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="732" t="inlineStr">
+      <c r="I3" s="795" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="733" t="n">
+      <c r="J3" s="796" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="734" t="inlineStr">
+      <c r="K3" s="797" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="724" t="inlineStr">
+      <c r="A4" s="787" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="725" t="inlineStr">
+      <c r="B4" s="788" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="726" t="n">
+      <c r="C4" s="789" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="727" t="n">
+      <c r="D4" s="790" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="728" t="n">
-        <v>4.659999847412109</v>
-      </c>
-      <c r="F4" s="729">
+      <c r="E4" s="791" t="n">
+        <v>4.679999828338623</v>
+      </c>
+      <c r="F4" s="792">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="730">
+      <c r="G4" s="793">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="731">
+      <c r="H4" s="794">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="732" t="inlineStr">
+      <c r="I4" s="795" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="733" t="n">
+      <c r="J4" s="796" t="n">
         <v>6.92</v>
       </c>
-      <c r="K4" s="734" t="inlineStr">
+      <c r="K4" s="797" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="724" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="725" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C5" s="726" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D5" s="727" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E5" s="728" t="n">
-        <v>6.900000095367432</v>
-      </c>
-      <c r="F5" s="729">
+      <c r="A5" s="787" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="788" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C5" s="789" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D5" s="790" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E5" s="791" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="792">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="730">
+      <c r="G5" s="793">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="731">
+      <c r="H5" s="794">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="732" t="inlineStr">
+      <c r="I5" s="795" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="735" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K5" s="736" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J5" s="796" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="K5" s="797" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="724" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="725" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C6" s="726" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D6" s="727" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E6" s="728" t="n">
-        <v>20.70000076293945</v>
-      </c>
-      <c r="F6" s="729">
+      <c r="A6" s="787" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="788" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="C6" s="789" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D6" s="790" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E6" s="791" t="n">
+        <v>6.849999904632568</v>
+      </c>
+      <c r="F6" s="792">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="730">
+      <c r="G6" s="793">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="731">
+      <c r="H6" s="794">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="732" t="inlineStr">
+      <c r="I6" s="795" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="737" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K6" s="738" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J6" s="798" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K6" s="799" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="724" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="725" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C7" s="726" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D7" s="727" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E7" s="728" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="F7" s="729">
+      <c r="A7" s="787" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="788" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C7" s="789" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D7" s="790" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E7" s="791" t="n">
+        <v>20.70000076293945</v>
+      </c>
+      <c r="F7" s="792">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="730">
+      <c r="G7" s="793">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="731">
+      <c r="H7" s="794">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="732" t="inlineStr">
+      <c r="I7" s="795" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="733" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K7" s="734" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J7" s="800" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K7" s="801" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="739" t="inlineStr">
+      <c r="A8" s="802" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B8" s="740" t="inlineStr">
+      <c r="B8" s="803" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C8" s="741" t="n">
+      <c r="C8" s="804" t="n">
         <v>2700</v>
       </c>
-      <c r="D8" s="742" t="n">
+      <c r="D8" s="805" t="n">
         <v>17.4</v>
       </c>
-      <c r="E8" s="743" t="n">
-        <v>16.39999961853027</v>
-      </c>
-      <c r="F8" s="744">
+      <c r="E8" s="806" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F8" s="807">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="745">
+      <c r="G8" s="808">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="746">
+      <c r="H8" s="809">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="747" t="inlineStr">
+      <c r="I8" s="810" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J8" s="748" t="n">
+      <c r="J8" s="811" t="n">
         <v>6.92</v>
       </c>
-      <c r="K8" s="749" t="inlineStr">
+      <c r="K8" s="812" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="750" t="inlineStr">
+      <c r="B9" s="813" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="751">
+      <c r="F9" s="814">
         <f>SUM(F3:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="752">
+      <c r="G9" s="815">
         <f>SUM(G3:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="753">
+      <c r="H9" s="816">
         <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
         <v/>
       </c>
@@ -3774,14 +3991,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="722" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  07 May 2026</t>
+      <c r="A1" s="785" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  08 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="754" t="inlineStr">
+      <c r="A3" s="817" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -3819,329 +4036,329 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="722" t="inlineStr">
+      <c r="A1" s="785" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="723" t="inlineStr">
+      <c r="A2" s="786" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="723" t="inlineStr">
+      <c r="B2" s="786" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="723" t="inlineStr">
+      <c r="C2" s="786" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="723" t="inlineStr">
+      <c r="D2" s="786" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="723" t="inlineStr">
+      <c r="E2" s="786" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="723" t="inlineStr">
+      <c r="F2" s="786" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="723" t="inlineStr">
+      <c r="G2" s="786" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="723" t="inlineStr">
+      <c r="H2" s="786" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="723" t="inlineStr">
+      <c r="I2" s="786" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="723" t="inlineStr">
+      <c r="J2" s="786" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="755" t="inlineStr">
+      <c r="A3" s="818" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="756" t="inlineStr">
+      <c r="B3" s="819" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="757" t="inlineStr">
+      <c r="C3" s="820" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="758" t="inlineStr">
+      <c r="D3" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="759" t="n">
+      <c r="E3" s="822" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="760" t="n">
+      <c r="F3" s="823" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="759" t="n">
+      <c r="G3" s="822" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="761">
+      <c r="H3" s="824">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="762" t="inlineStr">
+      <c r="I3" s="825" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="763" t="inlineStr">
+      <c r="J3" s="826" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="764" t="inlineStr">
+      <c r="A4" s="827" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="765" t="inlineStr">
+      <c r="B4" s="828" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="766" t="inlineStr">
+      <c r="C4" s="803" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="758" t="inlineStr">
+      <c r="D4" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="767" t="n">
+      <c r="E4" s="804" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="768" t="n">
+      <c r="F4" s="805" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="767" t="n">
+      <c r="G4" s="804" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="769">
+      <c r="H4" s="807">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="770" t="inlineStr">
+      <c r="I4" s="829" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="771" t="inlineStr">
+      <c r="J4" s="830" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="755" t="inlineStr">
+      <c r="A5" s="818" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="756" t="inlineStr">
+      <c r="B5" s="819" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="757" t="inlineStr">
+      <c r="C5" s="820" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="758" t="inlineStr">
+      <c r="D5" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="759" t="n">
+      <c r="E5" s="822" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="760" t="n">
+      <c r="F5" s="823" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="759" t="n">
+      <c r="G5" s="822" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="761">
+      <c r="H5" s="824">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="762" t="inlineStr">
+      <c r="I5" s="825" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="763" t="inlineStr">
+      <c r="J5" s="826" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="764" t="inlineStr">
+      <c r="A6" s="827" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="765" t="inlineStr">
+      <c r="B6" s="828" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="766" t="inlineStr">
+      <c r="C6" s="803" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="758" t="inlineStr">
+      <c r="D6" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="767" t="n">
+      <c r="E6" s="804" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="768" t="n">
+      <c r="F6" s="805" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="767" t="n">
+      <c r="G6" s="804" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="769">
+      <c r="H6" s="807">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="770" t="inlineStr">
+      <c r="I6" s="829" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="771" t="inlineStr">
+      <c r="J6" s="830" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="755" t="inlineStr">
+      <c r="A7" s="818" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="756" t="inlineStr">
+      <c r="B7" s="819" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="757" t="inlineStr">
+      <c r="C7" s="820" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="758" t="inlineStr">
+      <c r="D7" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="759" t="n">
+      <c r="E7" s="822" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="760" t="n">
+      <c r="F7" s="823" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="759" t="n">
+      <c r="G7" s="822" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="761">
+      <c r="H7" s="824">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="762" t="inlineStr">
+      <c r="I7" s="825" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="763" t="inlineStr">
+      <c r="J7" s="826" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="764" t="inlineStr">
+      <c r="A8" s="827" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="765" t="inlineStr">
+      <c r="B8" s="828" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="766" t="inlineStr">
+      <c r="C8" s="803" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="758" t="inlineStr">
+      <c r="D8" s="821" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="767" t="n">
+      <c r="E8" s="804" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="768" t="n">
+      <c r="F8" s="805" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="767" t="n">
+      <c r="G8" s="804" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="769">
+      <c r="H8" s="807">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="770" t="inlineStr">
+      <c r="I8" s="829" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="771" t="inlineStr">
+      <c r="J8" s="830" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
@@ -4153,11 +4370,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="772">
+      <c r="H10" s="831">
         <f>SUM(H3:H8)</f>
         <v/>
       </c>
-      <c r="I10" s="772">
+      <c r="I10" s="831">
         <f>SUM(I3:I8)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="168" formatCode="฿#,##0;(฿#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="169" formatCode="0.00%;(0.00%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,12 @@
       <color rgb="00FFC000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="832">
+  <cellXfs count="898">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2685,6 +2691,204 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3055,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3135,47 +3339,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="710" t="inlineStr">
+      <c r="A2" s="773" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="711" t="n">
+      <c r="B2" s="774" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="712" t="n">
+      <c r="C2" s="775" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="713" t="n">
+      <c r="D2" s="776" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="714" t="n">
+      <c r="E2" s="777" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="715" t="n">
+      <c r="F2" s="778" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="716" t="n">
+      <c r="G2" s="779" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="717" t="n">
+      <c r="H2" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="718" t="n">
+      <c r="I2" s="781" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="719" t="n">
+      <c r="J2" s="782" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="720" t="n">
+      <c r="K2" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="721" t="n">
+      <c r="L2" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="710" t="inlineStr">
+      <c r="A3" s="773" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -3215,7 +3419,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="710" t="inlineStr">
+      <c r="A4" s="773" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -3255,207 +3459,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="710" t="inlineStr">
+      <c r="A5" s="773" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="711" t="n">
+      <c r="B5" s="774" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="712" t="n">
+      <c r="C5" s="775" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="713" t="n">
+      <c r="D5" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="714" t="n">
+      <c r="E5" s="777" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="715" t="n">
+      <c r="F5" s="778" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="716" t="n">
+      <c r="G5" s="779" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="717" t="n">
+      <c r="H5" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="718" t="n">
+      <c r="I5" s="781" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="719" t="n">
+      <c r="J5" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="720" t="n">
+      <c r="K5" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="721" t="n">
+      <c r="L5" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="710" t="inlineStr">
+      <c r="A6" s="773" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="711" t="n">
+      <c r="B6" s="774" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="712" t="n">
+      <c r="C6" s="775" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="713" t="n">
+      <c r="D6" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="714" t="n">
+      <c r="E6" s="777" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="715" t="n">
+      <c r="F6" s="778" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="716" t="n">
+      <c r="G6" s="779" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="717" t="n">
+      <c r="H6" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="718" t="n">
+      <c r="I6" s="781" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="719" t="n">
+      <c r="J6" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="720" t="n">
+      <c r="K6" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="721" t="n">
+      <c r="L6" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="710" t="inlineStr">
+      <c r="A7" s="773" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="711" t="n">
+      <c r="B7" s="774" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="712" t="n">
+      <c r="C7" s="775" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="713" t="n">
+      <c r="D7" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="714" t="n">
+      <c r="E7" s="777" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="715" t="n">
+      <c r="F7" s="778" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="716" t="n">
+      <c r="G7" s="779" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="717" t="n">
+      <c r="H7" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="718" t="n">
+      <c r="I7" s="781" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="719" t="n">
+      <c r="J7" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="720" t="n">
+      <c r="K7" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="721" t="n">
+      <c r="L7" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="710" t="inlineStr">
+      <c r="A8" s="773" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="711" t="n">
+      <c r="B8" s="774" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="712" t="n">
+      <c r="C8" s="775" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="713" t="n">
+      <c r="D8" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="714" t="n">
+      <c r="E8" s="777" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="715" t="n">
+      <c r="F8" s="778" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="716" t="n">
+      <c r="G8" s="779" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="717" t="n">
+      <c r="H8" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="718" t="n">
+      <c r="I8" s="781" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="719" t="n">
+      <c r="J8" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="720" t="n">
+      <c r="K8" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="721" t="n">
+      <c r="L8" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="710" t="inlineStr">
+      <c r="A9" s="773" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="711" t="n">
+      <c r="B9" s="774" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="712" t="n">
+      <c r="C9" s="775" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="713" t="n">
+      <c r="D9" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="714" t="n">
+      <c r="E9" s="777" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="715" t="n">
+      <c r="F9" s="778" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="716" t="n">
+      <c r="G9" s="779" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="717" t="n">
+      <c r="H9" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="718" t="n">
+      <c r="I9" s="781" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="719" t="n">
+      <c r="J9" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="720" t="n">
+      <c r="K9" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="721" t="n">
+      <c r="L9" s="784" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="710" t="inlineStr">
+      <c r="A10" s="773" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -3495,42 +3699,42 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="710" t="inlineStr">
+      <c r="A11" s="773" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="711" t="n">
+      <c r="B11" s="774" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="712" t="n">
+      <c r="C11" s="775" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="713" t="n">
+      <c r="D11" s="776" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="714" t="n">
+      <c r="E11" s="777" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="715" t="n">
+      <c r="F11" s="778" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="716" t="n">
+      <c r="G11" s="779" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="717" t="n">
+      <c r="H11" s="780" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="718" t="n">
+      <c r="I11" s="781" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="719" t="n">
+      <c r="J11" s="782" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="720" t="n">
+      <c r="K11" s="783" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="721" t="n">
+      <c r="L11" s="784" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3571,6 +3775,46 @@
         <v>0</v>
       </c>
       <c r="L12" s="784" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="832" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B13" s="833" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="834" t="n">
+        <v>310489.1351679564</v>
+      </c>
+      <c r="D13" s="835" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E13" s="836" t="n">
+        <v>261758.9582204819</v>
+      </c>
+      <c r="F13" s="837" t="n">
+        <v>10489.13516795635</v>
+      </c>
+      <c r="G13" s="838" t="n">
+        <v>0.03496378389318784</v>
+      </c>
+      <c r="H13" s="839" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="840" t="n">
+        <v>-0.003526078236623923</v>
+      </c>
+      <c r="J13" s="841" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="843" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3586,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3603,361 +3847,453 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="785" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  08 May 2026</t>
+      <c r="A1" s="844" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  11 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="786" t="inlineStr">
+      <c r="A2" s="845" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="786" t="inlineStr">
+      <c r="B2" s="845" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="786" t="inlineStr">
+      <c r="C2" s="845" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="786" t="inlineStr">
+      <c r="D2" s="845" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="786" t="inlineStr">
+      <c r="E2" s="845" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="786" t="inlineStr">
+      <c r="F2" s="845" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="786" t="inlineStr">
+      <c r="G2" s="845" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="786" t="inlineStr">
+      <c r="H2" s="845" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="786" t="inlineStr">
+      <c r="I2" s="845" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="786" t="inlineStr">
+      <c r="J2" s="845" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="786" t="inlineStr">
+      <c r="K2" s="845" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="787" t="inlineStr">
+      <c r="A3" s="846" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="788" t="inlineStr">
+      <c r="B3" s="847" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="789" t="n">
+      <c r="C3" s="848" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="790" t="n">
+      <c r="D3" s="849" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="791" t="n">
-        <v>18.60000038146973</v>
-      </c>
-      <c r="F3" s="792">
+      <c r="E3" s="850" t="n">
+        <v>18.89999961853027</v>
+      </c>
+      <c r="F3" s="851">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="793">
+      <c r="G3" s="852">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="794">
+      <c r="H3" s="853">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="795" t="inlineStr">
+      <c r="I3" s="854" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="796" t="n">
+      <c r="J3" s="855" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="797" t="inlineStr">
+      <c r="K3" s="856" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="787" t="inlineStr">
+      <c r="A4" s="846" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="788" t="inlineStr">
+      <c r="B4" s="847" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="789" t="n">
+      <c r="C4" s="848" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="790" t="n">
+      <c r="D4" s="849" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="791" t="n">
-        <v>4.679999828338623</v>
-      </c>
-      <c r="F4" s="792">
+      <c r="E4" s="850" t="n">
+        <v>4.55620002746582</v>
+      </c>
+      <c r="F4" s="851">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="793">
+      <c r="G4" s="852">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="794">
+      <c r="H4" s="853">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="795" t="inlineStr">
+      <c r="I4" s="854" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="796" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K4" s="797" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J4" s="857" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="K4" s="858" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="787" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="788" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C5" s="789" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D5" s="790" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E5" s="791" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" s="792">
+      <c r="A5" s="846" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="847" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C5" s="848" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="849" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E5" s="850" t="n">
+        <v>20.79999923706055</v>
+      </c>
+      <c r="F5" s="851">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="793">
+      <c r="G5" s="852">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="794">
+      <c r="H5" s="853">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="795" t="inlineStr">
+      <c r="I5" s="854" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="796" t="n">
-        <v>6.52</v>
-      </c>
-      <c r="K5" s="797" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="J5" s="859" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K5" s="860" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="787" t="inlineStr">
-        <is>
-          <t>JASIF.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="788" t="inlineStr">
-        <is>
-          <t>JASIF</t>
-        </is>
-      </c>
-      <c r="C6" s="789" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D6" s="790" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E6" s="791" t="n">
-        <v>6.849999904632568</v>
-      </c>
-      <c r="F6" s="792">
+      <c r="A6" s="846" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="847" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C6" s="848" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D6" s="849" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E6" s="850" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F6" s="851">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="793">
+      <c r="G6" s="852">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="794">
+      <c r="H6" s="853">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="795" t="inlineStr">
+      <c r="I6" s="854" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="798" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="K6" s="799" t="inlineStr">
+      <c r="J6" s="857" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K6" s="858" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="787" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="788" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C7" s="789" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D7" s="790" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E7" s="791" t="n">
-        <v>20.70000076293945</v>
-      </c>
-      <c r="F7" s="792">
+      <c r="A7" s="861" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="862" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C7" s="863" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D7" s="864" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E7" s="865" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="866">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="793">
+      <c r="G7" s="867">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="794">
+      <c r="H7" s="868">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="795" t="inlineStr">
+      <c r="I7" s="869" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="800" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K7" s="801" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J7" s="870" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K7" s="871" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="802" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B8" s="803" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C8" s="804" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D8" s="805" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E8" s="806" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F8" s="807">
+      <c r="A8" s="846" t="inlineStr">
+        <is>
+          <t>KGI.BK</t>
+        </is>
+      </c>
+      <c r="B8" s="847" t="inlineStr">
+        <is>
+          <t>KGI</t>
+        </is>
+      </c>
+      <c r="C8" s="848" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D8" s="849" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E8" s="850" t="n">
+        <v>4.28000020980835</v>
+      </c>
+      <c r="F8" s="851">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="808">
+      <c r="G8" s="852">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="809">
+      <c r="H8" s="853">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="810" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="J8" s="811" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="K8" s="812" t="inlineStr">
-        <is>
-          <t>WEAK</t>
+      <c r="I8" s="854" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="J8" s="857" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="K8" s="858" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="813" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="846" t="inlineStr">
+        <is>
+          <t>BTSGIF.BK</t>
+        </is>
+      </c>
+      <c r="B9" s="847" t="inlineStr">
+        <is>
+          <t>BTSGIF</t>
+        </is>
+      </c>
+      <c r="C9" s="848" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D9" s="849" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E9" s="850" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="F9" s="851">
+        <f>C9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="852">
+        <f>F9-C9*D9</f>
+        <v/>
+      </c>
+      <c r="H9" s="853">
+        <f>(E9-D9)/D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="854" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="J9" s="857" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K9" s="858" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="846" t="inlineStr">
+        <is>
+          <t>TU.BK</t>
+        </is>
+      </c>
+      <c r="B10" s="847" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="C10" s="848" t="n">
+        <v>500</v>
+      </c>
+      <c r="D10" s="849" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E10" s="850" t="n">
+        <v>11.60000038146973</v>
+      </c>
+      <c r="F10" s="851">
+        <f>C10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="852">
+        <f>F10-C10*D10</f>
+        <v/>
+      </c>
+      <c r="H10" s="853">
+        <f>(E10-D10)/D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="854" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="J10" s="857" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="K10" s="858" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="872" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="814">
-        <f>SUM(F3:F8)</f>
+      <c r="F11" s="873">
+        <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G9" s="815">
-        <f>SUM(G3:G8)</f>
+      <c r="G11" s="874">
+        <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H9" s="816">
-        <f>G9/SUMPRODUCT(C3:C8,D3:D8)</f>
+      <c r="H11" s="875">
+        <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
     </row>
@@ -3991,14 +4327,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="785" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  08 May 2026</t>
+      <c r="A1" s="844" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  11 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="817" t="inlineStr">
+      <c r="A3" s="876" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -4020,7 +4356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4036,346 +4372,567 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="785" t="inlineStr">
+      <c r="A1" s="844" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="786" t="inlineStr">
+      <c r="A2" s="845" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="786" t="inlineStr">
+      <c r="B2" s="845" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="786" t="inlineStr">
+      <c r="C2" s="845" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="786" t="inlineStr">
+      <c r="D2" s="845" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="786" t="inlineStr">
+      <c r="E2" s="845" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="786" t="inlineStr">
+      <c r="F2" s="845" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="786" t="inlineStr">
+      <c r="G2" s="845" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="786" t="inlineStr">
+      <c r="H2" s="845" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="786" t="inlineStr">
+      <c r="I2" s="845" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="786" t="inlineStr">
+      <c r="J2" s="845" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="818" t="inlineStr">
+      <c r="A3" s="877" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="819" t="inlineStr">
+      <c r="B3" s="878" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="820" t="inlineStr">
+      <c r="C3" s="879" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="821" t="inlineStr">
+      <c r="D3" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="822" t="n">
+      <c r="E3" s="881" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="823" t="n">
+      <c r="F3" s="882" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="822" t="n">
+      <c r="G3" s="881" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="824">
+      <c r="H3" s="883">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="825" t="inlineStr">
+      <c r="I3" s="884" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="826" t="inlineStr">
+      <c r="J3" s="885" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="827" t="inlineStr">
+      <c r="A4" s="886" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="828" t="inlineStr">
+      <c r="B4" s="887" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="803" t="inlineStr">
+      <c r="C4" s="888" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="821" t="inlineStr">
+      <c r="D4" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="804" t="n">
+      <c r="E4" s="889" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="805" t="n">
+      <c r="F4" s="890" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="804" t="n">
+      <c r="G4" s="889" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="807">
+      <c r="H4" s="891">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="829" t="inlineStr">
+      <c r="I4" s="892" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="830" t="inlineStr">
+      <c r="J4" s="893" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="818" t="inlineStr">
+      <c r="A5" s="877" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="819" t="inlineStr">
+      <c r="B5" s="878" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="820" t="inlineStr">
+      <c r="C5" s="879" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="821" t="inlineStr">
+      <c r="D5" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="822" t="n">
+      <c r="E5" s="881" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="823" t="n">
+      <c r="F5" s="882" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="822" t="n">
+      <c r="G5" s="881" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="824">
+      <c r="H5" s="883">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="825" t="inlineStr">
+      <c r="I5" s="884" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="826" t="inlineStr">
+      <c r="J5" s="885" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="827" t="inlineStr">
+      <c r="A6" s="886" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="828" t="inlineStr">
+      <c r="B6" s="887" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="803" t="inlineStr">
+      <c r="C6" s="888" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="821" t="inlineStr">
+      <c r="D6" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="804" t="n">
+      <c r="E6" s="889" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="805" t="n">
+      <c r="F6" s="890" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="804" t="n">
+      <c r="G6" s="889" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="807">
+      <c r="H6" s="891">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="829" t="inlineStr">
+      <c r="I6" s="892" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="830" t="inlineStr">
+      <c r="J6" s="893" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="818" t="inlineStr">
+      <c r="A7" s="877" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="819" t="inlineStr">
+      <c r="B7" s="878" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="820" t="inlineStr">
+      <c r="C7" s="879" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="821" t="inlineStr">
+      <c r="D7" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="822" t="n">
+      <c r="E7" s="881" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="823" t="n">
+      <c r="F7" s="882" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="822" t="n">
+      <c r="G7" s="881" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="824">
+      <c r="H7" s="883">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="825" t="inlineStr">
+      <c r="I7" s="884" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="826" t="inlineStr">
+      <c r="J7" s="885" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="827" t="inlineStr">
+      <c r="A8" s="886" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="828" t="inlineStr">
+      <c r="B8" s="887" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="803" t="inlineStr">
+      <c r="C8" s="888" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="821" t="inlineStr">
+      <c r="D8" s="880" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="804" t="n">
+      <c r="E8" s="889" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="805" t="n">
+      <c r="F8" s="890" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="804" t="n">
+      <c r="G8" s="889" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="807">
+      <c r="H8" s="891">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="829" t="inlineStr">
+      <c r="I8" s="892" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="830" t="inlineStr">
+      <c r="J8" s="893" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="G10" s="52" t="inlineStr">
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="877" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B9" s="878" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="C9" s="879" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="D9" s="894" t="inlineStr">
+        <is>
+          <t>DIVIDEND</t>
+        </is>
+      </c>
+      <c r="E9" s="881" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F9" s="882" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G9" s="881" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" s="883">
+        <f>E9*F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="895" t="n">
+        <v>1725</v>
+      </c>
+      <c r="J9" s="885" t="inlineStr">
+        <is>
+          <t>Dividend ฿0.7500/share</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="886" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B10" s="887" t="inlineStr">
+        <is>
+          <t>JASIF.BK</t>
+        </is>
+      </c>
+      <c r="C10" s="888" t="inlineStr">
+        <is>
+          <t>JASIF</t>
+        </is>
+      </c>
+      <c r="D10" s="894" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E10" s="889" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F10" s="890" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" s="889" t="n">
+        <v>70</v>
+      </c>
+      <c r="H10" s="891">
+        <f>E10*F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="896" t="n">
+        <v>-234.5</v>
+      </c>
+      <c r="J10" s="893" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="877" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B11" s="878" t="inlineStr">
+        <is>
+          <t>KGI.BK</t>
+        </is>
+      </c>
+      <c r="C11" s="879" t="inlineStr">
+        <is>
+          <t>KGI</t>
+        </is>
+      </c>
+      <c r="D11" s="880" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E11" s="881" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F11" s="882" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="G11" s="881" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="883">
+        <f>E11*F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="884" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="885" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="886" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B12" s="887" t="inlineStr">
+        <is>
+          <t>TU.BK</t>
+        </is>
+      </c>
+      <c r="C12" s="888" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="D12" s="880" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E12" s="889" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" s="890" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G12" s="889" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="891">
+        <f>E12*F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="892" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="893" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="877" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="878" t="inlineStr">
+        <is>
+          <t>BTSGIF.BK</t>
+        </is>
+      </c>
+      <c r="C13" s="879" t="inlineStr">
+        <is>
+          <t>BTSGIF</t>
+        </is>
+      </c>
+      <c r="D13" s="880" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E13" s="881" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F13" s="882" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G13" s="881" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="883">
+        <f>E13*F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="884" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="885" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="G15" s="52" t="inlineStr">
         <is>
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H10" s="831">
-        <f>SUM(H3:H8)</f>
+      <c r="H15" s="897">
+        <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I10" s="831">
-        <f>SUM(I3:I8)</f>
+      <c r="I15" s="897">
+        <f>SUM(I3:I13)</f>
         <v/>
       </c>
     </row>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="898">
+  <cellXfs count="971">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2873,6 +2873,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3259,7 +3478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3339,47 +3558,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="773" t="inlineStr">
+      <c r="A2" s="832" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="774" t="n">
+      <c r="B2" s="833" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="775" t="n">
+      <c r="C2" s="834" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="776" t="n">
+      <c r="D2" s="835" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="777" t="n">
+      <c r="E2" s="836" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="778" t="n">
+      <c r="F2" s="837" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="779" t="n">
+      <c r="G2" s="838" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="780" t="n">
+      <c r="H2" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="781" t="n">
+      <c r="I2" s="840" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="782" t="n">
+      <c r="J2" s="841" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="783" t="n">
+      <c r="K2" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="784" t="n">
+      <c r="L2" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="773" t="inlineStr">
+      <c r="A3" s="832" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -3419,7 +3638,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="773" t="inlineStr">
+      <c r="A4" s="832" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -3459,207 +3678,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="773" t="inlineStr">
+      <c r="A5" s="832" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="774" t="n">
+      <c r="B5" s="833" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="775" t="n">
+      <c r="C5" s="834" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="776" t="n">
+      <c r="D5" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="777" t="n">
+      <c r="E5" s="836" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="778" t="n">
+      <c r="F5" s="837" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="779" t="n">
+      <c r="G5" s="838" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="780" t="n">
+      <c r="H5" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="781" t="n">
+      <c r="I5" s="840" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="782" t="n">
+      <c r="J5" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="783" t="n">
+      <c r="K5" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="784" t="n">
+      <c r="L5" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="773" t="inlineStr">
+      <c r="A6" s="832" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="774" t="n">
+      <c r="B6" s="833" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="775" t="n">
+      <c r="C6" s="834" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="776" t="n">
+      <c r="D6" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="777" t="n">
+      <c r="E6" s="836" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="778" t="n">
+      <c r="F6" s="837" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="779" t="n">
+      <c r="G6" s="838" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="780" t="n">
+      <c r="H6" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="781" t="n">
+      <c r="I6" s="840" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="782" t="n">
+      <c r="J6" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="783" t="n">
+      <c r="K6" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="784" t="n">
+      <c r="L6" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="773" t="inlineStr">
+      <c r="A7" s="832" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="774" t="n">
+      <c r="B7" s="833" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="775" t="n">
+      <c r="C7" s="834" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="776" t="n">
+      <c r="D7" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="777" t="n">
+      <c r="E7" s="836" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="778" t="n">
+      <c r="F7" s="837" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="779" t="n">
+      <c r="G7" s="838" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="780" t="n">
+      <c r="H7" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="781" t="n">
+      <c r="I7" s="840" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="782" t="n">
+      <c r="J7" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="783" t="n">
+      <c r="K7" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="784" t="n">
+      <c r="L7" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="773" t="inlineStr">
+      <c r="A8" s="832" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="774" t="n">
+      <c r="B8" s="833" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="775" t="n">
+      <c r="C8" s="834" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="776" t="n">
+      <c r="D8" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="777" t="n">
+      <c r="E8" s="836" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="778" t="n">
+      <c r="F8" s="837" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="779" t="n">
+      <c r="G8" s="838" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="780" t="n">
+      <c r="H8" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="781" t="n">
+      <c r="I8" s="840" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="782" t="n">
+      <c r="J8" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="783" t="n">
+      <c r="K8" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="784" t="n">
+      <c r="L8" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="773" t="inlineStr">
+      <c r="A9" s="832" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="774" t="n">
+      <c r="B9" s="833" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="775" t="n">
+      <c r="C9" s="834" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="776" t="n">
+      <c r="D9" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="777" t="n">
+      <c r="E9" s="836" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="778" t="n">
+      <c r="F9" s="837" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="779" t="n">
+      <c r="G9" s="838" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="780" t="n">
+      <c r="H9" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="781" t="n">
+      <c r="I9" s="840" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="782" t="n">
+      <c r="J9" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="783" t="n">
+      <c r="K9" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="784" t="n">
+      <c r="L9" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="773" t="inlineStr">
+      <c r="A10" s="832" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -3699,82 +3918,82 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="773" t="inlineStr">
+      <c r="A11" s="832" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="774" t="n">
+      <c r="B11" s="833" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="775" t="n">
+      <c r="C11" s="834" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="776" t="n">
+      <c r="D11" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="777" t="n">
+      <c r="E11" s="836" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="778" t="n">
+      <c r="F11" s="837" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="779" t="n">
+      <c r="G11" s="838" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="780" t="n">
+      <c r="H11" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="781" t="n">
+      <c r="I11" s="840" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="782" t="n">
+      <c r="J11" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="783" t="n">
+      <c r="K11" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="784" t="n">
+      <c r="L11" s="843" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="773" t="inlineStr">
+      <c r="A12" s="832" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="774" t="n">
+      <c r="B12" s="833" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="775" t="n">
+      <c r="C12" s="834" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="776" t="n">
+      <c r="D12" s="835" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="777" t="n">
+      <c r="E12" s="836" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="778" t="n">
+      <c r="F12" s="837" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="779" t="n">
+      <c r="G12" s="838" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="780" t="n">
+      <c r="H12" s="839" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="781" t="n">
+      <c r="I12" s="840" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="782" t="n">
+      <c r="J12" s="841" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="783" t="n">
+      <c r="K12" s="842" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="784" t="n">
+      <c r="L12" s="843" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3815,6 +4034,46 @@
         <v>0</v>
       </c>
       <c r="L13" s="843" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="898" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B14" s="899" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="900" t="n">
+        <v>304964.1755083799</v>
+      </c>
+      <c r="D14" s="901" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E14" s="902" t="n">
+        <v>256233.9985609055</v>
+      </c>
+      <c r="F14" s="903" t="n">
+        <v>4964.175508379936</v>
+      </c>
+      <c r="G14" s="904" t="n">
+        <v>0.01654725169459979</v>
+      </c>
+      <c r="H14" s="905" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="906" t="n">
+        <v>-0.0212577074499438</v>
+      </c>
+      <c r="J14" s="907" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="908" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="909" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3847,452 +4106,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="844" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  11 May 2026</t>
+      <c r="A1" s="910" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  12 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="845" t="inlineStr">
+      <c r="A2" s="911" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="845" t="inlineStr">
+      <c r="B2" s="911" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="845" t="inlineStr">
+      <c r="C2" s="911" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="845" t="inlineStr">
+      <c r="D2" s="911" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="845" t="inlineStr">
+      <c r="E2" s="911" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="845" t="inlineStr">
+      <c r="F2" s="911" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="845" t="inlineStr">
+      <c r="G2" s="911" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="845" t="inlineStr">
+      <c r="H2" s="911" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="845" t="inlineStr">
+      <c r="I2" s="911" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="845" t="inlineStr">
+      <c r="J2" s="911" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="845" t="inlineStr">
+      <c r="K2" s="911" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="846" t="inlineStr">
+      <c r="A3" s="912" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="847" t="inlineStr">
+      <c r="B3" s="913" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="848" t="n">
+      <c r="C3" s="914" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="849" t="n">
+      <c r="D3" s="915" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="850" t="n">
-        <v>18.89999961853027</v>
-      </c>
-      <c r="F3" s="851">
+      <c r="E3" s="916" t="n">
+        <v>17.89999961853027</v>
+      </c>
+      <c r="F3" s="917">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="852">
+      <c r="G3" s="918">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="853">
+      <c r="H3" s="919">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="854" t="inlineStr">
+      <c r="I3" s="920" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="855" t="n">
+      <c r="J3" s="921" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="856" t="inlineStr">
+      <c r="K3" s="922" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="846" t="inlineStr">
+      <c r="A4" s="912" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="847" t="inlineStr">
+      <c r="B4" s="913" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="848" t="n">
+      <c r="C4" s="914" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="849" t="n">
+      <c r="D4" s="915" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="850" t="n">
-        <v>4.55620002746582</v>
-      </c>
-      <c r="F4" s="851">
+      <c r="E4" s="916" t="n">
+        <v>4.539999961853027</v>
+      </c>
+      <c r="F4" s="917">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="852">
+      <c r="G4" s="918">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="853">
+      <c r="H4" s="919">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="854" t="inlineStr">
+      <c r="I4" s="920" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="857" t="n">
+      <c r="J4" s="923" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="858" t="inlineStr">
+      <c r="K4" s="924" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="846" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="847" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C5" s="848" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D5" s="849" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E5" s="850" t="n">
-        <v>20.79999923706055</v>
-      </c>
-      <c r="F5" s="851">
+      <c r="A5" s="912" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="913" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C5" s="914" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D5" s="915" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E5" s="916" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F5" s="917">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="852">
+      <c r="G5" s="918">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="853">
+      <c r="H5" s="919">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="854" t="inlineStr">
+      <c r="I5" s="920" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="859" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K5" s="860" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J5" s="923" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K5" s="924" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="846" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="847" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C6" s="848" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D6" s="849" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E6" s="850" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="F6" s="851">
+      <c r="A6" s="925" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="926" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C6" s="927" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D6" s="928" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E6" s="929" t="n">
+        <v>20.29999923706055</v>
+      </c>
+      <c r="F6" s="930">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="852">
+      <c r="G6" s="931">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="853">
+      <c r="H6" s="932">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="854" t="inlineStr">
+      <c r="I6" s="933" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="857" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="K6" s="858" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J6" s="934" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K6" s="935" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="861" t="inlineStr">
+      <c r="A7" s="936" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="862" t="inlineStr">
+      <c r="B7" s="937" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="863" t="n">
+      <c r="C7" s="938" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="864" t="n">
+      <c r="D7" s="939" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="865" t="n">
-        <v>17</v>
-      </c>
-      <c r="F7" s="866">
+      <c r="E7" s="940" t="n">
+        <v>16.70000076293945</v>
+      </c>
+      <c r="F7" s="941">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="867">
+      <c r="G7" s="942">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="868">
+      <c r="H7" s="943">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="869" t="inlineStr">
+      <c r="I7" s="944" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="870" t="n">
+      <c r="J7" s="945" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="871" t="inlineStr">
+      <c r="K7" s="946" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="846" t="inlineStr">
+      <c r="A8" s="925" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="847" t="inlineStr">
+      <c r="B8" s="926" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="848" t="n">
+      <c r="C8" s="927" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="849" t="n">
+      <c r="D8" s="928" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="850" t="n">
-        <v>4.28000020980835</v>
-      </c>
-      <c r="F8" s="851">
+      <c r="E8" s="929" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F8" s="930">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="852">
+      <c r="G8" s="931">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="853">
+      <c r="H8" s="932">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="854" t="inlineStr">
+      <c r="I8" s="933" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="857" t="n">
+      <c r="J8" s="947" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="858" t="inlineStr">
+      <c r="K8" s="948" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="846" t="inlineStr">
+      <c r="A9" s="912" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="847" t="inlineStr">
+      <c r="B9" s="913" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="848" t="n">
+      <c r="C9" s="914" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="849" t="n">
+      <c r="D9" s="915" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="850" t="n">
+      <c r="E9" s="916" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="851">
+      <c r="F9" s="917">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="852">
+      <c r="G9" s="918">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="853">
+      <c r="H9" s="919">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="854" t="inlineStr">
+      <c r="I9" s="920" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="857" t="n">
+      <c r="J9" s="923" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="858" t="inlineStr">
+      <c r="K9" s="924" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="846" t="inlineStr">
+      <c r="A10" s="925" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="847" t="inlineStr">
+      <c r="B10" s="926" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="848" t="n">
+      <c r="C10" s="927" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="849" t="n">
+      <c r="D10" s="928" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="850" t="n">
-        <v>11.60000038146973</v>
-      </c>
-      <c r="F10" s="851">
+      <c r="E10" s="929" t="n">
+        <v>11.39999961853027</v>
+      </c>
+      <c r="F10" s="930">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="852">
+      <c r="G10" s="931">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="853">
+      <c r="H10" s="932">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="854" t="inlineStr">
+      <c r="I10" s="933" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="857" t="n">
+      <c r="J10" s="947" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="858" t="inlineStr">
+      <c r="K10" s="948" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="872" t="inlineStr">
+      <c r="B11" s="949" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="873">
+      <c r="F11" s="950">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="874">
+      <c r="G11" s="951">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="875">
+      <c r="H11" s="952">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -4327,14 +4586,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="844" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  11 May 2026</t>
+      <c r="A1" s="910" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  12 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="876" t="inlineStr">
+      <c r="A3" s="953" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -4372,550 +4631,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="844" t="inlineStr">
+      <c r="A1" s="910" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="845" t="inlineStr">
+      <c r="A2" s="911" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="845" t="inlineStr">
+      <c r="B2" s="911" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="845" t="inlineStr">
+      <c r="C2" s="911" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="845" t="inlineStr">
+      <c r="D2" s="911" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="845" t="inlineStr">
+      <c r="E2" s="911" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="845" t="inlineStr">
+      <c r="F2" s="911" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="845" t="inlineStr">
+      <c r="G2" s="911" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="845" t="inlineStr">
+      <c r="H2" s="911" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="845" t="inlineStr">
+      <c r="I2" s="911" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="845" t="inlineStr">
+      <c r="J2" s="911" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="877" t="inlineStr">
+      <c r="A3" s="954" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="878" t="inlineStr">
+      <c r="B3" s="955" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="879" t="inlineStr">
+      <c r="C3" s="956" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="880" t="inlineStr">
+      <c r="D3" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="881" t="n">
+      <c r="E3" s="958" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="882" t="n">
+      <c r="F3" s="959" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="881" t="n">
+      <c r="G3" s="958" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="883">
+      <c r="H3" s="960">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="884" t="inlineStr">
+      <c r="I3" s="961" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="885" t="inlineStr">
+      <c r="J3" s="962" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="886" t="inlineStr">
+      <c r="A4" s="963" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="887" t="inlineStr">
+      <c r="B4" s="964" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="888" t="inlineStr">
+      <c r="C4" s="926" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="880" t="inlineStr">
+      <c r="D4" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="889" t="n">
+      <c r="E4" s="927" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="890" t="n">
+      <c r="F4" s="928" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="889" t="n">
+      <c r="G4" s="927" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="891">
+      <c r="H4" s="930">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="892" t="inlineStr">
+      <c r="I4" s="965" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="893" t="inlineStr">
+      <c r="J4" s="966" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="877" t="inlineStr">
+      <c r="A5" s="954" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="878" t="inlineStr">
+      <c r="B5" s="955" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="879" t="inlineStr">
+      <c r="C5" s="956" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="880" t="inlineStr">
+      <c r="D5" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="881" t="n">
+      <c r="E5" s="958" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="882" t="n">
+      <c r="F5" s="959" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="881" t="n">
+      <c r="G5" s="958" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="883">
+      <c r="H5" s="960">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="884" t="inlineStr">
+      <c r="I5" s="961" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="885" t="inlineStr">
+      <c r="J5" s="962" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="886" t="inlineStr">
+      <c r="A6" s="963" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="887" t="inlineStr">
+      <c r="B6" s="964" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="888" t="inlineStr">
+      <c r="C6" s="926" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="880" t="inlineStr">
+      <c r="D6" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="889" t="n">
+      <c r="E6" s="927" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="890" t="n">
+      <c r="F6" s="928" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="889" t="n">
+      <c r="G6" s="927" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="891">
+      <c r="H6" s="930">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="892" t="inlineStr">
+      <c r="I6" s="965" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="893" t="inlineStr">
+      <c r="J6" s="966" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="877" t="inlineStr">
+      <c r="A7" s="954" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="878" t="inlineStr">
+      <c r="B7" s="955" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="879" t="inlineStr">
+      <c r="C7" s="956" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="880" t="inlineStr">
+      <c r="D7" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="881" t="n">
+      <c r="E7" s="958" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="882" t="n">
+      <c r="F7" s="959" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="881" t="n">
+      <c r="G7" s="958" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="883">
+      <c r="H7" s="960">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="884" t="inlineStr">
+      <c r="I7" s="961" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="885" t="inlineStr">
+      <c r="J7" s="962" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="886" t="inlineStr">
+      <c r="A8" s="963" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="887" t="inlineStr">
+      <c r="B8" s="964" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="888" t="inlineStr">
+      <c r="C8" s="926" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="880" t="inlineStr">
+      <c r="D8" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="889" t="n">
+      <c r="E8" s="927" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="890" t="n">
+      <c r="F8" s="928" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="889" t="n">
+      <c r="G8" s="927" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="891">
+      <c r="H8" s="930">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="892" t="inlineStr">
+      <c r="I8" s="965" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="893" t="inlineStr">
+      <c r="J8" s="966" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="877" t="inlineStr">
+      <c r="A9" s="954" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="878" t="inlineStr">
+      <c r="B9" s="955" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="879" t="inlineStr">
+      <c r="C9" s="956" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="894" t="inlineStr">
+      <c r="D9" s="967" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="881" t="n">
+      <c r="E9" s="958" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="882" t="n">
+      <c r="F9" s="959" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="881" t="n">
+      <c r="G9" s="958" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="883">
+      <c r="H9" s="960">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="895" t="n">
+      <c r="I9" s="968" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="885" t="inlineStr">
+      <c r="J9" s="962" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="886" t="inlineStr">
+      <c r="A10" s="963" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="887" t="inlineStr">
+      <c r="B10" s="964" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="888" t="inlineStr">
+      <c r="C10" s="926" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="894" t="inlineStr">
+      <c r="D10" s="967" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="889" t="n">
+      <c r="E10" s="927" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="890" t="n">
+      <c r="F10" s="928" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="889" t="n">
+      <c r="G10" s="927" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="891">
+      <c r="H10" s="930">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="896" t="n">
+      <c r="I10" s="969" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="893" t="inlineStr">
+      <c r="J10" s="966" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="877" t="inlineStr">
+      <c r="A11" s="954" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="878" t="inlineStr">
+      <c r="B11" s="955" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="879" t="inlineStr">
+      <c r="C11" s="956" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="880" t="inlineStr">
+      <c r="D11" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="881" t="n">
+      <c r="E11" s="958" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="882" t="n">
+      <c r="F11" s="959" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="881" t="n">
+      <c r="G11" s="958" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="883">
+      <c r="H11" s="960">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="884" t="inlineStr">
+      <c r="I11" s="961" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="885" t="inlineStr">
+      <c r="J11" s="962" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="886" t="inlineStr">
+      <c r="A12" s="963" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="887" t="inlineStr">
+      <c r="B12" s="964" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="888" t="inlineStr">
+      <c r="C12" s="926" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="880" t="inlineStr">
+      <c r="D12" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="889" t="n">
+      <c r="E12" s="927" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="890" t="n">
+      <c r="F12" s="928" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="889" t="n">
+      <c r="G12" s="927" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="891">
+      <c r="H12" s="930">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="892" t="inlineStr">
+      <c r="I12" s="965" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="893" t="inlineStr">
+      <c r="J12" s="966" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="877" t="inlineStr">
+      <c r="A13" s="954" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="878" t="inlineStr">
+      <c r="B13" s="955" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="879" t="inlineStr">
+      <c r="C13" s="956" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="880" t="inlineStr">
+      <c r="D13" s="957" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="881" t="n">
+      <c r="E13" s="958" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="882" t="n">
+      <c r="F13" s="959" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="881" t="n">
+      <c r="G13" s="958" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="883">
+      <c r="H13" s="960">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="884" t="inlineStr">
+      <c r="I13" s="961" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="885" t="inlineStr">
+      <c r="J13" s="962" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -4927,11 +5186,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="897">
+      <c r="H15" s="970">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="897">
+      <c r="I15" s="970">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="971">
+  <cellXfs count="1044">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2873,6 +2873,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3478,7 +3697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3558,47 +3777,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="832" t="inlineStr">
+      <c r="A2" s="898" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="833" t="n">
+      <c r="B2" s="899" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="834" t="n">
+      <c r="C2" s="900" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="835" t="n">
+      <c r="D2" s="901" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="836" t="n">
+      <c r="E2" s="902" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="837" t="n">
+      <c r="F2" s="903" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="838" t="n">
+      <c r="G2" s="904" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="839" t="n">
+      <c r="H2" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="840" t="n">
+      <c r="I2" s="906" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="841" t="n">
+      <c r="J2" s="907" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="842" t="n">
+      <c r="K2" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="843" t="n">
+      <c r="L2" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="832" t="inlineStr">
+      <c r="A3" s="898" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -3638,7 +3857,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="832" t="inlineStr">
+      <c r="A4" s="898" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -3678,207 +3897,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="832" t="inlineStr">
+      <c r="A5" s="898" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="833" t="n">
+      <c r="B5" s="899" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="834" t="n">
+      <c r="C5" s="900" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="835" t="n">
+      <c r="D5" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="836" t="n">
+      <c r="E5" s="902" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="837" t="n">
+      <c r="F5" s="903" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="838" t="n">
+      <c r="G5" s="904" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="839" t="n">
+      <c r="H5" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="840" t="n">
+      <c r="I5" s="906" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="841" t="n">
+      <c r="J5" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="842" t="n">
+      <c r="K5" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="843" t="n">
+      <c r="L5" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="832" t="inlineStr">
+      <c r="A6" s="898" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="833" t="n">
+      <c r="B6" s="899" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="834" t="n">
+      <c r="C6" s="900" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="835" t="n">
+      <c r="D6" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="836" t="n">
+      <c r="E6" s="902" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="837" t="n">
+      <c r="F6" s="903" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="838" t="n">
+      <c r="G6" s="904" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="839" t="n">
+      <c r="H6" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="840" t="n">
+      <c r="I6" s="906" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="841" t="n">
+      <c r="J6" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="842" t="n">
+      <c r="K6" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="843" t="n">
+      <c r="L6" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="832" t="inlineStr">
+      <c r="A7" s="898" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="833" t="n">
+      <c r="B7" s="899" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="834" t="n">
+      <c r="C7" s="900" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="835" t="n">
+      <c r="D7" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="836" t="n">
+      <c r="E7" s="902" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="837" t="n">
+      <c r="F7" s="903" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="838" t="n">
+      <c r="G7" s="904" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="839" t="n">
+      <c r="H7" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="840" t="n">
+      <c r="I7" s="906" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="841" t="n">
+      <c r="J7" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="842" t="n">
+      <c r="K7" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="843" t="n">
+      <c r="L7" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="832" t="inlineStr">
+      <c r="A8" s="898" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="833" t="n">
+      <c r="B8" s="899" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="834" t="n">
+      <c r="C8" s="900" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="835" t="n">
+      <c r="D8" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="836" t="n">
+      <c r="E8" s="902" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="837" t="n">
+      <c r="F8" s="903" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="838" t="n">
+      <c r="G8" s="904" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="839" t="n">
+      <c r="H8" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="840" t="n">
+      <c r="I8" s="906" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="841" t="n">
+      <c r="J8" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="842" t="n">
+      <c r="K8" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="843" t="n">
+      <c r="L8" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="832" t="inlineStr">
+      <c r="A9" s="898" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="833" t="n">
+      <c r="B9" s="899" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="834" t="n">
+      <c r="C9" s="900" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="835" t="n">
+      <c r="D9" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="836" t="n">
+      <c r="E9" s="902" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="837" t="n">
+      <c r="F9" s="903" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="838" t="n">
+      <c r="G9" s="904" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="839" t="n">
+      <c r="H9" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="840" t="n">
+      <c r="I9" s="906" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="841" t="n">
+      <c r="J9" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="842" t="n">
+      <c r="K9" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="843" t="n">
+      <c r="L9" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="832" t="inlineStr">
+      <c r="A10" s="898" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -3918,122 +4137,122 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="832" t="inlineStr">
+      <c r="A11" s="898" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="833" t="n">
+      <c r="B11" s="899" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="834" t="n">
+      <c r="C11" s="900" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="835" t="n">
+      <c r="D11" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="836" t="n">
+      <c r="E11" s="902" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="837" t="n">
+      <c r="F11" s="903" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="838" t="n">
+      <c r="G11" s="904" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="839" t="n">
+      <c r="H11" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="840" t="n">
+      <c r="I11" s="906" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="841" t="n">
+      <c r="J11" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="842" t="n">
+      <c r="K11" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="843" t="n">
+      <c r="L11" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="832" t="inlineStr">
+      <c r="A12" s="898" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="833" t="n">
+      <c r="B12" s="899" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="834" t="n">
+      <c r="C12" s="900" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="835" t="n">
+      <c r="D12" s="901" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="836" t="n">
+      <c r="E12" s="902" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="837" t="n">
+      <c r="F12" s="903" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="838" t="n">
+      <c r="G12" s="904" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="839" t="n">
+      <c r="H12" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="840" t="n">
+      <c r="I12" s="906" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="841" t="n">
+      <c r="J12" s="907" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="842" t="n">
+      <c r="K12" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="843" t="n">
+      <c r="L12" s="909" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="832" t="inlineStr">
+      <c r="A13" s="898" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="833" t="n">
+      <c r="B13" s="899" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="834" t="n">
+      <c r="C13" s="900" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="835" t="n">
+      <c r="D13" s="901" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="836" t="n">
+      <c r="E13" s="902" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="837" t="n">
+      <c r="F13" s="903" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="838" t="n">
+      <c r="G13" s="904" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="839" t="n">
+      <c r="H13" s="905" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="840" t="n">
+      <c r="I13" s="906" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="841" t="n">
+      <c r="J13" s="907" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="842" t="n">
+      <c r="K13" s="908" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="843" t="n">
+      <c r="L13" s="909" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4074,6 +4293,46 @@
         <v>0</v>
       </c>
       <c r="L14" s="909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="971" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B15" s="972" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="973" t="n">
+        <v>302514.1766527891</v>
+      </c>
+      <c r="D15" s="974" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E15" s="975" t="n">
+        <v>253783.9997053146</v>
+      </c>
+      <c r="F15" s="976" t="n">
+        <v>2514.176652789116</v>
+      </c>
+      <c r="G15" s="977" t="n">
+        <v>0.008380588842630387</v>
+      </c>
+      <c r="H15" s="978" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="979" t="n">
+        <v>-0.0291206555902249</v>
+      </c>
+      <c r="J15" s="980" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="981" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="982" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4106,452 +4365,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="910" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  12 May 2026</t>
+      <c r="A1" s="983" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  13 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="911" t="inlineStr">
+      <c r="A2" s="984" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="911" t="inlineStr">
+      <c r="B2" s="984" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="911" t="inlineStr">
+      <c r="C2" s="984" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="911" t="inlineStr">
+      <c r="D2" s="984" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="911" t="inlineStr">
+      <c r="E2" s="984" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="911" t="inlineStr">
+      <c r="F2" s="984" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="911" t="inlineStr">
+      <c r="G2" s="984" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="911" t="inlineStr">
+      <c r="H2" s="984" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="911" t="inlineStr">
+      <c r="I2" s="984" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="911" t="inlineStr">
+      <c r="J2" s="984" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="911" t="inlineStr">
+      <c r="K2" s="984" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="912" t="inlineStr">
+      <c r="A3" s="985" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="913" t="inlineStr">
+      <c r="B3" s="986" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="914" t="n">
+      <c r="C3" s="987" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="915" t="n">
+      <c r="D3" s="988" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="916" t="n">
-        <v>17.89999961853027</v>
-      </c>
-      <c r="F3" s="917">
+      <c r="E3" s="989" t="n">
+        <v>17.70000076293945</v>
+      </c>
+      <c r="F3" s="990">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="918">
+      <c r="G3" s="991">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="919">
+      <c r="H3" s="992">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="920" t="inlineStr">
+      <c r="I3" s="993" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="921" t="n">
+      <c r="J3" s="994" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="922" t="inlineStr">
+      <c r="K3" s="995" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="912" t="inlineStr">
+      <c r="A4" s="985" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="913" t="inlineStr">
+      <c r="B4" s="986" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="914" t="n">
+      <c r="C4" s="987" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="915" t="n">
+      <c r="D4" s="988" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="916" t="n">
-        <v>4.539999961853027</v>
-      </c>
-      <c r="F4" s="917">
+      <c r="E4" s="989" t="n">
+        <v>4.440000057220459</v>
+      </c>
+      <c r="F4" s="990">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="918">
+      <c r="G4" s="991">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="919">
+      <c r="H4" s="992">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="920" t="inlineStr">
+      <c r="I4" s="993" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="923" t="n">
+      <c r="J4" s="996" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="924" t="inlineStr">
+      <c r="K4" s="997" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="912" t="inlineStr">
+      <c r="A5" s="985" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B5" s="913" t="inlineStr">
+      <c r="B5" s="986" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C5" s="914" t="n">
+      <c r="C5" s="987" t="n">
         <v>1600</v>
       </c>
-      <c r="D5" s="915" t="n">
+      <c r="D5" s="988" t="n">
         <v>29.25</v>
       </c>
-      <c r="E5" s="916" t="n">
+      <c r="E5" s="989" t="n">
         <v>29.5</v>
       </c>
-      <c r="F5" s="917">
+      <c r="F5" s="990">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="918">
+      <c r="G5" s="991">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="919">
+      <c r="H5" s="992">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="920" t="inlineStr">
+      <c r="I5" s="993" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="923" t="n">
+      <c r="J5" s="996" t="n">
         <v>5.88</v>
       </c>
-      <c r="K5" s="924" t="inlineStr">
+      <c r="K5" s="997" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="925" t="inlineStr">
+      <c r="A6" s="998" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B6" s="926" t="inlineStr">
+      <c r="B6" s="999" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C6" s="927" t="n">
+      <c r="C6" s="1000" t="n">
         <v>2300</v>
       </c>
-      <c r="D6" s="928" t="n">
+      <c r="D6" s="1001" t="n">
         <v>20.3</v>
       </c>
-      <c r="E6" s="929" t="n">
+      <c r="E6" s="1002" t="n">
         <v>20.29999923706055</v>
       </c>
-      <c r="F6" s="930">
+      <c r="F6" s="1003">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="931">
+      <c r="G6" s="1004">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="932">
+      <c r="H6" s="1005">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="933" t="inlineStr">
+      <c r="I6" s="1006" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="934" t="n">
+      <c r="J6" s="1007" t="n">
         <v>7.52</v>
       </c>
-      <c r="K6" s="935" t="inlineStr">
+      <c r="K6" s="1008" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="936" t="inlineStr">
+      <c r="A7" s="1009" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="937" t="inlineStr">
+      <c r="B7" s="1010" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="938" t="n">
+      <c r="C7" s="1011" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="939" t="n">
+      <c r="D7" s="1012" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="940" t="n">
-        <v>16.70000076293945</v>
-      </c>
-      <c r="F7" s="941">
+      <c r="E7" s="1013" t="n">
+        <v>16.39999961853027</v>
+      </c>
+      <c r="F7" s="1014">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="942">
+      <c r="G7" s="1015">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="943">
+      <c r="H7" s="1016">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="944" t="inlineStr">
+      <c r="I7" s="1017" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="945" t="n">
+      <c r="J7" s="1018" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="946" t="inlineStr">
+      <c r="K7" s="1019" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="925" t="inlineStr">
+      <c r="A8" s="998" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="926" t="inlineStr">
+      <c r="B8" s="999" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="927" t="n">
+      <c r="C8" s="1000" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="928" t="n">
+      <c r="D8" s="1001" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="929" t="n">
+      <c r="E8" s="1002" t="n">
         <v>4.21999979019165</v>
       </c>
-      <c r="F8" s="930">
+      <c r="F8" s="1003">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="931">
+      <c r="G8" s="1004">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="932">
+      <c r="H8" s="1005">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="933" t="inlineStr">
+      <c r="I8" s="1006" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="947" t="n">
+      <c r="J8" s="1020" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="948" t="inlineStr">
+      <c r="K8" s="1021" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="912" t="inlineStr">
+      <c r="A9" s="985" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="913" t="inlineStr">
+      <c r="B9" s="986" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="914" t="n">
+      <c r="C9" s="987" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="915" t="n">
+      <c r="D9" s="988" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="916" t="n">
+      <c r="E9" s="989" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="917">
+      <c r="F9" s="990">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="918">
+      <c r="G9" s="991">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="919">
+      <c r="H9" s="992">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="920" t="inlineStr">
+      <c r="I9" s="993" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="923" t="n">
+      <c r="J9" s="996" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="924" t="inlineStr">
+      <c r="K9" s="997" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="925" t="inlineStr">
+      <c r="A10" s="998" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="926" t="inlineStr">
+      <c r="B10" s="999" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="927" t="n">
+      <c r="C10" s="1000" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="928" t="n">
+      <c r="D10" s="1001" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="929" t="n">
+      <c r="E10" s="1002" t="n">
         <v>11.39999961853027</v>
       </c>
-      <c r="F10" s="930">
+      <c r="F10" s="1003">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="931">
+      <c r="G10" s="1004">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="932">
+      <c r="H10" s="1005">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="933" t="inlineStr">
+      <c r="I10" s="1006" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="947" t="n">
+      <c r="J10" s="1020" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="948" t="inlineStr">
+      <c r="K10" s="1021" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="949" t="inlineStr">
+      <c r="B11" s="1022" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="950">
+      <c r="F11" s="1023">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="951">
+      <c r="G11" s="1024">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="952">
+      <c r="H11" s="1025">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -4586,14 +4845,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="910" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  12 May 2026</t>
+      <c r="A1" s="983" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  13 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="953" t="inlineStr">
+      <c r="A3" s="1026" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -4631,550 +4890,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="910" t="inlineStr">
+      <c r="A1" s="983" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="911" t="inlineStr">
+      <c r="A2" s="984" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="911" t="inlineStr">
+      <c r="B2" s="984" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="911" t="inlineStr">
+      <c r="C2" s="984" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="911" t="inlineStr">
+      <c r="D2" s="984" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="911" t="inlineStr">
+      <c r="E2" s="984" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="911" t="inlineStr">
+      <c r="F2" s="984" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="911" t="inlineStr">
+      <c r="G2" s="984" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="911" t="inlineStr">
+      <c r="H2" s="984" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="911" t="inlineStr">
+      <c r="I2" s="984" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="911" t="inlineStr">
+      <c r="J2" s="984" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="954" t="inlineStr">
+      <c r="A3" s="1027" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="955" t="inlineStr">
+      <c r="B3" s="1028" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="956" t="inlineStr">
+      <c r="C3" s="1029" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="957" t="inlineStr">
+      <c r="D3" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="958" t="n">
+      <c r="E3" s="1031" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="959" t="n">
+      <c r="F3" s="1032" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="958" t="n">
+      <c r="G3" s="1031" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="960">
+      <c r="H3" s="1033">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="961" t="inlineStr">
+      <c r="I3" s="1034" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="962" t="inlineStr">
+      <c r="J3" s="1035" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="963" t="inlineStr">
+      <c r="A4" s="1036" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="964" t="inlineStr">
+      <c r="B4" s="1037" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="926" t="inlineStr">
+      <c r="C4" s="999" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="957" t="inlineStr">
+      <c r="D4" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="927" t="n">
+      <c r="E4" s="1000" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="928" t="n">
+      <c r="F4" s="1001" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="927" t="n">
+      <c r="G4" s="1000" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="930">
+      <c r="H4" s="1003">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="965" t="inlineStr">
+      <c r="I4" s="1038" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="966" t="inlineStr">
+      <c r="J4" s="1039" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="954" t="inlineStr">
+      <c r="A5" s="1027" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="955" t="inlineStr">
+      <c r="B5" s="1028" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="956" t="inlineStr">
+      <c r="C5" s="1029" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="957" t="inlineStr">
+      <c r="D5" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="958" t="n">
+      <c r="E5" s="1031" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="959" t="n">
+      <c r="F5" s="1032" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="958" t="n">
+      <c r="G5" s="1031" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="960">
+      <c r="H5" s="1033">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="961" t="inlineStr">
+      <c r="I5" s="1034" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="962" t="inlineStr">
+      <c r="J5" s="1035" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="963" t="inlineStr">
+      <c r="A6" s="1036" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="964" t="inlineStr">
+      <c r="B6" s="1037" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="926" t="inlineStr">
+      <c r="C6" s="999" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="957" t="inlineStr">
+      <c r="D6" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="927" t="n">
+      <c r="E6" s="1000" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="928" t="n">
+      <c r="F6" s="1001" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="927" t="n">
+      <c r="G6" s="1000" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="930">
+      <c r="H6" s="1003">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="965" t="inlineStr">
+      <c r="I6" s="1038" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="966" t="inlineStr">
+      <c r="J6" s="1039" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="954" t="inlineStr">
+      <c r="A7" s="1027" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="955" t="inlineStr">
+      <c r="B7" s="1028" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="956" t="inlineStr">
+      <c r="C7" s="1029" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="957" t="inlineStr">
+      <c r="D7" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="958" t="n">
+      <c r="E7" s="1031" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="959" t="n">
+      <c r="F7" s="1032" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="958" t="n">
+      <c r="G7" s="1031" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="960">
+      <c r="H7" s="1033">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="961" t="inlineStr">
+      <c r="I7" s="1034" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="962" t="inlineStr">
+      <c r="J7" s="1035" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="963" t="inlineStr">
+      <c r="A8" s="1036" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="964" t="inlineStr">
+      <c r="B8" s="1037" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="926" t="inlineStr">
+      <c r="C8" s="999" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="957" t="inlineStr">
+      <c r="D8" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="927" t="n">
+      <c r="E8" s="1000" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="928" t="n">
+      <c r="F8" s="1001" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="927" t="n">
+      <c r="G8" s="1000" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="930">
+      <c r="H8" s="1003">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="965" t="inlineStr">
+      <c r="I8" s="1038" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="966" t="inlineStr">
+      <c r="J8" s="1039" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="954" t="inlineStr">
+      <c r="A9" s="1027" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="955" t="inlineStr">
+      <c r="B9" s="1028" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="956" t="inlineStr">
+      <c r="C9" s="1029" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="967" t="inlineStr">
+      <c r="D9" s="1040" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="958" t="n">
+      <c r="E9" s="1031" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="959" t="n">
+      <c r="F9" s="1032" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="958" t="n">
+      <c r="G9" s="1031" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="960">
+      <c r="H9" s="1033">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="968" t="n">
+      <c r="I9" s="1041" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="962" t="inlineStr">
+      <c r="J9" s="1035" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="963" t="inlineStr">
+      <c r="A10" s="1036" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="964" t="inlineStr">
+      <c r="B10" s="1037" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="926" t="inlineStr">
+      <c r="C10" s="999" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="967" t="inlineStr">
+      <c r="D10" s="1040" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="927" t="n">
+      <c r="E10" s="1000" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="928" t="n">
+      <c r="F10" s="1001" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="927" t="n">
+      <c r="G10" s="1000" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="930">
+      <c r="H10" s="1003">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="969" t="n">
+      <c r="I10" s="1042" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="966" t="inlineStr">
+      <c r="J10" s="1039" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="954" t="inlineStr">
+      <c r="A11" s="1027" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="955" t="inlineStr">
+      <c r="B11" s="1028" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="956" t="inlineStr">
+      <c r="C11" s="1029" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="957" t="inlineStr">
+      <c r="D11" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="958" t="n">
+      <c r="E11" s="1031" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="959" t="n">
+      <c r="F11" s="1032" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="958" t="n">
+      <c r="G11" s="1031" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="960">
+      <c r="H11" s="1033">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="961" t="inlineStr">
+      <c r="I11" s="1034" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="962" t="inlineStr">
+      <c r="J11" s="1035" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="963" t="inlineStr">
+      <c r="A12" s="1036" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="964" t="inlineStr">
+      <c r="B12" s="1037" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="926" t="inlineStr">
+      <c r="C12" s="999" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="957" t="inlineStr">
+      <c r="D12" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="927" t="n">
+      <c r="E12" s="1000" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="928" t="n">
+      <c r="F12" s="1001" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="927" t="n">
+      <c r="G12" s="1000" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="930">
+      <c r="H12" s="1003">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="965" t="inlineStr">
+      <c r="I12" s="1038" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="966" t="inlineStr">
+      <c r="J12" s="1039" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="954" t="inlineStr">
+      <c r="A13" s="1027" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="955" t="inlineStr">
+      <c r="B13" s="1028" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="956" t="inlineStr">
+      <c r="C13" s="1029" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="957" t="inlineStr">
+      <c r="D13" s="1030" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="958" t="n">
+      <c r="E13" s="1031" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="959" t="n">
+      <c r="F13" s="1032" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="958" t="n">
+      <c r="G13" s="1031" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="960">
+      <c r="H13" s="1033">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="961" t="inlineStr">
+      <c r="I13" s="1034" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="962" t="inlineStr">
+      <c r="J13" s="1035" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -5186,11 +5445,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="970">
+      <c r="H15" s="1043">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="970">
+      <c r="I15" s="1043">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1044">
+  <cellXfs count="1117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3257,6 +3257,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3697,7 +3916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3777,47 +3996,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="898" t="inlineStr">
+      <c r="A2" s="971" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="899" t="n">
+      <c r="B2" s="972" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="900" t="n">
+      <c r="C2" s="973" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="901" t="n">
+      <c r="D2" s="974" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="902" t="n">
+      <c r="E2" s="975" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="903" t="n">
+      <c r="F2" s="976" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="904" t="n">
+      <c r="G2" s="977" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="905" t="n">
+      <c r="H2" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="906" t="n">
+      <c r="I2" s="979" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="907" t="n">
+      <c r="J2" s="980" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="908" t="n">
+      <c r="K2" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="909" t="n">
+      <c r="L2" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="898" t="inlineStr">
+      <c r="A3" s="971" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -3857,7 +4076,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="898" t="inlineStr">
+      <c r="A4" s="971" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -3897,207 +4116,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="898" t="inlineStr">
+      <c r="A5" s="971" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="899" t="n">
+      <c r="B5" s="972" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="900" t="n">
+      <c r="C5" s="973" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="901" t="n">
+      <c r="D5" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="902" t="n">
+      <c r="E5" s="975" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="903" t="n">
+      <c r="F5" s="976" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="904" t="n">
+      <c r="G5" s="977" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="905" t="n">
+      <c r="H5" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="906" t="n">
+      <c r="I5" s="979" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="907" t="n">
+      <c r="J5" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="908" t="n">
+      <c r="K5" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="909" t="n">
+      <c r="L5" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="898" t="inlineStr">
+      <c r="A6" s="971" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="899" t="n">
+      <c r="B6" s="972" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="900" t="n">
+      <c r="C6" s="973" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="901" t="n">
+      <c r="D6" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="902" t="n">
+      <c r="E6" s="975" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="903" t="n">
+      <c r="F6" s="976" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="904" t="n">
+      <c r="G6" s="977" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="905" t="n">
+      <c r="H6" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="906" t="n">
+      <c r="I6" s="979" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="907" t="n">
+      <c r="J6" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="908" t="n">
+      <c r="K6" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="909" t="n">
+      <c r="L6" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="898" t="inlineStr">
+      <c r="A7" s="971" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="899" t="n">
+      <c r="B7" s="972" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="900" t="n">
+      <c r="C7" s="973" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="901" t="n">
+      <c r="D7" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="902" t="n">
+      <c r="E7" s="975" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="903" t="n">
+      <c r="F7" s="976" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="904" t="n">
+      <c r="G7" s="977" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="905" t="n">
+      <c r="H7" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="906" t="n">
+      <c r="I7" s="979" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="907" t="n">
+      <c r="J7" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="908" t="n">
+      <c r="K7" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="909" t="n">
+      <c r="L7" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="898" t="inlineStr">
+      <c r="A8" s="971" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="899" t="n">
+      <c r="B8" s="972" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="900" t="n">
+      <c r="C8" s="973" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="901" t="n">
+      <c r="D8" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="902" t="n">
+      <c r="E8" s="975" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="903" t="n">
+      <c r="F8" s="976" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="904" t="n">
+      <c r="G8" s="977" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="905" t="n">
+      <c r="H8" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="906" t="n">
+      <c r="I8" s="979" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="907" t="n">
+      <c r="J8" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="908" t="n">
+      <c r="K8" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="909" t="n">
+      <c r="L8" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="898" t="inlineStr">
+      <c r="A9" s="971" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="899" t="n">
+      <c r="B9" s="972" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="900" t="n">
+      <c r="C9" s="973" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="901" t="n">
+      <c r="D9" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="902" t="n">
+      <c r="E9" s="975" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="903" t="n">
+      <c r="F9" s="976" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="904" t="n">
+      <c r="G9" s="977" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="905" t="n">
+      <c r="H9" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="906" t="n">
+      <c r="I9" s="979" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="907" t="n">
+      <c r="J9" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="908" t="n">
+      <c r="K9" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="909" t="n">
+      <c r="L9" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="898" t="inlineStr">
+      <c r="A10" s="971" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -4137,162 +4356,162 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="898" t="inlineStr">
+      <c r="A11" s="971" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="899" t="n">
+      <c r="B11" s="972" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="900" t="n">
+      <c r="C11" s="973" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="901" t="n">
+      <c r="D11" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="902" t="n">
+      <c r="E11" s="975" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="903" t="n">
+      <c r="F11" s="976" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="904" t="n">
+      <c r="G11" s="977" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="905" t="n">
+      <c r="H11" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="906" t="n">
+      <c r="I11" s="979" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="907" t="n">
+      <c r="J11" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="908" t="n">
+      <c r="K11" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="909" t="n">
+      <c r="L11" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="898" t="inlineStr">
+      <c r="A12" s="971" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="899" t="n">
+      <c r="B12" s="972" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="900" t="n">
+      <c r="C12" s="973" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="901" t="n">
+      <c r="D12" s="974" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="902" t="n">
+      <c r="E12" s="975" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="903" t="n">
+      <c r="F12" s="976" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="904" t="n">
+      <c r="G12" s="977" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="905" t="n">
+      <c r="H12" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="906" t="n">
+      <c r="I12" s="979" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="907" t="n">
+      <c r="J12" s="980" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="908" t="n">
+      <c r="K12" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="909" t="n">
+      <c r="L12" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="898" t="inlineStr">
+      <c r="A13" s="971" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="899" t="n">
+      <c r="B13" s="972" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="900" t="n">
+      <c r="C13" s="973" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="901" t="n">
+      <c r="D13" s="974" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="902" t="n">
+      <c r="E13" s="975" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="903" t="n">
+      <c r="F13" s="976" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="904" t="n">
+      <c r="G13" s="977" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="905" t="n">
+      <c r="H13" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="906" t="n">
+      <c r="I13" s="979" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="907" t="n">
+      <c r="J13" s="980" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="908" t="n">
+      <c r="K13" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="909" t="n">
+      <c r="L13" s="982" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="898" t="inlineStr">
+      <c r="A14" s="971" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="899" t="n">
+      <c r="B14" s="972" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="900" t="n">
+      <c r="C14" s="973" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="901" t="n">
+      <c r="D14" s="974" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="902" t="n">
+      <c r="E14" s="975" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="903" t="n">
+      <c r="F14" s="976" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="904" t="n">
+      <c r="G14" s="977" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="905" t="n">
+      <c r="H14" s="978" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="906" t="n">
+      <c r="I14" s="979" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="907" t="n">
+      <c r="J14" s="980" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="908" t="n">
+      <c r="K14" s="981" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="909" t="n">
+      <c r="L14" s="982" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4333,6 +4552,46 @@
         <v>0</v>
       </c>
       <c r="L15" s="982" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="1044" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B16" s="1045" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1046" t="n">
+        <v>304920.1800802946</v>
+      </c>
+      <c r="D16" s="1047" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E16" s="1048" t="n">
+        <v>256190.0031328201</v>
+      </c>
+      <c r="F16" s="1049" t="n">
+        <v>4920.180080294609</v>
+      </c>
+      <c r="G16" s="1050" t="n">
+        <v>0.0164006002676487</v>
+      </c>
+      <c r="H16" s="1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1052" t="n">
+        <v>-0.02139890497281406</v>
+      </c>
+      <c r="J16" s="1053" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" s="1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4365,452 +4624,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="983" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  13 May 2026</t>
+      <c r="A1" s="1056" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  14 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="984" t="inlineStr">
+      <c r="A2" s="1057" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="984" t="inlineStr">
+      <c r="B2" s="1057" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="984" t="inlineStr">
+      <c r="C2" s="1057" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="984" t="inlineStr">
+      <c r="D2" s="1057" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="984" t="inlineStr">
+      <c r="E2" s="1057" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="984" t="inlineStr">
+      <c r="F2" s="1057" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="984" t="inlineStr">
+      <c r="G2" s="1057" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="984" t="inlineStr">
+      <c r="H2" s="1057" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="984" t="inlineStr">
+      <c r="I2" s="1057" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="984" t="inlineStr">
+      <c r="J2" s="1057" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="984" t="inlineStr">
+      <c r="K2" s="1057" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="985" t="inlineStr">
+      <c r="A3" s="1058" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B3" s="986" t="inlineStr">
+      <c r="B3" s="1059" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C3" s="987" t="n">
+      <c r="C3" s="1060" t="n">
         <v>2800</v>
       </c>
-      <c r="D3" s="988" t="n">
+      <c r="D3" s="1061" t="n">
         <v>16.5</v>
       </c>
-      <c r="E3" s="989" t="n">
+      <c r="E3" s="1062" t="n">
         <v>17.70000076293945</v>
       </c>
-      <c r="F3" s="990">
+      <c r="F3" s="1063">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="991">
+      <c r="G3" s="1064">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="992">
+      <c r="H3" s="1065">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="993" t="inlineStr">
+      <c r="I3" s="1066" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="994" t="n">
+      <c r="J3" s="1067" t="n">
         <v>7.32</v>
       </c>
-      <c r="K3" s="995" t="inlineStr">
+      <c r="K3" s="1068" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="985" t="inlineStr">
+      <c r="A4" s="1058" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="986" t="inlineStr">
+      <c r="B4" s="1059" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="987" t="n">
+      <c r="C4" s="1060" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="988" t="n">
+      <c r="D4" s="1061" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="989" t="n">
-        <v>4.440000057220459</v>
-      </c>
-      <c r="F4" s="990">
+      <c r="E4" s="1062" t="n">
+        <v>4.559999942779541</v>
+      </c>
+      <c r="F4" s="1063">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="991">
+      <c r="G4" s="1064">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="992">
+      <c r="H4" s="1065">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="993" t="inlineStr">
+      <c r="I4" s="1066" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="996" t="n">
+      <c r="J4" s="1069" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="997" t="inlineStr">
+      <c r="K4" s="1070" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="985" t="inlineStr">
+      <c r="A5" s="1058" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B5" s="986" t="inlineStr">
+      <c r="B5" s="1059" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C5" s="987" t="n">
+      <c r="C5" s="1060" t="n">
         <v>1600</v>
       </c>
-      <c r="D5" s="988" t="n">
+      <c r="D5" s="1061" t="n">
         <v>29.25</v>
       </c>
-      <c r="E5" s="989" t="n">
+      <c r="E5" s="1062" t="n">
         <v>29.5</v>
       </c>
-      <c r="F5" s="990">
+      <c r="F5" s="1063">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="991">
+      <c r="G5" s="1064">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="992">
+      <c r="H5" s="1065">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="993" t="inlineStr">
+      <c r="I5" s="1066" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="996" t="n">
+      <c r="J5" s="1069" t="n">
         <v>5.88</v>
       </c>
-      <c r="K5" s="997" t="inlineStr">
+      <c r="K5" s="1070" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="998" t="inlineStr">
+      <c r="A6" s="1058" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B6" s="999" t="inlineStr">
+      <c r="B6" s="1059" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C6" s="1000" t="n">
+      <c r="C6" s="1060" t="n">
         <v>2300</v>
       </c>
-      <c r="D6" s="1001" t="n">
+      <c r="D6" s="1061" t="n">
         <v>20.3</v>
       </c>
-      <c r="E6" s="1002" t="n">
-        <v>20.29999923706055</v>
-      </c>
-      <c r="F6" s="1003">
+      <c r="E6" s="1062" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F6" s="1063">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1004">
+      <c r="G6" s="1064">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1005">
+      <c r="H6" s="1065">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1006" t="inlineStr">
+      <c r="I6" s="1066" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1007" t="n">
+      <c r="J6" s="1071" t="n">
         <v>7.52</v>
       </c>
-      <c r="K6" s="1008" t="inlineStr">
+      <c r="K6" s="1072" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1009" t="inlineStr">
+      <c r="A7" s="1073" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1010" t="inlineStr">
+      <c r="B7" s="1074" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1011" t="n">
+      <c r="C7" s="1075" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1012" t="n">
+      <c r="D7" s="1076" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1013" t="n">
-        <v>16.39999961853027</v>
-      </c>
-      <c r="F7" s="1014">
+      <c r="E7" s="1077" t="n">
+        <v>16.60000038146973</v>
+      </c>
+      <c r="F7" s="1078">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1015">
+      <c r="G7" s="1079">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1016">
+      <c r="H7" s="1080">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1017" t="inlineStr">
+      <c r="I7" s="1081" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1018" t="n">
+      <c r="J7" s="1082" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1019" t="inlineStr">
+      <c r="K7" s="1083" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="998" t="inlineStr">
+      <c r="A8" s="1058" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="999" t="inlineStr">
+      <c r="B8" s="1059" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1000" t="n">
+      <c r="C8" s="1060" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1001" t="n">
+      <c r="D8" s="1061" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1002" t="n">
-        <v>4.21999979019165</v>
-      </c>
-      <c r="F8" s="1003">
+      <c r="E8" s="1062" t="n">
+        <v>4.260000228881836</v>
+      </c>
+      <c r="F8" s="1063">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1004">
+      <c r="G8" s="1064">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1005">
+      <c r="H8" s="1065">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1006" t="inlineStr">
+      <c r="I8" s="1066" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1020" t="n">
+      <c r="J8" s="1069" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1021" t="inlineStr">
+      <c r="K8" s="1070" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="985" t="inlineStr">
+      <c r="A9" s="1058" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="986" t="inlineStr">
+      <c r="B9" s="1059" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="987" t="n">
+      <c r="C9" s="1060" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="988" t="n">
+      <c r="D9" s="1061" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="989" t="n">
+      <c r="E9" s="1062" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="990">
+      <c r="F9" s="1063">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="991">
+      <c r="G9" s="1064">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="992">
+      <c r="H9" s="1065">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="993" t="inlineStr">
+      <c r="I9" s="1066" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="996" t="n">
+      <c r="J9" s="1069" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="997" t="inlineStr">
+      <c r="K9" s="1070" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="998" t="inlineStr">
+      <c r="A10" s="1084" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="999" t="inlineStr">
+      <c r="B10" s="1085" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1000" t="n">
+      <c r="C10" s="1086" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1001" t="n">
+      <c r="D10" s="1087" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1002" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="F10" s="1003">
+      <c r="E10" s="1088" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F10" s="1089">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1004">
+      <c r="G10" s="1090">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1005">
+      <c r="H10" s="1091">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1006" t="inlineStr">
+      <c r="I10" s="1092" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1020" t="n">
+      <c r="J10" s="1093" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1021" t="inlineStr">
+      <c r="K10" s="1094" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1022" t="inlineStr">
+      <c r="B11" s="1095" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1023">
+      <c r="F11" s="1096">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1024">
+      <c r="G11" s="1097">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1025">
+      <c r="H11" s="1098">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -4845,14 +5104,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="983" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  13 May 2026</t>
+      <c r="A1" s="1056" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  14 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1026" t="inlineStr">
+      <c r="A3" s="1099" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -4890,550 +5149,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="983" t="inlineStr">
+      <c r="A1" s="1056" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="984" t="inlineStr">
+      <c r="A2" s="1057" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="984" t="inlineStr">
+      <c r="B2" s="1057" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="984" t="inlineStr">
+      <c r="C2" s="1057" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="984" t="inlineStr">
+      <c r="D2" s="1057" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="984" t="inlineStr">
+      <c r="E2" s="1057" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="984" t="inlineStr">
+      <c r="F2" s="1057" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="984" t="inlineStr">
+      <c r="G2" s="1057" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="984" t="inlineStr">
+      <c r="H2" s="1057" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="984" t="inlineStr">
+      <c r="I2" s="1057" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="984" t="inlineStr">
+      <c r="J2" s="1057" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1027" t="inlineStr">
+      <c r="A3" s="1100" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1028" t="inlineStr">
+      <c r="B3" s="1101" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1029" t="inlineStr">
+      <c r="C3" s="1102" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1030" t="inlineStr">
+      <c r="D3" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1031" t="n">
+      <c r="E3" s="1104" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1032" t="n">
+      <c r="F3" s="1105" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1031" t="n">
+      <c r="G3" s="1104" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1033">
+      <c r="H3" s="1106">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1034" t="inlineStr">
+      <c r="I3" s="1107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1035" t="inlineStr">
+      <c r="J3" s="1108" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1036" t="inlineStr">
+      <c r="A4" s="1109" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1037" t="inlineStr">
+      <c r="B4" s="1110" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="999" t="inlineStr">
+      <c r="C4" s="1085" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1030" t="inlineStr">
+      <c r="D4" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1000" t="n">
+      <c r="E4" s="1086" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1001" t="n">
+      <c r="F4" s="1087" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1000" t="n">
+      <c r="G4" s="1086" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1003">
+      <c r="H4" s="1089">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1038" t="inlineStr">
+      <c r="I4" s="1111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1039" t="inlineStr">
+      <c r="J4" s="1112" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1027" t="inlineStr">
+      <c r="A5" s="1100" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1028" t="inlineStr">
+      <c r="B5" s="1101" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1029" t="inlineStr">
+      <c r="C5" s="1102" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1030" t="inlineStr">
+      <c r="D5" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1031" t="n">
+      <c r="E5" s="1104" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1032" t="n">
+      <c r="F5" s="1105" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1031" t="n">
+      <c r="G5" s="1104" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1033">
+      <c r="H5" s="1106">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1034" t="inlineStr">
+      <c r="I5" s="1107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1035" t="inlineStr">
+      <c r="J5" s="1108" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1036" t="inlineStr">
+      <c r="A6" s="1109" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1037" t="inlineStr">
+      <c r="B6" s="1110" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="999" t="inlineStr">
+      <c r="C6" s="1085" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1030" t="inlineStr">
+      <c r="D6" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1000" t="n">
+      <c r="E6" s="1086" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1001" t="n">
+      <c r="F6" s="1087" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1000" t="n">
+      <c r="G6" s="1086" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1003">
+      <c r="H6" s="1089">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1038" t="inlineStr">
+      <c r="I6" s="1111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1039" t="inlineStr">
+      <c r="J6" s="1112" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1027" t="inlineStr">
+      <c r="A7" s="1100" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1028" t="inlineStr">
+      <c r="B7" s="1101" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1029" t="inlineStr">
+      <c r="C7" s="1102" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1030" t="inlineStr">
+      <c r="D7" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1031" t="n">
+      <c r="E7" s="1104" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1032" t="n">
+      <c r="F7" s="1105" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1031" t="n">
+      <c r="G7" s="1104" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1033">
+      <c r="H7" s="1106">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1034" t="inlineStr">
+      <c r="I7" s="1107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1035" t="inlineStr">
+      <c r="J7" s="1108" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1036" t="inlineStr">
+      <c r="A8" s="1109" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1037" t="inlineStr">
+      <c r="B8" s="1110" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="999" t="inlineStr">
+      <c r="C8" s="1085" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1030" t="inlineStr">
+      <c r="D8" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1000" t="n">
+      <c r="E8" s="1086" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1001" t="n">
+      <c r="F8" s="1087" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1000" t="n">
+      <c r="G8" s="1086" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1003">
+      <c r="H8" s="1089">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1038" t="inlineStr">
+      <c r="I8" s="1111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1039" t="inlineStr">
+      <c r="J8" s="1112" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1027" t="inlineStr">
+      <c r="A9" s="1100" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1028" t="inlineStr">
+      <c r="B9" s="1101" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1029" t="inlineStr">
+      <c r="C9" s="1102" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1040" t="inlineStr">
+      <c r="D9" s="1113" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1031" t="n">
+      <c r="E9" s="1104" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1032" t="n">
+      <c r="F9" s="1105" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1031" t="n">
+      <c r="G9" s="1104" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1033">
+      <c r="H9" s="1106">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1041" t="n">
+      <c r="I9" s="1114" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1035" t="inlineStr">
+      <c r="J9" s="1108" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1036" t="inlineStr">
+      <c r="A10" s="1109" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1037" t="inlineStr">
+      <c r="B10" s="1110" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="999" t="inlineStr">
+      <c r="C10" s="1085" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1040" t="inlineStr">
+      <c r="D10" s="1113" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1000" t="n">
+      <c r="E10" s="1086" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1001" t="n">
+      <c r="F10" s="1087" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1000" t="n">
+      <c r="G10" s="1086" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1003">
+      <c r="H10" s="1089">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1042" t="n">
+      <c r="I10" s="1115" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1039" t="inlineStr">
+      <c r="J10" s="1112" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1027" t="inlineStr">
+      <c r="A11" s="1100" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1028" t="inlineStr">
+      <c r="B11" s="1101" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1029" t="inlineStr">
+      <c r="C11" s="1102" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1030" t="inlineStr">
+      <c r="D11" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1031" t="n">
+      <c r="E11" s="1104" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1032" t="n">
+      <c r="F11" s="1105" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1031" t="n">
+      <c r="G11" s="1104" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1033">
+      <c r="H11" s="1106">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1034" t="inlineStr">
+      <c r="I11" s="1107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1035" t="inlineStr">
+      <c r="J11" s="1108" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1036" t="inlineStr">
+      <c r="A12" s="1109" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1037" t="inlineStr">
+      <c r="B12" s="1110" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="999" t="inlineStr">
+      <c r="C12" s="1085" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1030" t="inlineStr">
+      <c r="D12" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1000" t="n">
+      <c r="E12" s="1086" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1001" t="n">
+      <c r="F12" s="1087" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1000" t="n">
+      <c r="G12" s="1086" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1003">
+      <c r="H12" s="1089">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1038" t="inlineStr">
+      <c r="I12" s="1111" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1039" t="inlineStr">
+      <c r="J12" s="1112" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1027" t="inlineStr">
+      <c r="A13" s="1100" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1028" t="inlineStr">
+      <c r="B13" s="1101" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1029" t="inlineStr">
+      <c r="C13" s="1102" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1030" t="inlineStr">
+      <c r="D13" s="1103" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1031" t="n">
+      <c r="E13" s="1104" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1032" t="n">
+      <c r="F13" s="1105" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1031" t="n">
+      <c r="G13" s="1104" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1033">
+      <c r="H13" s="1106">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1034" t="inlineStr">
+      <c r="I13" s="1107" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1035" t="inlineStr">
+      <c r="J13" s="1108" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -5445,11 +5704,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1043">
+      <c r="H15" s="1116">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1043">
+      <c r="I15" s="1116">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1117">
+  <cellXfs count="1190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3410,6 +3410,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3916,7 +4135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3996,47 +4215,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="971" t="inlineStr">
+      <c r="A2" s="1044" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="972" t="n">
+      <c r="B2" s="1045" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="973" t="n">
+      <c r="C2" s="1046" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="974" t="n">
+      <c r="D2" s="1047" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="975" t="n">
+      <c r="E2" s="1048" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="976" t="n">
+      <c r="F2" s="1049" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="977" t="n">
+      <c r="G2" s="1050" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="978" t="n">
+      <c r="H2" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="979" t="n">
+      <c r="I2" s="1052" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="980" t="n">
+      <c r="J2" s="1053" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="981" t="n">
+      <c r="K2" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="982" t="n">
+      <c r="L2" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="971" t="inlineStr">
+      <c r="A3" s="1044" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -4076,7 +4295,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="971" t="inlineStr">
+      <c r="A4" s="1044" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -4116,207 +4335,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="971" t="inlineStr">
+      <c r="A5" s="1044" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="972" t="n">
+      <c r="B5" s="1045" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="973" t="n">
+      <c r="C5" s="1046" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="974" t="n">
+      <c r="D5" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="975" t="n">
+      <c r="E5" s="1048" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="976" t="n">
+      <c r="F5" s="1049" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="977" t="n">
+      <c r="G5" s="1050" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="978" t="n">
+      <c r="H5" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="979" t="n">
+      <c r="I5" s="1052" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="980" t="n">
+      <c r="J5" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="981" t="n">
+      <c r="K5" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="982" t="n">
+      <c r="L5" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="971" t="inlineStr">
+      <c r="A6" s="1044" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="972" t="n">
+      <c r="B6" s="1045" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="973" t="n">
+      <c r="C6" s="1046" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="974" t="n">
+      <c r="D6" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="975" t="n">
+      <c r="E6" s="1048" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="976" t="n">
+      <c r="F6" s="1049" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="977" t="n">
+      <c r="G6" s="1050" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="978" t="n">
+      <c r="H6" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="979" t="n">
+      <c r="I6" s="1052" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="980" t="n">
+      <c r="J6" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="981" t="n">
+      <c r="K6" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="982" t="n">
+      <c r="L6" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="971" t="inlineStr">
+      <c r="A7" s="1044" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="972" t="n">
+      <c r="B7" s="1045" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="973" t="n">
+      <c r="C7" s="1046" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="974" t="n">
+      <c r="D7" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="975" t="n">
+      <c r="E7" s="1048" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="976" t="n">
+      <c r="F7" s="1049" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="977" t="n">
+      <c r="G7" s="1050" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="978" t="n">
+      <c r="H7" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="979" t="n">
+      <c r="I7" s="1052" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="980" t="n">
+      <c r="J7" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="981" t="n">
+      <c r="K7" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="982" t="n">
+      <c r="L7" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="971" t="inlineStr">
+      <c r="A8" s="1044" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="972" t="n">
+      <c r="B8" s="1045" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="973" t="n">
+      <c r="C8" s="1046" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="974" t="n">
+      <c r="D8" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="975" t="n">
+      <c r="E8" s="1048" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="976" t="n">
+      <c r="F8" s="1049" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="977" t="n">
+      <c r="G8" s="1050" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="978" t="n">
+      <c r="H8" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="979" t="n">
+      <c r="I8" s="1052" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="980" t="n">
+      <c r="J8" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="981" t="n">
+      <c r="K8" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="982" t="n">
+      <c r="L8" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="971" t="inlineStr">
+      <c r="A9" s="1044" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="972" t="n">
+      <c r="B9" s="1045" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="973" t="n">
+      <c r="C9" s="1046" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="974" t="n">
+      <c r="D9" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="975" t="n">
+      <c r="E9" s="1048" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="976" t="n">
+      <c r="F9" s="1049" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="977" t="n">
+      <c r="G9" s="1050" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="978" t="n">
+      <c r="H9" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="979" t="n">
+      <c r="I9" s="1052" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="980" t="n">
+      <c r="J9" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="981" t="n">
+      <c r="K9" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="982" t="n">
+      <c r="L9" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="971" t="inlineStr">
+      <c r="A10" s="1044" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -4356,202 +4575,202 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="971" t="inlineStr">
+      <c r="A11" s="1044" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="972" t="n">
+      <c r="B11" s="1045" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="973" t="n">
+      <c r="C11" s="1046" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="974" t="n">
+      <c r="D11" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="975" t="n">
+      <c r="E11" s="1048" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="976" t="n">
+      <c r="F11" s="1049" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="977" t="n">
+      <c r="G11" s="1050" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="978" t="n">
+      <c r="H11" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="979" t="n">
+      <c r="I11" s="1052" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="980" t="n">
+      <c r="J11" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="981" t="n">
+      <c r="K11" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="982" t="n">
+      <c r="L11" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="971" t="inlineStr">
+      <c r="A12" s="1044" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="972" t="n">
+      <c r="B12" s="1045" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="973" t="n">
+      <c r="C12" s="1046" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="974" t="n">
+      <c r="D12" s="1047" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="975" t="n">
+      <c r="E12" s="1048" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="976" t="n">
+      <c r="F12" s="1049" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="977" t="n">
+      <c r="G12" s="1050" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="978" t="n">
+      <c r="H12" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="979" t="n">
+      <c r="I12" s="1052" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="980" t="n">
+      <c r="J12" s="1053" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="981" t="n">
+      <c r="K12" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="982" t="n">
+      <c r="L12" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="971" t="inlineStr">
+      <c r="A13" s="1044" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="972" t="n">
+      <c r="B13" s="1045" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="973" t="n">
+      <c r="C13" s="1046" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="974" t="n">
+      <c r="D13" s="1047" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="975" t="n">
+      <c r="E13" s="1048" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="976" t="n">
+      <c r="F13" s="1049" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="977" t="n">
+      <c r="G13" s="1050" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="978" t="n">
+      <c r="H13" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="979" t="n">
+      <c r="I13" s="1052" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="980" t="n">
+      <c r="J13" s="1053" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="981" t="n">
+      <c r="K13" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="982" t="n">
+      <c r="L13" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="971" t="inlineStr">
+      <c r="A14" s="1044" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="972" t="n">
+      <c r="B14" s="1045" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="973" t="n">
+      <c r="C14" s="1046" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="974" t="n">
+      <c r="D14" s="1047" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="975" t="n">
+      <c r="E14" s="1048" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="976" t="n">
+      <c r="F14" s="1049" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="977" t="n">
+      <c r="G14" s="1050" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="978" t="n">
+      <c r="H14" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="979" t="n">
+      <c r="I14" s="1052" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="980" t="n">
+      <c r="J14" s="1053" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="981" t="n">
+      <c r="K14" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="982" t="n">
+      <c r="L14" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="971" t="inlineStr">
+      <c r="A15" s="1044" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="972" t="n">
+      <c r="B15" s="1045" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="973" t="n">
+      <c r="C15" s="1046" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="974" t="n">
+      <c r="D15" s="1047" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="975" t="n">
+      <c r="E15" s="1048" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="976" t="n">
+      <c r="F15" s="1049" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="977" t="n">
+      <c r="G15" s="1050" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="978" t="n">
+      <c r="H15" s="1051" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="979" t="n">
+      <c r="I15" s="1052" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="980" t="n">
+      <c r="J15" s="1053" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="981" t="n">
+      <c r="K15" s="1054" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="982" t="n">
+      <c r="L15" s="1055" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4592,6 +4811,46 @@
         <v>0</v>
       </c>
       <c r="L16" s="1055" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="1117" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B17" s="1118" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1119" t="n">
+        <v>308166.1738375425</v>
+      </c>
+      <c r="D17" s="1120" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E17" s="1121" t="n">
+        <v>259435.9968900681</v>
+      </c>
+      <c r="F17" s="1122" t="n">
+        <v>8166.173837542534</v>
+      </c>
+      <c r="G17" s="1123" t="n">
+        <v>0.02722057945847511</v>
+      </c>
+      <c r="H17" s="1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1125" t="n">
+        <v>-0.01098131619775249</v>
+      </c>
+      <c r="J17" s="1126" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4624,452 +4883,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1056" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  14 May 2026</t>
+      <c r="A1" s="1129" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  15 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1057" t="inlineStr">
+      <c r="A2" s="1130" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1057" t="inlineStr">
+      <c r="B2" s="1130" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1057" t="inlineStr">
+      <c r="C2" s="1130" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1057" t="inlineStr">
+      <c r="D2" s="1130" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1057" t="inlineStr">
+      <c r="E2" s="1130" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1057" t="inlineStr">
+      <c r="F2" s="1130" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1057" t="inlineStr">
+      <c r="G2" s="1130" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1057" t="inlineStr">
+      <c r="H2" s="1130" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1057" t="inlineStr">
+      <c r="I2" s="1130" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1057" t="inlineStr">
+      <c r="J2" s="1130" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1057" t="inlineStr">
+      <c r="K2" s="1130" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1058" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="1059" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C3" s="1060" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D3" s="1061" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E3" s="1062" t="n">
-        <v>17.70000076293945</v>
-      </c>
-      <c r="F3" s="1063">
+      <c r="A3" s="1131" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="1132" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C3" s="1133" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D3" s="1134" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E3" s="1135" t="n">
+        <v>4.679999828338623</v>
+      </c>
+      <c r="F3" s="1136">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1064">
+      <c r="G3" s="1137">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1065">
+      <c r="H3" s="1138">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1066" t="inlineStr">
+      <c r="I3" s="1139" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1067" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="K3" s="1068" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+      <c r="J3" s="1140" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="K3" s="1141" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1058" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="1059" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C4" s="1060" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D4" s="1061" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E4" s="1062" t="n">
-        <v>4.559999942779541</v>
-      </c>
-      <c r="F4" s="1063">
+      <c r="A4" s="1131" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="1132" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C4" s="1133" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D4" s="1134" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E4" s="1135" t="n">
+        <v>17.89999961853027</v>
+      </c>
+      <c r="F4" s="1136">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1064">
+      <c r="G4" s="1137">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1065">
+      <c r="H4" s="1138">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1066" t="inlineStr">
+      <c r="I4" s="1139" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1069" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="K4" s="1070" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J4" s="1142" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K4" s="1143" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1058" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="1059" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C5" s="1060" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D5" s="1061" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E5" s="1062" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="F5" s="1063">
+      <c r="A5" s="1131" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="1132" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C5" s="1133" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="1134" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E5" s="1135" t="n">
+        <v>20.70000076293945</v>
+      </c>
+      <c r="F5" s="1136">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1064">
+      <c r="G5" s="1137">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1065">
+      <c r="H5" s="1138">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1066" t="inlineStr">
+      <c r="I5" s="1139" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1069" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="K5" s="1070" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J5" s="1144" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K5" s="1145" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1058" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="1059" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C6" s="1060" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D6" s="1061" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E6" s="1062" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F6" s="1063">
+      <c r="A6" s="1131" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="1132" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C6" s="1133" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D6" s="1134" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E6" s="1135" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F6" s="1136">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1064">
+      <c r="G6" s="1137">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1065">
+      <c r="H6" s="1138">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1066" t="inlineStr">
+      <c r="I6" s="1139" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1071" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K6" s="1072" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J6" s="1140" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K6" s="1141" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1073" t="inlineStr">
+      <c r="A7" s="1146" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1074" t="inlineStr">
+      <c r="B7" s="1147" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1075" t="n">
+      <c r="C7" s="1148" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1076" t="n">
+      <c r="D7" s="1149" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1077" t="n">
-        <v>16.60000038146973</v>
-      </c>
-      <c r="F7" s="1078">
+      <c r="E7" s="1150" t="n">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="F7" s="1151">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1079">
+      <c r="G7" s="1152">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1080">
+      <c r="H7" s="1153">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1081" t="inlineStr">
+      <c r="I7" s="1154" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1082" t="n">
+      <c r="J7" s="1155" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1083" t="inlineStr">
+      <c r="K7" s="1156" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1058" t="inlineStr">
+      <c r="A8" s="1157" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1059" t="inlineStr">
+      <c r="B8" s="1158" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1060" t="n">
+      <c r="C8" s="1159" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1061" t="n">
+      <c r="D8" s="1160" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1062" t="n">
-        <v>4.260000228881836</v>
-      </c>
-      <c r="F8" s="1063">
+      <c r="E8" s="1161" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F8" s="1162">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1064">
+      <c r="G8" s="1163">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1065">
+      <c r="H8" s="1164">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1066" t="inlineStr">
+      <c r="I8" s="1165" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1069" t="n">
+      <c r="J8" s="1166" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1070" t="inlineStr">
+      <c r="K8" s="1167" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1058" t="inlineStr">
+      <c r="A9" s="1131" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1059" t="inlineStr">
+      <c r="B9" s="1132" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1060" t="n">
+      <c r="C9" s="1133" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1061" t="n">
+      <c r="D9" s="1134" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1062" t="n">
+      <c r="E9" s="1135" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="1063">
+      <c r="F9" s="1136">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1064">
+      <c r="G9" s="1137">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1065">
+      <c r="H9" s="1138">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1066" t="inlineStr">
+      <c r="I9" s="1139" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1069" t="n">
+      <c r="J9" s="1140" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1070" t="inlineStr">
+      <c r="K9" s="1141" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1084" t="inlineStr">
+      <c r="A10" s="1131" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1085" t="inlineStr">
+      <c r="B10" s="1132" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1086" t="n">
+      <c r="C10" s="1133" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1087" t="n">
+      <c r="D10" s="1134" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1088" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F10" s="1089">
+      <c r="E10" s="1135" t="n">
+        <v>11.60000038146973</v>
+      </c>
+      <c r="F10" s="1136">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1090">
+      <c r="G10" s="1137">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1091">
+      <c r="H10" s="1138">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1092" t="inlineStr">
+      <c r="I10" s="1139" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1093" t="n">
+      <c r="J10" s="1140" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1094" t="inlineStr">
+      <c r="K10" s="1141" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1095" t="inlineStr">
+      <c r="B11" s="1168" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1096">
+      <c r="F11" s="1169">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1097">
+      <c r="G11" s="1170">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1098">
+      <c r="H11" s="1171">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -5104,14 +5363,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1056" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  14 May 2026</t>
+      <c r="A1" s="1129" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  15 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1099" t="inlineStr">
+      <c r="A3" s="1172" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -5149,550 +5408,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1056" t="inlineStr">
+      <c r="A1" s="1129" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1057" t="inlineStr">
+      <c r="A2" s="1130" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1057" t="inlineStr">
+      <c r="B2" s="1130" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1057" t="inlineStr">
+      <c r="C2" s="1130" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1057" t="inlineStr">
+      <c r="D2" s="1130" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1057" t="inlineStr">
+      <c r="E2" s="1130" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1057" t="inlineStr">
+      <c r="F2" s="1130" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1057" t="inlineStr">
+      <c r="G2" s="1130" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1057" t="inlineStr">
+      <c r="H2" s="1130" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1057" t="inlineStr">
+      <c r="I2" s="1130" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1057" t="inlineStr">
+      <c r="J2" s="1130" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1100" t="inlineStr">
+      <c r="A3" s="1173" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1101" t="inlineStr">
+      <c r="B3" s="1174" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1102" t="inlineStr">
+      <c r="C3" s="1175" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1103" t="inlineStr">
+      <c r="D3" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1104" t="n">
+      <c r="E3" s="1177" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1105" t="n">
+      <c r="F3" s="1178" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1104" t="n">
+      <c r="G3" s="1177" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1106">
+      <c r="H3" s="1179">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1107" t="inlineStr">
+      <c r="I3" s="1180" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1108" t="inlineStr">
+      <c r="J3" s="1181" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1109" t="inlineStr">
+      <c r="A4" s="1182" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1110" t="inlineStr">
+      <c r="B4" s="1183" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1085" t="inlineStr">
+      <c r="C4" s="1158" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1103" t="inlineStr">
+      <c r="D4" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1086" t="n">
+      <c r="E4" s="1159" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1087" t="n">
+      <c r="F4" s="1160" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1086" t="n">
+      <c r="G4" s="1159" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1089">
+      <c r="H4" s="1162">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1111" t="inlineStr">
+      <c r="I4" s="1184" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1112" t="inlineStr">
+      <c r="J4" s="1185" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1100" t="inlineStr">
+      <c r="A5" s="1173" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1101" t="inlineStr">
+      <c r="B5" s="1174" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1102" t="inlineStr">
+      <c r="C5" s="1175" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1103" t="inlineStr">
+      <c r="D5" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1104" t="n">
+      <c r="E5" s="1177" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1105" t="n">
+      <c r="F5" s="1178" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1104" t="n">
+      <c r="G5" s="1177" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1106">
+      <c r="H5" s="1179">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1107" t="inlineStr">
+      <c r="I5" s="1180" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1108" t="inlineStr">
+      <c r="J5" s="1181" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1109" t="inlineStr">
+      <c r="A6" s="1182" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1110" t="inlineStr">
+      <c r="B6" s="1183" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1085" t="inlineStr">
+      <c r="C6" s="1158" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1103" t="inlineStr">
+      <c r="D6" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1086" t="n">
+      <c r="E6" s="1159" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1087" t="n">
+      <c r="F6" s="1160" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1086" t="n">
+      <c r="G6" s="1159" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1089">
+      <c r="H6" s="1162">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1111" t="inlineStr">
+      <c r="I6" s="1184" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1112" t="inlineStr">
+      <c r="J6" s="1185" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1100" t="inlineStr">
+      <c r="A7" s="1173" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1101" t="inlineStr">
+      <c r="B7" s="1174" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1102" t="inlineStr">
+      <c r="C7" s="1175" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1103" t="inlineStr">
+      <c r="D7" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1104" t="n">
+      <c r="E7" s="1177" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1105" t="n">
+      <c r="F7" s="1178" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1104" t="n">
+      <c r="G7" s="1177" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1106">
+      <c r="H7" s="1179">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1107" t="inlineStr">
+      <c r="I7" s="1180" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1108" t="inlineStr">
+      <c r="J7" s="1181" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1109" t="inlineStr">
+      <c r="A8" s="1182" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1110" t="inlineStr">
+      <c r="B8" s="1183" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1085" t="inlineStr">
+      <c r="C8" s="1158" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1103" t="inlineStr">
+      <c r="D8" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1086" t="n">
+      <c r="E8" s="1159" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1087" t="n">
+      <c r="F8" s="1160" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1086" t="n">
+      <c r="G8" s="1159" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1089">
+      <c r="H8" s="1162">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1111" t="inlineStr">
+      <c r="I8" s="1184" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1112" t="inlineStr">
+      <c r="J8" s="1185" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1100" t="inlineStr">
+      <c r="A9" s="1173" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1101" t="inlineStr">
+      <c r="B9" s="1174" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1102" t="inlineStr">
+      <c r="C9" s="1175" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1113" t="inlineStr">
+      <c r="D9" s="1186" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1104" t="n">
+      <c r="E9" s="1177" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1105" t="n">
+      <c r="F9" s="1178" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1104" t="n">
+      <c r="G9" s="1177" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1106">
+      <c r="H9" s="1179">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1114" t="n">
+      <c r="I9" s="1187" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1108" t="inlineStr">
+      <c r="J9" s="1181" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1109" t="inlineStr">
+      <c r="A10" s="1182" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1110" t="inlineStr">
+      <c r="B10" s="1183" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1085" t="inlineStr">
+      <c r="C10" s="1158" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1113" t="inlineStr">
+      <c r="D10" s="1186" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1086" t="n">
+      <c r="E10" s="1159" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1087" t="n">
+      <c r="F10" s="1160" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1086" t="n">
+      <c r="G10" s="1159" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1089">
+      <c r="H10" s="1162">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1115" t="n">
+      <c r="I10" s="1188" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1112" t="inlineStr">
+      <c r="J10" s="1185" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1100" t="inlineStr">
+      <c r="A11" s="1173" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1101" t="inlineStr">
+      <c r="B11" s="1174" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1102" t="inlineStr">
+      <c r="C11" s="1175" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1103" t="inlineStr">
+      <c r="D11" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1104" t="n">
+      <c r="E11" s="1177" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1105" t="n">
+      <c r="F11" s="1178" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1104" t="n">
+      <c r="G11" s="1177" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1106">
+      <c r="H11" s="1179">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1107" t="inlineStr">
+      <c r="I11" s="1180" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1108" t="inlineStr">
+      <c r="J11" s="1181" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1109" t="inlineStr">
+      <c r="A12" s="1182" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1110" t="inlineStr">
+      <c r="B12" s="1183" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1085" t="inlineStr">
+      <c r="C12" s="1158" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1103" t="inlineStr">
+      <c r="D12" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1086" t="n">
+      <c r="E12" s="1159" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1087" t="n">
+      <c r="F12" s="1160" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1086" t="n">
+      <c r="G12" s="1159" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1089">
+      <c r="H12" s="1162">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1111" t="inlineStr">
+      <c r="I12" s="1184" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1112" t="inlineStr">
+      <c r="J12" s="1185" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1100" t="inlineStr">
+      <c r="A13" s="1173" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1101" t="inlineStr">
+      <c r="B13" s="1174" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1102" t="inlineStr">
+      <c r="C13" s="1175" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1103" t="inlineStr">
+      <c r="D13" s="1176" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1104" t="n">
+      <c r="E13" s="1177" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1105" t="n">
+      <c r="F13" s="1178" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1104" t="n">
+      <c r="G13" s="1177" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1106">
+      <c r="H13" s="1179">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1107" t="inlineStr">
+      <c r="I13" s="1180" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1108" t="inlineStr">
+      <c r="J13" s="1181" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -5704,11 +5963,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1116">
+      <c r="H15" s="1189">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1116">
+      <c r="I15" s="1189">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1190">
+  <cellXfs count="1265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3701,6 +3701,231 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4135,7 +4360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4215,47 +4440,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1044" t="inlineStr">
+      <c r="A2" s="1117" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1045" t="n">
+      <c r="B2" s="1118" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1046" t="n">
+      <c r="C2" s="1119" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1047" t="n">
+      <c r="D2" s="1120" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1048" t="n">
+      <c r="E2" s="1121" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1049" t="n">
+      <c r="F2" s="1122" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1050" t="n">
+      <c r="G2" s="1123" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1051" t="n">
+      <c r="H2" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1052" t="n">
+      <c r="I2" s="1125" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1053" t="n">
+      <c r="J2" s="1126" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1054" t="n">
+      <c r="K2" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1055" t="n">
+      <c r="L2" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1044" t="inlineStr">
+      <c r="A3" s="1117" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -4295,7 +4520,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1044" t="inlineStr">
+      <c r="A4" s="1117" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -4335,207 +4560,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1044" t="inlineStr">
+      <c r="A5" s="1117" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1045" t="n">
+      <c r="B5" s="1118" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1046" t="n">
+      <c r="C5" s="1119" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1047" t="n">
+      <c r="D5" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1048" t="n">
+      <c r="E5" s="1121" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1049" t="n">
+      <c r="F5" s="1122" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1050" t="n">
+      <c r="G5" s="1123" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1051" t="n">
+      <c r="H5" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1052" t="n">
+      <c r="I5" s="1125" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1053" t="n">
+      <c r="J5" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1054" t="n">
+      <c r="K5" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1055" t="n">
+      <c r="L5" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1044" t="inlineStr">
+      <c r="A6" s="1117" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1045" t="n">
+      <c r="B6" s="1118" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1046" t="n">
+      <c r="C6" s="1119" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1047" t="n">
+      <c r="D6" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1048" t="n">
+      <c r="E6" s="1121" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1049" t="n">
+      <c r="F6" s="1122" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1050" t="n">
+      <c r="G6" s="1123" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1051" t="n">
+      <c r="H6" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1052" t="n">
+      <c r="I6" s="1125" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1053" t="n">
+      <c r="J6" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1054" t="n">
+      <c r="K6" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1055" t="n">
+      <c r="L6" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1044" t="inlineStr">
+      <c r="A7" s="1117" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1045" t="n">
+      <c r="B7" s="1118" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1046" t="n">
+      <c r="C7" s="1119" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1047" t="n">
+      <c r="D7" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1048" t="n">
+      <c r="E7" s="1121" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1049" t="n">
+      <c r="F7" s="1122" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1050" t="n">
+      <c r="G7" s="1123" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1051" t="n">
+      <c r="H7" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1052" t="n">
+      <c r="I7" s="1125" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1053" t="n">
+      <c r="J7" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1054" t="n">
+      <c r="K7" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1055" t="n">
+      <c r="L7" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1044" t="inlineStr">
+      <c r="A8" s="1117" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1045" t="n">
+      <c r="B8" s="1118" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1046" t="n">
+      <c r="C8" s="1119" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1047" t="n">
+      <c r="D8" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1048" t="n">
+      <c r="E8" s="1121" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1049" t="n">
+      <c r="F8" s="1122" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1050" t="n">
+      <c r="G8" s="1123" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1051" t="n">
+      <c r="H8" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1052" t="n">
+      <c r="I8" s="1125" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1053" t="n">
+      <c r="J8" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1054" t="n">
+      <c r="K8" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1055" t="n">
+      <c r="L8" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1044" t="inlineStr">
+      <c r="A9" s="1117" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1045" t="n">
+      <c r="B9" s="1118" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1046" t="n">
+      <c r="C9" s="1119" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1047" t="n">
+      <c r="D9" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1048" t="n">
+      <c r="E9" s="1121" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1049" t="n">
+      <c r="F9" s="1122" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1050" t="n">
+      <c r="G9" s="1123" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1051" t="n">
+      <c r="H9" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1052" t="n">
+      <c r="I9" s="1125" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1053" t="n">
+      <c r="J9" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1054" t="n">
+      <c r="K9" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1055" t="n">
+      <c r="L9" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1044" t="inlineStr">
+      <c r="A10" s="1117" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -4575,242 +4800,242 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1044" t="inlineStr">
+      <c r="A11" s="1117" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1045" t="n">
+      <c r="B11" s="1118" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1046" t="n">
+      <c r="C11" s="1119" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1047" t="n">
+      <c r="D11" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1048" t="n">
+      <c r="E11" s="1121" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1049" t="n">
+      <c r="F11" s="1122" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1050" t="n">
+      <c r="G11" s="1123" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1051" t="n">
+      <c r="H11" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1052" t="n">
+      <c r="I11" s="1125" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1053" t="n">
+      <c r="J11" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1054" t="n">
+      <c r="K11" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1055" t="n">
+      <c r="L11" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1044" t="inlineStr">
+      <c r="A12" s="1117" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1045" t="n">
+      <c r="B12" s="1118" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1046" t="n">
+      <c r="C12" s="1119" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1047" t="n">
+      <c r="D12" s="1120" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1048" t="n">
+      <c r="E12" s="1121" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1049" t="n">
+      <c r="F12" s="1122" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1050" t="n">
+      <c r="G12" s="1123" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1051" t="n">
+      <c r="H12" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1052" t="n">
+      <c r="I12" s="1125" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1053" t="n">
+      <c r="J12" s="1126" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1054" t="n">
+      <c r="K12" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1055" t="n">
+      <c r="L12" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1044" t="inlineStr">
+      <c r="A13" s="1117" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1045" t="n">
+      <c r="B13" s="1118" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1046" t="n">
+      <c r="C13" s="1119" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1047" t="n">
+      <c r="D13" s="1120" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1048" t="n">
+      <c r="E13" s="1121" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1049" t="n">
+      <c r="F13" s="1122" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1050" t="n">
+      <c r="G13" s="1123" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1051" t="n">
+      <c r="H13" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1052" t="n">
+      <c r="I13" s="1125" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1053" t="n">
+      <c r="J13" s="1126" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1054" t="n">
+      <c r="K13" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1055" t="n">
+      <c r="L13" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1044" t="inlineStr">
+      <c r="A14" s="1117" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1045" t="n">
+      <c r="B14" s="1118" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1046" t="n">
+      <c r="C14" s="1119" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1047" t="n">
+      <c r="D14" s="1120" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1048" t="n">
+      <c r="E14" s="1121" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1049" t="n">
+      <c r="F14" s="1122" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1050" t="n">
+      <c r="G14" s="1123" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1051" t="n">
+      <c r="H14" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1052" t="n">
+      <c r="I14" s="1125" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1053" t="n">
+      <c r="J14" s="1126" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1054" t="n">
+      <c r="K14" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1055" t="n">
+      <c r="L14" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1044" t="inlineStr">
+      <c r="A15" s="1117" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1045" t="n">
+      <c r="B15" s="1118" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1046" t="n">
+      <c r="C15" s="1119" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1047" t="n">
+      <c r="D15" s="1120" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1048" t="n">
+      <c r="E15" s="1121" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1049" t="n">
+      <c r="F15" s="1122" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1050" t="n">
+      <c r="G15" s="1123" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1051" t="n">
+      <c r="H15" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1052" t="n">
+      <c r="I15" s="1125" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1053" t="n">
+      <c r="J15" s="1126" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1054" t="n">
+      <c r="K15" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1055" t="n">
+      <c r="L15" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1044" t="inlineStr">
+      <c r="A16" s="1117" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1045" t="n">
+      <c r="B16" s="1118" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1046" t="n">
+      <c r="C16" s="1119" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1047" t="n">
+      <c r="D16" s="1120" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1048" t="n">
+      <c r="E16" s="1121" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1049" t="n">
+      <c r="F16" s="1122" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1050" t="n">
+      <c r="G16" s="1123" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1051" t="n">
+      <c r="H16" s="1124" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1052" t="n">
+      <c r="I16" s="1125" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1053" t="n">
+      <c r="J16" s="1126" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1054" t="n">
+      <c r="K16" s="1127" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1055" t="n">
+      <c r="L16" s="1128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4851,6 +5076,46 @@
         <v>0</v>
       </c>
       <c r="L17" s="1128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="1190" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B18" s="1191" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1192" t="n">
+        <v>308376.1740664244</v>
+      </c>
+      <c r="D18" s="1193" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E18" s="1194" t="n">
+        <v>259645.9971189499</v>
+      </c>
+      <c r="F18" s="1195" t="n">
+        <v>8376.17406642437</v>
+      </c>
+      <c r="G18" s="1196" t="n">
+        <v>0.02792058022141457</v>
+      </c>
+      <c r="H18" s="1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1198" t="n">
+        <v>-0.01030734816491974</v>
+      </c>
+      <c r="J18" s="1199" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" s="1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4883,452 +5148,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1129" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  15 May 2026</t>
+      <c r="A1" s="1202" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  18 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1130" t="inlineStr">
+      <c r="A2" s="1203" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1130" t="inlineStr">
+      <c r="B2" s="1203" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1130" t="inlineStr">
+      <c r="C2" s="1203" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1130" t="inlineStr">
+      <c r="D2" s="1203" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1130" t="inlineStr">
+      <c r="E2" s="1203" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1130" t="inlineStr">
+      <c r="F2" s="1203" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1130" t="inlineStr">
+      <c r="G2" s="1203" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1130" t="inlineStr">
+      <c r="H2" s="1203" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1130" t="inlineStr">
+      <c r="I2" s="1203" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1130" t="inlineStr">
+      <c r="J2" s="1203" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1130" t="inlineStr">
+      <c r="K2" s="1203" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1131" t="inlineStr">
+      <c r="A3" s="1204" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1132" t="inlineStr">
+      <c r="B3" s="1205" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="1133" t="n">
+      <c r="C3" s="1206" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="1134" t="n">
+      <c r="D3" s="1207" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="1135" t="n">
+      <c r="E3" s="1208" t="n">
         <v>4.679999828338623</v>
       </c>
-      <c r="F3" s="1136">
+      <c r="F3" s="1209">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1137">
+      <c r="G3" s="1210">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1138">
+      <c r="H3" s="1211">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1139" t="inlineStr">
+      <c r="I3" s="1212" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1140" t="n">
+      <c r="J3" s="1213" t="n">
         <v>6.28</v>
       </c>
-      <c r="K3" s="1141" t="inlineStr">
+      <c r="K3" s="1214" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1131" t="inlineStr">
+      <c r="A4" s="1204" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B4" s="1132" t="inlineStr">
+      <c r="B4" s="1205" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C4" s="1133" t="n">
+      <c r="C4" s="1206" t="n">
         <v>2800</v>
       </c>
-      <c r="D4" s="1134" t="n">
+      <c r="D4" s="1207" t="n">
         <v>16.5</v>
       </c>
-      <c r="E4" s="1135" t="n">
-        <v>17.89999961853027</v>
-      </c>
-      <c r="F4" s="1136">
+      <c r="E4" s="1208" t="n">
+        <v>17.79999923706055</v>
+      </c>
+      <c r="F4" s="1209">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1137">
+      <c r="G4" s="1210">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1138">
+      <c r="H4" s="1211">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1139" t="inlineStr">
+      <c r="I4" s="1212" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1142" t="n">
+      <c r="J4" s="1215" t="n">
         <v>7.32</v>
       </c>
-      <c r="K4" s="1143" t="inlineStr">
+      <c r="K4" s="1216" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1131" t="inlineStr">
+      <c r="A5" s="1204" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B5" s="1132" t="inlineStr">
+      <c r="B5" s="1205" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C5" s="1133" t="n">
+      <c r="C5" s="1206" t="n">
         <v>2300</v>
       </c>
-      <c r="D5" s="1134" t="n">
+      <c r="D5" s="1207" t="n">
         <v>20.3</v>
       </c>
-      <c r="E5" s="1135" t="n">
-        <v>20.70000076293945</v>
-      </c>
-      <c r="F5" s="1136">
+      <c r="E5" s="1208" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="F5" s="1209">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1137">
+      <c r="G5" s="1210">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1138">
+      <c r="H5" s="1211">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1139" t="inlineStr">
+      <c r="I5" s="1212" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1144" t="n">
+      <c r="J5" s="1217" t="n">
         <v>7.52</v>
       </c>
-      <c r="K5" s="1145" t="inlineStr">
+      <c r="K5" s="1218" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1131" t="inlineStr">
+      <c r="A6" s="1219" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B6" s="1132" t="inlineStr">
+      <c r="B6" s="1220" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C6" s="1133" t="n">
+      <c r="C6" s="1221" t="n">
         <v>1600</v>
       </c>
-      <c r="D6" s="1134" t="n">
+      <c r="D6" s="1222" t="n">
         <v>29.25</v>
       </c>
-      <c r="E6" s="1135" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="F6" s="1136">
+      <c r="E6" s="1223" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F6" s="1224">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1137">
+      <c r="G6" s="1225">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1138">
+      <c r="H6" s="1226">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1139" t="inlineStr">
+      <c r="I6" s="1227" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1140" t="n">
+      <c r="J6" s="1228" t="n">
         <v>5.88</v>
       </c>
-      <c r="K6" s="1141" t="inlineStr">
+      <c r="K6" s="1229" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1146" t="inlineStr">
+      <c r="A7" s="1230" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1147" t="inlineStr">
+      <c r="B7" s="1231" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1148" t="n">
+      <c r="C7" s="1232" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1149" t="n">
+      <c r="D7" s="1233" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1150" t="n">
-        <v>16.79999923706055</v>
-      </c>
-      <c r="F7" s="1151">
+      <c r="E7" s="1234" t="n">
+        <v>16.70000076293945</v>
+      </c>
+      <c r="F7" s="1235">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1152">
+      <c r="G7" s="1236">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1153">
+      <c r="H7" s="1237">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1154" t="inlineStr">
+      <c r="I7" s="1238" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1155" t="n">
+      <c r="J7" s="1239" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1156" t="inlineStr">
+      <c r="K7" s="1240" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1157" t="inlineStr">
+      <c r="A8" s="1219" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1158" t="inlineStr">
+      <c r="B8" s="1220" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1159" t="n">
+      <c r="C8" s="1221" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1160" t="n">
+      <c r="D8" s="1222" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1161" t="n">
+      <c r="E8" s="1223" t="n">
         <v>4.21999979019165</v>
       </c>
-      <c r="F8" s="1162">
+      <c r="F8" s="1224">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1163">
+      <c r="G8" s="1241">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1164">
+      <c r="H8" s="1242">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1165" t="inlineStr">
+      <c r="I8" s="1227" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1166" t="n">
+      <c r="J8" s="1228" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1167" t="inlineStr">
+      <c r="K8" s="1229" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1131" t="inlineStr">
+      <c r="A9" s="1204" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1132" t="inlineStr">
+      <c r="B9" s="1205" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1133" t="n">
+      <c r="C9" s="1206" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1134" t="n">
+      <c r="D9" s="1207" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1135" t="n">
+      <c r="E9" s="1208" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="1136">
+      <c r="F9" s="1209">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1137">
+      <c r="G9" s="1210">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1138">
+      <c r="H9" s="1211">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1139" t="inlineStr">
+      <c r="I9" s="1212" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1140" t="n">
+      <c r="J9" s="1213" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1141" t="inlineStr">
+      <c r="K9" s="1214" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1131" t="inlineStr">
+      <c r="A10" s="1219" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1132" t="inlineStr">
+      <c r="B10" s="1220" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1133" t="n">
+      <c r="C10" s="1221" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1134" t="n">
+      <c r="D10" s="1222" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1135" t="n">
-        <v>11.60000038146973</v>
-      </c>
-      <c r="F10" s="1136">
+      <c r="E10" s="1223" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F10" s="1224">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1137">
+      <c r="G10" s="1241">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1138">
+      <c r="H10" s="1242">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1139" t="inlineStr">
+      <c r="I10" s="1227" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1140" t="n">
+      <c r="J10" s="1228" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1141" t="inlineStr">
+      <c r="K10" s="1229" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1168" t="inlineStr">
+      <c r="B11" s="1243" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1169">
+      <c r="F11" s="1244">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1170">
+      <c r="G11" s="1245">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1171">
+      <c r="H11" s="1246">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -5363,14 +5628,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1129" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  15 May 2026</t>
+      <c r="A1" s="1202" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  18 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1172" t="inlineStr">
+      <c r="A3" s="1247" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -5408,550 +5673,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1129" t="inlineStr">
+      <c r="A1" s="1202" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1130" t="inlineStr">
+      <c r="A2" s="1203" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1130" t="inlineStr">
+      <c r="B2" s="1203" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1130" t="inlineStr">
+      <c r="C2" s="1203" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1130" t="inlineStr">
+      <c r="D2" s="1203" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1130" t="inlineStr">
+      <c r="E2" s="1203" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1130" t="inlineStr">
+      <c r="F2" s="1203" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1130" t="inlineStr">
+      <c r="G2" s="1203" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1130" t="inlineStr">
+      <c r="H2" s="1203" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1130" t="inlineStr">
+      <c r="I2" s="1203" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1130" t="inlineStr">
+      <c r="J2" s="1203" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1173" t="inlineStr">
+      <c r="A3" s="1248" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1174" t="inlineStr">
+      <c r="B3" s="1249" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1175" t="inlineStr">
+      <c r="C3" s="1250" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1176" t="inlineStr">
+      <c r="D3" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1177" t="n">
+      <c r="E3" s="1252" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1178" t="n">
+      <c r="F3" s="1253" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1177" t="n">
+      <c r="G3" s="1252" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1179">
+      <c r="H3" s="1254">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1180" t="inlineStr">
+      <c r="I3" s="1255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1181" t="inlineStr">
+      <c r="J3" s="1256" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1182" t="inlineStr">
+      <c r="A4" s="1257" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1183" t="inlineStr">
+      <c r="B4" s="1258" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1158" t="inlineStr">
+      <c r="C4" s="1220" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1176" t="inlineStr">
+      <c r="D4" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1159" t="n">
+      <c r="E4" s="1221" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1160" t="n">
+      <c r="F4" s="1222" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1159" t="n">
+      <c r="G4" s="1221" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1162">
+      <c r="H4" s="1224">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1184" t="inlineStr">
+      <c r="I4" s="1259" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1185" t="inlineStr">
+      <c r="J4" s="1260" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1173" t="inlineStr">
+      <c r="A5" s="1248" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1174" t="inlineStr">
+      <c r="B5" s="1249" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1175" t="inlineStr">
+      <c r="C5" s="1250" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1176" t="inlineStr">
+      <c r="D5" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1177" t="n">
+      <c r="E5" s="1252" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1178" t="n">
+      <c r="F5" s="1253" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1177" t="n">
+      <c r="G5" s="1252" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1179">
+      <c r="H5" s="1254">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1180" t="inlineStr">
+      <c r="I5" s="1255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1181" t="inlineStr">
+      <c r="J5" s="1256" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1182" t="inlineStr">
+      <c r="A6" s="1257" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1183" t="inlineStr">
+      <c r="B6" s="1258" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1158" t="inlineStr">
+      <c r="C6" s="1220" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1176" t="inlineStr">
+      <c r="D6" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1159" t="n">
+      <c r="E6" s="1221" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1160" t="n">
+      <c r="F6" s="1222" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1159" t="n">
+      <c r="G6" s="1221" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1162">
+      <c r="H6" s="1224">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1184" t="inlineStr">
+      <c r="I6" s="1259" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1185" t="inlineStr">
+      <c r="J6" s="1260" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1173" t="inlineStr">
+      <c r="A7" s="1248" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1174" t="inlineStr">
+      <c r="B7" s="1249" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1175" t="inlineStr">
+      <c r="C7" s="1250" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1176" t="inlineStr">
+      <c r="D7" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1177" t="n">
+      <c r="E7" s="1252" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1178" t="n">
+      <c r="F7" s="1253" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1177" t="n">
+      <c r="G7" s="1252" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1179">
+      <c r="H7" s="1254">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1180" t="inlineStr">
+      <c r="I7" s="1255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1181" t="inlineStr">
+      <c r="J7" s="1256" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1182" t="inlineStr">
+      <c r="A8" s="1257" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1183" t="inlineStr">
+      <c r="B8" s="1258" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1158" t="inlineStr">
+      <c r="C8" s="1220" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1176" t="inlineStr">
+      <c r="D8" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1159" t="n">
+      <c r="E8" s="1221" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1160" t="n">
+      <c r="F8" s="1222" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1159" t="n">
+      <c r="G8" s="1221" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1162">
+      <c r="H8" s="1224">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1184" t="inlineStr">
+      <c r="I8" s="1259" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1185" t="inlineStr">
+      <c r="J8" s="1260" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1173" t="inlineStr">
+      <c r="A9" s="1248" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1174" t="inlineStr">
+      <c r="B9" s="1249" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1175" t="inlineStr">
+      <c r="C9" s="1250" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1186" t="inlineStr">
+      <c r="D9" s="1261" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1177" t="n">
+      <c r="E9" s="1252" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1178" t="n">
+      <c r="F9" s="1253" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1177" t="n">
+      <c r="G9" s="1252" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1179">
+      <c r="H9" s="1254">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1187" t="n">
+      <c r="I9" s="1262" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1181" t="inlineStr">
+      <c r="J9" s="1256" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1182" t="inlineStr">
+      <c r="A10" s="1257" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1183" t="inlineStr">
+      <c r="B10" s="1258" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1158" t="inlineStr">
+      <c r="C10" s="1220" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1186" t="inlineStr">
+      <c r="D10" s="1261" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1159" t="n">
+      <c r="E10" s="1221" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1160" t="n">
+      <c r="F10" s="1222" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1159" t="n">
+      <c r="G10" s="1221" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1162">
+      <c r="H10" s="1224">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1188" t="n">
+      <c r="I10" s="1263" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1185" t="inlineStr">
+      <c r="J10" s="1260" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1173" t="inlineStr">
+      <c r="A11" s="1248" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1174" t="inlineStr">
+      <c r="B11" s="1249" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1175" t="inlineStr">
+      <c r="C11" s="1250" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1176" t="inlineStr">
+      <c r="D11" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1177" t="n">
+      <c r="E11" s="1252" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1178" t="n">
+      <c r="F11" s="1253" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1177" t="n">
+      <c r="G11" s="1252" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1179">
+      <c r="H11" s="1254">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1180" t="inlineStr">
+      <c r="I11" s="1255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1181" t="inlineStr">
+      <c r="J11" s="1256" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1182" t="inlineStr">
+      <c r="A12" s="1257" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1183" t="inlineStr">
+      <c r="B12" s="1258" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1158" t="inlineStr">
+      <c r="C12" s="1220" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1176" t="inlineStr">
+      <c r="D12" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1159" t="n">
+      <c r="E12" s="1221" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1160" t="n">
+      <c r="F12" s="1222" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1159" t="n">
+      <c r="G12" s="1221" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1162">
+      <c r="H12" s="1224">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1184" t="inlineStr">
+      <c r="I12" s="1259" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1185" t="inlineStr">
+      <c r="J12" s="1260" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1173" t="inlineStr">
+      <c r="A13" s="1248" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1174" t="inlineStr">
+      <c r="B13" s="1249" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1175" t="inlineStr">
+      <c r="C13" s="1250" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1176" t="inlineStr">
+      <c r="D13" s="1251" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1177" t="n">
+      <c r="E13" s="1252" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1178" t="n">
+      <c r="F13" s="1253" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1177" t="n">
+      <c r="G13" s="1252" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1179">
+      <c r="H13" s="1254">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1180" t="inlineStr">
+      <c r="I13" s="1255" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1181" t="inlineStr">
+      <c r="J13" s="1256" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -5963,11 +6228,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1189">
+      <c r="H15" s="1264">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1189">
+      <c r="I15" s="1264">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1265">
+  <cellXfs count="1338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3926,6 +3926,225 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4360,7 +4579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4440,47 +4659,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1117" t="inlineStr">
+      <c r="A2" s="1190" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1118" t="n">
+      <c r="B2" s="1191" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1119" t="n">
+      <c r="C2" s="1192" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1120" t="n">
+      <c r="D2" s="1193" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1121" t="n">
+      <c r="E2" s="1194" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1122" t="n">
+      <c r="F2" s="1195" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1123" t="n">
+      <c r="G2" s="1196" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1124" t="n">
+      <c r="H2" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1125" t="n">
+      <c r="I2" s="1198" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1126" t="n">
+      <c r="J2" s="1199" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1127" t="n">
+      <c r="K2" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1128" t="n">
+      <c r="L2" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1117" t="inlineStr">
+      <c r="A3" s="1190" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -4520,7 +4739,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1117" t="inlineStr">
+      <c r="A4" s="1190" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -4560,207 +4779,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1117" t="inlineStr">
+      <c r="A5" s="1190" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1118" t="n">
+      <c r="B5" s="1191" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1119" t="n">
+      <c r="C5" s="1192" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1120" t="n">
+      <c r="D5" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1121" t="n">
+      <c r="E5" s="1194" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1122" t="n">
+      <c r="F5" s="1195" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1123" t="n">
+      <c r="G5" s="1196" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1124" t="n">
+      <c r="H5" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1125" t="n">
+      <c r="I5" s="1198" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1126" t="n">
+      <c r="J5" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1127" t="n">
+      <c r="K5" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1128" t="n">
+      <c r="L5" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1117" t="inlineStr">
+      <c r="A6" s="1190" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1118" t="n">
+      <c r="B6" s="1191" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1119" t="n">
+      <c r="C6" s="1192" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1120" t="n">
+      <c r="D6" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1121" t="n">
+      <c r="E6" s="1194" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1122" t="n">
+      <c r="F6" s="1195" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1123" t="n">
+      <c r="G6" s="1196" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1124" t="n">
+      <c r="H6" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1125" t="n">
+      <c r="I6" s="1198" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1126" t="n">
+      <c r="J6" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1127" t="n">
+      <c r="K6" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1128" t="n">
+      <c r="L6" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1117" t="inlineStr">
+      <c r="A7" s="1190" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1118" t="n">
+      <c r="B7" s="1191" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1119" t="n">
+      <c r="C7" s="1192" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1120" t="n">
+      <c r="D7" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1121" t="n">
+      <c r="E7" s="1194" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1122" t="n">
+      <c r="F7" s="1195" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1123" t="n">
+      <c r="G7" s="1196" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1124" t="n">
+      <c r="H7" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1125" t="n">
+      <c r="I7" s="1198" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1126" t="n">
+      <c r="J7" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1127" t="n">
+      <c r="K7" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1128" t="n">
+      <c r="L7" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1117" t="inlineStr">
+      <c r="A8" s="1190" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1118" t="n">
+      <c r="B8" s="1191" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1119" t="n">
+      <c r="C8" s="1192" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1120" t="n">
+      <c r="D8" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1121" t="n">
+      <c r="E8" s="1194" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1122" t="n">
+      <c r="F8" s="1195" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1123" t="n">
+      <c r="G8" s="1196" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1124" t="n">
+      <c r="H8" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1125" t="n">
+      <c r="I8" s="1198" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1126" t="n">
+      <c r="J8" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1127" t="n">
+      <c r="K8" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1128" t="n">
+      <c r="L8" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1117" t="inlineStr">
+      <c r="A9" s="1190" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1118" t="n">
+      <c r="B9" s="1191" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1119" t="n">
+      <c r="C9" s="1192" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1120" t="n">
+      <c r="D9" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1121" t="n">
+      <c r="E9" s="1194" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1122" t="n">
+      <c r="F9" s="1195" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1123" t="n">
+      <c r="G9" s="1196" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1124" t="n">
+      <c r="H9" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1125" t="n">
+      <c r="I9" s="1198" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1126" t="n">
+      <c r="J9" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1127" t="n">
+      <c r="K9" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1128" t="n">
+      <c r="L9" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1117" t="inlineStr">
+      <c r="A10" s="1190" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -4800,282 +5019,282 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1117" t="inlineStr">
+      <c r="A11" s="1190" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1118" t="n">
+      <c r="B11" s="1191" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1119" t="n">
+      <c r="C11" s="1192" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1120" t="n">
+      <c r="D11" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1121" t="n">
+      <c r="E11" s="1194" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1122" t="n">
+      <c r="F11" s="1195" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1123" t="n">
+      <c r="G11" s="1196" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1124" t="n">
+      <c r="H11" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1125" t="n">
+      <c r="I11" s="1198" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1126" t="n">
+      <c r="J11" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1127" t="n">
+      <c r="K11" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1128" t="n">
+      <c r="L11" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1117" t="inlineStr">
+      <c r="A12" s="1190" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1118" t="n">
+      <c r="B12" s="1191" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1119" t="n">
+      <c r="C12" s="1192" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1120" t="n">
+      <c r="D12" s="1193" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1121" t="n">
+      <c r="E12" s="1194" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1122" t="n">
+      <c r="F12" s="1195" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1123" t="n">
+      <c r="G12" s="1196" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1124" t="n">
+      <c r="H12" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1125" t="n">
+      <c r="I12" s="1198" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1126" t="n">
+      <c r="J12" s="1199" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1127" t="n">
+      <c r="K12" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1128" t="n">
+      <c r="L12" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1117" t="inlineStr">
+      <c r="A13" s="1190" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1118" t="n">
+      <c r="B13" s="1191" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1119" t="n">
+      <c r="C13" s="1192" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1120" t="n">
+      <c r="D13" s="1193" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1121" t="n">
+      <c r="E13" s="1194" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1122" t="n">
+      <c r="F13" s="1195" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1123" t="n">
+      <c r="G13" s="1196" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1124" t="n">
+      <c r="H13" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1125" t="n">
+      <c r="I13" s="1198" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1126" t="n">
+      <c r="J13" s="1199" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1127" t="n">
+      <c r="K13" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1128" t="n">
+      <c r="L13" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1117" t="inlineStr">
+      <c r="A14" s="1190" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1118" t="n">
+      <c r="B14" s="1191" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1119" t="n">
+      <c r="C14" s="1192" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1120" t="n">
+      <c r="D14" s="1193" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1121" t="n">
+      <c r="E14" s="1194" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1122" t="n">
+      <c r="F14" s="1195" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1123" t="n">
+      <c r="G14" s="1196" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1124" t="n">
+      <c r="H14" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1125" t="n">
+      <c r="I14" s="1198" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1126" t="n">
+      <c r="J14" s="1199" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1127" t="n">
+      <c r="K14" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1128" t="n">
+      <c r="L14" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1117" t="inlineStr">
+      <c r="A15" s="1190" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1118" t="n">
+      <c r="B15" s="1191" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1119" t="n">
+      <c r="C15" s="1192" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1120" t="n">
+      <c r="D15" s="1193" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1121" t="n">
+      <c r="E15" s="1194" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1122" t="n">
+      <c r="F15" s="1195" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1123" t="n">
+      <c r="G15" s="1196" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1124" t="n">
+      <c r="H15" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1125" t="n">
+      <c r="I15" s="1198" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1126" t="n">
+      <c r="J15" s="1199" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1127" t="n">
+      <c r="K15" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1128" t="n">
+      <c r="L15" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1117" t="inlineStr">
+      <c r="A16" s="1190" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1118" t="n">
+      <c r="B16" s="1191" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1119" t="n">
+      <c r="C16" s="1192" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1120" t="n">
+      <c r="D16" s="1193" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1121" t="n">
+      <c r="E16" s="1194" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1122" t="n">
+      <c r="F16" s="1195" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1123" t="n">
+      <c r="G16" s="1196" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1124" t="n">
+      <c r="H16" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1125" t="n">
+      <c r="I16" s="1198" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1126" t="n">
+      <c r="J16" s="1199" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1127" t="n">
+      <c r="K16" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1128" t="n">
+      <c r="L16" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1117" t="inlineStr">
+      <c r="A17" s="1190" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1118" t="n">
+      <c r="B17" s="1191" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1119" t="n">
+      <c r="C17" s="1192" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1120" t="n">
+      <c r="D17" s="1193" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1121" t="n">
+      <c r="E17" s="1194" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1122" t="n">
+      <c r="F17" s="1195" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1123" t="n">
+      <c r="G17" s="1196" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1124" t="n">
+      <c r="H17" s="1197" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1125" t="n">
+      <c r="I17" s="1198" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1126" t="n">
+      <c r="J17" s="1199" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1127" t="n">
+      <c r="K17" s="1200" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1128" t="n">
+      <c r="L17" s="1201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5116,6 +5335,46 @@
         <v>0</v>
       </c>
       <c r="L18" s="1201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="1265" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B19" s="1266" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1267" t="n">
+        <v>303508.175180316</v>
+      </c>
+      <c r="D19" s="1268" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E19" s="1269" t="n">
+        <v>254777.9982328415</v>
+      </c>
+      <c r="F19" s="1270" t="n">
+        <v>3508.175180315971</v>
+      </c>
+      <c r="G19" s="1271" t="n">
+        <v>0.01169391726771991</v>
+      </c>
+      <c r="H19" s="1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1273" t="n">
+        <v>-0.02593054843747088</v>
+      </c>
+      <c r="J19" s="1274" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5148,452 +5407,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1202" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  18 May 2026</t>
+      <c r="A1" s="1277" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  19 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1203" t="inlineStr">
+      <c r="A2" s="1278" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1203" t="inlineStr">
+      <c r="B2" s="1278" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1203" t="inlineStr">
+      <c r="C2" s="1278" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1203" t="inlineStr">
+      <c r="D2" s="1278" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1203" t="inlineStr">
+      <c r="E2" s="1278" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1203" t="inlineStr">
+      <c r="F2" s="1278" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1203" t="inlineStr">
+      <c r="G2" s="1278" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1203" t="inlineStr">
+      <c r="H2" s="1278" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1203" t="inlineStr">
+      <c r="I2" s="1278" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1203" t="inlineStr">
+      <c r="J2" s="1278" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1203" t="inlineStr">
+      <c r="K2" s="1278" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1204" t="inlineStr">
+      <c r="A3" s="1279" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1205" t="inlineStr">
+      <c r="B3" s="1280" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C3" s="1206" t="n">
+      <c r="C3" s="1281" t="n">
         <v>10800</v>
       </c>
-      <c r="D3" s="1207" t="n">
+      <c r="D3" s="1282" t="n">
         <v>4.38</v>
       </c>
-      <c r="E3" s="1208" t="n">
-        <v>4.679999828338623</v>
-      </c>
-      <c r="F3" s="1209">
+      <c r="E3" s="1283" t="n">
+        <v>4.619999885559082</v>
+      </c>
+      <c r="F3" s="1284">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1210">
+      <c r="G3" s="1285">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1211">
+      <c r="H3" s="1286">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1212" t="inlineStr">
+      <c r="I3" s="1287" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1213" t="n">
+      <c r="J3" s="1288" t="n">
         <v>6.28</v>
       </c>
-      <c r="K3" s="1214" t="inlineStr">
+      <c r="K3" s="1289" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1204" t="inlineStr">
-        <is>
-          <t>CK.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="1205" t="inlineStr">
-        <is>
-          <t>CK</t>
-        </is>
-      </c>
-      <c r="C4" s="1206" t="n">
-        <v>2800</v>
-      </c>
-      <c r="D4" s="1207" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="E4" s="1208" t="n">
-        <v>17.79999923706055</v>
-      </c>
-      <c r="F4" s="1209">
+      <c r="A4" s="1279" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="1280" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C4" s="1281" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D4" s="1282" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E4" s="1283" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F4" s="1284">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1210">
+      <c r="G4" s="1285">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1211">
+      <c r="H4" s="1286">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1212" t="inlineStr">
+      <c r="I4" s="1287" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1215" t="n">
-        <v>7.32</v>
-      </c>
-      <c r="K4" s="1216" t="inlineStr">
-        <is>
-          <t>WATCH</t>
+      <c r="J4" s="1290" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K4" s="1291" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1204" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B5" s="1205" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C5" s="1206" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D5" s="1207" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E5" s="1208" t="n">
-        <v>21.39999961853027</v>
-      </c>
-      <c r="F5" s="1209">
+      <c r="A5" s="1279" t="inlineStr">
+        <is>
+          <t>CK.BK</t>
+        </is>
+      </c>
+      <c r="B5" s="1280" t="inlineStr">
+        <is>
+          <t>CK</t>
+        </is>
+      </c>
+      <c r="C5" s="1281" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="1282" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E5" s="1283" t="n">
+        <v>17.39999961853027</v>
+      </c>
+      <c r="F5" s="1284">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1210">
+      <c r="G5" s="1285">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1211">
+      <c r="H5" s="1286">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1212" t="inlineStr">
+      <c r="I5" s="1287" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1217" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K5" s="1218" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J5" s="1292" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="K5" s="1293" t="inlineStr">
+        <is>
+          <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1219" t="inlineStr">
+      <c r="A6" s="1294" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B6" s="1220" t="inlineStr">
+      <c r="B6" s="1295" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C6" s="1221" t="n">
+      <c r="C6" s="1296" t="n">
         <v>1600</v>
       </c>
-      <c r="D6" s="1222" t="n">
+      <c r="D6" s="1297" t="n">
         <v>29.25</v>
       </c>
-      <c r="E6" s="1223" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F6" s="1224">
+      <c r="E6" s="1298" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="F6" s="1299">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1225">
+      <c r="G6" s="1300">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1226">
+      <c r="H6" s="1301">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1227" t="inlineStr">
+      <c r="I6" s="1302" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1228" t="n">
+      <c r="J6" s="1303" t="n">
         <v>5.88</v>
       </c>
-      <c r="K6" s="1229" t="inlineStr">
+      <c r="K6" s="1304" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1230" t="inlineStr">
+      <c r="A7" s="1305" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1231" t="inlineStr">
+      <c r="B7" s="1306" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1232" t="n">
+      <c r="C7" s="1307" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1233" t="n">
+      <c r="D7" s="1308" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1234" t="n">
-        <v>16.70000076293945</v>
-      </c>
-      <c r="F7" s="1235">
+      <c r="E7" s="1309" t="n">
+        <v>15.80000019073486</v>
+      </c>
+      <c r="F7" s="1310">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1236">
+      <c r="G7" s="1311">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1237">
+      <c r="H7" s="1312">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1238" t="inlineStr">
+      <c r="I7" s="1313" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1239" t="n">
+      <c r="J7" s="1314" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1240" t="inlineStr">
+      <c r="K7" s="1315" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1219" t="inlineStr">
+      <c r="A8" s="1294" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1220" t="inlineStr">
+      <c r="B8" s="1295" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1221" t="n">
+      <c r="C8" s="1296" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1222" t="n">
+      <c r="D8" s="1297" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1223" t="n">
+      <c r="E8" s="1298" t="n">
         <v>4.21999979019165</v>
       </c>
-      <c r="F8" s="1224">
+      <c r="F8" s="1299">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1241">
+      <c r="G8" s="1300">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1242">
+      <c r="H8" s="1301">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1227" t="inlineStr">
+      <c r="I8" s="1302" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1228" t="n">
+      <c r="J8" s="1303" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1229" t="inlineStr">
+      <c r="K8" s="1304" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1204" t="inlineStr">
+      <c r="A9" s="1279" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1205" t="inlineStr">
+      <c r="B9" s="1280" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1206" t="n">
+      <c r="C9" s="1281" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1207" t="n">
+      <c r="D9" s="1282" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1208" t="n">
+      <c r="E9" s="1283" t="n">
         <v>2.640000104904175</v>
       </c>
-      <c r="F9" s="1209">
+      <c r="F9" s="1284">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1210">
+      <c r="G9" s="1285">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1211">
+      <c r="H9" s="1286">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1212" t="inlineStr">
+      <c r="I9" s="1287" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1213" t="n">
+      <c r="J9" s="1288" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1214" t="inlineStr">
+      <c r="K9" s="1289" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1219" t="inlineStr">
+      <c r="A10" s="1305" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1220" t="inlineStr">
+      <c r="B10" s="1306" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1221" t="n">
+      <c r="C10" s="1307" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1222" t="n">
+      <c r="D10" s="1308" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1223" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F10" s="1224">
+      <c r="E10" s="1309" t="n">
+        <v>11.30000019073486</v>
+      </c>
+      <c r="F10" s="1310">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1241">
+      <c r="G10" s="1311">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1242">
+      <c r="H10" s="1312">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1227" t="inlineStr">
+      <c r="I10" s="1313" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1228" t="n">
+      <c r="J10" s="1314" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1229" t="inlineStr">
+      <c r="K10" s="1315" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1243" t="inlineStr">
+      <c r="B11" s="1316" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1244">
+      <c r="F11" s="1317">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1245">
+      <c r="G11" s="1318">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1246">
+      <c r="H11" s="1319">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -5628,14 +5887,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1202" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  18 May 2026</t>
+      <c r="A1" s="1277" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  19 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1247" t="inlineStr">
+      <c r="A3" s="1320" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -5673,550 +5932,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1202" t="inlineStr">
+      <c r="A1" s="1277" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1203" t="inlineStr">
+      <c r="A2" s="1278" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1203" t="inlineStr">
+      <c r="B2" s="1278" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1203" t="inlineStr">
+      <c r="C2" s="1278" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1203" t="inlineStr">
+      <c r="D2" s="1278" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1203" t="inlineStr">
+      <c r="E2" s="1278" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1203" t="inlineStr">
+      <c r="F2" s="1278" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1203" t="inlineStr">
+      <c r="G2" s="1278" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1203" t="inlineStr">
+      <c r="H2" s="1278" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1203" t="inlineStr">
+      <c r="I2" s="1278" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1203" t="inlineStr">
+      <c r="J2" s="1278" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1248" t="inlineStr">
+      <c r="A3" s="1321" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1249" t="inlineStr">
+      <c r="B3" s="1322" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1250" t="inlineStr">
+      <c r="C3" s="1323" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1251" t="inlineStr">
+      <c r="D3" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1252" t="n">
+      <c r="E3" s="1325" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1253" t="n">
+      <c r="F3" s="1326" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1252" t="n">
+      <c r="G3" s="1325" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1254">
+      <c r="H3" s="1327">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1255" t="inlineStr">
+      <c r="I3" s="1328" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1256" t="inlineStr">
+      <c r="J3" s="1329" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1257" t="inlineStr">
+      <c r="A4" s="1330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1258" t="inlineStr">
+      <c r="B4" s="1331" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1220" t="inlineStr">
+      <c r="C4" s="1295" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1251" t="inlineStr">
+      <c r="D4" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1221" t="n">
+      <c r="E4" s="1296" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1222" t="n">
+      <c r="F4" s="1297" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1221" t="n">
+      <c r="G4" s="1296" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1224">
+      <c r="H4" s="1299">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1259" t="inlineStr">
+      <c r="I4" s="1332" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1260" t="inlineStr">
+      <c r="J4" s="1333" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1248" t="inlineStr">
+      <c r="A5" s="1321" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1249" t="inlineStr">
+      <c r="B5" s="1322" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1250" t="inlineStr">
+      <c r="C5" s="1323" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1251" t="inlineStr">
+      <c r="D5" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1252" t="n">
+      <c r="E5" s="1325" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1253" t="n">
+      <c r="F5" s="1326" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1252" t="n">
+      <c r="G5" s="1325" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1254">
+      <c r="H5" s="1327">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1255" t="inlineStr">
+      <c r="I5" s="1328" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1256" t="inlineStr">
+      <c r="J5" s="1329" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1257" t="inlineStr">
+      <c r="A6" s="1330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1258" t="inlineStr">
+      <c r="B6" s="1331" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1220" t="inlineStr">
+      <c r="C6" s="1295" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1251" t="inlineStr">
+      <c r="D6" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1221" t="n">
+      <c r="E6" s="1296" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1222" t="n">
+      <c r="F6" s="1297" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1221" t="n">
+      <c r="G6" s="1296" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1224">
+      <c r="H6" s="1299">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1259" t="inlineStr">
+      <c r="I6" s="1332" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1260" t="inlineStr">
+      <c r="J6" s="1333" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1248" t="inlineStr">
+      <c r="A7" s="1321" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1249" t="inlineStr">
+      <c r="B7" s="1322" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1250" t="inlineStr">
+      <c r="C7" s="1323" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1251" t="inlineStr">
+      <c r="D7" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1252" t="n">
+      <c r="E7" s="1325" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1253" t="n">
+      <c r="F7" s="1326" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1252" t="n">
+      <c r="G7" s="1325" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1254">
+      <c r="H7" s="1327">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1255" t="inlineStr">
+      <c r="I7" s="1328" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1256" t="inlineStr">
+      <c r="J7" s="1329" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1257" t="inlineStr">
+      <c r="A8" s="1330" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1258" t="inlineStr">
+      <c r="B8" s="1331" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1220" t="inlineStr">
+      <c r="C8" s="1295" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1251" t="inlineStr">
+      <c r="D8" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1221" t="n">
+      <c r="E8" s="1296" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1222" t="n">
+      <c r="F8" s="1297" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1221" t="n">
+      <c r="G8" s="1296" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1224">
+      <c r="H8" s="1299">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1259" t="inlineStr">
+      <c r="I8" s="1332" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1260" t="inlineStr">
+      <c r="J8" s="1333" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1248" t="inlineStr">
+      <c r="A9" s="1321" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1249" t="inlineStr">
+      <c r="B9" s="1322" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1250" t="inlineStr">
+      <c r="C9" s="1323" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1261" t="inlineStr">
+      <c r="D9" s="1334" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1252" t="n">
+      <c r="E9" s="1325" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1253" t="n">
+      <c r="F9" s="1326" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1252" t="n">
+      <c r="G9" s="1325" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1254">
+      <c r="H9" s="1327">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1262" t="n">
+      <c r="I9" s="1335" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1256" t="inlineStr">
+      <c r="J9" s="1329" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1257" t="inlineStr">
+      <c r="A10" s="1330" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1258" t="inlineStr">
+      <c r="B10" s="1331" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1220" t="inlineStr">
+      <c r="C10" s="1295" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1261" t="inlineStr">
+      <c r="D10" s="1334" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1221" t="n">
+      <c r="E10" s="1296" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1222" t="n">
+      <c r="F10" s="1297" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1221" t="n">
+      <c r="G10" s="1296" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1224">
+      <c r="H10" s="1299">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1263" t="n">
+      <c r="I10" s="1336" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1260" t="inlineStr">
+      <c r="J10" s="1333" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1248" t="inlineStr">
+      <c r="A11" s="1321" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1249" t="inlineStr">
+      <c r="B11" s="1322" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1250" t="inlineStr">
+      <c r="C11" s="1323" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1251" t="inlineStr">
+      <c r="D11" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1252" t="n">
+      <c r="E11" s="1325" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1253" t="n">
+      <c r="F11" s="1326" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1252" t="n">
+      <c r="G11" s="1325" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1254">
+      <c r="H11" s="1327">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1255" t="inlineStr">
+      <c r="I11" s="1328" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1256" t="inlineStr">
+      <c r="J11" s="1329" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1257" t="inlineStr">
+      <c r="A12" s="1330" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1258" t="inlineStr">
+      <c r="B12" s="1331" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1220" t="inlineStr">
+      <c r="C12" s="1295" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1251" t="inlineStr">
+      <c r="D12" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1221" t="n">
+      <c r="E12" s="1296" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1222" t="n">
+      <c r="F12" s="1297" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1221" t="n">
+      <c r="G12" s="1296" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1224">
+      <c r="H12" s="1299">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1259" t="inlineStr">
+      <c r="I12" s="1332" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1260" t="inlineStr">
+      <c r="J12" s="1333" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1248" t="inlineStr">
+      <c r="A13" s="1321" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1249" t="inlineStr">
+      <c r="B13" s="1322" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1250" t="inlineStr">
+      <c r="C13" s="1323" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1251" t="inlineStr">
+      <c r="D13" s="1324" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1252" t="n">
+      <c r="E13" s="1325" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1253" t="n">
+      <c r="F13" s="1326" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1252" t="n">
+      <c r="G13" s="1325" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1254">
+      <c r="H13" s="1327">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1255" t="inlineStr">
+      <c r="I13" s="1328" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1256" t="inlineStr">
+      <c r="J13" s="1329" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6228,11 +6487,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1264">
+      <c r="H15" s="1337">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1264">
+      <c r="I15" s="1337">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1338">
+  <cellXfs count="1411">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4073,6 +4073,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4579,7 +4798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4659,47 +4878,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1190" t="inlineStr">
+      <c r="A2" s="1265" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1191" t="n">
+      <c r="B2" s="1266" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1192" t="n">
+      <c r="C2" s="1267" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1193" t="n">
+      <c r="D2" s="1268" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1194" t="n">
+      <c r="E2" s="1269" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1195" t="n">
+      <c r="F2" s="1270" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1196" t="n">
+      <c r="G2" s="1271" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1197" t="n">
+      <c r="H2" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1198" t="n">
+      <c r="I2" s="1273" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1199" t="n">
+      <c r="J2" s="1274" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1200" t="n">
+      <c r="K2" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1201" t="n">
+      <c r="L2" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1190" t="inlineStr">
+      <c r="A3" s="1265" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -4739,7 +4958,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1190" t="inlineStr">
+      <c r="A4" s="1265" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -4779,207 +4998,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1190" t="inlineStr">
+      <c r="A5" s="1265" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1191" t="n">
+      <c r="B5" s="1266" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1192" t="n">
+      <c r="C5" s="1267" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1193" t="n">
+      <c r="D5" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1194" t="n">
+      <c r="E5" s="1269" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1195" t="n">
+      <c r="F5" s="1270" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1196" t="n">
+      <c r="G5" s="1271" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1197" t="n">
+      <c r="H5" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1198" t="n">
+      <c r="I5" s="1273" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1199" t="n">
+      <c r="J5" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1200" t="n">
+      <c r="K5" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1201" t="n">
+      <c r="L5" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1190" t="inlineStr">
+      <c r="A6" s="1265" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1191" t="n">
+      <c r="B6" s="1266" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1192" t="n">
+      <c r="C6" s="1267" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1193" t="n">
+      <c r="D6" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1194" t="n">
+      <c r="E6" s="1269" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1195" t="n">
+      <c r="F6" s="1270" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1196" t="n">
+      <c r="G6" s="1271" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1197" t="n">
+      <c r="H6" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1198" t="n">
+      <c r="I6" s="1273" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1199" t="n">
+      <c r="J6" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1200" t="n">
+      <c r="K6" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1201" t="n">
+      <c r="L6" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1190" t="inlineStr">
+      <c r="A7" s="1265" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1191" t="n">
+      <c r="B7" s="1266" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1192" t="n">
+      <c r="C7" s="1267" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1193" t="n">
+      <c r="D7" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1194" t="n">
+      <c r="E7" s="1269" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1195" t="n">
+      <c r="F7" s="1270" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1196" t="n">
+      <c r="G7" s="1271" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1197" t="n">
+      <c r="H7" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1198" t="n">
+      <c r="I7" s="1273" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1199" t="n">
+      <c r="J7" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1200" t="n">
+      <c r="K7" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1201" t="n">
+      <c r="L7" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1190" t="inlineStr">
+      <c r="A8" s="1265" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1191" t="n">
+      <c r="B8" s="1266" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1192" t="n">
+      <c r="C8" s="1267" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1193" t="n">
+      <c r="D8" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1194" t="n">
+      <c r="E8" s="1269" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1195" t="n">
+      <c r="F8" s="1270" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1196" t="n">
+      <c r="G8" s="1271" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1197" t="n">
+      <c r="H8" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1198" t="n">
+      <c r="I8" s="1273" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1199" t="n">
+      <c r="J8" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1200" t="n">
+      <c r="K8" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1201" t="n">
+      <c r="L8" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1190" t="inlineStr">
+      <c r="A9" s="1265" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1191" t="n">
+      <c r="B9" s="1266" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1192" t="n">
+      <c r="C9" s="1267" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1193" t="n">
+      <c r="D9" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1194" t="n">
+      <c r="E9" s="1269" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1195" t="n">
+      <c r="F9" s="1270" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1196" t="n">
+      <c r="G9" s="1271" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1197" t="n">
+      <c r="H9" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1198" t="n">
+      <c r="I9" s="1273" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1199" t="n">
+      <c r="J9" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1200" t="n">
+      <c r="K9" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1201" t="n">
+      <c r="L9" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1190" t="inlineStr">
+      <c r="A10" s="1265" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -5019,322 +5238,322 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1190" t="inlineStr">
+      <c r="A11" s="1265" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1191" t="n">
+      <c r="B11" s="1266" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1192" t="n">
+      <c r="C11" s="1267" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1193" t="n">
+      <c r="D11" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1194" t="n">
+      <c r="E11" s="1269" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1195" t="n">
+      <c r="F11" s="1270" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1196" t="n">
+      <c r="G11" s="1271" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1197" t="n">
+      <c r="H11" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1198" t="n">
+      <c r="I11" s="1273" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1199" t="n">
+      <c r="J11" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1200" t="n">
+      <c r="K11" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1201" t="n">
+      <c r="L11" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1190" t="inlineStr">
+      <c r="A12" s="1265" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1191" t="n">
+      <c r="B12" s="1266" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1192" t="n">
+      <c r="C12" s="1267" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1193" t="n">
+      <c r="D12" s="1268" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1194" t="n">
+      <c r="E12" s="1269" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1195" t="n">
+      <c r="F12" s="1270" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1196" t="n">
+      <c r="G12" s="1271" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1197" t="n">
+      <c r="H12" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1198" t="n">
+      <c r="I12" s="1273" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1199" t="n">
+      <c r="J12" s="1274" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1200" t="n">
+      <c r="K12" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1201" t="n">
+      <c r="L12" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1190" t="inlineStr">
+      <c r="A13" s="1265" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1191" t="n">
+      <c r="B13" s="1266" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1192" t="n">
+      <c r="C13" s="1267" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1193" t="n">
+      <c r="D13" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1194" t="n">
+      <c r="E13" s="1269" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1195" t="n">
+      <c r="F13" s="1270" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1196" t="n">
+      <c r="G13" s="1271" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1197" t="n">
+      <c r="H13" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1198" t="n">
+      <c r="I13" s="1273" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1199" t="n">
+      <c r="J13" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1200" t="n">
+      <c r="K13" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1201" t="n">
+      <c r="L13" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1190" t="inlineStr">
+      <c r="A14" s="1265" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1191" t="n">
+      <c r="B14" s="1266" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1192" t="n">
+      <c r="C14" s="1267" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1193" t="n">
+      <c r="D14" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1194" t="n">
+      <c r="E14" s="1269" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1195" t="n">
+      <c r="F14" s="1270" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1196" t="n">
+      <c r="G14" s="1271" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1197" t="n">
+      <c r="H14" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1198" t="n">
+      <c r="I14" s="1273" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1199" t="n">
+      <c r="J14" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1200" t="n">
+      <c r="K14" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1201" t="n">
+      <c r="L14" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1190" t="inlineStr">
+      <c r="A15" s="1265" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1191" t="n">
+      <c r="B15" s="1266" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1192" t="n">
+      <c r="C15" s="1267" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1193" t="n">
+      <c r="D15" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1194" t="n">
+      <c r="E15" s="1269" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1195" t="n">
+      <c r="F15" s="1270" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1196" t="n">
+      <c r="G15" s="1271" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1197" t="n">
+      <c r="H15" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1198" t="n">
+      <c r="I15" s="1273" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1199" t="n">
+      <c r="J15" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1200" t="n">
+      <c r="K15" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1201" t="n">
+      <c r="L15" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1190" t="inlineStr">
+      <c r="A16" s="1265" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1191" t="n">
+      <c r="B16" s="1266" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1192" t="n">
+      <c r="C16" s="1267" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1193" t="n">
+      <c r="D16" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1194" t="n">
+      <c r="E16" s="1269" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1195" t="n">
+      <c r="F16" s="1270" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1196" t="n">
+      <c r="G16" s="1271" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1197" t="n">
+      <c r="H16" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1198" t="n">
+      <c r="I16" s="1273" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1199" t="n">
+      <c r="J16" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1200" t="n">
+      <c r="K16" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1201" t="n">
+      <c r="L16" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1190" t="inlineStr">
+      <c r="A17" s="1265" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1191" t="n">
+      <c r="B17" s="1266" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1192" t="n">
+      <c r="C17" s="1267" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1193" t="n">
+      <c r="D17" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1194" t="n">
+      <c r="E17" s="1269" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1195" t="n">
+      <c r="F17" s="1270" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1196" t="n">
+      <c r="G17" s="1271" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1197" t="n">
+      <c r="H17" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1198" t="n">
+      <c r="I17" s="1273" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1199" t="n">
+      <c r="J17" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1200" t="n">
+      <c r="K17" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1201" t="n">
+      <c r="L17" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1190" t="inlineStr">
+      <c r="A18" s="1265" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1191" t="n">
+      <c r="B18" s="1266" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1192" t="n">
+      <c r="C18" s="1267" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1193" t="n">
+      <c r="D18" s="1268" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1194" t="n">
+      <c r="E18" s="1269" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1195" t="n">
+      <c r="F18" s="1270" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1196" t="n">
+      <c r="G18" s="1271" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1197" t="n">
+      <c r="H18" s="1272" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1198" t="n">
+      <c r="I18" s="1273" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1199" t="n">
+      <c r="J18" s="1274" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1200" t="n">
+      <c r="K18" s="1275" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1201" t="n">
+      <c r="L18" s="1276" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5375,6 +5594,46 @@
         <v>0</v>
       </c>
       <c r="L19" s="1276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="1338" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B20" s="1339" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1340" t="n">
+        <v>313322.179959178</v>
+      </c>
+      <c r="D20" s="1341" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E20" s="1342" t="n">
+        <v>264592.0030117035</v>
+      </c>
+      <c r="F20" s="1343" t="n">
+        <v>13322.17995917797</v>
+      </c>
+      <c r="G20" s="1344" t="n">
+        <v>0.04440726653059324</v>
+      </c>
+      <c r="H20" s="1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1347" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5407,452 +5666,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1277" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  19 May 2026</t>
+      <c r="A1" s="1350" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  20 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1278" t="inlineStr">
+      <c r="A2" s="1351" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1278" t="inlineStr">
+      <c r="B2" s="1351" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1278" t="inlineStr">
+      <c r="C2" s="1351" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1278" t="inlineStr">
+      <c r="D2" s="1351" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1278" t="inlineStr">
+      <c r="E2" s="1351" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1278" t="inlineStr">
+      <c r="F2" s="1351" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1278" t="inlineStr">
+      <c r="G2" s="1351" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1278" t="inlineStr">
+      <c r="H2" s="1351" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1278" t="inlineStr">
+      <c r="I2" s="1351" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1278" t="inlineStr">
+      <c r="J2" s="1351" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1278" t="inlineStr">
+      <c r="K2" s="1351" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1279" t="inlineStr">
-        <is>
-          <t>WHA.BK</t>
-        </is>
-      </c>
-      <c r="B3" s="1280" t="inlineStr">
-        <is>
-          <t>WHA</t>
-        </is>
-      </c>
-      <c r="C3" s="1281" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D3" s="1282" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E3" s="1283" t="n">
-        <v>4.619999885559082</v>
-      </c>
-      <c r="F3" s="1284">
+      <c r="A3" s="1352" t="inlineStr">
+        <is>
+          <t>AMATA.BK</t>
+        </is>
+      </c>
+      <c r="B3" s="1353" t="inlineStr">
+        <is>
+          <t>AMATA</t>
+        </is>
+      </c>
+      <c r="C3" s="1354" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D3" s="1355" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E3" s="1356" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1357">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1285">
+      <c r="G3" s="1358">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1286">
+      <c r="H3" s="1359">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1287" t="inlineStr">
+      <c r="I3" s="1360" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1288" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="K3" s="1289" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+      <c r="J3" s="1361" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="K3" s="1362" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1279" t="inlineStr">
-        <is>
-          <t>AMATA.BK</t>
-        </is>
-      </c>
-      <c r="B4" s="1280" t="inlineStr">
-        <is>
-          <t>AMATA</t>
-        </is>
-      </c>
-      <c r="C4" s="1281" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D4" s="1282" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E4" s="1283" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F4" s="1284">
+      <c r="A4" s="1352" t="inlineStr">
+        <is>
+          <t>WHA.BK</t>
+        </is>
+      </c>
+      <c r="B4" s="1353" t="inlineStr">
+        <is>
+          <t>WHA</t>
+        </is>
+      </c>
+      <c r="C4" s="1354" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D4" s="1355" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E4" s="1356" t="n">
+        <v>4.840000152587891</v>
+      </c>
+      <c r="F4" s="1357">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1285">
+      <c r="G4" s="1358">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1286">
+      <c r="H4" s="1359">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1287" t="inlineStr">
+      <c r="I4" s="1360" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1290" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="K4" s="1291" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="J4" s="1363" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="K4" s="1364" t="inlineStr">
+        <is>
+          <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1279" t="inlineStr">
+      <c r="A5" s="1352" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1280" t="inlineStr">
+      <c r="B5" s="1353" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1281" t="n">
+      <c r="C5" s="1354" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1282" t="n">
+      <c r="D5" s="1355" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1283" t="n">
-        <v>17.39999961853027</v>
-      </c>
-      <c r="F5" s="1284">
+      <c r="E5" s="1356" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F5" s="1357">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1285">
+      <c r="G5" s="1358">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1286">
+      <c r="H5" s="1359">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1287" t="inlineStr">
+      <c r="I5" s="1360" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1292" t="n">
+      <c r="J5" s="1365" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1293" t="inlineStr">
+      <c r="K5" s="1366" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1294" t="inlineStr">
+      <c r="A6" s="1367" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B6" s="1295" t="inlineStr">
+      <c r="B6" s="1368" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C6" s="1296" t="n">
+      <c r="C6" s="1369" t="n">
         <v>1600</v>
       </c>
-      <c r="D6" s="1297" t="n">
+      <c r="D6" s="1370" t="n">
         <v>29.25</v>
       </c>
-      <c r="E6" s="1298" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="F6" s="1299">
+      <c r="E6" s="1371" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1372">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1300">
+      <c r="G6" s="1373">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1301">
+      <c r="H6" s="1374">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1302" t="inlineStr">
+      <c r="I6" s="1375" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1303" t="n">
+      <c r="J6" s="1376" t="n">
         <v>5.88</v>
       </c>
-      <c r="K6" s="1304" t="inlineStr">
+      <c r="K6" s="1377" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1305" t="inlineStr">
+      <c r="A7" s="1378" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1306" t="inlineStr">
+      <c r="B7" s="1379" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1307" t="n">
+      <c r="C7" s="1380" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1308" t="n">
+      <c r="D7" s="1381" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1309" t="n">
-        <v>15.80000019073486</v>
-      </c>
-      <c r="F7" s="1310">
+      <c r="E7" s="1382" t="n">
+        <v>16.20000076293945</v>
+      </c>
+      <c r="F7" s="1383">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1311">
+      <c r="G7" s="1384">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1312">
+      <c r="H7" s="1385">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1313" t="inlineStr">
+      <c r="I7" s="1386" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1314" t="n">
+      <c r="J7" s="1387" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1315" t="inlineStr">
+      <c r="K7" s="1388" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1294" t="inlineStr">
+      <c r="A8" s="1367" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1295" t="inlineStr">
+      <c r="B8" s="1368" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1296" t="n">
+      <c r="C8" s="1369" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1297" t="n">
+      <c r="D8" s="1370" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1298" t="n">
-        <v>4.21999979019165</v>
-      </c>
-      <c r="F8" s="1299">
+      <c r="E8" s="1371" t="n">
+        <v>4.199999809265137</v>
+      </c>
+      <c r="F8" s="1372">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1300">
+      <c r="G8" s="1373">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1301">
+      <c r="H8" s="1374">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1302" t="inlineStr">
+      <c r="I8" s="1375" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1303" t="n">
+      <c r="J8" s="1376" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1304" t="inlineStr">
+      <c r="K8" s="1377" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1279" t="inlineStr">
+      <c r="A9" s="1367" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1280" t="inlineStr">
+      <c r="B9" s="1368" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1281" t="n">
+      <c r="C9" s="1369" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1282" t="n">
+      <c r="D9" s="1370" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1283" t="n">
-        <v>2.640000104904175</v>
-      </c>
-      <c r="F9" s="1284">
+      <c r="E9" s="1371" t="n">
+        <v>2.599999904632568</v>
+      </c>
+      <c r="F9" s="1372">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1285">
+      <c r="G9" s="1373">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1286">
+      <c r="H9" s="1374">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1287" t="inlineStr">
+      <c r="I9" s="1375" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1288" t="n">
+      <c r="J9" s="1376" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1289" t="inlineStr">
+      <c r="K9" s="1377" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1305" t="inlineStr">
+      <c r="A10" s="1367" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1306" t="inlineStr">
+      <c r="B10" s="1368" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1307" t="n">
+      <c r="C10" s="1369" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1308" t="n">
+      <c r="D10" s="1370" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1309" t="n">
-        <v>11.30000019073486</v>
-      </c>
-      <c r="F10" s="1310">
+      <c r="E10" s="1371" t="n">
+        <v>11.39999961853027</v>
+      </c>
+      <c r="F10" s="1372">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1311">
+      <c r="G10" s="1373">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1312">
+      <c r="H10" s="1374">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1313" t="inlineStr">
+      <c r="I10" s="1375" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1314" t="n">
+      <c r="J10" s="1376" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1315" t="inlineStr">
+      <c r="K10" s="1377" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1316" t="inlineStr">
+      <c r="B11" s="1389" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1317">
+      <c r="F11" s="1390">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1318">
+      <c r="G11" s="1391">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1319">
+      <c r="H11" s="1392">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -5887,14 +6146,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1277" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  19 May 2026</t>
+      <c r="A1" s="1350" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  20 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1320" t="inlineStr">
+      <c r="A3" s="1393" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -5932,550 +6191,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1277" t="inlineStr">
+      <c r="A1" s="1350" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1278" t="inlineStr">
+      <c r="A2" s="1351" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1278" t="inlineStr">
+      <c r="B2" s="1351" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1278" t="inlineStr">
+      <c r="C2" s="1351" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1278" t="inlineStr">
+      <c r="D2" s="1351" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1278" t="inlineStr">
+      <c r="E2" s="1351" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1278" t="inlineStr">
+      <c r="F2" s="1351" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1278" t="inlineStr">
+      <c r="G2" s="1351" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1278" t="inlineStr">
+      <c r="H2" s="1351" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1278" t="inlineStr">
+      <c r="I2" s="1351" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1278" t="inlineStr">
+      <c r="J2" s="1351" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1321" t="inlineStr">
+      <c r="A3" s="1394" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1322" t="inlineStr">
+      <c r="B3" s="1395" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1323" t="inlineStr">
+      <c r="C3" s="1396" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1324" t="inlineStr">
+      <c r="D3" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1325" t="n">
+      <c r="E3" s="1398" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1326" t="n">
+      <c r="F3" s="1399" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1325" t="n">
+      <c r="G3" s="1398" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1327">
+      <c r="H3" s="1400">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1328" t="inlineStr">
+      <c r="I3" s="1401" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1329" t="inlineStr">
+      <c r="J3" s="1402" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1330" t="inlineStr">
+      <c r="A4" s="1403" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1331" t="inlineStr">
+      <c r="B4" s="1404" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1295" t="inlineStr">
+      <c r="C4" s="1368" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1324" t="inlineStr">
+      <c r="D4" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1296" t="n">
+      <c r="E4" s="1369" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1297" t="n">
+      <c r="F4" s="1370" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1296" t="n">
+      <c r="G4" s="1369" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1299">
+      <c r="H4" s="1372">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1332" t="inlineStr">
+      <c r="I4" s="1405" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1333" t="inlineStr">
+      <c r="J4" s="1406" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1321" t="inlineStr">
+      <c r="A5" s="1394" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1322" t="inlineStr">
+      <c r="B5" s="1395" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1323" t="inlineStr">
+      <c r="C5" s="1396" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1324" t="inlineStr">
+      <c r="D5" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1325" t="n">
+      <c r="E5" s="1398" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1326" t="n">
+      <c r="F5" s="1399" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1325" t="n">
+      <c r="G5" s="1398" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1327">
+      <c r="H5" s="1400">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1328" t="inlineStr">
+      <c r="I5" s="1401" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1329" t="inlineStr">
+      <c r="J5" s="1402" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1330" t="inlineStr">
+      <c r="A6" s="1403" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1331" t="inlineStr">
+      <c r="B6" s="1404" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1295" t="inlineStr">
+      <c r="C6" s="1368" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1324" t="inlineStr">
+      <c r="D6" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1296" t="n">
+      <c r="E6" s="1369" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1297" t="n">
+      <c r="F6" s="1370" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1296" t="n">
+      <c r="G6" s="1369" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1299">
+      <c r="H6" s="1372">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1332" t="inlineStr">
+      <c r="I6" s="1405" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1333" t="inlineStr">
+      <c r="J6" s="1406" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1321" t="inlineStr">
+      <c r="A7" s="1394" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1322" t="inlineStr">
+      <c r="B7" s="1395" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1323" t="inlineStr">
+      <c r="C7" s="1396" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1324" t="inlineStr">
+      <c r="D7" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1325" t="n">
+      <c r="E7" s="1398" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1326" t="n">
+      <c r="F7" s="1399" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1325" t="n">
+      <c r="G7" s="1398" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1327">
+      <c r="H7" s="1400">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1328" t="inlineStr">
+      <c r="I7" s="1401" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1329" t="inlineStr">
+      <c r="J7" s="1402" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1330" t="inlineStr">
+      <c r="A8" s="1403" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1331" t="inlineStr">
+      <c r="B8" s="1404" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1295" t="inlineStr">
+      <c r="C8" s="1368" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1324" t="inlineStr">
+      <c r="D8" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1296" t="n">
+      <c r="E8" s="1369" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1297" t="n">
+      <c r="F8" s="1370" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1296" t="n">
+      <c r="G8" s="1369" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1299">
+      <c r="H8" s="1372">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1332" t="inlineStr">
+      <c r="I8" s="1405" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1333" t="inlineStr">
+      <c r="J8" s="1406" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1321" t="inlineStr">
+      <c r="A9" s="1394" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1322" t="inlineStr">
+      <c r="B9" s="1395" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1323" t="inlineStr">
+      <c r="C9" s="1396" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1334" t="inlineStr">
+      <c r="D9" s="1407" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1325" t="n">
+      <c r="E9" s="1398" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1326" t="n">
+      <c r="F9" s="1399" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1325" t="n">
+      <c r="G9" s="1398" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1327">
+      <c r="H9" s="1400">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1335" t="n">
+      <c r="I9" s="1408" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1329" t="inlineStr">
+      <c r="J9" s="1402" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1330" t="inlineStr">
+      <c r="A10" s="1403" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1331" t="inlineStr">
+      <c r="B10" s="1404" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1295" t="inlineStr">
+      <c r="C10" s="1368" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1334" t="inlineStr">
+      <c r="D10" s="1407" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1296" t="n">
+      <c r="E10" s="1369" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1297" t="n">
+      <c r="F10" s="1370" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1296" t="n">
+      <c r="G10" s="1369" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1299">
+      <c r="H10" s="1372">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1336" t="n">
+      <c r="I10" s="1409" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1333" t="inlineStr">
+      <c r="J10" s="1406" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1321" t="inlineStr">
+      <c r="A11" s="1394" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1322" t="inlineStr">
+      <c r="B11" s="1395" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1323" t="inlineStr">
+      <c r="C11" s="1396" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1324" t="inlineStr">
+      <c r="D11" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1325" t="n">
+      <c r="E11" s="1398" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1326" t="n">
+      <c r="F11" s="1399" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1325" t="n">
+      <c r="G11" s="1398" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1327">
+      <c r="H11" s="1400">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1328" t="inlineStr">
+      <c r="I11" s="1401" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1329" t="inlineStr">
+      <c r="J11" s="1402" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1330" t="inlineStr">
+      <c r="A12" s="1403" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1331" t="inlineStr">
+      <c r="B12" s="1404" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1295" t="inlineStr">
+      <c r="C12" s="1368" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1324" t="inlineStr">
+      <c r="D12" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1296" t="n">
+      <c r="E12" s="1369" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1297" t="n">
+      <c r="F12" s="1370" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1296" t="n">
+      <c r="G12" s="1369" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1299">
+      <c r="H12" s="1372">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1332" t="inlineStr">
+      <c r="I12" s="1405" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1333" t="inlineStr">
+      <c r="J12" s="1406" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1321" t="inlineStr">
+      <c r="A13" s="1394" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1322" t="inlineStr">
+      <c r="B13" s="1395" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1323" t="inlineStr">
+      <c r="C13" s="1396" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1324" t="inlineStr">
+      <c r="D13" s="1397" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1325" t="n">
+      <c r="E13" s="1398" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1326" t="n">
+      <c r="F13" s="1399" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1325" t="n">
+      <c r="G13" s="1398" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1327">
+      <c r="H13" s="1400">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1328" t="inlineStr">
+      <c r="I13" s="1401" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1329" t="inlineStr">
+      <c r="J13" s="1402" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6487,11 +6746,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1337">
+      <c r="H15" s="1410">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1337">
+      <c r="I15" s="1410">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1411">
+  <cellXfs count="1484">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4073,6 +4073,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4798,7 +5017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4878,47 +5097,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1265" t="inlineStr">
+      <c r="A2" s="1338" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1266" t="n">
+      <c r="B2" s="1339" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1267" t="n">
+      <c r="C2" s="1340" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1268" t="n">
+      <c r="D2" s="1341" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1269" t="n">
+      <c r="E2" s="1342" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1270" t="n">
+      <c r="F2" s="1343" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1271" t="n">
+      <c r="G2" s="1344" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1272" t="n">
+      <c r="H2" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1273" t="n">
+      <c r="I2" s="1346" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1274" t="n">
+      <c r="J2" s="1347" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1275" t="n">
+      <c r="K2" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1276" t="n">
+      <c r="L2" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1265" t="inlineStr">
+      <c r="A3" s="1338" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -4958,7 +5177,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1265" t="inlineStr">
+      <c r="A4" s="1338" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -4998,207 +5217,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1265" t="inlineStr">
+      <c r="A5" s="1338" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1266" t="n">
+      <c r="B5" s="1339" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1267" t="n">
+      <c r="C5" s="1340" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1268" t="n">
+      <c r="D5" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1269" t="n">
+      <c r="E5" s="1342" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1270" t="n">
+      <c r="F5" s="1343" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1271" t="n">
+      <c r="G5" s="1344" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1272" t="n">
+      <c r="H5" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1273" t="n">
+      <c r="I5" s="1346" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1274" t="n">
+      <c r="J5" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1275" t="n">
+      <c r="K5" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1276" t="n">
+      <c r="L5" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1265" t="inlineStr">
+      <c r="A6" s="1338" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1266" t="n">
+      <c r="B6" s="1339" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1267" t="n">
+      <c r="C6" s="1340" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1268" t="n">
+      <c r="D6" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1269" t="n">
+      <c r="E6" s="1342" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1270" t="n">
+      <c r="F6" s="1343" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1271" t="n">
+      <c r="G6" s="1344" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1272" t="n">
+      <c r="H6" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1273" t="n">
+      <c r="I6" s="1346" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1274" t="n">
+      <c r="J6" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1275" t="n">
+      <c r="K6" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1276" t="n">
+      <c r="L6" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1265" t="inlineStr">
+      <c r="A7" s="1338" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1266" t="n">
+      <c r="B7" s="1339" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1267" t="n">
+      <c r="C7" s="1340" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1268" t="n">
+      <c r="D7" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1269" t="n">
+      <c r="E7" s="1342" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1270" t="n">
+      <c r="F7" s="1343" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1271" t="n">
+      <c r="G7" s="1344" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1272" t="n">
+      <c r="H7" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1273" t="n">
+      <c r="I7" s="1346" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1274" t="n">
+      <c r="J7" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1275" t="n">
+      <c r="K7" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1276" t="n">
+      <c r="L7" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1265" t="inlineStr">
+      <c r="A8" s="1338" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1266" t="n">
+      <c r="B8" s="1339" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1267" t="n">
+      <c r="C8" s="1340" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1268" t="n">
+      <c r="D8" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1269" t="n">
+      <c r="E8" s="1342" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1270" t="n">
+      <c r="F8" s="1343" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1271" t="n">
+      <c r="G8" s="1344" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1272" t="n">
+      <c r="H8" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1273" t="n">
+      <c r="I8" s="1346" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1274" t="n">
+      <c r="J8" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1275" t="n">
+      <c r="K8" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1276" t="n">
+      <c r="L8" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1265" t="inlineStr">
+      <c r="A9" s="1338" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1266" t="n">
+      <c r="B9" s="1339" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1267" t="n">
+      <c r="C9" s="1340" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1268" t="n">
+      <c r="D9" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1269" t="n">
+      <c r="E9" s="1342" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1270" t="n">
+      <c r="F9" s="1343" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1271" t="n">
+      <c r="G9" s="1344" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1272" t="n">
+      <c r="H9" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1273" t="n">
+      <c r="I9" s="1346" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1274" t="n">
+      <c r="J9" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1275" t="n">
+      <c r="K9" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1276" t="n">
+      <c r="L9" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1265" t="inlineStr">
+      <c r="A10" s="1338" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -5238,362 +5457,362 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1265" t="inlineStr">
+      <c r="A11" s="1338" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1266" t="n">
+      <c r="B11" s="1339" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1267" t="n">
+      <c r="C11" s="1340" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1268" t="n">
+      <c r="D11" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1269" t="n">
+      <c r="E11" s="1342" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1270" t="n">
+      <c r="F11" s="1343" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1271" t="n">
+      <c r="G11" s="1344" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1272" t="n">
+      <c r="H11" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1273" t="n">
+      <c r="I11" s="1346" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1274" t="n">
+      <c r="J11" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1275" t="n">
+      <c r="K11" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1276" t="n">
+      <c r="L11" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1265" t="inlineStr">
+      <c r="A12" s="1338" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1266" t="n">
+      <c r="B12" s="1339" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1267" t="n">
+      <c r="C12" s="1340" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1268" t="n">
+      <c r="D12" s="1341" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1269" t="n">
+      <c r="E12" s="1342" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1270" t="n">
+      <c r="F12" s="1343" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1271" t="n">
+      <c r="G12" s="1344" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1272" t="n">
+      <c r="H12" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1273" t="n">
+      <c r="I12" s="1346" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1274" t="n">
+      <c r="J12" s="1347" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1275" t="n">
+      <c r="K12" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1276" t="n">
+      <c r="L12" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1265" t="inlineStr">
+      <c r="A13" s="1338" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1266" t="n">
+      <c r="B13" s="1339" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1267" t="n">
+      <c r="C13" s="1340" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1268" t="n">
+      <c r="D13" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1269" t="n">
+      <c r="E13" s="1342" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1270" t="n">
+      <c r="F13" s="1343" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1271" t="n">
+      <c r="G13" s="1344" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1272" t="n">
+      <c r="H13" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1273" t="n">
+      <c r="I13" s="1346" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1274" t="n">
+      <c r="J13" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1275" t="n">
+      <c r="K13" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1276" t="n">
+      <c r="L13" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1265" t="inlineStr">
+      <c r="A14" s="1338" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1266" t="n">
+      <c r="B14" s="1339" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1267" t="n">
+      <c r="C14" s="1340" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1268" t="n">
+      <c r="D14" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1269" t="n">
+      <c r="E14" s="1342" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1270" t="n">
+      <c r="F14" s="1343" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1271" t="n">
+      <c r="G14" s="1344" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1272" t="n">
+      <c r="H14" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1273" t="n">
+      <c r="I14" s="1346" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1274" t="n">
+      <c r="J14" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1275" t="n">
+      <c r="K14" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1276" t="n">
+      <c r="L14" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1265" t="inlineStr">
+      <c r="A15" s="1338" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1266" t="n">
+      <c r="B15" s="1339" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1267" t="n">
+      <c r="C15" s="1340" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1268" t="n">
+      <c r="D15" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1269" t="n">
+      <c r="E15" s="1342" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1270" t="n">
+      <c r="F15" s="1343" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1271" t="n">
+      <c r="G15" s="1344" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1272" t="n">
+      <c r="H15" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1273" t="n">
+      <c r="I15" s="1346" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1274" t="n">
+      <c r="J15" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1275" t="n">
+      <c r="K15" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1276" t="n">
+      <c r="L15" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1265" t="inlineStr">
+      <c r="A16" s="1338" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1266" t="n">
+      <c r="B16" s="1339" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1267" t="n">
+      <c r="C16" s="1340" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1268" t="n">
+      <c r="D16" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1269" t="n">
+      <c r="E16" s="1342" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1270" t="n">
+      <c r="F16" s="1343" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1271" t="n">
+      <c r="G16" s="1344" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1272" t="n">
+      <c r="H16" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1273" t="n">
+      <c r="I16" s="1346" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1274" t="n">
+      <c r="J16" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1275" t="n">
+      <c r="K16" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1276" t="n">
+      <c r="L16" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1265" t="inlineStr">
+      <c r="A17" s="1338" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1266" t="n">
+      <c r="B17" s="1339" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1267" t="n">
+      <c r="C17" s="1340" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1268" t="n">
+      <c r="D17" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1269" t="n">
+      <c r="E17" s="1342" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1270" t="n">
+      <c r="F17" s="1343" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1271" t="n">
+      <c r="G17" s="1344" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1272" t="n">
+      <c r="H17" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1273" t="n">
+      <c r="I17" s="1346" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1274" t="n">
+      <c r="J17" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1275" t="n">
+      <c r="K17" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1276" t="n">
+      <c r="L17" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1265" t="inlineStr">
+      <c r="A18" s="1338" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1266" t="n">
+      <c r="B18" s="1339" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1267" t="n">
+      <c r="C18" s="1340" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1268" t="n">
+      <c r="D18" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1269" t="n">
+      <c r="E18" s="1342" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1270" t="n">
+      <c r="F18" s="1343" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1271" t="n">
+      <c r="G18" s="1344" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1272" t="n">
+      <c r="H18" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1273" t="n">
+      <c r="I18" s="1346" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1274" t="n">
+      <c r="J18" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1275" t="n">
+      <c r="K18" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1276" t="n">
+      <c r="L18" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1265" t="inlineStr">
+      <c r="A19" s="1338" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1266" t="n">
+      <c r="B19" s="1339" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1267" t="n">
+      <c r="C19" s="1340" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1268" t="n">
+      <c r="D19" s="1341" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1269" t="n">
+      <c r="E19" s="1342" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1270" t="n">
+      <c r="F19" s="1343" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1271" t="n">
+      <c r="G19" s="1344" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1272" t="n">
+      <c r="H19" s="1345" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1273" t="n">
+      <c r="I19" s="1346" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1274" t="n">
+      <c r="J19" s="1347" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1275" t="n">
+      <c r="K19" s="1348" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="1276" t="n">
+      <c r="L19" s="1349" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5634,6 +5853,46 @@
         <v>0</v>
       </c>
       <c r="L20" s="1349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="1411" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B21" s="1412" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1413" t="n">
+        <v>313566.1793926954</v>
+      </c>
+      <c r="D21" s="1414" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E21" s="1415" t="n">
+        <v>264836.0024452209</v>
+      </c>
+      <c r="F21" s="1416" t="n">
+        <v>13566.17939269543</v>
+      </c>
+      <c r="G21" s="1417" t="n">
+        <v>0.04522059797565142</v>
+      </c>
+      <c r="H21" s="1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1420" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5666,452 +5925,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1350" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  20 May 2026</t>
+      <c r="A1" s="1423" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  21 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1351" t="inlineStr">
+      <c r="A2" s="1424" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1351" t="inlineStr">
+      <c r="B2" s="1424" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1351" t="inlineStr">
+      <c r="C2" s="1424" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1351" t="inlineStr">
+      <c r="D2" s="1424" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1351" t="inlineStr">
+      <c r="E2" s="1424" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1351" t="inlineStr">
+      <c r="F2" s="1424" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1351" t="inlineStr">
+      <c r="G2" s="1424" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1351" t="inlineStr">
+      <c r="H2" s="1424" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1351" t="inlineStr">
+      <c r="I2" s="1424" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1351" t="inlineStr">
+      <c r="J2" s="1424" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1351" t="inlineStr">
+      <c r="K2" s="1424" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1352" t="inlineStr">
+      <c r="A3" s="1425" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1353" t="inlineStr">
+      <c r="B3" s="1426" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1354" t="n">
+      <c r="C3" s="1427" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1355" t="n">
+      <c r="D3" s="1428" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1356" t="n">
+      <c r="E3" s="1429" t="n">
         <v>24</v>
       </c>
-      <c r="F3" s="1357">
+      <c r="F3" s="1430">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1358">
+      <c r="G3" s="1431">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1359">
+      <c r="H3" s="1432">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1360" t="inlineStr">
+      <c r="I3" s="1433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1361" t="n">
+      <c r="J3" s="1434" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1362" t="inlineStr">
+      <c r="K3" s="1435" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1352" t="inlineStr">
+      <c r="A4" s="1425" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1353" t="inlineStr">
+      <c r="B4" s="1426" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1354" t="n">
+      <c r="C4" s="1427" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1355" t="n">
+      <c r="D4" s="1428" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1356" t="n">
-        <v>4.840000152587891</v>
-      </c>
-      <c r="F4" s="1357">
+      <c r="E4" s="1429" t="n">
+        <v>4.800000190734863</v>
+      </c>
+      <c r="F4" s="1430">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1358">
+      <c r="G4" s="1431">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1359">
+      <c r="H4" s="1432">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1360" t="inlineStr">
+      <c r="I4" s="1433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1363" t="n">
+      <c r="J4" s="1436" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1364" t="inlineStr">
+      <c r="K4" s="1437" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1352" t="inlineStr">
+      <c r="A5" s="1425" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1353" t="inlineStr">
+      <c r="B5" s="1426" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1354" t="n">
+      <c r="C5" s="1427" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1355" t="n">
+      <c r="D5" s="1428" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1356" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F5" s="1357">
+      <c r="E5" s="1429" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1430">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1358">
+      <c r="G5" s="1431">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1359">
+      <c r="H5" s="1432">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1360" t="inlineStr">
+      <c r="I5" s="1433" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1365" t="n">
+      <c r="J5" s="1438" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1366" t="inlineStr">
+      <c r="K5" s="1439" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1367" t="inlineStr">
+      <c r="A6" s="1440" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B6" s="1368" t="inlineStr">
+      <c r="B6" s="1441" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C6" s="1369" t="n">
+      <c r="C6" s="1442" t="n">
         <v>1600</v>
       </c>
-      <c r="D6" s="1370" t="n">
+      <c r="D6" s="1443" t="n">
         <v>29.25</v>
       </c>
-      <c r="E6" s="1371" t="n">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1372">
+      <c r="E6" s="1444" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="F6" s="1445">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1373">
+      <c r="G6" s="1446">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1374">
+      <c r="H6" s="1447">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1375" t="inlineStr">
+      <c r="I6" s="1448" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1376" t="n">
+      <c r="J6" s="1449" t="n">
         <v>5.88</v>
       </c>
-      <c r="K6" s="1377" t="inlineStr">
+      <c r="K6" s="1450" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1378" t="inlineStr">
+      <c r="A7" s="1451" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B7" s="1379" t="inlineStr">
+      <c r="B7" s="1452" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C7" s="1380" t="n">
+      <c r="C7" s="1453" t="n">
         <v>2700</v>
       </c>
-      <c r="D7" s="1381" t="n">
+      <c r="D7" s="1454" t="n">
         <v>17.4</v>
       </c>
-      <c r="E7" s="1382" t="n">
-        <v>16.20000076293945</v>
-      </c>
-      <c r="F7" s="1383">
+      <c r="E7" s="1455" t="n">
+        <v>16.10000038146973</v>
+      </c>
+      <c r="F7" s="1456">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1384">
+      <c r="G7" s="1457">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1385">
+      <c r="H7" s="1458">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1386" t="inlineStr">
+      <c r="I7" s="1459" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1387" t="n">
+      <c r="J7" s="1460" t="n">
         <v>5.68</v>
       </c>
-      <c r="K7" s="1388" t="inlineStr">
+      <c r="K7" s="1461" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1367" t="inlineStr">
+      <c r="A8" s="1440" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1368" t="inlineStr">
+      <c r="B8" s="1441" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1369" t="n">
+      <c r="C8" s="1442" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1370" t="n">
+      <c r="D8" s="1443" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1371" t="n">
+      <c r="E8" s="1444" t="n">
         <v>4.199999809265137</v>
       </c>
-      <c r="F8" s="1372">
+      <c r="F8" s="1445">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1373">
+      <c r="G8" s="1446">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1374">
+      <c r="H8" s="1447">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1375" t="inlineStr">
+      <c r="I8" s="1448" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1376" t="n">
+      <c r="J8" s="1449" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1377" t="inlineStr">
+      <c r="K8" s="1450" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1367" t="inlineStr">
+      <c r="A9" s="1440" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1368" t="inlineStr">
+      <c r="B9" s="1441" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1369" t="n">
+      <c r="C9" s="1442" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1370" t="n">
+      <c r="D9" s="1443" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1371" t="n">
-        <v>2.599999904632568</v>
-      </c>
-      <c r="F9" s="1372">
+      <c r="E9" s="1444" t="n">
+        <v>2.619999885559082</v>
+      </c>
+      <c r="F9" s="1445">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1373">
+      <c r="G9" s="1446">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1374">
+      <c r="H9" s="1447">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1375" t="inlineStr">
+      <c r="I9" s="1448" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1376" t="n">
+      <c r="J9" s="1449" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1377" t="inlineStr">
+      <c r="K9" s="1450" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1367" t="inlineStr">
+      <c r="A10" s="1451" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1368" t="inlineStr">
+      <c r="B10" s="1452" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1369" t="n">
+      <c r="C10" s="1453" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1370" t="n">
+      <c r="D10" s="1454" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1371" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="F10" s="1372">
+      <c r="E10" s="1455" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="F10" s="1456">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1373">
+      <c r="G10" s="1457">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1374">
+      <c r="H10" s="1458">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1375" t="inlineStr">
+      <c r="I10" s="1459" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1376" t="n">
+      <c r="J10" s="1460" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1377" t="inlineStr">
+      <c r="K10" s="1461" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1389" t="inlineStr">
+      <c r="B11" s="1462" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1390">
+      <c r="F11" s="1463">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1391">
+      <c r="G11" s="1464">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1392">
+      <c r="H11" s="1465">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -6146,14 +6405,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1350" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  20 May 2026</t>
+      <c r="A1" s="1423" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  21 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1393" t="inlineStr">
+      <c r="A3" s="1466" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -6191,550 +6450,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1350" t="inlineStr">
+      <c r="A1" s="1423" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1351" t="inlineStr">
+      <c r="A2" s="1424" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1351" t="inlineStr">
+      <c r="B2" s="1424" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1351" t="inlineStr">
+      <c r="C2" s="1424" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1351" t="inlineStr">
+      <c r="D2" s="1424" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1351" t="inlineStr">
+      <c r="E2" s="1424" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1351" t="inlineStr">
+      <c r="F2" s="1424" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1351" t="inlineStr">
+      <c r="G2" s="1424" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1351" t="inlineStr">
+      <c r="H2" s="1424" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1351" t="inlineStr">
+      <c r="I2" s="1424" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1351" t="inlineStr">
+      <c r="J2" s="1424" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1394" t="inlineStr">
+      <c r="A3" s="1467" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1395" t="inlineStr">
+      <c r="B3" s="1468" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1396" t="inlineStr">
+      <c r="C3" s="1469" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1397" t="inlineStr">
+      <c r="D3" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1398" t="n">
+      <c r="E3" s="1471" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1399" t="n">
+      <c r="F3" s="1472" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1398" t="n">
+      <c r="G3" s="1471" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1400">
+      <c r="H3" s="1473">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1401" t="inlineStr">
+      <c r="I3" s="1474" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1402" t="inlineStr">
+      <c r="J3" s="1475" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1403" t="inlineStr">
+      <c r="A4" s="1476" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1404" t="inlineStr">
+      <c r="B4" s="1477" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1368" t="inlineStr">
+      <c r="C4" s="1441" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1397" t="inlineStr">
+      <c r="D4" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1369" t="n">
+      <c r="E4" s="1442" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1370" t="n">
+      <c r="F4" s="1443" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1369" t="n">
+      <c r="G4" s="1442" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1372">
+      <c r="H4" s="1445">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1405" t="inlineStr">
+      <c r="I4" s="1478" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1406" t="inlineStr">
+      <c r="J4" s="1479" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1394" t="inlineStr">
+      <c r="A5" s="1467" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1395" t="inlineStr">
+      <c r="B5" s="1468" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1396" t="inlineStr">
+      <c r="C5" s="1469" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1397" t="inlineStr">
+      <c r="D5" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1398" t="n">
+      <c r="E5" s="1471" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1399" t="n">
+      <c r="F5" s="1472" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1398" t="n">
+      <c r="G5" s="1471" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1400">
+      <c r="H5" s="1473">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1401" t="inlineStr">
+      <c r="I5" s="1474" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1402" t="inlineStr">
+      <c r="J5" s="1475" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1403" t="inlineStr">
+      <c r="A6" s="1476" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1404" t="inlineStr">
+      <c r="B6" s="1477" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1368" t="inlineStr">
+      <c r="C6" s="1441" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1397" t="inlineStr">
+      <c r="D6" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1369" t="n">
+      <c r="E6" s="1442" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1370" t="n">
+      <c r="F6" s="1443" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1369" t="n">
+      <c r="G6" s="1442" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1372">
+      <c r="H6" s="1445">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1405" t="inlineStr">
+      <c r="I6" s="1478" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1406" t="inlineStr">
+      <c r="J6" s="1479" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1394" t="inlineStr">
+      <c r="A7" s="1467" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1395" t="inlineStr">
+      <c r="B7" s="1468" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1396" t="inlineStr">
+      <c r="C7" s="1469" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1397" t="inlineStr">
+      <c r="D7" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1398" t="n">
+      <c r="E7" s="1471" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1399" t="n">
+      <c r="F7" s="1472" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1398" t="n">
+      <c r="G7" s="1471" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1400">
+      <c r="H7" s="1473">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1401" t="inlineStr">
+      <c r="I7" s="1474" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1402" t="inlineStr">
+      <c r="J7" s="1475" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1403" t="inlineStr">
+      <c r="A8" s="1476" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1404" t="inlineStr">
+      <c r="B8" s="1477" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1368" t="inlineStr">
+      <c r="C8" s="1441" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1397" t="inlineStr">
+      <c r="D8" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1369" t="n">
+      <c r="E8" s="1442" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1370" t="n">
+      <c r="F8" s="1443" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1369" t="n">
+      <c r="G8" s="1442" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1372">
+      <c r="H8" s="1445">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1405" t="inlineStr">
+      <c r="I8" s="1478" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1406" t="inlineStr">
+      <c r="J8" s="1479" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1394" t="inlineStr">
+      <c r="A9" s="1467" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1395" t="inlineStr">
+      <c r="B9" s="1468" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1396" t="inlineStr">
+      <c r="C9" s="1469" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1407" t="inlineStr">
+      <c r="D9" s="1480" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1398" t="n">
+      <c r="E9" s="1471" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1399" t="n">
+      <c r="F9" s="1472" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1398" t="n">
+      <c r="G9" s="1471" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1400">
+      <c r="H9" s="1473">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1408" t="n">
+      <c r="I9" s="1481" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1402" t="inlineStr">
+      <c r="J9" s="1475" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1403" t="inlineStr">
+      <c r="A10" s="1476" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1404" t="inlineStr">
+      <c r="B10" s="1477" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1368" t="inlineStr">
+      <c r="C10" s="1441" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1407" t="inlineStr">
+      <c r="D10" s="1480" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1369" t="n">
+      <c r="E10" s="1442" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1370" t="n">
+      <c r="F10" s="1443" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1369" t="n">
+      <c r="G10" s="1442" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1372">
+      <c r="H10" s="1445">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1409" t="n">
+      <c r="I10" s="1482" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1406" t="inlineStr">
+      <c r="J10" s="1479" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1394" t="inlineStr">
+      <c r="A11" s="1467" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1395" t="inlineStr">
+      <c r="B11" s="1468" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1396" t="inlineStr">
+      <c r="C11" s="1469" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1397" t="inlineStr">
+      <c r="D11" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1398" t="n">
+      <c r="E11" s="1471" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1399" t="n">
+      <c r="F11" s="1472" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1398" t="n">
+      <c r="G11" s="1471" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1400">
+      <c r="H11" s="1473">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1401" t="inlineStr">
+      <c r="I11" s="1474" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1402" t="inlineStr">
+      <c r="J11" s="1475" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1403" t="inlineStr">
+      <c r="A12" s="1476" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1404" t="inlineStr">
+      <c r="B12" s="1477" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1368" t="inlineStr">
+      <c r="C12" s="1441" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1397" t="inlineStr">
+      <c r="D12" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1369" t="n">
+      <c r="E12" s="1442" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1370" t="n">
+      <c r="F12" s="1443" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1369" t="n">
+      <c r="G12" s="1442" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1372">
+      <c r="H12" s="1445">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1405" t="inlineStr">
+      <c r="I12" s="1478" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1406" t="inlineStr">
+      <c r="J12" s="1479" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1394" t="inlineStr">
+      <c r="A13" s="1467" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1395" t="inlineStr">
+      <c r="B13" s="1468" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1396" t="inlineStr">
+      <c r="C13" s="1469" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1397" t="inlineStr">
+      <c r="D13" s="1470" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1398" t="n">
+      <c r="E13" s="1471" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1399" t="n">
+      <c r="F13" s="1472" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1398" t="n">
+      <c r="G13" s="1471" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1400">
+      <c r="H13" s="1473">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1401" t="inlineStr">
+      <c r="I13" s="1474" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1402" t="inlineStr">
+      <c r="J13" s="1475" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -6746,11 +7005,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1410">
+      <c r="H15" s="1483">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1410">
+      <c r="I15" s="1483">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1484">
+  <cellXfs count="1557">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4073,6 +4073,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5017,7 +5236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5097,47 +5316,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1338" t="inlineStr">
+      <c r="A2" s="1411" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1339" t="n">
+      <c r="B2" s="1412" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1340" t="n">
+      <c r="C2" s="1413" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1341" t="n">
+      <c r="D2" s="1414" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1342" t="n">
+      <c r="E2" s="1415" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1343" t="n">
+      <c r="F2" s="1416" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1344" t="n">
+      <c r="G2" s="1417" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1345" t="n">
+      <c r="H2" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1346" t="n">
+      <c r="I2" s="1419" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1347" t="n">
+      <c r="J2" s="1420" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1348" t="n">
+      <c r="K2" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1349" t="n">
+      <c r="L2" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1338" t="inlineStr">
+      <c r="A3" s="1411" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -5177,7 +5396,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1338" t="inlineStr">
+      <c r="A4" s="1411" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -5217,207 +5436,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1338" t="inlineStr">
+      <c r="A5" s="1411" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1339" t="n">
+      <c r="B5" s="1412" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1340" t="n">
+      <c r="C5" s="1413" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1341" t="n">
+      <c r="D5" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1342" t="n">
+      <c r="E5" s="1415" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1343" t="n">
+      <c r="F5" s="1416" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1344" t="n">
+      <c r="G5" s="1417" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1345" t="n">
+      <c r="H5" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1346" t="n">
+      <c r="I5" s="1419" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1347" t="n">
+      <c r="J5" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1348" t="n">
+      <c r="K5" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1349" t="n">
+      <c r="L5" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1338" t="inlineStr">
+      <c r="A6" s="1411" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1339" t="n">
+      <c r="B6" s="1412" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1340" t="n">
+      <c r="C6" s="1413" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1341" t="n">
+      <c r="D6" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1342" t="n">
+      <c r="E6" s="1415" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1343" t="n">
+      <c r="F6" s="1416" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1344" t="n">
+      <c r="G6" s="1417" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1345" t="n">
+      <c r="H6" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1346" t="n">
+      <c r="I6" s="1419" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1347" t="n">
+      <c r="J6" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1348" t="n">
+      <c r="K6" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1349" t="n">
+      <c r="L6" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1338" t="inlineStr">
+      <c r="A7" s="1411" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1339" t="n">
+      <c r="B7" s="1412" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1340" t="n">
+      <c r="C7" s="1413" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1341" t="n">
+      <c r="D7" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1342" t="n">
+      <c r="E7" s="1415" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1343" t="n">
+      <c r="F7" s="1416" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1344" t="n">
+      <c r="G7" s="1417" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1345" t="n">
+      <c r="H7" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1346" t="n">
+      <c r="I7" s="1419" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1347" t="n">
+      <c r="J7" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1348" t="n">
+      <c r="K7" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1349" t="n">
+      <c r="L7" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1338" t="inlineStr">
+      <c r="A8" s="1411" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1339" t="n">
+      <c r="B8" s="1412" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1340" t="n">
+      <c r="C8" s="1413" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1341" t="n">
+      <c r="D8" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1342" t="n">
+      <c r="E8" s="1415" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1343" t="n">
+      <c r="F8" s="1416" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1344" t="n">
+      <c r="G8" s="1417" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1345" t="n">
+      <c r="H8" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1346" t="n">
+      <c r="I8" s="1419" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1347" t="n">
+      <c r="J8" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1348" t="n">
+      <c r="K8" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1349" t="n">
+      <c r="L8" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1338" t="inlineStr">
+      <c r="A9" s="1411" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1339" t="n">
+      <c r="B9" s="1412" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1340" t="n">
+      <c r="C9" s="1413" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1341" t="n">
+      <c r="D9" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1342" t="n">
+      <c r="E9" s="1415" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1343" t="n">
+      <c r="F9" s="1416" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1344" t="n">
+      <c r="G9" s="1417" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1345" t="n">
+      <c r="H9" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1346" t="n">
+      <c r="I9" s="1419" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1347" t="n">
+      <c r="J9" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1348" t="n">
+      <c r="K9" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1349" t="n">
+      <c r="L9" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1338" t="inlineStr">
+      <c r="A10" s="1411" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -5457,402 +5676,402 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1338" t="inlineStr">
+      <c r="A11" s="1411" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1339" t="n">
+      <c r="B11" s="1412" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1340" t="n">
+      <c r="C11" s="1413" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1341" t="n">
+      <c r="D11" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1342" t="n">
+      <c r="E11" s="1415" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1343" t="n">
+      <c r="F11" s="1416" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1344" t="n">
+      <c r="G11" s="1417" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1345" t="n">
+      <c r="H11" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1346" t="n">
+      <c r="I11" s="1419" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1347" t="n">
+      <c r="J11" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1348" t="n">
+      <c r="K11" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1349" t="n">
+      <c r="L11" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1338" t="inlineStr">
+      <c r="A12" s="1411" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1339" t="n">
+      <c r="B12" s="1412" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1340" t="n">
+      <c r="C12" s="1413" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1341" t="n">
+      <c r="D12" s="1414" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1342" t="n">
+      <c r="E12" s="1415" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1343" t="n">
+      <c r="F12" s="1416" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1344" t="n">
+      <c r="G12" s="1417" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1345" t="n">
+      <c r="H12" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1346" t="n">
+      <c r="I12" s="1419" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1347" t="n">
+      <c r="J12" s="1420" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1348" t="n">
+      <c r="K12" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1349" t="n">
+      <c r="L12" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1338" t="inlineStr">
+      <c r="A13" s="1411" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1339" t="n">
+      <c r="B13" s="1412" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1340" t="n">
+      <c r="C13" s="1413" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1341" t="n">
+      <c r="D13" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1342" t="n">
+      <c r="E13" s="1415" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1343" t="n">
+      <c r="F13" s="1416" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1344" t="n">
+      <c r="G13" s="1417" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1345" t="n">
+      <c r="H13" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1346" t="n">
+      <c r="I13" s="1419" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1347" t="n">
+      <c r="J13" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1348" t="n">
+      <c r="K13" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1349" t="n">
+      <c r="L13" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1338" t="inlineStr">
+      <c r="A14" s="1411" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1339" t="n">
+      <c r="B14" s="1412" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1340" t="n">
+      <c r="C14" s="1413" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1341" t="n">
+      <c r="D14" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1342" t="n">
+      <c r="E14" s="1415" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1343" t="n">
+      <c r="F14" s="1416" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1344" t="n">
+      <c r="G14" s="1417" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1345" t="n">
+      <c r="H14" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1346" t="n">
+      <c r="I14" s="1419" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1347" t="n">
+      <c r="J14" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1348" t="n">
+      <c r="K14" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1349" t="n">
+      <c r="L14" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1338" t="inlineStr">
+      <c r="A15" s="1411" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1339" t="n">
+      <c r="B15" s="1412" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1340" t="n">
+      <c r="C15" s="1413" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1341" t="n">
+      <c r="D15" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1342" t="n">
+      <c r="E15" s="1415" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1343" t="n">
+      <c r="F15" s="1416" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1344" t="n">
+      <c r="G15" s="1417" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1345" t="n">
+      <c r="H15" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1346" t="n">
+      <c r="I15" s="1419" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1347" t="n">
+      <c r="J15" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1348" t="n">
+      <c r="K15" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1349" t="n">
+      <c r="L15" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1338" t="inlineStr">
+      <c r="A16" s="1411" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1339" t="n">
+      <c r="B16" s="1412" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1340" t="n">
+      <c r="C16" s="1413" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1341" t="n">
+      <c r="D16" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1342" t="n">
+      <c r="E16" s="1415" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1343" t="n">
+      <c r="F16" s="1416" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1344" t="n">
+      <c r="G16" s="1417" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1345" t="n">
+      <c r="H16" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1346" t="n">
+      <c r="I16" s="1419" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1347" t="n">
+      <c r="J16" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1348" t="n">
+      <c r="K16" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1349" t="n">
+      <c r="L16" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1338" t="inlineStr">
+      <c r="A17" s="1411" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1339" t="n">
+      <c r="B17" s="1412" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1340" t="n">
+      <c r="C17" s="1413" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1341" t="n">
+      <c r="D17" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1342" t="n">
+      <c r="E17" s="1415" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1343" t="n">
+      <c r="F17" s="1416" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1344" t="n">
+      <c r="G17" s="1417" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1345" t="n">
+      <c r="H17" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1346" t="n">
+      <c r="I17" s="1419" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1347" t="n">
+      <c r="J17" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1348" t="n">
+      <c r="K17" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1349" t="n">
+      <c r="L17" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1338" t="inlineStr">
+      <c r="A18" s="1411" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1339" t="n">
+      <c r="B18" s="1412" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1340" t="n">
+      <c r="C18" s="1413" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1341" t="n">
+      <c r="D18" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1342" t="n">
+      <c r="E18" s="1415" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1343" t="n">
+      <c r="F18" s="1416" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1344" t="n">
+      <c r="G18" s="1417" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1345" t="n">
+      <c r="H18" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1346" t="n">
+      <c r="I18" s="1419" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1347" t="n">
+      <c r="J18" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1348" t="n">
+      <c r="K18" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1349" t="n">
+      <c r="L18" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1338" t="inlineStr">
+      <c r="A19" s="1411" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1339" t="n">
+      <c r="B19" s="1412" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1340" t="n">
+      <c r="C19" s="1413" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1341" t="n">
+      <c r="D19" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1342" t="n">
+      <c r="E19" s="1415" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1343" t="n">
+      <c r="F19" s="1416" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1344" t="n">
+      <c r="G19" s="1417" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1345" t="n">
+      <c r="H19" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1346" t="n">
+      <c r="I19" s="1419" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1347" t="n">
+      <c r="J19" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1348" t="n">
+      <c r="K19" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="1349" t="n">
+      <c r="L19" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1338" t="inlineStr">
+      <c r="A20" s="1411" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1339" t="n">
+      <c r="B20" s="1412" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1340" t="n">
+      <c r="C20" s="1413" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1341" t="n">
+      <c r="D20" s="1414" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1342" t="n">
+      <c r="E20" s="1415" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1343" t="n">
+      <c r="F20" s="1416" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1344" t="n">
+      <c r="G20" s="1417" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1345" t="n">
+      <c r="H20" s="1418" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="1346" t="n">
+      <c r="I20" s="1419" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="1347" t="n">
+      <c r="J20" s="1420" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1348" t="n">
+      <c r="K20" s="1421" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="1349" t="n">
+      <c r="L20" s="1422" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5893,6 +6112,46 @@
         <v>0</v>
       </c>
       <c r="L21" s="1422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="1484" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B22" s="1485" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1486" t="n">
+        <v>321999.1744259596</v>
+      </c>
+      <c r="D22" s="1487" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E22" s="1488" t="n">
+        <v>273268.9974784851</v>
+      </c>
+      <c r="F22" s="1489" t="n">
+        <v>21999.17442595959</v>
+      </c>
+      <c r="G22" s="1490" t="n">
+        <v>0.07333058141986529</v>
+      </c>
+      <c r="H22" s="1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1493" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5925,452 +6184,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1423" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  21 May 2026</t>
+      <c r="A1" s="1496" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  22 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1424" t="inlineStr">
+      <c r="A2" s="1497" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1424" t="inlineStr">
+      <c r="B2" s="1497" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1424" t="inlineStr">
+      <c r="C2" s="1497" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1424" t="inlineStr">
+      <c r="D2" s="1497" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1424" t="inlineStr">
+      <c r="E2" s="1497" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1424" t="inlineStr">
+      <c r="F2" s="1497" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1424" t="inlineStr">
+      <c r="G2" s="1497" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1424" t="inlineStr">
+      <c r="H2" s="1497" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1424" t="inlineStr">
+      <c r="I2" s="1497" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1424" t="inlineStr">
+      <c r="J2" s="1497" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1424" t="inlineStr">
+      <c r="K2" s="1497" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1425" t="inlineStr">
+      <c r="A3" s="1498" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1426" t="inlineStr">
+      <c r="B3" s="1499" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1427" t="n">
+      <c r="C3" s="1500" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1428" t="n">
+      <c r="D3" s="1501" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1429" t="n">
-        <v>24</v>
-      </c>
-      <c r="F3" s="1430">
+      <c r="E3" s="1502" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F3" s="1503">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1431">
+      <c r="G3" s="1504">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1432">
+      <c r="H3" s="1505">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1433" t="inlineStr">
+      <c r="I3" s="1506" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1434" t="n">
+      <c r="J3" s="1507" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1435" t="inlineStr">
+      <c r="K3" s="1508" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1425" t="inlineStr">
+      <c r="A4" s="1498" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1426" t="inlineStr">
+      <c r="B4" s="1499" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1427" t="n">
+      <c r="C4" s="1500" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1428" t="n">
+      <c r="D4" s="1501" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1429" t="n">
-        <v>4.800000190734863</v>
-      </c>
-      <c r="F4" s="1430">
+      <c r="E4" s="1502" t="n">
+        <v>4.880000114440918</v>
+      </c>
+      <c r="F4" s="1503">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1431">
+      <c r="G4" s="1504">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1432">
+      <c r="H4" s="1505">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1433" t="inlineStr">
+      <c r="I4" s="1506" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1436" t="n">
+      <c r="J4" s="1509" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1437" t="inlineStr">
+      <c r="K4" s="1510" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1425" t="inlineStr">
+      <c r="A5" s="1498" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1426" t="inlineStr">
+      <c r="B5" s="1499" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1427" t="n">
+      <c r="C5" s="1500" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1428" t="n">
+      <c r="D5" s="1501" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1429" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1430">
+      <c r="E5" s="1502" t="n">
+        <v>17.89999961853027</v>
+      </c>
+      <c r="F5" s="1503">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1431">
+      <c r="G5" s="1504">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1432">
+      <c r="H5" s="1505">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1433" t="inlineStr">
+      <c r="I5" s="1506" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1438" t="n">
+      <c r="J5" s="1511" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1439" t="inlineStr">
+      <c r="K5" s="1512" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1440" t="inlineStr">
-        <is>
-          <t>KTC.BK</t>
-        </is>
-      </c>
-      <c r="B6" s="1441" t="inlineStr">
-        <is>
-          <t>KTC</t>
-        </is>
-      </c>
-      <c r="C6" s="1442" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D6" s="1443" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="E6" s="1444" t="n">
-        <v>28.75</v>
-      </c>
-      <c r="F6" s="1445">
+      <c r="A6" s="1498" t="inlineStr">
+        <is>
+          <t>TIDLOR.BK</t>
+        </is>
+      </c>
+      <c r="B6" s="1499" t="inlineStr">
+        <is>
+          <t>TIDLOR</t>
+        </is>
+      </c>
+      <c r="C6" s="1500" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D6" s="1501" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E6" s="1502" t="n">
+        <v>17.79999923706055</v>
+      </c>
+      <c r="F6" s="1503">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1446">
+      <c r="G6" s="1504">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1447">
+      <c r="H6" s="1505">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1448" t="inlineStr">
+      <c r="I6" s="1506" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1449" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="K6" s="1450" t="inlineStr">
+      <c r="J6" s="1509" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K6" s="1510" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1451" t="inlineStr">
-        <is>
-          <t>TIDLOR.BK</t>
-        </is>
-      </c>
-      <c r="B7" s="1452" t="inlineStr">
-        <is>
-          <t>TIDLOR</t>
-        </is>
-      </c>
-      <c r="C7" s="1453" t="n">
-        <v>2700</v>
-      </c>
-      <c r="D7" s="1454" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E7" s="1455" t="n">
-        <v>16.10000038146973</v>
-      </c>
-      <c r="F7" s="1456">
+      <c r="A7" s="1513" t="inlineStr">
+        <is>
+          <t>KTC.BK</t>
+        </is>
+      </c>
+      <c r="B7" s="1514" t="inlineStr">
+        <is>
+          <t>KTC</t>
+        </is>
+      </c>
+      <c r="C7" s="1515" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D7" s="1516" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="E7" s="1517" t="n">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1518">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1457">
+      <c r="G7" s="1519">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1458">
+      <c r="H7" s="1520">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1459" t="inlineStr">
+      <c r="I7" s="1521" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1460" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K7" s="1461" t="inlineStr">
+      <c r="J7" s="1522" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K7" s="1523" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1440" t="inlineStr">
+      <c r="A8" s="1513" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1441" t="inlineStr">
+      <c r="B8" s="1514" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1442" t="n">
+      <c r="C8" s="1515" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1443" t="n">
+      <c r="D8" s="1516" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1444" t="n">
-        <v>4.199999809265137</v>
-      </c>
-      <c r="F8" s="1445">
+      <c r="E8" s="1517" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F8" s="1518">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1446">
+      <c r="G8" s="1519">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1447">
+      <c r="H8" s="1520">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1448" t="inlineStr">
+      <c r="I8" s="1521" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1449" t="n">
+      <c r="J8" s="1522" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1450" t="inlineStr">
+      <c r="K8" s="1523" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1440" t="inlineStr">
+      <c r="A9" s="1513" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1441" t="inlineStr">
+      <c r="B9" s="1514" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1442" t="n">
+      <c r="C9" s="1515" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1443" t="n">
+      <c r="D9" s="1516" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1444" t="n">
-        <v>2.619999885559082</v>
-      </c>
-      <c r="F9" s="1445">
+      <c r="E9" s="1517" t="n">
+        <v>2.599999904632568</v>
+      </c>
+      <c r="F9" s="1518">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1446">
+      <c r="G9" s="1519">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1447">
+      <c r="H9" s="1520">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1448" t="inlineStr">
+      <c r="I9" s="1521" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1449" t="n">
+      <c r="J9" s="1522" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1450" t="inlineStr">
+      <c r="K9" s="1523" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1451" t="inlineStr">
+      <c r="A10" s="1524" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1452" t="inlineStr">
+      <c r="B10" s="1525" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1453" t="n">
+      <c r="C10" s="1526" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1454" t="n">
+      <c r="D10" s="1527" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1455" t="n">
+      <c r="E10" s="1528" t="n">
         <v>11.19999980926514</v>
       </c>
-      <c r="F10" s="1456">
+      <c r="F10" s="1529">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1457">
+      <c r="G10" s="1530">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1458">
+      <c r="H10" s="1531">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1459" t="inlineStr">
+      <c r="I10" s="1532" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1460" t="n">
+      <c r="J10" s="1533" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1461" t="inlineStr">
+      <c r="K10" s="1534" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1462" t="inlineStr">
+      <c r="B11" s="1535" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1463">
+      <c r="F11" s="1536">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1464">
+      <c r="G11" s="1537">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1465">
+      <c r="H11" s="1538">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -6405,14 +6664,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1423" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  21 May 2026</t>
+      <c r="A1" s="1496" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  22 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1466" t="inlineStr">
+      <c r="A3" s="1539" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -6450,550 +6709,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1423" t="inlineStr">
+      <c r="A1" s="1496" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1424" t="inlineStr">
+      <c r="A2" s="1497" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1424" t="inlineStr">
+      <c r="B2" s="1497" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1424" t="inlineStr">
+      <c r="C2" s="1497" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1424" t="inlineStr">
+      <c r="D2" s="1497" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1424" t="inlineStr">
+      <c r="E2" s="1497" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1424" t="inlineStr">
+      <c r="F2" s="1497" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1424" t="inlineStr">
+      <c r="G2" s="1497" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1424" t="inlineStr">
+      <c r="H2" s="1497" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1424" t="inlineStr">
+      <c r="I2" s="1497" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1424" t="inlineStr">
+      <c r="J2" s="1497" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1467" t="inlineStr">
+      <c r="A3" s="1540" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1468" t="inlineStr">
+      <c r="B3" s="1541" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1469" t="inlineStr">
+      <c r="C3" s="1542" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1470" t="inlineStr">
+      <c r="D3" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1471" t="n">
+      <c r="E3" s="1544" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1472" t="n">
+      <c r="F3" s="1545" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1471" t="n">
+      <c r="G3" s="1544" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1473">
+      <c r="H3" s="1546">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1474" t="inlineStr">
+      <c r="I3" s="1547" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1475" t="inlineStr">
+      <c r="J3" s="1548" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1476" t="inlineStr">
+      <c r="A4" s="1549" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1477" t="inlineStr">
+      <c r="B4" s="1550" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1441" t="inlineStr">
+      <c r="C4" s="1514" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1470" t="inlineStr">
+      <c r="D4" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1442" t="n">
+      <c r="E4" s="1515" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1443" t="n">
+      <c r="F4" s="1516" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1442" t="n">
+      <c r="G4" s="1515" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1445">
+      <c r="H4" s="1518">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1478" t="inlineStr">
+      <c r="I4" s="1551" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1479" t="inlineStr">
+      <c r="J4" s="1552" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1467" t="inlineStr">
+      <c r="A5" s="1540" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1468" t="inlineStr">
+      <c r="B5" s="1541" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1469" t="inlineStr">
+      <c r="C5" s="1542" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1470" t="inlineStr">
+      <c r="D5" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1471" t="n">
+      <c r="E5" s="1544" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1472" t="n">
+      <c r="F5" s="1545" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1471" t="n">
+      <c r="G5" s="1544" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1473">
+      <c r="H5" s="1546">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1474" t="inlineStr">
+      <c r="I5" s="1547" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1475" t="inlineStr">
+      <c r="J5" s="1548" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1476" t="inlineStr">
+      <c r="A6" s="1549" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1477" t="inlineStr">
+      <c r="B6" s="1550" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1441" t="inlineStr">
+      <c r="C6" s="1514" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1470" t="inlineStr">
+      <c r="D6" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1442" t="n">
+      <c r="E6" s="1515" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1443" t="n">
+      <c r="F6" s="1516" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1442" t="n">
+      <c r="G6" s="1515" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1445">
+      <c r="H6" s="1518">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1478" t="inlineStr">
+      <c r="I6" s="1551" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1479" t="inlineStr">
+      <c r="J6" s="1552" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1467" t="inlineStr">
+      <c r="A7" s="1540" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1468" t="inlineStr">
+      <c r="B7" s="1541" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1469" t="inlineStr">
+      <c r="C7" s="1542" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1470" t="inlineStr">
+      <c r="D7" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1471" t="n">
+      <c r="E7" s="1544" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1472" t="n">
+      <c r="F7" s="1545" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1471" t="n">
+      <c r="G7" s="1544" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1473">
+      <c r="H7" s="1546">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1474" t="inlineStr">
+      <c r="I7" s="1547" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1475" t="inlineStr">
+      <c r="J7" s="1548" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1476" t="inlineStr">
+      <c r="A8" s="1549" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1477" t="inlineStr">
+      <c r="B8" s="1550" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1441" t="inlineStr">
+      <c r="C8" s="1514" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1470" t="inlineStr">
+      <c r="D8" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1442" t="n">
+      <c r="E8" s="1515" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1443" t="n">
+      <c r="F8" s="1516" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1442" t="n">
+      <c r="G8" s="1515" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1445">
+      <c r="H8" s="1518">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1478" t="inlineStr">
+      <c r="I8" s="1551" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1479" t="inlineStr">
+      <c r="J8" s="1552" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1467" t="inlineStr">
+      <c r="A9" s="1540" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1468" t="inlineStr">
+      <c r="B9" s="1541" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1469" t="inlineStr">
+      <c r="C9" s="1542" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1480" t="inlineStr">
+      <c r="D9" s="1553" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1471" t="n">
+      <c r="E9" s="1544" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1472" t="n">
+      <c r="F9" s="1545" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1471" t="n">
+      <c r="G9" s="1544" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1473">
+      <c r="H9" s="1546">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1481" t="n">
+      <c r="I9" s="1554" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1475" t="inlineStr">
+      <c r="J9" s="1548" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1476" t="inlineStr">
+      <c r="A10" s="1549" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1477" t="inlineStr">
+      <c r="B10" s="1550" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1441" t="inlineStr">
+      <c r="C10" s="1514" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1480" t="inlineStr">
+      <c r="D10" s="1553" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1442" t="n">
+      <c r="E10" s="1515" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1443" t="n">
+      <c r="F10" s="1516" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1442" t="n">
+      <c r="G10" s="1515" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1445">
+      <c r="H10" s="1518">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1482" t="n">
+      <c r="I10" s="1555" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1479" t="inlineStr">
+      <c r="J10" s="1552" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1467" t="inlineStr">
+      <c r="A11" s="1540" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1468" t="inlineStr">
+      <c r="B11" s="1541" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1469" t="inlineStr">
+      <c r="C11" s="1542" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1470" t="inlineStr">
+      <c r="D11" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1471" t="n">
+      <c r="E11" s="1544" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1472" t="n">
+      <c r="F11" s="1545" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1471" t="n">
+      <c r="G11" s="1544" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1473">
+      <c r="H11" s="1546">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1474" t="inlineStr">
+      <c r="I11" s="1547" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1475" t="inlineStr">
+      <c r="J11" s="1548" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1476" t="inlineStr">
+      <c r="A12" s="1549" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1477" t="inlineStr">
+      <c r="B12" s="1550" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1441" t="inlineStr">
+      <c r="C12" s="1514" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1470" t="inlineStr">
+      <c r="D12" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1442" t="n">
+      <c r="E12" s="1515" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1443" t="n">
+      <c r="F12" s="1516" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1442" t="n">
+      <c r="G12" s="1515" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1445">
+      <c r="H12" s="1518">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1478" t="inlineStr">
+      <c r="I12" s="1551" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1479" t="inlineStr">
+      <c r="J12" s="1552" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1467" t="inlineStr">
+      <c r="A13" s="1540" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1468" t="inlineStr">
+      <c r="B13" s="1541" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1469" t="inlineStr">
+      <c r="C13" s="1542" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1470" t="inlineStr">
+      <c r="D13" s="1543" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1471" t="n">
+      <c r="E13" s="1544" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1472" t="n">
+      <c r="F13" s="1545" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1471" t="n">
+      <c r="G13" s="1544" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1473">
+      <c r="H13" s="1546">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1474" t="inlineStr">
+      <c r="I13" s="1547" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1475" t="inlineStr">
+      <c r="J13" s="1548" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -7005,11 +7264,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1483">
+      <c r="H15" s="1556">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1483">
+      <c r="I15" s="1556">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1557">
+  <cellXfs count="1630">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4073,6 +4073,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5236,7 +5455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5316,47 +5535,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1411" t="inlineStr">
+      <c r="A2" s="1484" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1412" t="n">
+      <c r="B2" s="1485" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1413" t="n">
+      <c r="C2" s="1486" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1414" t="n">
+      <c r="D2" s="1487" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1415" t="n">
+      <c r="E2" s="1488" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1416" t="n">
+      <c r="F2" s="1489" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1417" t="n">
+      <c r="G2" s="1490" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1418" t="n">
+      <c r="H2" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1419" t="n">
+      <c r="I2" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1420" t="n">
+      <c r="J2" s="1493" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1421" t="n">
+      <c r="K2" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1422" t="n">
+      <c r="L2" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1411" t="inlineStr">
+      <c r="A3" s="1484" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -5396,7 +5615,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1411" t="inlineStr">
+      <c r="A4" s="1484" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -5436,207 +5655,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1411" t="inlineStr">
+      <c r="A5" s="1484" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1412" t="n">
+      <c r="B5" s="1485" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1413" t="n">
+      <c r="C5" s="1486" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1414" t="n">
+      <c r="D5" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1415" t="n">
+      <c r="E5" s="1488" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1416" t="n">
+      <c r="F5" s="1489" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1417" t="n">
+      <c r="G5" s="1490" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1418" t="n">
+      <c r="H5" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1419" t="n">
+      <c r="I5" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1420" t="n">
+      <c r="J5" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1421" t="n">
+      <c r="K5" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1422" t="n">
+      <c r="L5" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1411" t="inlineStr">
+      <c r="A6" s="1484" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1412" t="n">
+      <c r="B6" s="1485" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1413" t="n">
+      <c r="C6" s="1486" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1414" t="n">
+      <c r="D6" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1415" t="n">
+      <c r="E6" s="1488" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1416" t="n">
+      <c r="F6" s="1489" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1417" t="n">
+      <c r="G6" s="1490" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1418" t="n">
+      <c r="H6" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1419" t="n">
+      <c r="I6" s="1492" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1420" t="n">
+      <c r="J6" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1421" t="n">
+      <c r="K6" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1422" t="n">
+      <c r="L6" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1411" t="inlineStr">
+      <c r="A7" s="1484" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1412" t="n">
+      <c r="B7" s="1485" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1413" t="n">
+      <c r="C7" s="1486" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1414" t="n">
+      <c r="D7" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1415" t="n">
+      <c r="E7" s="1488" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1416" t="n">
+      <c r="F7" s="1489" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1417" t="n">
+      <c r="G7" s="1490" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1418" t="n">
+      <c r="H7" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1419" t="n">
+      <c r="I7" s="1492" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1420" t="n">
+      <c r="J7" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1421" t="n">
+      <c r="K7" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1422" t="n">
+      <c r="L7" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1411" t="inlineStr">
+      <c r="A8" s="1484" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1412" t="n">
+      <c r="B8" s="1485" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1413" t="n">
+      <c r="C8" s="1486" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1414" t="n">
+      <c r="D8" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1415" t="n">
+      <c r="E8" s="1488" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1416" t="n">
+      <c r="F8" s="1489" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1417" t="n">
+      <c r="G8" s="1490" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1418" t="n">
+      <c r="H8" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1419" t="n">
+      <c r="I8" s="1492" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1420" t="n">
+      <c r="J8" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1421" t="n">
+      <c r="K8" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1422" t="n">
+      <c r="L8" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1411" t="inlineStr">
+      <c r="A9" s="1484" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1412" t="n">
+      <c r="B9" s="1485" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1413" t="n">
+      <c r="C9" s="1486" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1414" t="n">
+      <c r="D9" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1415" t="n">
+      <c r="E9" s="1488" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1416" t="n">
+      <c r="F9" s="1489" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1417" t="n">
+      <c r="G9" s="1490" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1418" t="n">
+      <c r="H9" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1419" t="n">
+      <c r="I9" s="1492" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1420" t="n">
+      <c r="J9" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1421" t="n">
+      <c r="K9" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1422" t="n">
+      <c r="L9" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1411" t="inlineStr">
+      <c r="A10" s="1484" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -5676,442 +5895,442 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1411" t="inlineStr">
+      <c r="A11" s="1484" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1412" t="n">
+      <c r="B11" s="1485" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1413" t="n">
+      <c r="C11" s="1486" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1414" t="n">
+      <c r="D11" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1415" t="n">
+      <c r="E11" s="1488" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1416" t="n">
+      <c r="F11" s="1489" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1417" t="n">
+      <c r="G11" s="1490" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1418" t="n">
+      <c r="H11" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1419" t="n">
+      <c r="I11" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1420" t="n">
+      <c r="J11" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1421" t="n">
+      <c r="K11" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1422" t="n">
+      <c r="L11" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1411" t="inlineStr">
+      <c r="A12" s="1484" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1412" t="n">
+      <c r="B12" s="1485" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1413" t="n">
+      <c r="C12" s="1486" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1414" t="n">
+      <c r="D12" s="1487" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1415" t="n">
+      <c r="E12" s="1488" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1416" t="n">
+      <c r="F12" s="1489" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1417" t="n">
+      <c r="G12" s="1490" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1418" t="n">
+      <c r="H12" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1419" t="n">
+      <c r="I12" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1420" t="n">
+      <c r="J12" s="1493" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1421" t="n">
+      <c r="K12" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1422" t="n">
+      <c r="L12" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1411" t="inlineStr">
+      <c r="A13" s="1484" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1412" t="n">
+      <c r="B13" s="1485" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1413" t="n">
+      <c r="C13" s="1486" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1414" t="n">
+      <c r="D13" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1415" t="n">
+      <c r="E13" s="1488" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1416" t="n">
+      <c r="F13" s="1489" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1417" t="n">
+      <c r="G13" s="1490" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1418" t="n">
+      <c r="H13" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1419" t="n">
+      <c r="I13" s="1492" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1420" t="n">
+      <c r="J13" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1421" t="n">
+      <c r="K13" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1422" t="n">
+      <c r="L13" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1411" t="inlineStr">
+      <c r="A14" s="1484" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1412" t="n">
+      <c r="B14" s="1485" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1413" t="n">
+      <c r="C14" s="1486" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1414" t="n">
+      <c r="D14" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1415" t="n">
+      <c r="E14" s="1488" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1416" t="n">
+      <c r="F14" s="1489" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1417" t="n">
+      <c r="G14" s="1490" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1418" t="n">
+      <c r="H14" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1419" t="n">
+      <c r="I14" s="1492" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1420" t="n">
+      <c r="J14" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1421" t="n">
+      <c r="K14" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1422" t="n">
+      <c r="L14" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1411" t="inlineStr">
+      <c r="A15" s="1484" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1412" t="n">
+      <c r="B15" s="1485" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1413" t="n">
+      <c r="C15" s="1486" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1414" t="n">
+      <c r="D15" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1415" t="n">
+      <c r="E15" s="1488" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1416" t="n">
+      <c r="F15" s="1489" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1417" t="n">
+      <c r="G15" s="1490" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1418" t="n">
+      <c r="H15" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1419" t="n">
+      <c r="I15" s="1492" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1420" t="n">
+      <c r="J15" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1421" t="n">
+      <c r="K15" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1422" t="n">
+      <c r="L15" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1411" t="inlineStr">
+      <c r="A16" s="1484" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1412" t="n">
+      <c r="B16" s="1485" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1413" t="n">
+      <c r="C16" s="1486" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1414" t="n">
+      <c r="D16" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1415" t="n">
+      <c r="E16" s="1488" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1416" t="n">
+      <c r="F16" s="1489" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1417" t="n">
+      <c r="G16" s="1490" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1418" t="n">
+      <c r="H16" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1419" t="n">
+      <c r="I16" s="1492" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1420" t="n">
+      <c r="J16" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1421" t="n">
+      <c r="K16" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1422" t="n">
+      <c r="L16" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1411" t="inlineStr">
+      <c r="A17" s="1484" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1412" t="n">
+      <c r="B17" s="1485" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1413" t="n">
+      <c r="C17" s="1486" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1414" t="n">
+      <c r="D17" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1415" t="n">
+      <c r="E17" s="1488" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1416" t="n">
+      <c r="F17" s="1489" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1417" t="n">
+      <c r="G17" s="1490" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1418" t="n">
+      <c r="H17" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1419" t="n">
+      <c r="I17" s="1492" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1420" t="n">
+      <c r="J17" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1421" t="n">
+      <c r="K17" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1422" t="n">
+      <c r="L17" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1411" t="inlineStr">
+      <c r="A18" s="1484" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1412" t="n">
+      <c r="B18" s="1485" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1413" t="n">
+      <c r="C18" s="1486" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1414" t="n">
+      <c r="D18" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1415" t="n">
+      <c r="E18" s="1488" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1416" t="n">
+      <c r="F18" s="1489" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1417" t="n">
+      <c r="G18" s="1490" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1418" t="n">
+      <c r="H18" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1419" t="n">
+      <c r="I18" s="1492" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1420" t="n">
+      <c r="J18" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1421" t="n">
+      <c r="K18" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1422" t="n">
+      <c r="L18" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1411" t="inlineStr">
+      <c r="A19" s="1484" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1412" t="n">
+      <c r="B19" s="1485" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1413" t="n">
+      <c r="C19" s="1486" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1414" t="n">
+      <c r="D19" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1415" t="n">
+      <c r="E19" s="1488" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1416" t="n">
+      <c r="F19" s="1489" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1417" t="n">
+      <c r="G19" s="1490" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1418" t="n">
+      <c r="H19" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1419" t="n">
+      <c r="I19" s="1492" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1420" t="n">
+      <c r="J19" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1421" t="n">
+      <c r="K19" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="1422" t="n">
+      <c r="L19" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1411" t="inlineStr">
+      <c r="A20" s="1484" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1412" t="n">
+      <c r="B20" s="1485" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1413" t="n">
+      <c r="C20" s="1486" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1414" t="n">
+      <c r="D20" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1415" t="n">
+      <c r="E20" s="1488" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1416" t="n">
+      <c r="F20" s="1489" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1417" t="n">
+      <c r="G20" s="1490" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1418" t="n">
+      <c r="H20" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="1419" t="n">
+      <c r="I20" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="1420" t="n">
+      <c r="J20" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1421" t="n">
+      <c r="K20" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="1422" t="n">
+      <c r="L20" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1411" t="inlineStr">
+      <c r="A21" s="1484" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B21" s="1412" t="n">
+      <c r="B21" s="1485" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="1413" t="n">
+      <c r="C21" s="1486" t="n">
         <v>313566.1793926954</v>
       </c>
-      <c r="D21" s="1414" t="n">
+      <c r="D21" s="1487" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E21" s="1415" t="n">
+      <c r="E21" s="1488" t="n">
         <v>264836.0024452209</v>
       </c>
-      <c r="F21" s="1416" t="n">
+      <c r="F21" s="1489" t="n">
         <v>13566.17939269543</v>
       </c>
-      <c r="G21" s="1417" t="n">
+      <c r="G21" s="1490" t="n">
         <v>0.04522059797565142</v>
       </c>
-      <c r="H21" s="1418" t="n">
+      <c r="H21" s="1491" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="1419" t="n">
+      <c r="I21" s="1492" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1420" t="n">
+      <c r="J21" s="1493" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="1421" t="n">
+      <c r="K21" s="1494" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1422" t="n">
+      <c r="L21" s="1495" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6152,6 +6371,46 @@
         <v>0</v>
       </c>
       <c r="L22" s="1495" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="1557" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B23" s="1558" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1559" t="n">
+        <v>323626.1765698195</v>
+      </c>
+      <c r="D23" s="1560" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E23" s="1561" t="n">
+        <v>274895.999622345</v>
+      </c>
+      <c r="F23" s="1562" t="n">
+        <v>23626.17656981945</v>
+      </c>
+      <c r="G23" s="1563" t="n">
+        <v>0.07875392189939817</v>
+      </c>
+      <c r="H23" s="1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1566" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" s="1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6184,452 +6443,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1496" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  22 May 2026</t>
+      <c r="A1" s="1569" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  25 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1497" t="inlineStr">
+      <c r="A2" s="1570" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1497" t="inlineStr">
+      <c r="B2" s="1570" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1497" t="inlineStr">
+      <c r="C2" s="1570" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1497" t="inlineStr">
+      <c r="D2" s="1570" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1497" t="inlineStr">
+      <c r="E2" s="1570" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1497" t="inlineStr">
+      <c r="F2" s="1570" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1497" t="inlineStr">
+      <c r="G2" s="1570" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1497" t="inlineStr">
+      <c r="H2" s="1570" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1497" t="inlineStr">
+      <c r="I2" s="1570" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1497" t="inlineStr">
+      <c r="J2" s="1570" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1497" t="inlineStr">
+      <c r="K2" s="1570" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1498" t="inlineStr">
+      <c r="A3" s="1571" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1499" t="inlineStr">
+      <c r="B3" s="1572" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1500" t="n">
+      <c r="C3" s="1573" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1501" t="n">
+      <c r="D3" s="1574" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1502" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="F3" s="1503">
+      <c r="E3" s="1575" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1576">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1504">
+      <c r="G3" s="1577">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1505">
+      <c r="H3" s="1578">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1506" t="inlineStr">
+      <c r="I3" s="1579" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1507" t="n">
+      <c r="J3" s="1580" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1508" t="inlineStr">
+      <c r="K3" s="1581" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1498" t="inlineStr">
+      <c r="A4" s="1571" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1499" t="inlineStr">
+      <c r="B4" s="1572" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1500" t="n">
+      <c r="C4" s="1573" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1501" t="n">
+      <c r="D4" s="1574" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1502" t="n">
-        <v>4.880000114440918</v>
-      </c>
-      <c r="F4" s="1503">
+      <c r="E4" s="1575" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1576">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1504">
+      <c r="G4" s="1577">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1505">
+      <c r="H4" s="1578">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1506" t="inlineStr">
+      <c r="I4" s="1579" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1509" t="n">
+      <c r="J4" s="1582" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1510" t="inlineStr">
+      <c r="K4" s="1583" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1498" t="inlineStr">
+      <c r="A5" s="1571" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1499" t="inlineStr">
+      <c r="B5" s="1572" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1500" t="n">
+      <c r="C5" s="1573" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1501" t="n">
+      <c r="D5" s="1574" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1502" t="n">
-        <v>17.89999961853027</v>
-      </c>
-      <c r="F5" s="1503">
+      <c r="E5" s="1575" t="n">
+        <v>18.20000076293945</v>
+      </c>
+      <c r="F5" s="1576">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1504">
+      <c r="G5" s="1577">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1505">
+      <c r="H5" s="1578">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1506" t="inlineStr">
+      <c r="I5" s="1579" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1511" t="n">
+      <c r="J5" s="1584" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1512" t="inlineStr">
+      <c r="K5" s="1585" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1498" t="inlineStr">
+      <c r="A6" s="1571" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B6" s="1499" t="inlineStr">
+      <c r="B6" s="1572" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C6" s="1500" t="n">
+      <c r="C6" s="1573" t="n">
         <v>2700</v>
       </c>
-      <c r="D6" s="1501" t="n">
+      <c r="D6" s="1574" t="n">
         <v>17.4</v>
       </c>
-      <c r="E6" s="1502" t="n">
+      <c r="E6" s="1575" t="n">
         <v>17.79999923706055</v>
       </c>
-      <c r="F6" s="1503">
+      <c r="F6" s="1576">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1504">
+      <c r="G6" s="1577">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1505">
+      <c r="H6" s="1578">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1506" t="inlineStr">
+      <c r="I6" s="1579" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1509" t="n">
+      <c r="J6" s="1582" t="n">
         <v>5.68</v>
       </c>
-      <c r="K6" s="1510" t="inlineStr">
+      <c r="K6" s="1583" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1513" t="inlineStr">
+      <c r="A7" s="1586" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="1514" t="inlineStr">
+      <c r="B7" s="1587" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="1515" t="n">
+      <c r="C7" s="1588" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="1516" t="n">
+      <c r="D7" s="1589" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="1517" t="n">
+      <c r="E7" s="1590" t="n">
         <v>29</v>
       </c>
-      <c r="F7" s="1518">
+      <c r="F7" s="1591">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1519">
+      <c r="G7" s="1592">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1520">
+      <c r="H7" s="1593">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1521" t="inlineStr">
+      <c r="I7" s="1594" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1522" t="n">
+      <c r="J7" s="1595" t="n">
         <v>5.88</v>
       </c>
-      <c r="K7" s="1523" t="inlineStr">
+      <c r="K7" s="1596" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1513" t="inlineStr">
+      <c r="A8" s="1586" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1514" t="inlineStr">
+      <c r="B8" s="1587" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1515" t="n">
+      <c r="C8" s="1588" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1516" t="n">
+      <c r="D8" s="1589" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1517" t="n">
-        <v>4.21999979019165</v>
-      </c>
-      <c r="F8" s="1518">
+      <c r="E8" s="1590" t="n">
+        <v>4.199999809265137</v>
+      </c>
+      <c r="F8" s="1591">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1519">
+      <c r="G8" s="1592">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1520">
+      <c r="H8" s="1593">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1521" t="inlineStr">
+      <c r="I8" s="1594" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1522" t="n">
+      <c r="J8" s="1595" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1523" t="inlineStr">
+      <c r="K8" s="1596" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1513" t="inlineStr">
+      <c r="A9" s="1586" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1514" t="inlineStr">
+      <c r="B9" s="1587" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1515" t="n">
+      <c r="C9" s="1588" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1516" t="n">
+      <c r="D9" s="1589" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1517" t="n">
-        <v>2.599999904632568</v>
-      </c>
-      <c r="F9" s="1518">
+      <c r="E9" s="1590" t="n">
+        <v>2.619999885559082</v>
+      </c>
+      <c r="F9" s="1591">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1519">
+      <c r="G9" s="1592">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1520">
+      <c r="H9" s="1593">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1521" t="inlineStr">
+      <c r="I9" s="1594" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1522" t="n">
+      <c r="J9" s="1595" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1523" t="inlineStr">
+      <c r="K9" s="1596" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1524" t="inlineStr">
+      <c r="A10" s="1597" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1525" t="inlineStr">
+      <c r="B10" s="1598" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1526" t="n">
+      <c r="C10" s="1599" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1527" t="n">
+      <c r="D10" s="1600" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1528" t="n">
-        <v>11.19999980926514</v>
-      </c>
-      <c r="F10" s="1529">
+      <c r="E10" s="1601" t="n">
+        <v>11.30000019073486</v>
+      </c>
+      <c r="F10" s="1602">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1530">
+      <c r="G10" s="1603">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1531">
+      <c r="H10" s="1604">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1532" t="inlineStr">
+      <c r="I10" s="1605" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1533" t="n">
+      <c r="J10" s="1606" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1534" t="inlineStr">
+      <c r="K10" s="1607" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1535" t="inlineStr">
+      <c r="B11" s="1608" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1536">
+      <c r="F11" s="1609">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1537">
+      <c r="G11" s="1610">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1538">
+      <c r="H11" s="1611">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -6664,14 +6923,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1496" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  22 May 2026</t>
+      <c r="A1" s="1569" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  25 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1539" t="inlineStr">
+      <c r="A3" s="1612" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -6709,550 +6968,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1496" t="inlineStr">
+      <c r="A1" s="1569" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1497" t="inlineStr">
+      <c r="A2" s="1570" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1497" t="inlineStr">
+      <c r="B2" s="1570" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1497" t="inlineStr">
+      <c r="C2" s="1570" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1497" t="inlineStr">
+      <c r="D2" s="1570" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1497" t="inlineStr">
+      <c r="E2" s="1570" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1497" t="inlineStr">
+      <c r="F2" s="1570" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1497" t="inlineStr">
+      <c r="G2" s="1570" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1497" t="inlineStr">
+      <c r="H2" s="1570" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1497" t="inlineStr">
+      <c r="I2" s="1570" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1497" t="inlineStr">
+      <c r="J2" s="1570" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1540" t="inlineStr">
+      <c r="A3" s="1613" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1541" t="inlineStr">
+      <c r="B3" s="1614" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1542" t="inlineStr">
+      <c r="C3" s="1615" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1543" t="inlineStr">
+      <c r="D3" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1544" t="n">
+      <c r="E3" s="1617" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1545" t="n">
+      <c r="F3" s="1618" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1544" t="n">
+      <c r="G3" s="1617" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1546">
+      <c r="H3" s="1619">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1547" t="inlineStr">
+      <c r="I3" s="1620" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1548" t="inlineStr">
+      <c r="J3" s="1621" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1549" t="inlineStr">
+      <c r="A4" s="1622" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1550" t="inlineStr">
+      <c r="B4" s="1623" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1514" t="inlineStr">
+      <c r="C4" s="1587" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1543" t="inlineStr">
+      <c r="D4" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1515" t="n">
+      <c r="E4" s="1588" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1516" t="n">
+      <c r="F4" s="1589" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1515" t="n">
+      <c r="G4" s="1588" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1518">
+      <c r="H4" s="1591">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1551" t="inlineStr">
+      <c r="I4" s="1624" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1552" t="inlineStr">
+      <c r="J4" s="1625" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1540" t="inlineStr">
+      <c r="A5" s="1613" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1541" t="inlineStr">
+      <c r="B5" s="1614" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1542" t="inlineStr">
+      <c r="C5" s="1615" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1543" t="inlineStr">
+      <c r="D5" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1544" t="n">
+      <c r="E5" s="1617" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1545" t="n">
+      <c r="F5" s="1618" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1544" t="n">
+      <c r="G5" s="1617" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1546">
+      <c r="H5" s="1619">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1547" t="inlineStr">
+      <c r="I5" s="1620" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1548" t="inlineStr">
+      <c r="J5" s="1621" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1549" t="inlineStr">
+      <c r="A6" s="1622" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1550" t="inlineStr">
+      <c r="B6" s="1623" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1514" t="inlineStr">
+      <c r="C6" s="1587" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1543" t="inlineStr">
+      <c r="D6" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1515" t="n">
+      <c r="E6" s="1588" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1516" t="n">
+      <c r="F6" s="1589" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1515" t="n">
+      <c r="G6" s="1588" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1518">
+      <c r="H6" s="1591">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1551" t="inlineStr">
+      <c r="I6" s="1624" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1552" t="inlineStr">
+      <c r="J6" s="1625" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1540" t="inlineStr">
+      <c r="A7" s="1613" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1541" t="inlineStr">
+      <c r="B7" s="1614" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1542" t="inlineStr">
+      <c r="C7" s="1615" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1543" t="inlineStr">
+      <c r="D7" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1544" t="n">
+      <c r="E7" s="1617" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1545" t="n">
+      <c r="F7" s="1618" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1544" t="n">
+      <c r="G7" s="1617" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1546">
+      <c r="H7" s="1619">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1547" t="inlineStr">
+      <c r="I7" s="1620" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1548" t="inlineStr">
+      <c r="J7" s="1621" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1549" t="inlineStr">
+      <c r="A8" s="1622" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1550" t="inlineStr">
+      <c r="B8" s="1623" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1514" t="inlineStr">
+      <c r="C8" s="1587" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1543" t="inlineStr">
+      <c r="D8" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1515" t="n">
+      <c r="E8" s="1588" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1516" t="n">
+      <c r="F8" s="1589" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1515" t="n">
+      <c r="G8" s="1588" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1518">
+      <c r="H8" s="1591">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1551" t="inlineStr">
+      <c r="I8" s="1624" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1552" t="inlineStr">
+      <c r="J8" s="1625" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1540" t="inlineStr">
+      <c r="A9" s="1613" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1541" t="inlineStr">
+      <c r="B9" s="1614" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1542" t="inlineStr">
+      <c r="C9" s="1615" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1553" t="inlineStr">
+      <c r="D9" s="1626" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1544" t="n">
+      <c r="E9" s="1617" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1545" t="n">
+      <c r="F9" s="1618" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1544" t="n">
+      <c r="G9" s="1617" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1546">
+      <c r="H9" s="1619">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1554" t="n">
+      <c r="I9" s="1627" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1548" t="inlineStr">
+      <c r="J9" s="1621" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1549" t="inlineStr">
+      <c r="A10" s="1622" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1550" t="inlineStr">
+      <c r="B10" s="1623" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1514" t="inlineStr">
+      <c r="C10" s="1587" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1553" t="inlineStr">
+      <c r="D10" s="1626" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1515" t="n">
+      <c r="E10" s="1588" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1516" t="n">
+      <c r="F10" s="1589" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1515" t="n">
+      <c r="G10" s="1588" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1518">
+      <c r="H10" s="1591">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1555" t="n">
+      <c r="I10" s="1628" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1552" t="inlineStr">
+      <c r="J10" s="1625" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1540" t="inlineStr">
+      <c r="A11" s="1613" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1541" t="inlineStr">
+      <c r="B11" s="1614" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1542" t="inlineStr">
+      <c r="C11" s="1615" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1543" t="inlineStr">
+      <c r="D11" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1544" t="n">
+      <c r="E11" s="1617" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1545" t="n">
+      <c r="F11" s="1618" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1544" t="n">
+      <c r="G11" s="1617" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1546">
+      <c r="H11" s="1619">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1547" t="inlineStr">
+      <c r="I11" s="1620" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1548" t="inlineStr">
+      <c r="J11" s="1621" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1549" t="inlineStr">
+      <c r="A12" s="1622" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1550" t="inlineStr">
+      <c r="B12" s="1623" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1514" t="inlineStr">
+      <c r="C12" s="1587" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1543" t="inlineStr">
+      <c r="D12" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1515" t="n">
+      <c r="E12" s="1588" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1516" t="n">
+      <c r="F12" s="1589" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1515" t="n">
+      <c r="G12" s="1588" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1518">
+      <c r="H12" s="1591">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1551" t="inlineStr">
+      <c r="I12" s="1624" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1552" t="inlineStr">
+      <c r="J12" s="1625" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1540" t="inlineStr">
+      <c r="A13" s="1613" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1541" t="inlineStr">
+      <c r="B13" s="1614" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1542" t="inlineStr">
+      <c r="C13" s="1615" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1543" t="inlineStr">
+      <c r="D13" s="1616" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1544" t="n">
+      <c r="E13" s="1617" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1545" t="n">
+      <c r="F13" s="1618" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1544" t="n">
+      <c r="G13" s="1617" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1546">
+      <c r="H13" s="1619">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1547" t="inlineStr">
+      <c r="I13" s="1620" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1548" t="inlineStr">
+      <c r="J13" s="1621" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -7264,11 +7523,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1556">
+      <c r="H15" s="1629">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1556">
+      <c r="I15" s="1629">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1630">
+  <cellXfs count="1692">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5021,6 +5021,192 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5455,7 +5641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5535,47 +5721,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1484" t="inlineStr">
+      <c r="A2" s="1557" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1485" t="n">
+      <c r="B2" s="1558" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1486" t="n">
+      <c r="C2" s="1559" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1487" t="n">
+      <c r="D2" s="1560" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1488" t="n">
+      <c r="E2" s="1561" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1489" t="n">
+      <c r="F2" s="1562" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1490" t="n">
+      <c r="G2" s="1563" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1491" t="n">
+      <c r="H2" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1492" t="n">
+      <c r="I2" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1493" t="n">
+      <c r="J2" s="1566" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1494" t="n">
+      <c r="K2" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1495" t="n">
+      <c r="L2" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1484" t="inlineStr">
+      <c r="A3" s="1557" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -5615,7 +5801,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1484" t="inlineStr">
+      <c r="A4" s="1557" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -5655,207 +5841,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1484" t="inlineStr">
+      <c r="A5" s="1557" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1485" t="n">
+      <c r="B5" s="1558" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1486" t="n">
+      <c r="C5" s="1559" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1487" t="n">
+      <c r="D5" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1488" t="n">
+      <c r="E5" s="1561" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1489" t="n">
+      <c r="F5" s="1562" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1490" t="n">
+      <c r="G5" s="1563" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1491" t="n">
+      <c r="H5" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1492" t="n">
+      <c r="I5" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1493" t="n">
+      <c r="J5" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1494" t="n">
+      <c r="K5" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1495" t="n">
+      <c r="L5" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1484" t="inlineStr">
+      <c r="A6" s="1557" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1485" t="n">
+      <c r="B6" s="1558" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1486" t="n">
+      <c r="C6" s="1559" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1487" t="n">
+      <c r="D6" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1488" t="n">
+      <c r="E6" s="1561" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1489" t="n">
+      <c r="F6" s="1562" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1490" t="n">
+      <c r="G6" s="1563" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1491" t="n">
+      <c r="H6" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1492" t="n">
+      <c r="I6" s="1565" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1493" t="n">
+      <c r="J6" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1494" t="n">
+      <c r="K6" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1495" t="n">
+      <c r="L6" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1484" t="inlineStr">
+      <c r="A7" s="1557" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1485" t="n">
+      <c r="B7" s="1558" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1486" t="n">
+      <c r="C7" s="1559" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1487" t="n">
+      <c r="D7" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1488" t="n">
+      <c r="E7" s="1561" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1489" t="n">
+      <c r="F7" s="1562" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1490" t="n">
+      <c r="G7" s="1563" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1491" t="n">
+      <c r="H7" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1492" t="n">
+      <c r="I7" s="1565" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1493" t="n">
+      <c r="J7" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1494" t="n">
+      <c r="K7" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1495" t="n">
+      <c r="L7" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1484" t="inlineStr">
+      <c r="A8" s="1557" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1485" t="n">
+      <c r="B8" s="1558" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1486" t="n">
+      <c r="C8" s="1559" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1487" t="n">
+      <c r="D8" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1488" t="n">
+      <c r="E8" s="1561" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1489" t="n">
+      <c r="F8" s="1562" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1490" t="n">
+      <c r="G8" s="1563" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1491" t="n">
+      <c r="H8" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1492" t="n">
+      <c r="I8" s="1565" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1493" t="n">
+      <c r="J8" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1494" t="n">
+      <c r="K8" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1495" t="n">
+      <c r="L8" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1484" t="inlineStr">
+      <c r="A9" s="1557" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1485" t="n">
+      <c r="B9" s="1558" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1486" t="n">
+      <c r="C9" s="1559" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1487" t="n">
+      <c r="D9" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1488" t="n">
+      <c r="E9" s="1561" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1489" t="n">
+      <c r="F9" s="1562" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1490" t="n">
+      <c r="G9" s="1563" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1491" t="n">
+      <c r="H9" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1492" t="n">
+      <c r="I9" s="1565" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1493" t="n">
+      <c r="J9" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1494" t="n">
+      <c r="K9" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1495" t="n">
+      <c r="L9" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1484" t="inlineStr">
+      <c r="A10" s="1557" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -5895,482 +6081,482 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1484" t="inlineStr">
+      <c r="A11" s="1557" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1485" t="n">
+      <c r="B11" s="1558" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1486" t="n">
+      <c r="C11" s="1559" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1487" t="n">
+      <c r="D11" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1488" t="n">
+      <c r="E11" s="1561" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1489" t="n">
+      <c r="F11" s="1562" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1490" t="n">
+      <c r="G11" s="1563" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1491" t="n">
+      <c r="H11" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1492" t="n">
+      <c r="I11" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1493" t="n">
+      <c r="J11" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1494" t="n">
+      <c r="K11" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1495" t="n">
+      <c r="L11" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1484" t="inlineStr">
+      <c r="A12" s="1557" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1485" t="n">
+      <c r="B12" s="1558" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1486" t="n">
+      <c r="C12" s="1559" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1487" t="n">
+      <c r="D12" s="1560" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1488" t="n">
+      <c r="E12" s="1561" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1489" t="n">
+      <c r="F12" s="1562" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1490" t="n">
+      <c r="G12" s="1563" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1491" t="n">
+      <c r="H12" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1492" t="n">
+      <c r="I12" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1493" t="n">
+      <c r="J12" s="1566" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1494" t="n">
+      <c r="K12" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1495" t="n">
+      <c r="L12" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1484" t="inlineStr">
+      <c r="A13" s="1557" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1485" t="n">
+      <c r="B13" s="1558" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1486" t="n">
+      <c r="C13" s="1559" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1487" t="n">
+      <c r="D13" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1488" t="n">
+      <c r="E13" s="1561" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1489" t="n">
+      <c r="F13" s="1562" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1490" t="n">
+      <c r="G13" s="1563" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1491" t="n">
+      <c r="H13" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1492" t="n">
+      <c r="I13" s="1565" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1493" t="n">
+      <c r="J13" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1494" t="n">
+      <c r="K13" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1495" t="n">
+      <c r="L13" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1484" t="inlineStr">
+      <c r="A14" s="1557" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1485" t="n">
+      <c r="B14" s="1558" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1486" t="n">
+      <c r="C14" s="1559" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1487" t="n">
+      <c r="D14" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1488" t="n">
+      <c r="E14" s="1561" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1489" t="n">
+      <c r="F14" s="1562" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1490" t="n">
+      <c r="G14" s="1563" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1491" t="n">
+      <c r="H14" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1492" t="n">
+      <c r="I14" s="1565" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1493" t="n">
+      <c r="J14" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1494" t="n">
+      <c r="K14" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1495" t="n">
+      <c r="L14" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1484" t="inlineStr">
+      <c r="A15" s="1557" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1485" t="n">
+      <c r="B15" s="1558" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1486" t="n">
+      <c r="C15" s="1559" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1487" t="n">
+      <c r="D15" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1488" t="n">
+      <c r="E15" s="1561" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1489" t="n">
+      <c r="F15" s="1562" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1490" t="n">
+      <c r="G15" s="1563" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1491" t="n">
+      <c r="H15" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1492" t="n">
+      <c r="I15" s="1565" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1493" t="n">
+      <c r="J15" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1494" t="n">
+      <c r="K15" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1495" t="n">
+      <c r="L15" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1484" t="inlineStr">
+      <c r="A16" s="1557" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1485" t="n">
+      <c r="B16" s="1558" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1486" t="n">
+      <c r="C16" s="1559" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1487" t="n">
+      <c r="D16" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1488" t="n">
+      <c r="E16" s="1561" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1489" t="n">
+      <c r="F16" s="1562" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1490" t="n">
+      <c r="G16" s="1563" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1491" t="n">
+      <c r="H16" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1492" t="n">
+      <c r="I16" s="1565" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1493" t="n">
+      <c r="J16" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1494" t="n">
+      <c r="K16" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1495" t="n">
+      <c r="L16" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1484" t="inlineStr">
+      <c r="A17" s="1557" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1485" t="n">
+      <c r="B17" s="1558" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1486" t="n">
+      <c r="C17" s="1559" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1487" t="n">
+      <c r="D17" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1488" t="n">
+      <c r="E17" s="1561" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1489" t="n">
+      <c r="F17" s="1562" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1490" t="n">
+      <c r="G17" s="1563" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1491" t="n">
+      <c r="H17" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1492" t="n">
+      <c r="I17" s="1565" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1493" t="n">
+      <c r="J17" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1494" t="n">
+      <c r="K17" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1495" t="n">
+      <c r="L17" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1484" t="inlineStr">
+      <c r="A18" s="1557" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1485" t="n">
+      <c r="B18" s="1558" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1486" t="n">
+      <c r="C18" s="1559" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1487" t="n">
+      <c r="D18" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1488" t="n">
+      <c r="E18" s="1561" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1489" t="n">
+      <c r="F18" s="1562" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1490" t="n">
+      <c r="G18" s="1563" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1491" t="n">
+      <c r="H18" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1492" t="n">
+      <c r="I18" s="1565" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1493" t="n">
+      <c r="J18" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1494" t="n">
+      <c r="K18" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1495" t="n">
+      <c r="L18" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1484" t="inlineStr">
+      <c r="A19" s="1557" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1485" t="n">
+      <c r="B19" s="1558" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1486" t="n">
+      <c r="C19" s="1559" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1487" t="n">
+      <c r="D19" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1488" t="n">
+      <c r="E19" s="1561" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1489" t="n">
+      <c r="F19" s="1562" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1490" t="n">
+      <c r="G19" s="1563" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1491" t="n">
+      <c r="H19" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1492" t="n">
+      <c r="I19" s="1565" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1493" t="n">
+      <c r="J19" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1494" t="n">
+      <c r="K19" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="1495" t="n">
+      <c r="L19" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1484" t="inlineStr">
+      <c r="A20" s="1557" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1485" t="n">
+      <c r="B20" s="1558" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1486" t="n">
+      <c r="C20" s="1559" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1487" t="n">
+      <c r="D20" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1488" t="n">
+      <c r="E20" s="1561" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1489" t="n">
+      <c r="F20" s="1562" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1490" t="n">
+      <c r="G20" s="1563" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1491" t="n">
+      <c r="H20" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="1492" t="n">
+      <c r="I20" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="1493" t="n">
+      <c r="J20" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1494" t="n">
+      <c r="K20" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="1495" t="n">
+      <c r="L20" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1484" t="inlineStr">
+      <c r="A21" s="1557" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B21" s="1485" t="n">
+      <c r="B21" s="1558" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="1486" t="n">
+      <c r="C21" s="1559" t="n">
         <v>313566.1793926954</v>
       </c>
-      <c r="D21" s="1487" t="n">
+      <c r="D21" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E21" s="1488" t="n">
+      <c r="E21" s="1561" t="n">
         <v>264836.0024452209</v>
       </c>
-      <c r="F21" s="1489" t="n">
+      <c r="F21" s="1562" t="n">
         <v>13566.17939269543</v>
       </c>
-      <c r="G21" s="1490" t="n">
+      <c r="G21" s="1563" t="n">
         <v>0.04522059797565142</v>
       </c>
-      <c r="H21" s="1491" t="n">
+      <c r="H21" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="1492" t="n">
+      <c r="I21" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1493" t="n">
+      <c r="J21" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="1494" t="n">
+      <c r="K21" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1495" t="n">
+      <c r="L21" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1484" t="inlineStr">
+      <c r="A22" s="1557" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B22" s="1485" t="n">
+      <c r="B22" s="1558" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="1486" t="n">
+      <c r="C22" s="1559" t="n">
         <v>321999.1744259596</v>
       </c>
-      <c r="D22" s="1487" t="n">
+      <c r="D22" s="1560" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E22" s="1488" t="n">
+      <c r="E22" s="1561" t="n">
         <v>273268.9974784851</v>
       </c>
-      <c r="F22" s="1489" t="n">
+      <c r="F22" s="1562" t="n">
         <v>21999.17442595959</v>
       </c>
-      <c r="G22" s="1490" t="n">
+      <c r="G22" s="1563" t="n">
         <v>0.07333058141986529</v>
       </c>
-      <c r="H22" s="1491" t="n">
+      <c r="H22" s="1564" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="1492" t="n">
+      <c r="I22" s="1565" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1493" t="n">
+      <c r="J22" s="1566" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="1494" t="n">
+      <c r="K22" s="1567" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1495" t="n">
+      <c r="L22" s="1568" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6411,6 +6597,46 @@
         <v>0</v>
       </c>
       <c r="L23" s="1568" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="1630" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B24" s="1631" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1632" t="n">
+        <v>327462.1705511808</v>
+      </c>
+      <c r="D24" s="1633" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E24" s="1634" t="n">
+        <v>278731.9936037064</v>
+      </c>
+      <c r="F24" s="1635" t="n">
+        <v>27462.17055118084</v>
+      </c>
+      <c r="G24" s="1636" t="n">
+        <v>0.09154056850393615</v>
+      </c>
+      <c r="H24" s="1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1639" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6443,452 +6669,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1569" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  25 May 2026</t>
+      <c r="A1" s="1642" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  26 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1570" t="inlineStr">
+      <c r="A2" s="1643" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1570" t="inlineStr">
+      <c r="B2" s="1643" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1570" t="inlineStr">
+      <c r="C2" s="1643" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1570" t="inlineStr">
+      <c r="D2" s="1643" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1570" t="inlineStr">
+      <c r="E2" s="1643" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1570" t="inlineStr">
+      <c r="F2" s="1643" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1570" t="inlineStr">
+      <c r="G2" s="1643" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1570" t="inlineStr">
+      <c r="H2" s="1643" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1570" t="inlineStr">
+      <c r="I2" s="1643" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1570" t="inlineStr">
+      <c r="J2" s="1643" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1570" t="inlineStr">
+      <c r="K2" s="1643" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1571" t="inlineStr">
+      <c r="A3" s="1644" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1572" t="inlineStr">
+      <c r="B3" s="1645" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1573" t="n">
+      <c r="C3" s="1646" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1574" t="n">
+      <c r="D3" s="1647" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1575" t="n">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1576">
+      <c r="E3" s="1648" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="F3" s="1649">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1577">
+      <c r="G3" s="1650">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1578">
+      <c r="H3" s="1651">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1579" t="inlineStr">
+      <c r="I3" s="1652" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1580" t="n">
+      <c r="J3" s="1653" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1581" t="inlineStr">
+      <c r="K3" s="1654" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1571" t="inlineStr">
+      <c r="A4" s="1644" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1572" t="inlineStr">
+      <c r="B4" s="1645" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1573" t="n">
+      <c r="C4" s="1646" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1574" t="n">
+      <c r="D4" s="1647" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1575" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1576">
+      <c r="E4" s="1648" t="n">
+        <v>5.099999904632568</v>
+      </c>
+      <c r="F4" s="1649">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1577">
+      <c r="G4" s="1650">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1578">
+      <c r="H4" s="1651">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1579" t="inlineStr">
+      <c r="I4" s="1652" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1582" t="n">
+      <c r="J4" s="1655" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1583" t="inlineStr">
+      <c r="K4" s="1656" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1571" t="inlineStr">
+      <c r="A5" s="1644" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1572" t="inlineStr">
+      <c r="B5" s="1645" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1573" t="n">
+      <c r="C5" s="1646" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1574" t="n">
+      <c r="D5" s="1647" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1575" t="n">
-        <v>18.20000076293945</v>
-      </c>
-      <c r="F5" s="1576">
+      <c r="E5" s="1648" t="n">
+        <v>18.29999923706055</v>
+      </c>
+      <c r="F5" s="1649">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1577">
+      <c r="G5" s="1650">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1578">
+      <c r="H5" s="1651">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1579" t="inlineStr">
+      <c r="I5" s="1652" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1584" t="n">
+      <c r="J5" s="1657" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1585" t="inlineStr">
+      <c r="K5" s="1658" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1571" t="inlineStr">
+      <c r="A6" s="1644" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B6" s="1572" t="inlineStr">
+      <c r="B6" s="1645" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C6" s="1573" t="n">
+      <c r="C6" s="1646" t="n">
         <v>2700</v>
       </c>
-      <c r="D6" s="1574" t="n">
+      <c r="D6" s="1647" t="n">
         <v>17.4</v>
       </c>
-      <c r="E6" s="1575" t="n">
-        <v>17.79999923706055</v>
-      </c>
-      <c r="F6" s="1576">
+      <c r="E6" s="1648" t="n">
+        <v>18.29999923706055</v>
+      </c>
+      <c r="F6" s="1649">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1577">
+      <c r="G6" s="1650">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1578">
+      <c r="H6" s="1651">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1579" t="inlineStr">
+      <c r="I6" s="1652" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1582" t="n">
+      <c r="J6" s="1655" t="n">
         <v>5.68</v>
       </c>
-      <c r="K6" s="1583" t="inlineStr">
+      <c r="K6" s="1656" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1586" t="inlineStr">
+      <c r="A7" s="1644" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="1587" t="inlineStr">
+      <c r="B7" s="1645" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="1588" t="n">
+      <c r="C7" s="1646" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="1589" t="n">
+      <c r="D7" s="1647" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="1590" t="n">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1591">
+      <c r="E7" s="1648" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F7" s="1649">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1592">
+      <c r="G7" s="1650">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1593">
+      <c r="H7" s="1651">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1594" t="inlineStr">
+      <c r="I7" s="1652" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1595" t="n">
+      <c r="J7" s="1655" t="n">
         <v>5.88</v>
       </c>
-      <c r="K7" s="1596" t="inlineStr">
+      <c r="K7" s="1656" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1586" t="inlineStr">
+      <c r="A8" s="1644" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1587" t="inlineStr">
+      <c r="B8" s="1645" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1588" t="n">
+      <c r="C8" s="1646" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1589" t="n">
+      <c r="D8" s="1647" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1590" t="n">
-        <v>4.199999809265137</v>
-      </c>
-      <c r="F8" s="1591">
+      <c r="E8" s="1648" t="n">
+        <v>4.239999771118164</v>
+      </c>
+      <c r="F8" s="1649">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1592">
+      <c r="G8" s="1650">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1593">
+      <c r="H8" s="1651">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1594" t="inlineStr">
+      <c r="I8" s="1652" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1595" t="n">
+      <c r="J8" s="1655" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1596" t="inlineStr">
+      <c r="K8" s="1656" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1586" t="inlineStr">
+      <c r="A9" s="1644" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1587" t="inlineStr">
+      <c r="B9" s="1645" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1588" t="n">
+      <c r="C9" s="1646" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1589" t="n">
+      <c r="D9" s="1647" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1590" t="n">
-        <v>2.619999885559082</v>
-      </c>
-      <c r="F9" s="1591">
+      <c r="E9" s="1648" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="F9" s="1649">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1592">
+      <c r="G9" s="1650">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1593">
+      <c r="H9" s="1651">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1594" t="inlineStr">
+      <c r="I9" s="1652" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1595" t="n">
+      <c r="J9" s="1655" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1596" t="inlineStr">
+      <c r="K9" s="1656" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1597" t="inlineStr">
+      <c r="A10" s="1659" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1598" t="inlineStr">
+      <c r="B10" s="1660" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1599" t="n">
+      <c r="C10" s="1661" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1600" t="n">
+      <c r="D10" s="1662" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1601" t="n">
-        <v>11.30000019073486</v>
-      </c>
-      <c r="F10" s="1602">
+      <c r="E10" s="1663" t="n">
+        <v>11.39999961853027</v>
+      </c>
+      <c r="F10" s="1664">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1603">
+      <c r="G10" s="1665">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1604">
+      <c r="H10" s="1666">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1605" t="inlineStr">
+      <c r="I10" s="1667" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1606" t="n">
+      <c r="J10" s="1668" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1607" t="inlineStr">
+      <c r="K10" s="1669" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1608" t="inlineStr">
+      <c r="B11" s="1670" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1609">
+      <c r="F11" s="1671">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1610">
+      <c r="G11" s="1672">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1611">
+      <c r="H11" s="1673">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -6923,14 +7149,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1569" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  25 May 2026</t>
+      <c r="A1" s="1642" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  26 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1612" t="inlineStr">
+      <c r="A3" s="1674" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -6968,550 +7194,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1569" t="inlineStr">
+      <c r="A1" s="1642" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1570" t="inlineStr">
+      <c r="A2" s="1643" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1570" t="inlineStr">
+      <c r="B2" s="1643" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1570" t="inlineStr">
+      <c r="C2" s="1643" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1570" t="inlineStr">
+      <c r="D2" s="1643" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1570" t="inlineStr">
+      <c r="E2" s="1643" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1570" t="inlineStr">
+      <c r="F2" s="1643" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1570" t="inlineStr">
+      <c r="G2" s="1643" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1570" t="inlineStr">
+      <c r="H2" s="1643" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1570" t="inlineStr">
+      <c r="I2" s="1643" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1570" t="inlineStr">
+      <c r="J2" s="1643" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1613" t="inlineStr">
+      <c r="A3" s="1675" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1614" t="inlineStr">
+      <c r="B3" s="1676" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1615" t="inlineStr">
+      <c r="C3" s="1677" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1616" t="inlineStr">
+      <c r="D3" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1617" t="n">
+      <c r="E3" s="1679" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1618" t="n">
+      <c r="F3" s="1680" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1617" t="n">
+      <c r="G3" s="1679" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1619">
+      <c r="H3" s="1681">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1620" t="inlineStr">
+      <c r="I3" s="1682" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1621" t="inlineStr">
+      <c r="J3" s="1683" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1622" t="inlineStr">
+      <c r="A4" s="1684" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1623" t="inlineStr">
+      <c r="B4" s="1685" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1587" t="inlineStr">
+      <c r="C4" s="1660" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1616" t="inlineStr">
+      <c r="D4" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1588" t="n">
+      <c r="E4" s="1661" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1589" t="n">
+      <c r="F4" s="1662" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1588" t="n">
+      <c r="G4" s="1661" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1591">
+      <c r="H4" s="1664">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1624" t="inlineStr">
+      <c r="I4" s="1686" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1625" t="inlineStr">
+      <c r="J4" s="1687" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1613" t="inlineStr">
+      <c r="A5" s="1675" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1614" t="inlineStr">
+      <c r="B5" s="1676" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1615" t="inlineStr">
+      <c r="C5" s="1677" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1616" t="inlineStr">
+      <c r="D5" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1617" t="n">
+      <c r="E5" s="1679" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1618" t="n">
+      <c r="F5" s="1680" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1617" t="n">
+      <c r="G5" s="1679" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1619">
+      <c r="H5" s="1681">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1620" t="inlineStr">
+      <c r="I5" s="1682" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1621" t="inlineStr">
+      <c r="J5" s="1683" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1622" t="inlineStr">
+      <c r="A6" s="1684" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1623" t="inlineStr">
+      <c r="B6" s="1685" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1587" t="inlineStr">
+      <c r="C6" s="1660" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1616" t="inlineStr">
+      <c r="D6" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1588" t="n">
+      <c r="E6" s="1661" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1589" t="n">
+      <c r="F6" s="1662" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1588" t="n">
+      <c r="G6" s="1661" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1591">
+      <c r="H6" s="1664">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1624" t="inlineStr">
+      <c r="I6" s="1686" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1625" t="inlineStr">
+      <c r="J6" s="1687" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1613" t="inlineStr">
+      <c r="A7" s="1675" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1614" t="inlineStr">
+      <c r="B7" s="1676" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1615" t="inlineStr">
+      <c r="C7" s="1677" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1616" t="inlineStr">
+      <c r="D7" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1617" t="n">
+      <c r="E7" s="1679" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1618" t="n">
+      <c r="F7" s="1680" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1617" t="n">
+      <c r="G7" s="1679" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1619">
+      <c r="H7" s="1681">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1620" t="inlineStr">
+      <c r="I7" s="1682" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1621" t="inlineStr">
+      <c r="J7" s="1683" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1622" t="inlineStr">
+      <c r="A8" s="1684" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1623" t="inlineStr">
+      <c r="B8" s="1685" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1587" t="inlineStr">
+      <c r="C8" s="1660" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1616" t="inlineStr">
+      <c r="D8" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1588" t="n">
+      <c r="E8" s="1661" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1589" t="n">
+      <c r="F8" s="1662" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1588" t="n">
+      <c r="G8" s="1661" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1591">
+      <c r="H8" s="1664">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1624" t="inlineStr">
+      <c r="I8" s="1686" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1625" t="inlineStr">
+      <c r="J8" s="1687" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1613" t="inlineStr">
+      <c r="A9" s="1675" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1614" t="inlineStr">
+      <c r="B9" s="1676" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1615" t="inlineStr">
+      <c r="C9" s="1677" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1626" t="inlineStr">
+      <c r="D9" s="1688" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1617" t="n">
+      <c r="E9" s="1679" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1618" t="n">
+      <c r="F9" s="1680" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1617" t="n">
+      <c r="G9" s="1679" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1619">
+      <c r="H9" s="1681">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1627" t="n">
+      <c r="I9" s="1689" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1621" t="inlineStr">
+      <c r="J9" s="1683" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1622" t="inlineStr">
+      <c r="A10" s="1684" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1623" t="inlineStr">
+      <c r="B10" s="1685" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1587" t="inlineStr">
+      <c r="C10" s="1660" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1626" t="inlineStr">
+      <c r="D10" s="1688" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1588" t="n">
+      <c r="E10" s="1661" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1589" t="n">
+      <c r="F10" s="1662" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1588" t="n">
+      <c r="G10" s="1661" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1591">
+      <c r="H10" s="1664">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1628" t="n">
+      <c r="I10" s="1690" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1625" t="inlineStr">
+      <c r="J10" s="1687" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1613" t="inlineStr">
+      <c r="A11" s="1675" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1614" t="inlineStr">
+      <c r="B11" s="1676" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1615" t="inlineStr">
+      <c r="C11" s="1677" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1616" t="inlineStr">
+      <c r="D11" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1617" t="n">
+      <c r="E11" s="1679" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1618" t="n">
+      <c r="F11" s="1680" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1617" t="n">
+      <c r="G11" s="1679" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1619">
+      <c r="H11" s="1681">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1620" t="inlineStr">
+      <c r="I11" s="1682" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1621" t="inlineStr">
+      <c r="J11" s="1683" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1622" t="inlineStr">
+      <c r="A12" s="1684" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1623" t="inlineStr">
+      <c r="B12" s="1685" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1587" t="inlineStr">
+      <c r="C12" s="1660" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1616" t="inlineStr">
+      <c r="D12" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1588" t="n">
+      <c r="E12" s="1661" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1589" t="n">
+      <c r="F12" s="1662" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1588" t="n">
+      <c r="G12" s="1661" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1591">
+      <c r="H12" s="1664">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1624" t="inlineStr">
+      <c r="I12" s="1686" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1625" t="inlineStr">
+      <c r="J12" s="1687" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1613" t="inlineStr">
+      <c r="A13" s="1675" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1614" t="inlineStr">
+      <c r="B13" s="1676" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1615" t="inlineStr">
+      <c r="C13" s="1677" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1616" t="inlineStr">
+      <c r="D13" s="1678" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1617" t="n">
+      <c r="E13" s="1679" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1618" t="n">
+      <c r="F13" s="1680" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1617" t="n">
+      <c r="G13" s="1679" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1619">
+      <c r="H13" s="1681">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1620" t="inlineStr">
+      <c r="I13" s="1682" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1621" t="inlineStr">
+      <c r="J13" s="1683" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -7523,11 +7749,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1629">
+      <c r="H15" s="1691">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1629">
+      <c r="I15" s="1691">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1692">
+  <cellXfs count="1765">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5207,6 +5207,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5641,7 +5860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5721,47 +5940,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1557" t="inlineStr">
+      <c r="A2" s="1630" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1558" t="n">
+      <c r="B2" s="1631" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1559" t="n">
+      <c r="C2" s="1632" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1560" t="n">
+      <c r="D2" s="1633" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1561" t="n">
+      <c r="E2" s="1634" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1562" t="n">
+      <c r="F2" s="1635" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1563" t="n">
+      <c r="G2" s="1636" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1564" t="n">
+      <c r="H2" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="1565" t="n">
+      <c r="I2" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="1566" t="n">
+      <c r="J2" s="1639" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1567" t="n">
+      <c r="K2" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="1568" t="n">
+      <c r="L2" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1557" t="inlineStr">
+      <c r="A3" s="1630" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -5801,7 +6020,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1557" t="inlineStr">
+      <c r="A4" s="1630" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -5841,207 +6060,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1557" t="inlineStr">
+      <c r="A5" s="1630" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1558" t="n">
+      <c r="B5" s="1631" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1559" t="n">
+      <c r="C5" s="1632" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1560" t="n">
+      <c r="D5" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1561" t="n">
+      <c r="E5" s="1634" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1562" t="n">
+      <c r="F5" s="1635" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1563" t="n">
+      <c r="G5" s="1636" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1564" t="n">
+      <c r="H5" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1565" t="n">
+      <c r="I5" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="1566" t="n">
+      <c r="J5" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1567" t="n">
+      <c r="K5" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="1568" t="n">
+      <c r="L5" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1557" t="inlineStr">
+      <c r="A6" s="1630" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1558" t="n">
+      <c r="B6" s="1631" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1559" t="n">
+      <c r="C6" s="1632" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1560" t="n">
+      <c r="D6" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1561" t="n">
+      <c r="E6" s="1634" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1562" t="n">
+      <c r="F6" s="1635" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1563" t="n">
+      <c r="G6" s="1636" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1564" t="n">
+      <c r="H6" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1565" t="n">
+      <c r="I6" s="1638" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1566" t="n">
+      <c r="J6" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1567" t="n">
+      <c r="K6" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="1568" t="n">
+      <c r="L6" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1557" t="inlineStr">
+      <c r="A7" s="1630" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1558" t="n">
+      <c r="B7" s="1631" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1559" t="n">
+      <c r="C7" s="1632" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1560" t="n">
+      <c r="D7" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1561" t="n">
+      <c r="E7" s="1634" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1562" t="n">
+      <c r="F7" s="1635" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1563" t="n">
+      <c r="G7" s="1636" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1564" t="n">
+      <c r="H7" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1565" t="n">
+      <c r="I7" s="1638" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1566" t="n">
+      <c r="J7" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1567" t="n">
+      <c r="K7" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="1568" t="n">
+      <c r="L7" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1557" t="inlineStr">
+      <c r="A8" s="1630" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1558" t="n">
+      <c r="B8" s="1631" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1559" t="n">
+      <c r="C8" s="1632" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1560" t="n">
+      <c r="D8" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1561" t="n">
+      <c r="E8" s="1634" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1562" t="n">
+      <c r="F8" s="1635" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1563" t="n">
+      <c r="G8" s="1636" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1564" t="n">
+      <c r="H8" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1565" t="n">
+      <c r="I8" s="1638" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1566" t="n">
+      <c r="J8" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1567" t="n">
+      <c r="K8" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="1568" t="n">
+      <c r="L8" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1557" t="inlineStr">
+      <c r="A9" s="1630" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1558" t="n">
+      <c r="B9" s="1631" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1559" t="n">
+      <c r="C9" s="1632" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1560" t="n">
+      <c r="D9" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1561" t="n">
+      <c r="E9" s="1634" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1562" t="n">
+      <c r="F9" s="1635" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1563" t="n">
+      <c r="G9" s="1636" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1564" t="n">
+      <c r="H9" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1565" t="n">
+      <c r="I9" s="1638" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1566" t="n">
+      <c r="J9" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1567" t="n">
+      <c r="K9" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="1568" t="n">
+      <c r="L9" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1557" t="inlineStr">
+      <c r="A10" s="1630" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -6081,522 +6300,522 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1557" t="inlineStr">
+      <c r="A11" s="1630" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1558" t="n">
+      <c r="B11" s="1631" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1559" t="n">
+      <c r="C11" s="1632" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1560" t="n">
+      <c r="D11" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1561" t="n">
+      <c r="E11" s="1634" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1562" t="n">
+      <c r="F11" s="1635" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1563" t="n">
+      <c r="G11" s="1636" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1564" t="n">
+      <c r="H11" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1565" t="n">
+      <c r="I11" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="1566" t="n">
+      <c r="J11" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1567" t="n">
+      <c r="K11" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="1568" t="n">
+      <c r="L11" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1557" t="inlineStr">
+      <c r="A12" s="1630" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1558" t="n">
+      <c r="B12" s="1631" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1559" t="n">
+      <c r="C12" s="1632" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1560" t="n">
+      <c r="D12" s="1633" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1561" t="n">
+      <c r="E12" s="1634" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1562" t="n">
+      <c r="F12" s="1635" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1563" t="n">
+      <c r="G12" s="1636" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1564" t="n">
+      <c r="H12" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1565" t="n">
+      <c r="I12" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="1566" t="n">
+      <c r="J12" s="1639" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1567" t="n">
+      <c r="K12" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="1568" t="n">
+      <c r="L12" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1557" t="inlineStr">
+      <c r="A13" s="1630" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1558" t="n">
+      <c r="B13" s="1631" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1559" t="n">
+      <c r="C13" s="1632" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1560" t="n">
+      <c r="D13" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1561" t="n">
+      <c r="E13" s="1634" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1562" t="n">
+      <c r="F13" s="1635" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1563" t="n">
+      <c r="G13" s="1636" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1564" t="n">
+      <c r="H13" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1565" t="n">
+      <c r="I13" s="1638" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1566" t="n">
+      <c r="J13" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1567" t="n">
+      <c r="K13" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="1568" t="n">
+      <c r="L13" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1557" t="inlineStr">
+      <c r="A14" s="1630" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1558" t="n">
+      <c r="B14" s="1631" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1559" t="n">
+      <c r="C14" s="1632" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1560" t="n">
+      <c r="D14" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1561" t="n">
+      <c r="E14" s="1634" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1562" t="n">
+      <c r="F14" s="1635" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1563" t="n">
+      <c r="G14" s="1636" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1564" t="n">
+      <c r="H14" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1565" t="n">
+      <c r="I14" s="1638" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1566" t="n">
+      <c r="J14" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1567" t="n">
+      <c r="K14" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="1568" t="n">
+      <c r="L14" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1557" t="inlineStr">
+      <c r="A15" s="1630" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1558" t="n">
+      <c r="B15" s="1631" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1559" t="n">
+      <c r="C15" s="1632" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1560" t="n">
+      <c r="D15" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1561" t="n">
+      <c r="E15" s="1634" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1562" t="n">
+      <c r="F15" s="1635" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1563" t="n">
+      <c r="G15" s="1636" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1564" t="n">
+      <c r="H15" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1565" t="n">
+      <c r="I15" s="1638" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1566" t="n">
+      <c r="J15" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1567" t="n">
+      <c r="K15" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="1568" t="n">
+      <c r="L15" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1557" t="inlineStr">
+      <c r="A16" s="1630" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1558" t="n">
+      <c r="B16" s="1631" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1559" t="n">
+      <c r="C16" s="1632" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1560" t="n">
+      <c r="D16" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1561" t="n">
+      <c r="E16" s="1634" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1562" t="n">
+      <c r="F16" s="1635" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1563" t="n">
+      <c r="G16" s="1636" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1564" t="n">
+      <c r="H16" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1565" t="n">
+      <c r="I16" s="1638" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1566" t="n">
+      <c r="J16" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1567" t="n">
+      <c r="K16" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="1568" t="n">
+      <c r="L16" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1557" t="inlineStr">
+      <c r="A17" s="1630" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1558" t="n">
+      <c r="B17" s="1631" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1559" t="n">
+      <c r="C17" s="1632" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1560" t="n">
+      <c r="D17" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1561" t="n">
+      <c r="E17" s="1634" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1562" t="n">
+      <c r="F17" s="1635" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1563" t="n">
+      <c r="G17" s="1636" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1564" t="n">
+      <c r="H17" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1565" t="n">
+      <c r="I17" s="1638" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1566" t="n">
+      <c r="J17" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1567" t="n">
+      <c r="K17" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="1568" t="n">
+      <c r="L17" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1557" t="inlineStr">
+      <c r="A18" s="1630" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1558" t="n">
+      <c r="B18" s="1631" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1559" t="n">
+      <c r="C18" s="1632" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1560" t="n">
+      <c r="D18" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1561" t="n">
+      <c r="E18" s="1634" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1562" t="n">
+      <c r="F18" s="1635" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1563" t="n">
+      <c r="G18" s="1636" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1564" t="n">
+      <c r="H18" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1565" t="n">
+      <c r="I18" s="1638" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1566" t="n">
+      <c r="J18" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1567" t="n">
+      <c r="K18" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="1568" t="n">
+      <c r="L18" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1557" t="inlineStr">
+      <c r="A19" s="1630" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1558" t="n">
+      <c r="B19" s="1631" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1559" t="n">
+      <c r="C19" s="1632" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1560" t="n">
+      <c r="D19" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1561" t="n">
+      <c r="E19" s="1634" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1562" t="n">
+      <c r="F19" s="1635" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1563" t="n">
+      <c r="G19" s="1636" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1564" t="n">
+      <c r="H19" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1565" t="n">
+      <c r="I19" s="1638" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1566" t="n">
+      <c r="J19" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1567" t="n">
+      <c r="K19" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="1568" t="n">
+      <c r="L19" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1557" t="inlineStr">
+      <c r="A20" s="1630" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1558" t="n">
+      <c r="B20" s="1631" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1559" t="n">
+      <c r="C20" s="1632" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1560" t="n">
+      <c r="D20" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1561" t="n">
+      <c r="E20" s="1634" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1562" t="n">
+      <c r="F20" s="1635" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1563" t="n">
+      <c r="G20" s="1636" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1564" t="n">
+      <c r="H20" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="1565" t="n">
+      <c r="I20" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="1566" t="n">
+      <c r="J20" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1567" t="n">
+      <c r="K20" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="1568" t="n">
+      <c r="L20" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1557" t="inlineStr">
+      <c r="A21" s="1630" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B21" s="1558" t="n">
+      <c r="B21" s="1631" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="1559" t="n">
+      <c r="C21" s="1632" t="n">
         <v>313566.1793926954</v>
       </c>
-      <c r="D21" s="1560" t="n">
+      <c r="D21" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E21" s="1561" t="n">
+      <c r="E21" s="1634" t="n">
         <v>264836.0024452209</v>
       </c>
-      <c r="F21" s="1562" t="n">
+      <c r="F21" s="1635" t="n">
         <v>13566.17939269543</v>
       </c>
-      <c r="G21" s="1563" t="n">
+      <c r="G21" s="1636" t="n">
         <v>0.04522059797565142</v>
       </c>
-      <c r="H21" s="1564" t="n">
+      <c r="H21" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="1565" t="n">
+      <c r="I21" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="1566" t="n">
+      <c r="J21" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="1567" t="n">
+      <c r="K21" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="1568" t="n">
+      <c r="L21" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1557" t="inlineStr">
+      <c r="A22" s="1630" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B22" s="1558" t="n">
+      <c r="B22" s="1631" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="1559" t="n">
+      <c r="C22" s="1632" t="n">
         <v>321999.1744259596</v>
       </c>
-      <c r="D22" s="1560" t="n">
+      <c r="D22" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E22" s="1561" t="n">
+      <c r="E22" s="1634" t="n">
         <v>273268.9974784851</v>
       </c>
-      <c r="F22" s="1562" t="n">
+      <c r="F22" s="1635" t="n">
         <v>21999.17442595959</v>
       </c>
-      <c r="G22" s="1563" t="n">
+      <c r="G22" s="1636" t="n">
         <v>0.07333058141986529</v>
       </c>
-      <c r="H22" s="1564" t="n">
+      <c r="H22" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="1565" t="n">
+      <c r="I22" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="1566" t="n">
+      <c r="J22" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="1567" t="n">
+      <c r="K22" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="1568" t="n">
+      <c r="L22" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1557" t="inlineStr">
+      <c r="A23" s="1630" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B23" s="1558" t="n">
+      <c r="B23" s="1631" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="1559" t="n">
+      <c r="C23" s="1632" t="n">
         <v>323626.1765698195</v>
       </c>
-      <c r="D23" s="1560" t="n">
+      <c r="D23" s="1633" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E23" s="1561" t="n">
+      <c r="E23" s="1634" t="n">
         <v>274895.999622345</v>
       </c>
-      <c r="F23" s="1562" t="n">
+      <c r="F23" s="1635" t="n">
         <v>23626.17656981945</v>
       </c>
-      <c r="G23" s="1563" t="n">
+      <c r="G23" s="1636" t="n">
         <v>0.07875392189939817</v>
       </c>
-      <c r="H23" s="1564" t="n">
+      <c r="H23" s="1637" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="1565" t="n">
+      <c r="I23" s="1638" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="1566" t="n">
+      <c r="J23" s="1639" t="n">
         <v>8</v>
       </c>
-      <c r="K23" s="1567" t="n">
+      <c r="K23" s="1640" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="1568" t="n">
+      <c r="L23" s="1641" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6637,6 +6856,46 @@
         <v>0</v>
       </c>
       <c r="L24" s="1641" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="1692" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B25" s="1693" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1694" t="n">
+        <v>324376.1747578382</v>
+      </c>
+      <c r="D25" s="1695" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E25" s="1696" t="n">
+        <v>275645.9978103638</v>
+      </c>
+      <c r="F25" s="1697" t="n">
+        <v>24376.17475783825</v>
+      </c>
+      <c r="G25" s="1698" t="n">
+        <v>0.08125391585946083</v>
+      </c>
+      <c r="H25" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1700" t="n">
+        <v>-0.009423976479934384</v>
+      </c>
+      <c r="J25" s="1701" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6669,452 +6928,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1642" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  26 May 2026</t>
+      <c r="A1" s="1704" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  27 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1643" t="inlineStr">
+      <c r="A2" s="1705" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1643" t="inlineStr">
+      <c r="B2" s="1705" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1643" t="inlineStr">
+      <c r="C2" s="1705" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1643" t="inlineStr">
+      <c r="D2" s="1705" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1643" t="inlineStr">
+      <c r="E2" s="1705" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1643" t="inlineStr">
+      <c r="F2" s="1705" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1643" t="inlineStr">
+      <c r="G2" s="1705" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1643" t="inlineStr">
+      <c r="H2" s="1705" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1643" t="inlineStr">
+      <c r="I2" s="1705" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1643" t="inlineStr">
+      <c r="J2" s="1705" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1643" t="inlineStr">
+      <c r="K2" s="1705" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1644" t="inlineStr">
+      <c r="A3" s="1706" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1645" t="inlineStr">
+      <c r="B3" s="1707" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1646" t="n">
+      <c r="C3" s="1708" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1647" t="n">
+      <c r="D3" s="1709" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1648" t="n">
-        <v>24.89999961853027</v>
-      </c>
-      <c r="F3" s="1649">
+      <c r="E3" s="1710" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="F3" s="1711">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1650">
+      <c r="G3" s="1712">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1651">
+      <c r="H3" s="1713">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1652" t="inlineStr">
+      <c r="I3" s="1714" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1653" t="n">
+      <c r="J3" s="1715" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1654" t="inlineStr">
+      <c r="K3" s="1716" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1644" t="inlineStr">
+      <c r="A4" s="1706" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1645" t="inlineStr">
+      <c r="B4" s="1707" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1646" t="n">
+      <c r="C4" s="1708" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1647" t="n">
+      <c r="D4" s="1709" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1648" t="n">
-        <v>5.099999904632568</v>
-      </c>
-      <c r="F4" s="1649">
+      <c r="E4" s="1710" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1711">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1650">
+      <c r="G4" s="1712">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1651">
+      <c r="H4" s="1713">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1652" t="inlineStr">
+      <c r="I4" s="1714" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1655" t="n">
+      <c r="J4" s="1717" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1656" t="inlineStr">
+      <c r="K4" s="1718" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1644" t="inlineStr">
+      <c r="A5" s="1706" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1645" t="inlineStr">
+      <c r="B5" s="1707" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1646" t="n">
+      <c r="C5" s="1708" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1647" t="n">
+      <c r="D5" s="1709" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1648" t="n">
-        <v>18.29999923706055</v>
-      </c>
-      <c r="F5" s="1649">
+      <c r="E5" s="1710" t="n">
+        <v>17.70000076293945</v>
+      </c>
+      <c r="F5" s="1711">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1650">
+      <c r="G5" s="1712">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1651">
+      <c r="H5" s="1713">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1652" t="inlineStr">
+      <c r="I5" s="1714" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1657" t="n">
+      <c r="J5" s="1719" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1658" t="inlineStr">
+      <c r="K5" s="1720" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1644" t="inlineStr">
+      <c r="A6" s="1706" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B6" s="1645" t="inlineStr">
+      <c r="B6" s="1707" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C6" s="1646" t="n">
+      <c r="C6" s="1708" t="n">
         <v>2700</v>
       </c>
-      <c r="D6" s="1647" t="n">
+      <c r="D6" s="1709" t="n">
         <v>17.4</v>
       </c>
-      <c r="E6" s="1648" t="n">
+      <c r="E6" s="1710" t="n">
         <v>18.29999923706055</v>
       </c>
-      <c r="F6" s="1649">
+      <c r="F6" s="1711">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1650">
+      <c r="G6" s="1712">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1651">
+      <c r="H6" s="1713">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1652" t="inlineStr">
+      <c r="I6" s="1714" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1655" t="n">
+      <c r="J6" s="1717" t="n">
         <v>5.68</v>
       </c>
-      <c r="K6" s="1656" t="inlineStr">
+      <c r="K6" s="1718" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1644" t="inlineStr">
+      <c r="A7" s="1706" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="1645" t="inlineStr">
+      <c r="B7" s="1707" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="1646" t="n">
+      <c r="C7" s="1708" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="1647" t="n">
+      <c r="D7" s="1709" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="1648" t="n">
+      <c r="E7" s="1710" t="n">
         <v>29.75</v>
       </c>
-      <c r="F7" s="1649">
+      <c r="F7" s="1711">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1650">
+      <c r="G7" s="1712">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1651">
+      <c r="H7" s="1713">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1652" t="inlineStr">
+      <c r="I7" s="1714" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1655" t="n">
+      <c r="J7" s="1717" t="n">
         <v>5.88</v>
       </c>
-      <c r="K7" s="1656" t="inlineStr">
+      <c r="K7" s="1718" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1644" t="inlineStr">
+      <c r="A8" s="1706" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1645" t="inlineStr">
+      <c r="B8" s="1707" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1646" t="n">
+      <c r="C8" s="1708" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1647" t="n">
+      <c r="D8" s="1709" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1648" t="n">
+      <c r="E8" s="1710" t="n">
         <v>4.239999771118164</v>
       </c>
-      <c r="F8" s="1649">
+      <c r="F8" s="1711">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1650">
+      <c r="G8" s="1712">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1651">
+      <c r="H8" s="1713">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1652" t="inlineStr">
+      <c r="I8" s="1714" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1655" t="n">
+      <c r="J8" s="1717" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1656" t="inlineStr">
+      <c r="K8" s="1718" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1644" t="inlineStr">
+      <c r="A9" s="1721" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1645" t="inlineStr">
+      <c r="B9" s="1722" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1646" t="n">
+      <c r="C9" s="1723" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1647" t="n">
+      <c r="D9" s="1724" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1648" t="n">
-        <v>2.640000104904175</v>
-      </c>
-      <c r="F9" s="1649">
+      <c r="E9" s="1725" t="n">
+        <v>2.619999885559082</v>
+      </c>
+      <c r="F9" s="1726">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1650">
+      <c r="G9" s="1727">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1651">
+      <c r="H9" s="1728">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1652" t="inlineStr">
+      <c r="I9" s="1729" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1655" t="n">
+      <c r="J9" s="1730" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1656" t="inlineStr">
+      <c r="K9" s="1731" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1659" t="inlineStr">
+      <c r="A10" s="1732" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1660" t="inlineStr">
+      <c r="B10" s="1733" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1661" t="n">
+      <c r="C10" s="1734" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1662" t="n">
+      <c r="D10" s="1735" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1663" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="F10" s="1664">
+      <c r="E10" s="1736" t="n">
+        <v>11.30000019073486</v>
+      </c>
+      <c r="F10" s="1737">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1665">
+      <c r="G10" s="1738">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1666">
+      <c r="H10" s="1739">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1667" t="inlineStr">
+      <c r="I10" s="1740" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1668" t="n">
+      <c r="J10" s="1741" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1669" t="inlineStr">
+      <c r="K10" s="1742" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1670" t="inlineStr">
+      <c r="B11" s="1743" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1671">
+      <c r="F11" s="1744">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1672">
+      <c r="G11" s="1745">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1673">
+      <c r="H11" s="1746">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -7149,14 +7408,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1642" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  26 May 2026</t>
+      <c r="A1" s="1704" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  27 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1674" t="inlineStr">
+      <c r="A3" s="1747" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -7194,550 +7453,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1642" t="inlineStr">
+      <c r="A1" s="1704" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1643" t="inlineStr">
+      <c r="A2" s="1705" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1643" t="inlineStr">
+      <c r="B2" s="1705" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1643" t="inlineStr">
+      <c r="C2" s="1705" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1643" t="inlineStr">
+      <c r="D2" s="1705" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1643" t="inlineStr">
+      <c r="E2" s="1705" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1643" t="inlineStr">
+      <c r="F2" s="1705" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1643" t="inlineStr">
+      <c r="G2" s="1705" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1643" t="inlineStr">
+      <c r="H2" s="1705" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1643" t="inlineStr">
+      <c r="I2" s="1705" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1643" t="inlineStr">
+      <c r="J2" s="1705" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1675" t="inlineStr">
+      <c r="A3" s="1748" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1676" t="inlineStr">
+      <c r="B3" s="1749" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1677" t="inlineStr">
+      <c r="C3" s="1750" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1678" t="inlineStr">
+      <c r="D3" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1679" t="n">
+      <c r="E3" s="1752" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1680" t="n">
+      <c r="F3" s="1753" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1679" t="n">
+      <c r="G3" s="1752" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1681">
+      <c r="H3" s="1754">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1682" t="inlineStr">
+      <c r="I3" s="1755" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1683" t="inlineStr">
+      <c r="J3" s="1756" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1684" t="inlineStr">
+      <c r="A4" s="1757" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1685" t="inlineStr">
+      <c r="B4" s="1758" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1660" t="inlineStr">
+      <c r="C4" s="1722" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1678" t="inlineStr">
+      <c r="D4" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1661" t="n">
+      <c r="E4" s="1723" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1662" t="n">
+      <c r="F4" s="1724" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1661" t="n">
+      <c r="G4" s="1723" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1664">
+      <c r="H4" s="1726">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1686" t="inlineStr">
+      <c r="I4" s="1759" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1687" t="inlineStr">
+      <c r="J4" s="1760" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1675" t="inlineStr">
+      <c r="A5" s="1748" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1676" t="inlineStr">
+      <c r="B5" s="1749" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1677" t="inlineStr">
+      <c r="C5" s="1750" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1678" t="inlineStr">
+      <c r="D5" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1679" t="n">
+      <c r="E5" s="1752" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1680" t="n">
+      <c r="F5" s="1753" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1679" t="n">
+      <c r="G5" s="1752" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1681">
+      <c r="H5" s="1754">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1682" t="inlineStr">
+      <c r="I5" s="1755" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1683" t="inlineStr">
+      <c r="J5" s="1756" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1684" t="inlineStr">
+      <c r="A6" s="1757" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1685" t="inlineStr">
+      <c r="B6" s="1758" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1660" t="inlineStr">
+      <c r="C6" s="1722" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1678" t="inlineStr">
+      <c r="D6" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1661" t="n">
+      <c r="E6" s="1723" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1662" t="n">
+      <c r="F6" s="1724" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1661" t="n">
+      <c r="G6" s="1723" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1664">
+      <c r="H6" s="1726">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1686" t="inlineStr">
+      <c r="I6" s="1759" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1687" t="inlineStr">
+      <c r="J6" s="1760" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1675" t="inlineStr">
+      <c r="A7" s="1748" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1676" t="inlineStr">
+      <c r="B7" s="1749" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1677" t="inlineStr">
+      <c r="C7" s="1750" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1678" t="inlineStr">
+      <c r="D7" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1679" t="n">
+      <c r="E7" s="1752" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1680" t="n">
+      <c r="F7" s="1753" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1679" t="n">
+      <c r="G7" s="1752" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1681">
+      <c r="H7" s="1754">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1682" t="inlineStr">
+      <c r="I7" s="1755" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1683" t="inlineStr">
+      <c r="J7" s="1756" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1684" t="inlineStr">
+      <c r="A8" s="1757" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1685" t="inlineStr">
+      <c r="B8" s="1758" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1660" t="inlineStr">
+      <c r="C8" s="1722" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1678" t="inlineStr">
+      <c r="D8" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1661" t="n">
+      <c r="E8" s="1723" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1662" t="n">
+      <c r="F8" s="1724" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1661" t="n">
+      <c r="G8" s="1723" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1664">
+      <c r="H8" s="1726">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1686" t="inlineStr">
+      <c r="I8" s="1759" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1687" t="inlineStr">
+      <c r="J8" s="1760" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1675" t="inlineStr">
+      <c r="A9" s="1748" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1676" t="inlineStr">
+      <c r="B9" s="1749" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1677" t="inlineStr">
+      <c r="C9" s="1750" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1688" t="inlineStr">
+      <c r="D9" s="1761" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1679" t="n">
+      <c r="E9" s="1752" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1680" t="n">
+      <c r="F9" s="1753" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1679" t="n">
+      <c r="G9" s="1752" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1681">
+      <c r="H9" s="1754">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1689" t="n">
+      <c r="I9" s="1762" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1683" t="inlineStr">
+      <c r="J9" s="1756" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1684" t="inlineStr">
+      <c r="A10" s="1757" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1685" t="inlineStr">
+      <c r="B10" s="1758" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1660" t="inlineStr">
+      <c r="C10" s="1722" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1688" t="inlineStr">
+      <c r="D10" s="1761" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1661" t="n">
+      <c r="E10" s="1723" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1662" t="n">
+      <c r="F10" s="1724" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1661" t="n">
+      <c r="G10" s="1723" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1664">
+      <c r="H10" s="1726">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1690" t="n">
+      <c r="I10" s="1763" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1687" t="inlineStr">
+      <c r="J10" s="1760" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1675" t="inlineStr">
+      <c r="A11" s="1748" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1676" t="inlineStr">
+      <c r="B11" s="1749" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1677" t="inlineStr">
+      <c r="C11" s="1750" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1678" t="inlineStr">
+      <c r="D11" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1679" t="n">
+      <c r="E11" s="1752" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1680" t="n">
+      <c r="F11" s="1753" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1679" t="n">
+      <c r="G11" s="1752" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1681">
+      <c r="H11" s="1754">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1682" t="inlineStr">
+      <c r="I11" s="1755" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1683" t="inlineStr">
+      <c r="J11" s="1756" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1684" t="inlineStr">
+      <c r="A12" s="1757" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1685" t="inlineStr">
+      <c r="B12" s="1758" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1660" t="inlineStr">
+      <c r="C12" s="1722" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1678" t="inlineStr">
+      <c r="D12" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1661" t="n">
+      <c r="E12" s="1723" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1662" t="n">
+      <c r="F12" s="1724" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1661" t="n">
+      <c r="G12" s="1723" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1664">
+      <c r="H12" s="1726">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1686" t="inlineStr">
+      <c r="I12" s="1759" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1687" t="inlineStr">
+      <c r="J12" s="1760" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1675" t="inlineStr">
+      <c r="A13" s="1748" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1676" t="inlineStr">
+      <c r="B13" s="1749" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1677" t="inlineStr">
+      <c r="C13" s="1750" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1678" t="inlineStr">
+      <c r="D13" s="1751" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1679" t="n">
+      <c r="E13" s="1752" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1680" t="n">
+      <c r="F13" s="1753" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1679" t="n">
+      <c r="G13" s="1752" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1681">
+      <c r="H13" s="1754">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1682" t="inlineStr">
+      <c r="I13" s="1755" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1683" t="inlineStr">
+      <c r="J13" s="1756" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -7749,11 +8008,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1691">
+      <c r="H15" s="1764">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1691">
+      <c r="I15" s="1764">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1765">
+  <cellXfs count="1838">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5207,6 +5207,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5860,7 +6079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5940,47 +6159,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1630" t="inlineStr">
+      <c r="A2" s="1692" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1631" t="n">
+      <c r="B2" s="1693" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1632" t="n">
+      <c r="C2" s="1694" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1633" t="n">
+      <c r="D2" s="1695" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1634" t="n">
+      <c r="E2" s="1696" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1635" t="n">
+      <c r="F2" s="1697" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1636" t="n">
+      <c r="G2" s="1698" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1639" t="n">
+      <c r="H2" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1701" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1641" t="n">
+      <c r="K2" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1630" t="inlineStr">
+      <c r="A3" s="1692" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -6020,7 +6239,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1630" t="inlineStr">
+      <c r="A4" s="1692" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -6060,207 +6279,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1630" t="inlineStr">
+      <c r="A5" s="1692" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1631" t="n">
+      <c r="B5" s="1693" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1632" t="n">
+      <c r="C5" s="1694" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1633" t="n">
+      <c r="D5" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1634" t="n">
+      <c r="E5" s="1696" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1635" t="n">
+      <c r="F5" s="1697" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1636" t="n">
+      <c r="G5" s="1698" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1639" t="n">
+      <c r="H5" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1641" t="n">
+      <c r="K5" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1630" t="inlineStr">
+      <c r="A6" s="1692" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1631" t="n">
+      <c r="B6" s="1693" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1632" t="n">
+      <c r="C6" s="1694" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1633" t="n">
+      <c r="D6" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1634" t="n">
+      <c r="E6" s="1696" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1635" t="n">
+      <c r="F6" s="1697" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1636" t="n">
+      <c r="G6" s="1698" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1638" t="n">
+      <c r="H6" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1700" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1639" t="n">
+      <c r="J6" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1641" t="n">
+      <c r="K6" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1630" t="inlineStr">
+      <c r="A7" s="1692" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1631" t="n">
+      <c r="B7" s="1693" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1632" t="n">
+      <c r="C7" s="1694" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1633" t="n">
+      <c r="D7" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1634" t="n">
+      <c r="E7" s="1696" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1635" t="n">
+      <c r="F7" s="1697" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1636" t="n">
+      <c r="G7" s="1698" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1638" t="n">
+      <c r="H7" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1700" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1639" t="n">
+      <c r="J7" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1641" t="n">
+      <c r="K7" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1630" t="inlineStr">
+      <c r="A8" s="1692" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1631" t="n">
+      <c r="B8" s="1693" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1632" t="n">
+      <c r="C8" s="1694" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1633" t="n">
+      <c r="D8" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1634" t="n">
+      <c r="E8" s="1696" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1635" t="n">
+      <c r="F8" s="1697" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1636" t="n">
+      <c r="G8" s="1698" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1638" t="n">
+      <c r="H8" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1700" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1639" t="n">
+      <c r="J8" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1641" t="n">
+      <c r="K8" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1630" t="inlineStr">
+      <c r="A9" s="1692" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1631" t="n">
+      <c r="B9" s="1693" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1632" t="n">
+      <c r="C9" s="1694" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1633" t="n">
+      <c r="D9" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1634" t="n">
+      <c r="E9" s="1696" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1635" t="n">
+      <c r="F9" s="1697" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1636" t="n">
+      <c r="G9" s="1698" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1638" t="n">
+      <c r="H9" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1700" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1639" t="n">
+      <c r="J9" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1641" t="n">
+      <c r="K9" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1630" t="inlineStr">
+      <c r="A10" s="1692" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -6300,562 +6519,562 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1630" t="inlineStr">
+      <c r="A11" s="1692" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1631" t="n">
+      <c r="B11" s="1693" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1632" t="n">
+      <c r="C11" s="1694" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1633" t="n">
+      <c r="D11" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1634" t="n">
+      <c r="E11" s="1696" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1635" t="n">
+      <c r="F11" s="1697" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1636" t="n">
+      <c r="G11" s="1698" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1639" t="n">
+      <c r="H11" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1641" t="n">
+      <c r="K11" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1630" t="inlineStr">
+      <c r="A12" s="1692" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1631" t="n">
+      <c r="B12" s="1693" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1632" t="n">
+      <c r="C12" s="1694" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1633" t="n">
+      <c r="D12" s="1695" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1634" t="n">
+      <c r="E12" s="1696" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1635" t="n">
+      <c r="F12" s="1697" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1636" t="n">
+      <c r="G12" s="1698" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1639" t="n">
+      <c r="H12" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1701" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1641" t="n">
+      <c r="K12" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1630" t="inlineStr">
+      <c r="A13" s="1692" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1631" t="n">
+      <c r="B13" s="1693" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1632" t="n">
+      <c r="C13" s="1694" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1633" t="n">
+      <c r="D13" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1634" t="n">
+      <c r="E13" s="1696" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1635" t="n">
+      <c r="F13" s="1697" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1636" t="n">
+      <c r="G13" s="1698" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1638" t="n">
+      <c r="H13" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1700" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1639" t="n">
+      <c r="J13" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1641" t="n">
+      <c r="K13" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1630" t="inlineStr">
+      <c r="A14" s="1692" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1631" t="n">
+      <c r="B14" s="1693" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1632" t="n">
+      <c r="C14" s="1694" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1633" t="n">
+      <c r="D14" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1634" t="n">
+      <c r="E14" s="1696" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1635" t="n">
+      <c r="F14" s="1697" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1636" t="n">
+      <c r="G14" s="1698" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1638" t="n">
+      <c r="H14" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1700" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1639" t="n">
+      <c r="J14" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1641" t="n">
+      <c r="K14" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1630" t="inlineStr">
+      <c r="A15" s="1692" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1631" t="n">
+      <c r="B15" s="1693" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1632" t="n">
+      <c r="C15" s="1694" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1633" t="n">
+      <c r="D15" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1634" t="n">
+      <c r="E15" s="1696" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1635" t="n">
+      <c r="F15" s="1697" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1636" t="n">
+      <c r="G15" s="1698" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1638" t="n">
+      <c r="H15" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1700" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1639" t="n">
+      <c r="J15" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1641" t="n">
+      <c r="K15" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1630" t="inlineStr">
+      <c r="A16" s="1692" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1631" t="n">
+      <c r="B16" s="1693" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1632" t="n">
+      <c r="C16" s="1694" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1633" t="n">
+      <c r="D16" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1634" t="n">
+      <c r="E16" s="1696" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1635" t="n">
+      <c r="F16" s="1697" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1636" t="n">
+      <c r="G16" s="1698" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1638" t="n">
+      <c r="H16" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1700" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1639" t="n">
+      <c r="J16" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1641" t="n">
+      <c r="K16" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1630" t="inlineStr">
+      <c r="A17" s="1692" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1631" t="n">
+      <c r="B17" s="1693" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1632" t="n">
+      <c r="C17" s="1694" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1633" t="n">
+      <c r="D17" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1634" t="n">
+      <c r="E17" s="1696" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1635" t="n">
+      <c r="F17" s="1697" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1636" t="n">
+      <c r="G17" s="1698" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1638" t="n">
+      <c r="H17" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1700" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1639" t="n">
+      <c r="J17" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1641" t="n">
+      <c r="K17" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1630" t="inlineStr">
+      <c r="A18" s="1692" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1631" t="n">
+      <c r="B18" s="1693" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1632" t="n">
+      <c r="C18" s="1694" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1633" t="n">
+      <c r="D18" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1634" t="n">
+      <c r="E18" s="1696" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1635" t="n">
+      <c r="F18" s="1697" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1636" t="n">
+      <c r="G18" s="1698" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1638" t="n">
+      <c r="H18" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1700" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1639" t="n">
+      <c r="J18" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1641" t="n">
+      <c r="K18" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1630" t="inlineStr">
+      <c r="A19" s="1692" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1631" t="n">
+      <c r="B19" s="1693" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1632" t="n">
+      <c r="C19" s="1694" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1633" t="n">
+      <c r="D19" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1634" t="n">
+      <c r="E19" s="1696" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1635" t="n">
+      <c r="F19" s="1697" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1636" t="n">
+      <c r="G19" s="1698" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1638" t="n">
+      <c r="H19" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1700" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1639" t="n">
+      <c r="J19" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1641" t="n">
+      <c r="K19" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1630" t="inlineStr">
+      <c r="A20" s="1692" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1631" t="n">
+      <c r="B20" s="1693" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1632" t="n">
+      <c r="C20" s="1694" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1633" t="n">
+      <c r="D20" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1634" t="n">
+      <c r="E20" s="1696" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1635" t="n">
+      <c r="F20" s="1697" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1636" t="n">
+      <c r="G20" s="1698" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1639" t="n">
+      <c r="H20" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1641" t="n">
+      <c r="K20" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1630" t="inlineStr">
+      <c r="A21" s="1692" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B21" s="1631" t="n">
+      <c r="B21" s="1693" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="1632" t="n">
+      <c r="C21" s="1694" t="n">
         <v>313566.1793926954</v>
       </c>
-      <c r="D21" s="1633" t="n">
+      <c r="D21" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E21" s="1634" t="n">
+      <c r="E21" s="1696" t="n">
         <v>264836.0024452209</v>
       </c>
-      <c r="F21" s="1635" t="n">
+      <c r="F21" s="1697" t="n">
         <v>13566.17939269543</v>
       </c>
-      <c r="G21" s="1636" t="n">
+      <c r="G21" s="1698" t="n">
         <v>0.04522059797565142</v>
       </c>
-      <c r="H21" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1639" t="n">
+      <c r="H21" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1641" t="n">
+      <c r="K21" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1630" t="inlineStr">
+      <c r="A22" s="1692" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B22" s="1631" t="n">
+      <c r="B22" s="1693" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="1632" t="n">
+      <c r="C22" s="1694" t="n">
         <v>321999.1744259596</v>
       </c>
-      <c r="D22" s="1633" t="n">
+      <c r="D22" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E22" s="1634" t="n">
+      <c r="E22" s="1696" t="n">
         <v>273268.9974784851</v>
       </c>
-      <c r="F22" s="1635" t="n">
+      <c r="F22" s="1697" t="n">
         <v>21999.17442595959</v>
       </c>
-      <c r="G22" s="1636" t="n">
+      <c r="G22" s="1698" t="n">
         <v>0.07333058141986529</v>
       </c>
-      <c r="H22" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1639" t="n">
+      <c r="H22" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1641" t="n">
+      <c r="K22" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1630" t="inlineStr">
+      <c r="A23" s="1692" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B23" s="1631" t="n">
+      <c r="B23" s="1693" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="1632" t="n">
+      <c r="C23" s="1694" t="n">
         <v>323626.1765698195</v>
       </c>
-      <c r="D23" s="1633" t="n">
+      <c r="D23" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E23" s="1634" t="n">
+      <c r="E23" s="1696" t="n">
         <v>274895.999622345</v>
       </c>
-      <c r="F23" s="1635" t="n">
+      <c r="F23" s="1697" t="n">
         <v>23626.17656981945</v>
       </c>
-      <c r="G23" s="1636" t="n">
+      <c r="G23" s="1698" t="n">
         <v>0.07875392189939817</v>
       </c>
-      <c r="H23" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1639" t="n">
+      <c r="H23" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K23" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1641" t="n">
+      <c r="K23" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1630" t="inlineStr">
+      <c r="A24" s="1692" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B24" s="1631" t="n">
+      <c r="B24" s="1693" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="1632" t="n">
+      <c r="C24" s="1694" t="n">
         <v>327462.1705511808</v>
       </c>
-      <c r="D24" s="1633" t="n">
+      <c r="D24" s="1695" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E24" s="1634" t="n">
+      <c r="E24" s="1696" t="n">
         <v>278731.9936037064</v>
       </c>
-      <c r="F24" s="1635" t="n">
+      <c r="F24" s="1697" t="n">
         <v>27462.17055118084</v>
       </c>
-      <c r="G24" s="1636" t="n">
+      <c r="G24" s="1698" t="n">
         <v>0.09154056850393615</v>
       </c>
-      <c r="H24" s="1637" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1638" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1639" t="n">
+      <c r="H24" s="1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1701" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="1640" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1641" t="n">
+      <c r="K24" s="1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1703" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6896,6 +7115,46 @@
         <v>0</v>
       </c>
       <c r="L25" s="1703" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="1765" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B26" s="1766" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1767" t="n">
+        <v>325656.1784008741</v>
+      </c>
+      <c r="D26" s="1768" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E26" s="1769" t="n">
+        <v>276926.0014533997</v>
+      </c>
+      <c r="F26" s="1770" t="n">
+        <v>25656.17840087414</v>
+      </c>
+      <c r="G26" s="1771" t="n">
+        <v>0.08552059466958047</v>
+      </c>
+      <c r="H26" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1773" t="n">
+        <v>-0.005515116898134752</v>
+      </c>
+      <c r="J26" s="1774" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6928,452 +7187,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1704" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  27 May 2026</t>
+      <c r="A1" s="1777" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  28 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1705" t="inlineStr">
+      <c r="A2" s="1778" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1705" t="inlineStr">
+      <c r="B2" s="1778" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1705" t="inlineStr">
+      <c r="C2" s="1778" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1705" t="inlineStr">
+      <c r="D2" s="1778" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1705" t="inlineStr">
+      <c r="E2" s="1778" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1705" t="inlineStr">
+      <c r="F2" s="1778" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1705" t="inlineStr">
+      <c r="G2" s="1778" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1705" t="inlineStr">
+      <c r="H2" s="1778" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1705" t="inlineStr">
+      <c r="I2" s="1778" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1705" t="inlineStr">
+      <c r="J2" s="1778" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1705" t="inlineStr">
+      <c r="K2" s="1778" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1706" t="inlineStr">
+      <c r="A3" s="1779" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1707" t="inlineStr">
+      <c r="B3" s="1780" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1708" t="n">
+      <c r="C3" s="1781" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1709" t="n">
+      <c r="D3" s="1782" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1710" t="n">
-        <v>24.79999923706055</v>
-      </c>
-      <c r="F3" s="1711">
+      <c r="E3" s="1783" t="n">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1784">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1712">
+      <c r="G3" s="1785">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1713">
+      <c r="H3" s="1786">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1714" t="inlineStr">
+      <c r="I3" s="1787" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1715" t="n">
+      <c r="J3" s="1788" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1716" t="inlineStr">
+      <c r="K3" s="1789" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1706" t="inlineStr">
+      <c r="A4" s="1779" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1707" t="inlineStr">
+      <c r="B4" s="1780" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1708" t="n">
+      <c r="C4" s="1781" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1709" t="n">
+      <c r="D4" s="1782" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1710" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1711">
+      <c r="E4" s="1783" t="n">
+        <v>5.099999904632568</v>
+      </c>
+      <c r="F4" s="1784">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1712">
+      <c r="G4" s="1785">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1713">
+      <c r="H4" s="1786">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1714" t="inlineStr">
+      <c r="I4" s="1787" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1717" t="n">
+      <c r="J4" s="1790" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1718" t="inlineStr">
+      <c r="K4" s="1791" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1706" t="inlineStr">
+      <c r="A5" s="1779" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1707" t="inlineStr">
+      <c r="B5" s="1780" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1708" t="n">
+      <c r="C5" s="1781" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1709" t="n">
+      <c r="D5" s="1782" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1710" t="n">
-        <v>17.70000076293945</v>
-      </c>
-      <c r="F5" s="1711">
+      <c r="E5" s="1783" t="n">
+        <v>17.60000038146973</v>
+      </c>
+      <c r="F5" s="1784">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1712">
+      <c r="G5" s="1785">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1713">
+      <c r="H5" s="1786">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1714" t="inlineStr">
+      <c r="I5" s="1787" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1719" t="n">
+      <c r="J5" s="1792" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1720" t="inlineStr">
+      <c r="K5" s="1793" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1706" t="inlineStr">
+      <c r="A6" s="1779" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B6" s="1707" t="inlineStr">
+      <c r="B6" s="1780" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C6" s="1708" t="n">
+      <c r="C6" s="1781" t="n">
         <v>2700</v>
       </c>
-      <c r="D6" s="1709" t="n">
+      <c r="D6" s="1782" t="n">
         <v>17.4</v>
       </c>
-      <c r="E6" s="1710" t="n">
-        <v>18.29999923706055</v>
-      </c>
-      <c r="F6" s="1711">
+      <c r="E6" s="1783" t="n">
+        <v>18.20000076293945</v>
+      </c>
+      <c r="F6" s="1784">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1712">
+      <c r="G6" s="1785">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1713">
+      <c r="H6" s="1786">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1714" t="inlineStr">
+      <c r="I6" s="1787" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1717" t="n">
+      <c r="J6" s="1790" t="n">
         <v>5.68</v>
       </c>
-      <c r="K6" s="1718" t="inlineStr">
+      <c r="K6" s="1791" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1706" t="inlineStr">
+      <c r="A7" s="1779" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="1707" t="inlineStr">
+      <c r="B7" s="1780" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="1708" t="n">
+      <c r="C7" s="1781" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="1709" t="n">
+      <c r="D7" s="1782" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="1710" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="F7" s="1711">
+      <c r="E7" s="1783" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1784">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1712">
+      <c r="G7" s="1785">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1713">
+      <c r="H7" s="1786">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1714" t="inlineStr">
+      <c r="I7" s="1787" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1717" t="n">
+      <c r="J7" s="1790" t="n">
         <v>5.88</v>
       </c>
-      <c r="K7" s="1718" t="inlineStr">
+      <c r="K7" s="1791" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1706" t="inlineStr">
+      <c r="A8" s="1794" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1707" t="inlineStr">
+      <c r="B8" s="1795" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1708" t="n">
+      <c r="C8" s="1796" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1709" t="n">
+      <c r="D8" s="1797" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1710" t="n">
-        <v>4.239999771118164</v>
-      </c>
-      <c r="F8" s="1711">
+      <c r="E8" s="1798" t="n">
+        <v>4.199999809265137</v>
+      </c>
+      <c r="F8" s="1799">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1712">
+      <c r="G8" s="1800">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1713">
+      <c r="H8" s="1801">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1714" t="inlineStr">
+      <c r="I8" s="1802" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1717" t="n">
+      <c r="J8" s="1803" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1718" t="inlineStr">
+      <c r="K8" s="1804" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1721" t="inlineStr">
+      <c r="A9" s="1794" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1722" t="inlineStr">
+      <c r="B9" s="1795" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1723" t="n">
+      <c r="C9" s="1796" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1724" t="n">
+      <c r="D9" s="1797" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1725" t="n">
+      <c r="E9" s="1798" t="n">
         <v>2.619999885559082</v>
       </c>
-      <c r="F9" s="1726">
+      <c r="F9" s="1799">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1727">
+      <c r="G9" s="1800">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1728">
+      <c r="H9" s="1801">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1729" t="inlineStr">
+      <c r="I9" s="1802" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1730" t="n">
+      <c r="J9" s="1803" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1731" t="inlineStr">
+      <c r="K9" s="1804" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1732" t="inlineStr">
+      <c r="A10" s="1805" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1733" t="inlineStr">
+      <c r="B10" s="1806" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1734" t="n">
+      <c r="C10" s="1807" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1735" t="n">
+      <c r="D10" s="1808" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1736" t="n">
-        <v>11.30000019073486</v>
-      </c>
-      <c r="F10" s="1737">
+      <c r="E10" s="1809" t="n">
+        <v>11.19999980926514</v>
+      </c>
+      <c r="F10" s="1810">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1738">
+      <c r="G10" s="1811">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1739">
+      <c r="H10" s="1812">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1740" t="inlineStr">
+      <c r="I10" s="1813" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1741" t="n">
+      <c r="J10" s="1814" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1742" t="inlineStr">
+      <c r="K10" s="1815" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1743" t="inlineStr">
+      <c r="B11" s="1816" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1744">
+      <c r="F11" s="1817">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1745">
+      <c r="G11" s="1818">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1746">
+      <c r="H11" s="1819">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -7408,14 +7667,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1704" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  27 May 2026</t>
+      <c r="A1" s="1777" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  28 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1747" t="inlineStr">
+      <c r="A3" s="1820" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -7453,550 +7712,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1704" t="inlineStr">
+      <c r="A1" s="1777" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1705" t="inlineStr">
+      <c r="A2" s="1778" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1705" t="inlineStr">
+      <c r="B2" s="1778" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1705" t="inlineStr">
+      <c r="C2" s="1778" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1705" t="inlineStr">
+      <c r="D2" s="1778" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1705" t="inlineStr">
+      <c r="E2" s="1778" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1705" t="inlineStr">
+      <c r="F2" s="1778" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1705" t="inlineStr">
+      <c r="G2" s="1778" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1705" t="inlineStr">
+      <c r="H2" s="1778" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1705" t="inlineStr">
+      <c r="I2" s="1778" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1705" t="inlineStr">
+      <c r="J2" s="1778" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1748" t="inlineStr">
+      <c r="A3" s="1821" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1749" t="inlineStr">
+      <c r="B3" s="1822" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1750" t="inlineStr">
+      <c r="C3" s="1823" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1751" t="inlineStr">
+      <c r="D3" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1752" t="n">
+      <c r="E3" s="1825" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1753" t="n">
+      <c r="F3" s="1826" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1752" t="n">
+      <c r="G3" s="1825" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1754">
+      <c r="H3" s="1827">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1755" t="inlineStr">
+      <c r="I3" s="1828" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1756" t="inlineStr">
+      <c r="J3" s="1829" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1757" t="inlineStr">
+      <c r="A4" s="1830" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1758" t="inlineStr">
+      <c r="B4" s="1831" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1722" t="inlineStr">
+      <c r="C4" s="1795" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1751" t="inlineStr">
+      <c r="D4" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1723" t="n">
+      <c r="E4" s="1796" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1724" t="n">
+      <c r="F4" s="1797" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1723" t="n">
+      <c r="G4" s="1796" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1726">
+      <c r="H4" s="1799">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1759" t="inlineStr">
+      <c r="I4" s="1832" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1760" t="inlineStr">
+      <c r="J4" s="1833" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1748" t="inlineStr">
+      <c r="A5" s="1821" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1749" t="inlineStr">
+      <c r="B5" s="1822" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1750" t="inlineStr">
+      <c r="C5" s="1823" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1751" t="inlineStr">
+      <c r="D5" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1752" t="n">
+      <c r="E5" s="1825" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1753" t="n">
+      <c r="F5" s="1826" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1752" t="n">
+      <c r="G5" s="1825" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1754">
+      <c r="H5" s="1827">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1755" t="inlineStr">
+      <c r="I5" s="1828" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1756" t="inlineStr">
+      <c r="J5" s="1829" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1757" t="inlineStr">
+      <c r="A6" s="1830" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1758" t="inlineStr">
+      <c r="B6" s="1831" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1722" t="inlineStr">
+      <c r="C6" s="1795" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1751" t="inlineStr">
+      <c r="D6" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1723" t="n">
+      <c r="E6" s="1796" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1724" t="n">
+      <c r="F6" s="1797" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1723" t="n">
+      <c r="G6" s="1796" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1726">
+      <c r="H6" s="1799">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1759" t="inlineStr">
+      <c r="I6" s="1832" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1760" t="inlineStr">
+      <c r="J6" s="1833" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1748" t="inlineStr">
+      <c r="A7" s="1821" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1749" t="inlineStr">
+      <c r="B7" s="1822" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1750" t="inlineStr">
+      <c r="C7" s="1823" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1751" t="inlineStr">
+      <c r="D7" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1752" t="n">
+      <c r="E7" s="1825" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1753" t="n">
+      <c r="F7" s="1826" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1752" t="n">
+      <c r="G7" s="1825" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1754">
+      <c r="H7" s="1827">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1755" t="inlineStr">
+      <c r="I7" s="1828" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1756" t="inlineStr">
+      <c r="J7" s="1829" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1757" t="inlineStr">
+      <c r="A8" s="1830" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1758" t="inlineStr">
+      <c r="B8" s="1831" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1722" t="inlineStr">
+      <c r="C8" s="1795" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1751" t="inlineStr">
+      <c r="D8" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1723" t="n">
+      <c r="E8" s="1796" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1724" t="n">
+      <c r="F8" s="1797" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1723" t="n">
+      <c r="G8" s="1796" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1726">
+      <c r="H8" s="1799">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1759" t="inlineStr">
+      <c r="I8" s="1832" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1760" t="inlineStr">
+      <c r="J8" s="1833" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1748" t="inlineStr">
+      <c r="A9" s="1821" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1749" t="inlineStr">
+      <c r="B9" s="1822" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1750" t="inlineStr">
+      <c r="C9" s="1823" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1761" t="inlineStr">
+      <c r="D9" s="1834" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1752" t="n">
+      <c r="E9" s="1825" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1753" t="n">
+      <c r="F9" s="1826" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1752" t="n">
+      <c r="G9" s="1825" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1754">
+      <c r="H9" s="1827">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1762" t="n">
+      <c r="I9" s="1835" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1756" t="inlineStr">
+      <c r="J9" s="1829" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1757" t="inlineStr">
+      <c r="A10" s="1830" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1758" t="inlineStr">
+      <c r="B10" s="1831" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1722" t="inlineStr">
+      <c r="C10" s="1795" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1761" t="inlineStr">
+      <c r="D10" s="1834" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1723" t="n">
+      <c r="E10" s="1796" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1724" t="n">
+      <c r="F10" s="1797" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1723" t="n">
+      <c r="G10" s="1796" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1726">
+      <c r="H10" s="1799">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1763" t="n">
+      <c r="I10" s="1836" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1760" t="inlineStr">
+      <c r="J10" s="1833" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1748" t="inlineStr">
+      <c r="A11" s="1821" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1749" t="inlineStr">
+      <c r="B11" s="1822" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1750" t="inlineStr">
+      <c r="C11" s="1823" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1751" t="inlineStr">
+      <c r="D11" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1752" t="n">
+      <c r="E11" s="1825" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1753" t="n">
+      <c r="F11" s="1826" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1752" t="n">
+      <c r="G11" s="1825" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1754">
+      <c r="H11" s="1827">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1755" t="inlineStr">
+      <c r="I11" s="1828" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1756" t="inlineStr">
+      <c r="J11" s="1829" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1757" t="inlineStr">
+      <c r="A12" s="1830" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1758" t="inlineStr">
+      <c r="B12" s="1831" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1722" t="inlineStr">
+      <c r="C12" s="1795" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1751" t="inlineStr">
+      <c r="D12" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1723" t="n">
+      <c r="E12" s="1796" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1724" t="n">
+      <c r="F12" s="1797" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1723" t="n">
+      <c r="G12" s="1796" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1726">
+      <c r="H12" s="1799">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1759" t="inlineStr">
+      <c r="I12" s="1832" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1760" t="inlineStr">
+      <c r="J12" s="1833" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1748" t="inlineStr">
+      <c r="A13" s="1821" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1749" t="inlineStr">
+      <c r="B13" s="1822" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1750" t="inlineStr">
+      <c r="C13" s="1823" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1751" t="inlineStr">
+      <c r="D13" s="1824" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1752" t="n">
+      <c r="E13" s="1825" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1753" t="n">
+      <c r="F13" s="1826" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1752" t="n">
+      <c r="G13" s="1825" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1754">
+      <c r="H13" s="1827">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1755" t="inlineStr">
+      <c r="I13" s="1828" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1756" t="inlineStr">
+      <c r="J13" s="1829" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -8008,11 +8267,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1764">
+      <c r="H15" s="1837">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1764">
+      <c r="I15" s="1837">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1838">
+  <cellXfs count="1911">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5207,6 +5207,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6079,7 +6298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6159,47 +6378,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1692" t="inlineStr">
+      <c r="A2" s="1765" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1693" t="n">
+      <c r="B2" s="1766" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1694" t="n">
+      <c r="C2" s="1767" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1695" t="n">
+      <c r="D2" s="1768" t="n">
         <v>29448.30848187208</v>
       </c>
-      <c r="E2" s="1696" t="n">
+      <c r="E2" s="1769" t="n">
         <v>274299.9974489212</v>
       </c>
-      <c r="F2" s="1697" t="n">
+      <c r="F2" s="1770" t="n">
         <v>3748.305930793285</v>
       </c>
-      <c r="G2" s="1698" t="n">
+      <c r="G2" s="1771" t="n">
         <v>0.01249435310264429</v>
       </c>
-      <c r="H2" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1701" t="n">
+      <c r="H2" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1774" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1703" t="n">
+      <c r="K2" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1692" t="inlineStr">
+      <c r="A3" s="1765" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
@@ -6239,7 +6458,7 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1692" t="inlineStr">
+      <c r="A4" s="1765" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
@@ -6279,207 +6498,207 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1692" t="inlineStr">
+      <c r="A5" s="1765" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B5" s="1693" t="n">
+      <c r="B5" s="1766" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="1694" t="n">
+      <c r="C5" s="1767" t="n">
         <v>304153.8160982132</v>
       </c>
-      <c r="D5" s="1695" t="n">
+      <c r="D5" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E5" s="1696" t="n">
+      <c r="E5" s="1769" t="n">
         <v>285729.9982070923</v>
       </c>
-      <c r="F5" s="1697" t="n">
+      <c r="F5" s="1770" t="n">
         <v>4153.816098213196</v>
       </c>
-      <c r="G5" s="1698" t="n">
+      <c r="G5" s="1771" t="n">
         <v>0.01384605366071065</v>
       </c>
-      <c r="H5" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1701" t="n">
+      <c r="H5" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1703" t="n">
+      <c r="K5" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1692" t="inlineStr">
+      <c r="A6" s="1765" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B6" s="1693" t="n">
+      <c r="B6" s="1766" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="1694" t="n">
+      <c r="C6" s="1767" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D6" s="1695" t="n">
+      <c r="D6" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E6" s="1696" t="n">
+      <c r="E6" s="1769" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F6" s="1697" t="n">
+      <c r="F6" s="1770" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G6" s="1698" t="n">
+      <c r="G6" s="1771" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H6" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1700" t="n">
+      <c r="H6" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1773" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J6" s="1701" t="n">
+      <c r="J6" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K6" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1703" t="n">
+      <c r="K6" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1692" t="inlineStr">
+      <c r="A7" s="1765" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="B7" s="1693" t="n">
+      <c r="B7" s="1766" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="1694" t="n">
+      <c r="C7" s="1767" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D7" s="1695" t="n">
+      <c r="D7" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E7" s="1696" t="n">
+      <c r="E7" s="1769" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F7" s="1697" t="n">
+      <c r="F7" s="1770" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G7" s="1698" t="n">
+      <c r="G7" s="1771" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H7" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1700" t="n">
+      <c r="H7" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1773" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J7" s="1701" t="n">
+      <c r="J7" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1703" t="n">
+      <c r="K7" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1692" t="inlineStr">
+      <c r="A8" s="1765" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="B8" s="1693" t="n">
+      <c r="B8" s="1766" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="1694" t="n">
+      <c r="C8" s="1767" t="n">
         <v>302787.819642067</v>
       </c>
-      <c r="D8" s="1695" t="n">
+      <c r="D8" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E8" s="1696" t="n">
+      <c r="E8" s="1769" t="n">
         <v>284364.001750946</v>
       </c>
-      <c r="F8" s="1697" t="n">
+      <c r="F8" s="1770" t="n">
         <v>2787.819642066956</v>
       </c>
-      <c r="G8" s="1698" t="n">
+      <c r="G8" s="1771" t="n">
         <v>0.009292732140223185</v>
       </c>
-      <c r="H8" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1700" t="n">
+      <c r="H8" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1773" t="n">
         <v>-0.004491136996634464</v>
       </c>
-      <c r="J8" s="1701" t="n">
+      <c r="J8" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1703" t="n">
+      <c r="K8" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1692" t="inlineStr">
+      <c r="A9" s="1765" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1693" t="n">
+      <c r="B9" s="1766" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="1694" t="n">
+      <c r="C9" s="1767" t="n">
         <v>301062.819642067</v>
       </c>
-      <c r="D9" s="1695" t="n">
+      <c r="D9" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E9" s="1696" t="n">
+      <c r="E9" s="1769" t="n">
         <v>282639.001750946</v>
       </c>
-      <c r="F9" s="1697" t="n">
+      <c r="F9" s="1770" t="n">
         <v>1062.819642066956</v>
       </c>
-      <c r="G9" s="1698" t="n">
+      <c r="G9" s="1771" t="n">
         <v>0.003542732140223185</v>
       </c>
-      <c r="H9" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1700" t="n">
+      <c r="H9" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1773" t="n">
         <v>-0.01016260948423589</v>
       </c>
-      <c r="J9" s="1701" t="n">
+      <c r="J9" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K9" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1703" t="n">
+      <c r="K9" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1692" t="inlineStr">
+      <c r="A10" s="1765" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
@@ -6519,602 +6738,602 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1692" t="inlineStr">
+      <c r="A11" s="1765" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="B11" s="1693" t="n">
+      <c r="B11" s="1766" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="1694" t="n">
+      <c r="C11" s="1767" t="n">
         <v>308341.8176355362</v>
       </c>
-      <c r="D11" s="1695" t="n">
+      <c r="D11" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E11" s="1696" t="n">
+      <c r="E11" s="1769" t="n">
         <v>289917.9997444153</v>
       </c>
-      <c r="F11" s="1697" t="n">
+      <c r="F11" s="1770" t="n">
         <v>8341.817635536194</v>
       </c>
-      <c r="G11" s="1698" t="n">
+      <c r="G11" s="1771" t="n">
         <v>0.02780605878512065</v>
       </c>
-      <c r="H11" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1701" t="n">
+      <c r="H11" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1703" t="n">
+      <c r="K11" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1692" t="inlineStr">
+      <c r="A12" s="1765" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1693" t="n">
+      <c r="B12" s="1766" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="1694" t="n">
+      <c r="C12" s="1767" t="n">
         <v>311587.818192482</v>
       </c>
-      <c r="D12" s="1695" t="n">
+      <c r="D12" s="1768" t="n">
         <v>18423.81789112091</v>
       </c>
-      <c r="E12" s="1696" t="n">
+      <c r="E12" s="1769" t="n">
         <v>293164.0003013611</v>
       </c>
-      <c r="F12" s="1697" t="n">
+      <c r="F12" s="1770" t="n">
         <v>11587.81819248199</v>
       </c>
-      <c r="G12" s="1698" t="n">
+      <c r="G12" s="1771" t="n">
         <v>0.03862606064160665</v>
       </c>
-      <c r="H12" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1701" t="n">
+      <c r="H12" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1774" t="n">
         <v>6</v>
       </c>
-      <c r="K12" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1703" t="n">
+      <c r="K12" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1692" t="inlineStr">
+      <c r="A13" s="1765" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="B13" s="1693" t="n">
+      <c r="B13" s="1766" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="1694" t="n">
+      <c r="C13" s="1767" t="n">
         <v>310489.1351679564</v>
       </c>
-      <c r="D13" s="1695" t="n">
+      <c r="D13" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E13" s="1696" t="n">
+      <c r="E13" s="1769" t="n">
         <v>261758.9582204819</v>
       </c>
-      <c r="F13" s="1697" t="n">
+      <c r="F13" s="1770" t="n">
         <v>10489.13516795635</v>
       </c>
-      <c r="G13" s="1698" t="n">
+      <c r="G13" s="1771" t="n">
         <v>0.03496378389318784</v>
       </c>
-      <c r="H13" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1700" t="n">
+      <c r="H13" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1773" t="n">
         <v>-0.003526078236623923</v>
       </c>
-      <c r="J13" s="1701" t="n">
+      <c r="J13" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1703" t="n">
+      <c r="K13" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1692" t="inlineStr">
+      <c r="A14" s="1765" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="B14" s="1693" t="n">
+      <c r="B14" s="1766" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="1694" t="n">
+      <c r="C14" s="1767" t="n">
         <v>304964.1755083799</v>
       </c>
-      <c r="D14" s="1695" t="n">
+      <c r="D14" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E14" s="1696" t="n">
+      <c r="E14" s="1769" t="n">
         <v>256233.9985609055</v>
       </c>
-      <c r="F14" s="1697" t="n">
+      <c r="F14" s="1770" t="n">
         <v>4964.175508379936</v>
       </c>
-      <c r="G14" s="1698" t="n">
+      <c r="G14" s="1771" t="n">
         <v>0.01654725169459979</v>
       </c>
-      <c r="H14" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1700" t="n">
+      <c r="H14" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1773" t="n">
         <v>-0.0212577074499438</v>
       </c>
-      <c r="J14" s="1701" t="n">
+      <c r="J14" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K14" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1703" t="n">
+      <c r="K14" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1692" t="inlineStr">
+      <c r="A15" s="1765" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="B15" s="1693" t="n">
+      <c r="B15" s="1766" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="1694" t="n">
+      <c r="C15" s="1767" t="n">
         <v>302514.1766527891</v>
       </c>
-      <c r="D15" s="1695" t="n">
+      <c r="D15" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E15" s="1696" t="n">
+      <c r="E15" s="1769" t="n">
         <v>253783.9997053146</v>
       </c>
-      <c r="F15" s="1697" t="n">
+      <c r="F15" s="1770" t="n">
         <v>2514.176652789116</v>
       </c>
-      <c r="G15" s="1698" t="n">
+      <c r="G15" s="1771" t="n">
         <v>0.008380588842630387</v>
       </c>
-      <c r="H15" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1700" t="n">
+      <c r="H15" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1773" t="n">
         <v>-0.0291206555902249</v>
       </c>
-      <c r="J15" s="1701" t="n">
+      <c r="J15" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K15" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1703" t="n">
+      <c r="K15" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1692" t="inlineStr">
+      <c r="A16" s="1765" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="B16" s="1693" t="n">
+      <c r="B16" s="1766" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="1694" t="n">
+      <c r="C16" s="1767" t="n">
         <v>304920.1800802946</v>
       </c>
-      <c r="D16" s="1695" t="n">
+      <c r="D16" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E16" s="1696" t="n">
+      <c r="E16" s="1769" t="n">
         <v>256190.0031328201</v>
       </c>
-      <c r="F16" s="1697" t="n">
+      <c r="F16" s="1770" t="n">
         <v>4920.180080294609</v>
       </c>
-      <c r="G16" s="1698" t="n">
+      <c r="G16" s="1771" t="n">
         <v>0.0164006002676487</v>
       </c>
-      <c r="H16" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1700" t="n">
+      <c r="H16" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1773" t="n">
         <v>-0.02139890497281406</v>
       </c>
-      <c r="J16" s="1701" t="n">
+      <c r="J16" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1703" t="n">
+      <c r="K16" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1692" t="inlineStr">
+      <c r="A17" s="1765" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B17" s="1693" t="n">
+      <c r="B17" s="1766" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="1694" t="n">
+      <c r="C17" s="1767" t="n">
         <v>308166.1738375425</v>
       </c>
-      <c r="D17" s="1695" t="n">
+      <c r="D17" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E17" s="1696" t="n">
+      <c r="E17" s="1769" t="n">
         <v>259435.9968900681</v>
       </c>
-      <c r="F17" s="1697" t="n">
+      <c r="F17" s="1770" t="n">
         <v>8166.173837542534</v>
       </c>
-      <c r="G17" s="1698" t="n">
+      <c r="G17" s="1771" t="n">
         <v>0.02722057945847511</v>
       </c>
-      <c r="H17" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1700" t="n">
+      <c r="H17" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1773" t="n">
         <v>-0.01098131619775249</v>
       </c>
-      <c r="J17" s="1701" t="n">
+      <c r="J17" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K17" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1703" t="n">
+      <c r="K17" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1692" t="inlineStr">
+      <c r="A18" s="1765" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="B18" s="1693" t="n">
+      <c r="B18" s="1766" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="1694" t="n">
+      <c r="C18" s="1767" t="n">
         <v>308376.1740664244</v>
       </c>
-      <c r="D18" s="1695" t="n">
+      <c r="D18" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E18" s="1696" t="n">
+      <c r="E18" s="1769" t="n">
         <v>259645.9971189499</v>
       </c>
-      <c r="F18" s="1697" t="n">
+      <c r="F18" s="1770" t="n">
         <v>8376.17406642437</v>
       </c>
-      <c r="G18" s="1698" t="n">
+      <c r="G18" s="1771" t="n">
         <v>0.02792058022141457</v>
       </c>
-      <c r="H18" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1700" t="n">
+      <c r="H18" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1773" t="n">
         <v>-0.01030734816491974</v>
       </c>
-      <c r="J18" s="1701" t="n">
+      <c r="J18" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K18" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1703" t="n">
+      <c r="K18" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1692" t="inlineStr">
+      <c r="A19" s="1765" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="B19" s="1693" t="n">
+      <c r="B19" s="1766" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="1694" t="n">
+      <c r="C19" s="1767" t="n">
         <v>303508.175180316</v>
       </c>
-      <c r="D19" s="1695" t="n">
+      <c r="D19" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E19" s="1696" t="n">
+      <c r="E19" s="1769" t="n">
         <v>254777.9982328415</v>
       </c>
-      <c r="F19" s="1697" t="n">
+      <c r="F19" s="1770" t="n">
         <v>3508.175180315971</v>
       </c>
-      <c r="G19" s="1698" t="n">
+      <c r="G19" s="1771" t="n">
         <v>0.01169391726771991</v>
       </c>
-      <c r="H19" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1700" t="n">
+      <c r="H19" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1773" t="n">
         <v>-0.02593054843747088</v>
       </c>
-      <c r="J19" s="1701" t="n">
+      <c r="J19" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K19" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1703" t="n">
+      <c r="K19" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1692" t="inlineStr">
+      <c r="A20" s="1765" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B20" s="1693" t="n">
+      <c r="B20" s="1766" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1694" t="n">
+      <c r="C20" s="1767" t="n">
         <v>313322.179959178</v>
       </c>
-      <c r="D20" s="1695" t="n">
+      <c r="D20" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E20" s="1696" t="n">
+      <c r="E20" s="1769" t="n">
         <v>264592.0030117035</v>
       </c>
-      <c r="F20" s="1697" t="n">
+      <c r="F20" s="1770" t="n">
         <v>13322.17995917797</v>
       </c>
-      <c r="G20" s="1698" t="n">
+      <c r="G20" s="1771" t="n">
         <v>0.04440726653059324</v>
       </c>
-      <c r="H20" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1701" t="n">
+      <c r="H20" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K20" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1703" t="n">
+      <c r="K20" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1692" t="inlineStr">
+      <c r="A21" s="1765" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B21" s="1693" t="n">
+      <c r="B21" s="1766" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="1694" t="n">
+      <c r="C21" s="1767" t="n">
         <v>313566.1793926954</v>
       </c>
-      <c r="D21" s="1695" t="n">
+      <c r="D21" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E21" s="1696" t="n">
+      <c r="E21" s="1769" t="n">
         <v>264836.0024452209</v>
       </c>
-      <c r="F21" s="1697" t="n">
+      <c r="F21" s="1770" t="n">
         <v>13566.17939269543</v>
       </c>
-      <c r="G21" s="1698" t="n">
+      <c r="G21" s="1771" t="n">
         <v>0.04522059797565142</v>
       </c>
-      <c r="H21" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1701" t="n">
+      <c r="H21" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1703" t="n">
+      <c r="K21" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1692" t="inlineStr">
+      <c r="A22" s="1765" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B22" s="1693" t="n">
+      <c r="B22" s="1766" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="1694" t="n">
+      <c r="C22" s="1767" t="n">
         <v>321999.1744259596</v>
       </c>
-      <c r="D22" s="1695" t="n">
+      <c r="D22" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E22" s="1696" t="n">
+      <c r="E22" s="1769" t="n">
         <v>273268.9974784851</v>
       </c>
-      <c r="F22" s="1697" t="n">
+      <c r="F22" s="1770" t="n">
         <v>21999.17442595959</v>
       </c>
-      <c r="G22" s="1698" t="n">
+      <c r="G22" s="1771" t="n">
         <v>0.07333058141986529</v>
       </c>
-      <c r="H22" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1701" t="n">
+      <c r="H22" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1703" t="n">
+      <c r="K22" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1692" t="inlineStr">
+      <c r="A23" s="1765" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="B23" s="1693" t="n">
+      <c r="B23" s="1766" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="1694" t="n">
+      <c r="C23" s="1767" t="n">
         <v>323626.1765698195</v>
       </c>
-      <c r="D23" s="1695" t="n">
+      <c r="D23" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E23" s="1696" t="n">
+      <c r="E23" s="1769" t="n">
         <v>274895.999622345</v>
       </c>
-      <c r="F23" s="1697" t="n">
+      <c r="F23" s="1770" t="n">
         <v>23626.17656981945</v>
       </c>
-      <c r="G23" s="1698" t="n">
+      <c r="G23" s="1771" t="n">
         <v>0.07875392189939817</v>
       </c>
-      <c r="H23" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1701" t="n">
+      <c r="H23" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K23" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1703" t="n">
+      <c r="K23" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1692" t="inlineStr">
+      <c r="A24" s="1765" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="B24" s="1693" t="n">
+      <c r="B24" s="1766" t="n">
         <v>22</v>
       </c>
-      <c r="C24" s="1694" t="n">
+      <c r="C24" s="1767" t="n">
         <v>327462.1705511808</v>
       </c>
-      <c r="D24" s="1695" t="n">
+      <c r="D24" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E24" s="1696" t="n">
+      <c r="E24" s="1769" t="n">
         <v>278731.9936037064</v>
       </c>
-      <c r="F24" s="1697" t="n">
+      <c r="F24" s="1770" t="n">
         <v>27462.17055118084</v>
       </c>
-      <c r="G24" s="1698" t="n">
+      <c r="G24" s="1771" t="n">
         <v>0.09154056850393615</v>
       </c>
-      <c r="H24" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1700" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1701" t="n">
+      <c r="H24" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1703" t="n">
+      <c r="K24" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="1692" t="inlineStr">
+      <c r="A25" s="1765" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="B25" s="1693" t="n">
+      <c r="B25" s="1766" t="n">
         <v>23</v>
       </c>
-      <c r="C25" s="1694" t="n">
+      <c r="C25" s="1767" t="n">
         <v>324376.1747578382</v>
       </c>
-      <c r="D25" s="1695" t="n">
+      <c r="D25" s="1768" t="n">
         <v>48730.17694747448</v>
       </c>
-      <c r="E25" s="1696" t="n">
+      <c r="E25" s="1769" t="n">
         <v>275645.9978103638</v>
       </c>
-      <c r="F25" s="1697" t="n">
+      <c r="F25" s="1770" t="n">
         <v>24376.17475783825</v>
       </c>
-      <c r="G25" s="1698" t="n">
+      <c r="G25" s="1771" t="n">
         <v>0.08125391585946083</v>
       </c>
-      <c r="H25" s="1699" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1700" t="n">
+      <c r="H25" s="1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1773" t="n">
         <v>-0.009423976479934384</v>
       </c>
-      <c r="J25" s="1701" t="n">
+      <c r="J25" s="1774" t="n">
         <v>8</v>
       </c>
-      <c r="K25" s="1702" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1703" t="n">
+      <c r="K25" s="1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1776" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7155,6 +7374,46 @@
         <v>0</v>
       </c>
       <c r="L26" s="1776" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="1838" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B27" s="1839" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" s="1840" t="n">
+        <v>324000.1746157408</v>
+      </c>
+      <c r="D27" s="1841" t="n">
+        <v>48730.17694747448</v>
+      </c>
+      <c r="E27" s="1842" t="n">
+        <v>275269.9976682663</v>
+      </c>
+      <c r="F27" s="1843" t="n">
+        <v>24000.17461574078</v>
+      </c>
+      <c r="G27" s="1844" t="n">
+        <v>0.08000058205246924</v>
+      </c>
+      <c r="H27" s="1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1846" t="n">
+        <v>-0.01057220114803755</v>
+      </c>
+      <c r="J27" s="1847" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" s="1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1849" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7187,452 +7446,452 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1777" t="inlineStr">
-        <is>
-          <t>Current Holdings  —  28 May 2026</t>
+      <c r="A1" s="1850" t="inlineStr">
+        <is>
+          <t>Current Holdings  —  29 May 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1778" t="inlineStr">
+      <c r="A2" s="1851" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B2" s="1778" t="inlineStr">
+      <c r="B2" s="1851" t="inlineStr">
         <is>
           <t>Stock Name</t>
         </is>
       </c>
-      <c r="C2" s="1778" t="inlineStr">
+      <c r="C2" s="1851" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="D2" s="1778" t="inlineStr">
+      <c r="D2" s="1851" t="inlineStr">
         <is>
           <t>Avg Cost (฿)</t>
         </is>
       </c>
-      <c r="E2" s="1778" t="inlineStr">
+      <c r="E2" s="1851" t="inlineStr">
         <is>
           <t>Current Price (฿)</t>
         </is>
       </c>
-      <c r="F2" s="1778" t="inlineStr">
+      <c r="F2" s="1851" t="inlineStr">
         <is>
           <t>Market Value (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1778" t="inlineStr">
+      <c r="G2" s="1851" t="inlineStr">
         <is>
           <t>Unrealised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="H2" s="1778" t="inlineStr">
+      <c r="H2" s="1851" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I2" s="1778" t="inlineStr">
+      <c r="I2" s="1851" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J2" s="1778" t="inlineStr">
+      <c r="J2" s="1851" t="inlineStr">
         <is>
           <t>Comp Score</t>
         </is>
       </c>
-      <c r="K2" s="1778" t="inlineStr">
+      <c r="K2" s="1851" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1779" t="inlineStr">
+      <c r="A3" s="1852" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="B3" s="1780" t="inlineStr">
+      <c r="B3" s="1853" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="C3" s="1781" t="n">
+      <c r="C3" s="1854" t="n">
         <v>2300</v>
       </c>
-      <c r="D3" s="1782" t="n">
+      <c r="D3" s="1855" t="n">
         <v>20.3</v>
       </c>
-      <c r="E3" s="1783" t="n">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1784">
+      <c r="E3" s="1856" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="F3" s="1857">
         <f>C3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="1785">
+      <c r="G3" s="1858">
         <f>F3-C3*D3</f>
         <v/>
       </c>
-      <c r="H3" s="1786">
+      <c r="H3" s="1859">
         <f>(E3-D3)/D3</f>
         <v/>
       </c>
-      <c r="I3" s="1787" t="inlineStr">
+      <c r="I3" s="1860" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J3" s="1788" t="n">
+      <c r="J3" s="1861" t="n">
         <v>7.52</v>
       </c>
-      <c r="K3" s="1789" t="inlineStr">
+      <c r="K3" s="1862" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1779" t="inlineStr">
+      <c r="A4" s="1852" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="B4" s="1780" t="inlineStr">
+      <c r="B4" s="1853" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="C4" s="1781" t="n">
+      <c r="C4" s="1854" t="n">
         <v>10800</v>
       </c>
-      <c r="D4" s="1782" t="n">
+      <c r="D4" s="1855" t="n">
         <v>4.38</v>
       </c>
-      <c r="E4" s="1783" t="n">
-        <v>5.099999904632568</v>
-      </c>
-      <c r="F4" s="1784">
+      <c r="E4" s="1856" t="n">
+        <v>4.960000038146973</v>
+      </c>
+      <c r="F4" s="1857">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="1785">
+      <c r="G4" s="1858">
         <f>F4-C4*D4</f>
         <v/>
       </c>
-      <c r="H4" s="1786">
+      <c r="H4" s="1859">
         <f>(E4-D4)/D4</f>
         <v/>
       </c>
-      <c r="I4" s="1787" t="inlineStr">
+      <c r="I4" s="1860" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J4" s="1790" t="n">
+      <c r="J4" s="1863" t="n">
         <v>6.28</v>
       </c>
-      <c r="K4" s="1791" t="inlineStr">
+      <c r="K4" s="1864" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1779" t="inlineStr">
+      <c r="A5" s="1852" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="B5" s="1780" t="inlineStr">
+      <c r="B5" s="1853" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="C5" s="1781" t="n">
+      <c r="C5" s="1854" t="n">
         <v>2800</v>
       </c>
-      <c r="D5" s="1782" t="n">
+      <c r="D5" s="1855" t="n">
         <v>16.5</v>
       </c>
-      <c r="E5" s="1783" t="n">
-        <v>17.60000038146973</v>
-      </c>
-      <c r="F5" s="1784">
+      <c r="E5" s="1856" t="n">
+        <v>17.79999923706055</v>
+      </c>
+      <c r="F5" s="1857">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="1785">
+      <c r="G5" s="1858">
         <f>F5-C5*D5</f>
         <v/>
       </c>
-      <c r="H5" s="1786">
+      <c r="H5" s="1859">
         <f>(E5-D5)/D5</f>
         <v/>
       </c>
-      <c r="I5" s="1787" t="inlineStr">
+      <c r="I5" s="1860" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J5" s="1792" t="n">
+      <c r="J5" s="1865" t="n">
         <v>7.32</v>
       </c>
-      <c r="K5" s="1793" t="inlineStr">
+      <c r="K5" s="1866" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1779" t="inlineStr">
+      <c r="A6" s="1852" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="B6" s="1780" t="inlineStr">
+      <c r="B6" s="1853" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="C6" s="1781" t="n">
+      <c r="C6" s="1854" t="n">
         <v>2700</v>
       </c>
-      <c r="D6" s="1782" t="n">
+      <c r="D6" s="1855" t="n">
         <v>17.4</v>
       </c>
-      <c r="E6" s="1783" t="n">
-        <v>18.20000076293945</v>
-      </c>
-      <c r="F6" s="1784">
+      <c r="E6" s="1856" t="n">
+        <v>18.10000038146973</v>
+      </c>
+      <c r="F6" s="1857">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="1785">
+      <c r="G6" s="1858">
         <f>F6-C6*D6</f>
         <v/>
       </c>
-      <c r="H6" s="1786">
+      <c r="H6" s="1859">
         <f>(E6-D6)/D6</f>
         <v/>
       </c>
-      <c r="I6" s="1787" t="inlineStr">
+      <c r="I6" s="1860" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J6" s="1790" t="n">
+      <c r="J6" s="1863" t="n">
         <v>5.68</v>
       </c>
-      <c r="K6" s="1791" t="inlineStr">
+      <c r="K6" s="1864" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1779" t="inlineStr">
+      <c r="A7" s="1852" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="B7" s="1780" t="inlineStr">
+      <c r="B7" s="1853" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="C7" s="1781" t="n">
+      <c r="C7" s="1854" t="n">
         <v>1600</v>
       </c>
-      <c r="D7" s="1782" t="n">
+      <c r="D7" s="1855" t="n">
         <v>29.25</v>
       </c>
-      <c r="E7" s="1783" t="n">
+      <c r="E7" s="1856" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="1784">
+      <c r="F7" s="1857">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="1785">
+      <c r="G7" s="1858">
         <f>F7-C7*D7</f>
         <v/>
       </c>
-      <c r="H7" s="1786">
+      <c r="H7" s="1859">
         <f>(E7-D7)/D7</f>
         <v/>
       </c>
-      <c r="I7" s="1787" t="inlineStr">
+      <c r="I7" s="1860" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="J7" s="1790" t="n">
+      <c r="J7" s="1863" t="n">
         <v>5.88</v>
       </c>
-      <c r="K7" s="1791" t="inlineStr">
+      <c r="K7" s="1864" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1794" t="inlineStr">
+      <c r="A8" s="1867" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="B8" s="1795" t="inlineStr">
+      <c r="B8" s="1868" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="C8" s="1796" t="n">
+      <c r="C8" s="1869" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="1797" t="n">
+      <c r="D8" s="1870" t="n">
         <v>4.22</v>
       </c>
-      <c r="E8" s="1798" t="n">
-        <v>4.199999809265137</v>
-      </c>
-      <c r="F8" s="1799">
+      <c r="E8" s="1871" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F8" s="1872">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="1800">
+      <c r="G8" s="1873">
         <f>F8-C8*D8</f>
         <v/>
       </c>
-      <c r="H8" s="1801">
+      <c r="H8" s="1874">
         <f>(E8-D8)/D8</f>
         <v/>
       </c>
-      <c r="I8" s="1802" t="inlineStr">
+      <c r="I8" s="1875" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J8" s="1803" t="n">
+      <c r="J8" s="1876" t="n">
         <v>6.32</v>
       </c>
-      <c r="K8" s="1804" t="inlineStr">
+      <c r="K8" s="1877" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1794" t="inlineStr">
+      <c r="A9" s="1852" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="B9" s="1795" t="inlineStr">
+      <c r="B9" s="1853" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="C9" s="1796" t="n">
+      <c r="C9" s="1854" t="n">
         <v>2300</v>
       </c>
-      <c r="D9" s="1797" t="n">
+      <c r="D9" s="1855" t="n">
         <v>2.62</v>
       </c>
-      <c r="E9" s="1798" t="n">
-        <v>2.619999885559082</v>
-      </c>
-      <c r="F9" s="1799">
+      <c r="E9" s="1856" t="n">
+        <v>2.640000104904175</v>
+      </c>
+      <c r="F9" s="1857">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="1800">
+      <c r="G9" s="1858">
         <f>F9-C9*D9</f>
         <v/>
       </c>
-      <c r="H9" s="1801">
+      <c r="H9" s="1859">
         <f>(E9-D9)/D9</f>
         <v/>
       </c>
-      <c r="I9" s="1802" t="inlineStr">
+      <c r="I9" s="1860" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J9" s="1803" t="n">
+      <c r="J9" s="1863" t="n">
         <v>5.48</v>
       </c>
-      <c r="K9" s="1804" t="inlineStr">
+      <c r="K9" s="1864" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1805" t="inlineStr">
+      <c r="A10" s="1878" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="B10" s="1806" t="inlineStr">
+      <c r="B10" s="1879" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="C10" s="1807" t="n">
+      <c r="C10" s="1880" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="1808" t="n">
+      <c r="D10" s="1881" t="n">
         <v>11.6</v>
       </c>
-      <c r="E10" s="1809" t="n">
-        <v>11.19999980926514</v>
-      </c>
-      <c r="F10" s="1810">
+      <c r="E10" s="1882" t="n">
+        <v>11.10000038146973</v>
+      </c>
+      <c r="F10" s="1883">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="1811">
+      <c r="G10" s="1884">
         <f>F10-C10*D10</f>
         <v/>
       </c>
-      <c r="H10" s="1812">
+      <c r="H10" s="1885">
         <f>(E10-D10)/D10</f>
         <v/>
       </c>
-      <c r="I10" s="1813" t="inlineStr">
+      <c r="I10" s="1886" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="J10" s="1814" t="n">
+      <c r="J10" s="1887" t="n">
         <v>6.08</v>
       </c>
-      <c r="K10" s="1815" t="inlineStr">
+      <c r="K10" s="1888" t="inlineStr">
         <is>
           <t>AVOID</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="1816" t="inlineStr">
+      <c r="B11" s="1889" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="1817">
+      <c r="F11" s="1890">
         <f>SUM(F3:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="1818">
+      <c r="G11" s="1891">
         <f>SUM(G3:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="1819">
+      <c r="H11" s="1892">
         <f>G11/SUMPRODUCT(C3:C10,D3:D10)</f>
         <v/>
       </c>
@@ -7667,14 +7926,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1777" t="inlineStr">
-        <is>
-          <t>Today's Trades  —  28 May 2026</t>
+      <c r="A1" s="1850" t="inlineStr">
+        <is>
+          <t>Today's Trades  —  29 May 2026</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1820" t="inlineStr">
+      <c r="A3" s="1893" t="inlineStr">
         <is>
           <t>No trades were executed today.</t>
         </is>
@@ -7712,550 +7971,550 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1777" t="inlineStr">
+      <c r="A1" s="1850" t="inlineStr">
         <is>
           <t>Complete Trade History  —  since 2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="1778" t="inlineStr">
+      <c r="A2" s="1851" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="1778" t="inlineStr">
+      <c r="B2" s="1851" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C2" s="1778" t="inlineStr">
+      <c r="C2" s="1851" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D2" s="1778" t="inlineStr">
+      <c r="D2" s="1851" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E2" s="1778" t="inlineStr">
+      <c r="E2" s="1851" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="F2" s="1778" t="inlineStr">
+      <c r="F2" s="1851" t="inlineStr">
         <is>
           <t>Price (฿)</t>
         </is>
       </c>
-      <c r="G2" s="1778" t="inlineStr">
+      <c r="G2" s="1851" t="inlineStr">
         <is>
           <t>Lots</t>
         </is>
       </c>
-      <c r="H2" s="1778" t="inlineStr">
+      <c r="H2" s="1851" t="inlineStr">
         <is>
           <t>Value (฿)</t>
         </is>
       </c>
-      <c r="I2" s="1778" t="inlineStr">
+      <c r="I2" s="1851" t="inlineStr">
         <is>
           <t>Realised P&amp;L (฿)</t>
         </is>
       </c>
-      <c r="J2" s="1778" t="inlineStr">
+      <c r="J2" s="1851" t="inlineStr">
         <is>
           <t>Reason / Signal</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="1821" t="inlineStr">
+      <c r="A3" s="1894" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B3" s="1822" t="inlineStr">
+      <c r="B3" s="1895" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C3" s="1823" t="inlineStr">
+      <c r="C3" s="1896" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D3" s="1824" t="inlineStr">
+      <c r="D3" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E3" s="1825" t="n">
+      <c r="E3" s="1898" t="n">
         <v>2300</v>
       </c>
-      <c r="F3" s="1826" t="n">
+      <c r="F3" s="1899" t="n">
         <v>20.3</v>
       </c>
-      <c r="G3" s="1825" t="n">
+      <c r="G3" s="1898" t="n">
         <v>23</v>
       </c>
-      <c r="H3" s="1827">
+      <c r="H3" s="1900">
         <f>E3*F3</f>
         <v/>
       </c>
-      <c r="I3" s="1828" t="inlineStr">
+      <c r="I3" s="1901" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" s="1829" t="inlineStr">
+      <c r="J3" s="1902" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1830" t="inlineStr">
+      <c r="A4" s="1903" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B4" s="1831" t="inlineStr">
+      <c r="B4" s="1904" t="inlineStr">
         <is>
           <t>CK.BK</t>
         </is>
       </c>
-      <c r="C4" s="1795" t="inlineStr">
+      <c r="C4" s="1868" t="inlineStr">
         <is>
           <t>CK</t>
         </is>
       </c>
-      <c r="D4" s="1824" t="inlineStr">
+      <c r="D4" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E4" s="1796" t="n">
+      <c r="E4" s="1869" t="n">
         <v>2800</v>
       </c>
-      <c r="F4" s="1797" t="n">
+      <c r="F4" s="1870" t="n">
         <v>16.5</v>
       </c>
-      <c r="G4" s="1796" t="n">
+      <c r="G4" s="1869" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="1799">
+      <c r="H4" s="1872">
         <f>E4*F4</f>
         <v/>
       </c>
-      <c r="I4" s="1832" t="inlineStr">
+      <c r="I4" s="1905" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="1833" t="inlineStr">
+      <c r="J4" s="1906" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="1821" t="inlineStr">
+      <c r="A5" s="1894" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B5" s="1822" t="inlineStr">
+      <c r="B5" s="1895" t="inlineStr">
         <is>
           <t>TIDLOR.BK</t>
         </is>
       </c>
-      <c r="C5" s="1823" t="inlineStr">
+      <c r="C5" s="1896" t="inlineStr">
         <is>
           <t>TIDLOR</t>
         </is>
       </c>
-      <c r="D5" s="1824" t="inlineStr">
+      <c r="D5" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E5" s="1825" t="n">
+      <c r="E5" s="1898" t="n">
         <v>2700</v>
       </c>
-      <c r="F5" s="1826" t="n">
+      <c r="F5" s="1899" t="n">
         <v>17.4</v>
       </c>
-      <c r="G5" s="1825" t="n">
+      <c r="G5" s="1898" t="n">
         <v>27</v>
       </c>
-      <c r="H5" s="1827">
+      <c r="H5" s="1900">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="I5" s="1828" t="inlineStr">
+      <c r="I5" s="1901" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="1829" t="inlineStr">
+      <c r="J5" s="1902" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="1830" t="inlineStr">
+      <c r="A6" s="1903" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B6" s="1831" t="inlineStr">
+      <c r="B6" s="1904" t="inlineStr">
         <is>
           <t>WHA.BK</t>
         </is>
       </c>
-      <c r="C6" s="1795" t="inlineStr">
+      <c r="C6" s="1868" t="inlineStr">
         <is>
           <t>WHA</t>
         </is>
       </c>
-      <c r="D6" s="1824" t="inlineStr">
+      <c r="D6" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E6" s="1796" t="n">
+      <c r="E6" s="1869" t="n">
         <v>10800</v>
       </c>
-      <c r="F6" s="1797" t="n">
+      <c r="F6" s="1870" t="n">
         <v>4.38</v>
       </c>
-      <c r="G6" s="1796" t="n">
+      <c r="G6" s="1869" t="n">
         <v>108</v>
       </c>
-      <c r="H6" s="1799">
+      <c r="H6" s="1872">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="I6" s="1832" t="inlineStr">
+      <c r="I6" s="1905" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="1833" t="inlineStr">
+      <c r="J6" s="1906" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="1821" t="inlineStr">
+      <c r="A7" s="1894" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B7" s="1822" t="inlineStr">
+      <c r="B7" s="1895" t="inlineStr">
         <is>
           <t>KTC.BK</t>
         </is>
       </c>
-      <c r="C7" s="1823" t="inlineStr">
+      <c r="C7" s="1896" t="inlineStr">
         <is>
           <t>KTC</t>
         </is>
       </c>
-      <c r="D7" s="1824" t="inlineStr">
+      <c r="D7" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E7" s="1825" t="n">
+      <c r="E7" s="1898" t="n">
         <v>1600</v>
       </c>
-      <c r="F7" s="1826" t="n">
+      <c r="F7" s="1899" t="n">
         <v>29.25</v>
       </c>
-      <c r="G7" s="1825" t="n">
+      <c r="G7" s="1898" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1827">
+      <c r="H7" s="1900">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="I7" s="1828" t="inlineStr">
+      <c r="I7" s="1901" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="1829" t="inlineStr">
+      <c r="J7" s="1902" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="1830" t="inlineStr">
+      <c r="A8" s="1903" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="B8" s="1831" t="inlineStr">
+      <c r="B8" s="1904" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C8" s="1795" t="inlineStr">
+      <c r="C8" s="1868" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D8" s="1824" t="inlineStr">
+      <c r="D8" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E8" s="1796" t="n">
+      <c r="E8" s="1869" t="n">
         <v>7000</v>
       </c>
-      <c r="F8" s="1797" t="n">
+      <c r="F8" s="1870" t="n">
         <v>6.7</v>
       </c>
-      <c r="G8" s="1796" t="n">
+      <c r="G8" s="1869" t="n">
         <v>70</v>
       </c>
-      <c r="H8" s="1799">
+      <c r="H8" s="1872">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="I8" s="1832" t="inlineStr">
+      <c r="I8" s="1905" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="1833" t="inlineStr">
+      <c r="J8" s="1906" t="inlineStr">
         <is>
           <t>BUY (Day 1)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="1821" t="inlineStr">
+      <c r="A9" s="1894" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="B9" s="1822" t="inlineStr">
+      <c r="B9" s="1895" t="inlineStr">
         <is>
           <t>AMATA.BK</t>
         </is>
       </c>
-      <c r="C9" s="1823" t="inlineStr">
+      <c r="C9" s="1896" t="inlineStr">
         <is>
           <t>AMATA</t>
         </is>
       </c>
-      <c r="D9" s="1834" t="inlineStr">
+      <c r="D9" s="1907" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="E9" s="1825" t="n">
+      <c r="E9" s="1898" t="n">
         <v>2300</v>
       </c>
-      <c r="F9" s="1826" t="n">
+      <c r="F9" s="1899" t="n">
         <v>0.75</v>
       </c>
-      <c r="G9" s="1825" t="n">
+      <c r="G9" s="1898" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="1827">
+      <c r="H9" s="1900">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="I9" s="1835" t="n">
+      <c r="I9" s="1908" t="n">
         <v>1725</v>
       </c>
-      <c r="J9" s="1829" t="inlineStr">
+      <c r="J9" s="1902" t="inlineStr">
         <is>
           <t>Dividend ฿0.7500/share</t>
         </is>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="1830" t="inlineStr">
+      <c r="A10" s="1903" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B10" s="1831" t="inlineStr">
+      <c r="B10" s="1904" t="inlineStr">
         <is>
           <t>JASIF.BK</t>
         </is>
       </c>
-      <c r="C10" s="1795" t="inlineStr">
+      <c r="C10" s="1868" t="inlineStr">
         <is>
           <t>JASIF</t>
         </is>
       </c>
-      <c r="D10" s="1834" t="inlineStr">
+      <c r="D10" s="1907" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="E10" s="1796" t="n">
+      <c r="E10" s="1869" t="n">
         <v>7000</v>
       </c>
-      <c r="F10" s="1797" t="n">
+      <c r="F10" s="1870" t="n">
         <v>6.7</v>
       </c>
-      <c r="G10" s="1796" t="n">
+      <c r="G10" s="1869" t="n">
         <v>70</v>
       </c>
-      <c r="H10" s="1799">
+      <c r="H10" s="1872">
         <f>E10*F10</f>
         <v/>
       </c>
-      <c r="I10" s="1836" t="n">
+      <c r="I10" s="1909" t="n">
         <v>-234.5</v>
       </c>
-      <c r="J10" s="1833" t="inlineStr">
+      <c r="J10" s="1906" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="1821" t="inlineStr">
+      <c r="A11" s="1894" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B11" s="1822" t="inlineStr">
+      <c r="B11" s="1895" t="inlineStr">
         <is>
           <t>KGI.BK</t>
         </is>
       </c>
-      <c r="C11" s="1823" t="inlineStr">
+      <c r="C11" s="1896" t="inlineStr">
         <is>
           <t>KGI</t>
         </is>
       </c>
-      <c r="D11" s="1824" t="inlineStr">
+      <c r="D11" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E11" s="1825" t="n">
+      <c r="E11" s="1898" t="n">
         <v>1500</v>
       </c>
-      <c r="F11" s="1826" t="n">
+      <c r="F11" s="1899" t="n">
         <v>4.22</v>
       </c>
-      <c r="G11" s="1825" t="n">
+      <c r="G11" s="1898" t="n">
         <v>15</v>
       </c>
-      <c r="H11" s="1827">
+      <c r="H11" s="1900">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="I11" s="1828" t="inlineStr">
+      <c r="I11" s="1901" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="1829" t="inlineStr">
+      <c r="J11" s="1902" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="1830" t="inlineStr">
+      <c r="A12" s="1903" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B12" s="1831" t="inlineStr">
+      <c r="B12" s="1904" t="inlineStr">
         <is>
           <t>TU.BK</t>
         </is>
       </c>
-      <c r="C12" s="1795" t="inlineStr">
+      <c r="C12" s="1868" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="D12" s="1824" t="inlineStr">
+      <c r="D12" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E12" s="1796" t="n">
+      <c r="E12" s="1869" t="n">
         <v>500</v>
       </c>
-      <c r="F12" s="1797" t="n">
+      <c r="F12" s="1870" t="n">
         <v>11.6</v>
       </c>
-      <c r="G12" s="1796" t="n">
+      <c r="G12" s="1869" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="1799">
+      <c r="H12" s="1872">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="I12" s="1832" t="inlineStr">
+      <c r="I12" s="1905" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="1833" t="inlineStr">
+      <c r="J12" s="1906" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="1821" t="inlineStr">
+      <c r="A13" s="1894" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B13" s="1822" t="inlineStr">
+      <c r="B13" s="1895" t="inlineStr">
         <is>
           <t>BTSGIF.BK</t>
         </is>
       </c>
-      <c r="C13" s="1823" t="inlineStr">
+      <c r="C13" s="1896" t="inlineStr">
         <is>
           <t>BTSGIF</t>
         </is>
       </c>
-      <c r="D13" s="1824" t="inlineStr">
+      <c r="D13" s="1897" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="E13" s="1825" t="n">
+      <c r="E13" s="1898" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="1826" t="n">
+      <c r="F13" s="1899" t="n">
         <v>2.62</v>
       </c>
-      <c r="G13" s="1825" t="n">
+      <c r="G13" s="1898" t="n">
         <v>23</v>
       </c>
-      <c r="H13" s="1827">
+      <c r="H13" s="1900">
         <f>E13*F13</f>
         <v/>
       </c>
-      <c r="I13" s="1828" t="inlineStr">
+      <c r="I13" s="1901" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="1829" t="inlineStr">
+      <c r="J13" s="1902" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -8267,11 +8526,11 @@
           <t>TOTAL TRADES</t>
         </is>
       </c>
-      <c r="H15" s="1837">
+      <c r="H15" s="1910">
         <f>SUM(H3:H13)</f>
         <v/>
       </c>
-      <c r="I15" s="1837">
+      <c r="I15" s="1910">
         <f>SUM(I3:I13)</f>
         <v/>
       </c>

--- a/Portfolio_Reports/Portfolio_Master.xlsx
+++ b/Portfolio_Reports/Portfolio_Master.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1911">
+  <cellXfs count="1984">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -5207,6 +5207,225 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6298,7 +6517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6378,47 +6597,47 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1765" t="inlineStr">
+      <c r="A2" s="1838" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="B2" s="1766" t="n">
+      <c r="B2" s="1839" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="1767" t="n">
+      <c r="C2" s="1840" t="n">
         <v>303748.3059307933</v>
       </c>
-      <c r="D2" s="1768" t="n">
+      <c r="D2" s